--- a/templates/Declaration_template.xlsx
+++ b/templates/Declaration_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="540" windowWidth="13095" windowHeight="10935"/>
+    <workbookView xWindow="270" yWindow="540" windowWidth="13095" windowHeight="10935" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Титул" sheetId="1" r:id="rId1"/>
@@ -19347,7 +19347,7 @@
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
     </row>
-    <row r="15" spans="1:40" ht="19.5" customHeight="1">
+    <row r="15" spans="1:40" ht="21" customHeight="1">
       <c r="A15" s="92" t="s">
         <v>56</v>
       </c>
@@ -19477,7 +19477,7 @@
       <c r="AM17" s="3"/>
       <c r="AN17" s="3"/>
     </row>
-    <row r="18" spans="1:40" ht="17.25" customHeight="1">
+    <row r="18" spans="1:40" ht="21" customHeight="1">
       <c r="A18" s="91" t="s">
         <v>54</v>
       </c>
@@ -19565,7 +19565,7 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="1:40" ht="19.5" customHeight="1">
+    <row r="20" spans="1:40" ht="21" customHeight="1">
       <c r="A20" s="92" t="s">
         <v>59</v>
       </c>
@@ -19695,7 +19695,7 @@
       <c r="AM22" s="3"/>
       <c r="AN22" s="3"/>
     </row>
-    <row r="23" spans="1:40" ht="17.25" customHeight="1">
+    <row r="23" spans="1:40" ht="21" customHeight="1">
       <c r="A23" s="92" t="s">
         <v>61</v>
       </c>
@@ -19825,7 +19825,7 @@
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
     </row>
-    <row r="26" spans="1:40" ht="12.75">
+    <row r="26" spans="1:40" ht="21" customHeight="1">
       <c r="A26" s="91" t="s">
         <v>54</v>
       </c>
@@ -19913,7 +19913,7 @@
       <c r="AM27" s="3"/>
       <c r="AN27" s="3"/>
     </row>
-    <row r="28" spans="1:40" ht="12.75">
+    <row r="28" spans="1:40" ht="21" customHeight="1">
       <c r="A28" s="93" t="s">
         <v>64</v>
       </c>
@@ -20043,7 +20043,7 @@
       <c r="AM30" s="3"/>
       <c r="AN30" s="3"/>
     </row>
-    <row r="31" spans="1:40" ht="17.25" customHeight="1">
+    <row r="31" spans="1:40" ht="21" customHeight="1">
       <c r="A31" s="93" t="s">
         <v>66</v>
       </c>
@@ -20173,7 +20173,7 @@
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
     </row>
-    <row r="34" spans="1:40" ht="12.75">
+    <row r="34" spans="1:40" ht="21" customHeight="1">
       <c r="A34" s="94" t="s">
         <v>54</v>
       </c>
@@ -20261,7 +20261,7 @@
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
     </row>
-    <row r="36" spans="1:40" ht="12.75">
+    <row r="36" spans="1:40" ht="21" customHeight="1">
       <c r="A36" s="93" t="s">
         <v>69</v>
       </c>
@@ -20391,7 +20391,7 @@
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
     </row>
-    <row r="39" spans="1:40" ht="17.25" customHeight="1">
+    <row r="39" spans="1:40" ht="21" customHeight="1">
       <c r="A39" s="93" t="s">
         <v>71</v>
       </c>
@@ -20479,7 +20479,7 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="1:40" ht="17.25" customHeight="1">
+    <row r="41" spans="1:40" ht="21" customHeight="1">
       <c r="A41" s="93" t="s">
         <v>73</v>
       </c>

--- a/templates/Declaration_template.xlsx
+++ b/templates/Declaration_template.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="239">
   <si>
     <t>ИНН</t>
   </si>
@@ -246,9 +246,6 @@
   </si>
   <si>
     <t>Подпись</t>
-  </si>
-  <si>
-    <t>Лавренов</t>
   </si>
   <si>
     <t>Дата</t>
@@ -482,9 +479,6 @@
   </si>
   <si>
     <t>(подпись)</t>
-  </si>
-  <si>
-    <t>25.03.2026</t>
   </si>
   <si>
     <t>(дата)</t>
@@ -1493,7 +1487,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1665,8 +1659,14 @@
       <color theme="1"/>
       <name val="Arimo"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1682,6 +1682,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
@@ -1946,7 +1952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2319,6 +2325,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7066,7 +7075,7 @@
       <c r="P50" s="89"/>
       <c r="Q50" s="89"/>
       <c r="R50" s="79" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S50" s="42"/>
       <c r="T50" s="42"/>
@@ -7076,7 +7085,7 @@
       <c r="X50" s="49"/>
       <c r="Y50" s="50"/>
       <c r="Z50" s="84" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA50" s="53"/>
       <c r="AB50" s="49"/>
@@ -7084,7 +7093,7 @@
       <c r="AD50" s="49"/>
       <c r="AE50" s="50"/>
       <c r="AF50" s="84" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG50" s="53"/>
       <c r="AH50" s="49"/>
@@ -7118,7 +7127,7 @@
       <c r="BJ50" s="54"/>
       <c r="BK50" s="50"/>
       <c r="BL50" s="84" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BM50" s="53"/>
       <c r="BN50" s="54"/>
@@ -7126,7 +7135,7 @@
       <c r="BP50" s="54"/>
       <c r="BQ50" s="50"/>
       <c r="BR50" s="84" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BS50" s="53"/>
       <c r="BT50" s="54"/>
@@ -7141,7 +7150,7 @@
     </row>
     <row r="51" spans="1:80" ht="6" customHeight="1">
       <c r="A51" s="83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
@@ -7596,7 +7605,7 @@
       <c r="AP56" s="3"/>
       <c r="AQ56" s="7"/>
       <c r="AR56" s="82" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AS56" s="42"/>
       <c r="AT56" s="42"/>
@@ -7721,7 +7730,7 @@
     </row>
     <row r="58" spans="1:80" ht="17.25" customHeight="1">
       <c r="A58" s="85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="42"/>
       <c r="C58" s="42"/>
@@ -9507,7 +9516,7 @@
     </row>
     <row r="9" spans="1:75" ht="48.75" customHeight="1">
       <c r="A9" s="147" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
@@ -9586,7 +9595,7 @@
     </row>
     <row r="10" spans="1:75" ht="69.75" customHeight="1">
       <c r="A10" s="129" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
@@ -9596,7 +9605,7 @@
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="129" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J10" s="42"/>
       <c r="K10" s="42"/>
@@ -9618,7 +9627,7 @@
       <c r="AA10" s="42"/>
       <c r="AB10" s="42"/>
       <c r="AC10" s="129" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD10" s="42"/>
       <c r="AE10" s="42"/>
@@ -9646,7 +9655,7 @@
       <c r="BA10" s="42"/>
       <c r="BB10" s="42"/>
       <c r="BC10" s="129" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="BD10" s="42"/>
       <c r="BE10" s="42"/>
@@ -9681,7 +9690,7 @@
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="148" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
@@ -9703,7 +9712,7 @@
       <c r="AA11" s="42"/>
       <c r="AB11" s="42"/>
       <c r="AC11" s="148" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AD11" s="42"/>
       <c r="AE11" s="42"/>
@@ -9731,7 +9740,7 @@
       <c r="BA11" s="42"/>
       <c r="BB11" s="42"/>
       <c r="BC11" s="148" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="BD11" s="42"/>
       <c r="BE11" s="42"/>
@@ -9845,7 +9854,7 @@
       <c r="K13" s="132"/>
       <c r="L13" s="50"/>
       <c r="M13" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N13" s="53"/>
       <c r="O13" s="132"/>
@@ -9853,7 +9862,7 @@
       <c r="Q13" s="132"/>
       <c r="R13" s="50"/>
       <c r="S13" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="132"/>
@@ -10003,7 +10012,7 @@
       <c r="K15" s="132"/>
       <c r="L15" s="50"/>
       <c r="M15" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N15" s="53"/>
       <c r="O15" s="132"/>
@@ -10011,7 +10020,7 @@
       <c r="Q15" s="132"/>
       <c r="R15" s="50"/>
       <c r="S15" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T15" s="53"/>
       <c r="U15" s="132"/>
@@ -10161,7 +10170,7 @@
       <c r="K17" s="132"/>
       <c r="L17" s="50"/>
       <c r="M17" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N17" s="53"/>
       <c r="O17" s="132"/>
@@ -10169,7 +10178,7 @@
       <c r="Q17" s="132"/>
       <c r="R17" s="50"/>
       <c r="S17" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T17" s="53"/>
       <c r="U17" s="132"/>
@@ -10319,7 +10328,7 @@
       <c r="K19" s="132"/>
       <c r="L19" s="50"/>
       <c r="M19" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N19" s="53"/>
       <c r="O19" s="132"/>
@@ -10327,7 +10336,7 @@
       <c r="Q19" s="132"/>
       <c r="R19" s="50"/>
       <c r="S19" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T19" s="53"/>
       <c r="U19" s="132"/>
@@ -10477,7 +10486,7 @@
       <c r="K21" s="132"/>
       <c r="L21" s="50"/>
       <c r="M21" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N21" s="53"/>
       <c r="O21" s="132"/>
@@ -10485,7 +10494,7 @@
       <c r="Q21" s="132"/>
       <c r="R21" s="50"/>
       <c r="S21" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T21" s="53"/>
       <c r="U21" s="132"/>
@@ -10635,7 +10644,7 @@
       <c r="K23" s="132"/>
       <c r="L23" s="50"/>
       <c r="M23" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N23" s="53"/>
       <c r="O23" s="132"/>
@@ -10643,7 +10652,7 @@
       <c r="Q23" s="132"/>
       <c r="R23" s="50"/>
       <c r="S23" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T23" s="53"/>
       <c r="U23" s="132"/>
@@ -10793,7 +10802,7 @@
       <c r="K25" s="132"/>
       <c r="L25" s="50"/>
       <c r="M25" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N25" s="53"/>
       <c r="O25" s="132"/>
@@ -10801,7 +10810,7 @@
       <c r="Q25" s="132"/>
       <c r="R25" s="50"/>
       <c r="S25" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T25" s="53"/>
       <c r="U25" s="132"/>
@@ -10951,7 +10960,7 @@
       <c r="K27" s="132"/>
       <c r="L27" s="50"/>
       <c r="M27" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N27" s="53"/>
       <c r="O27" s="132"/>
@@ -10959,7 +10968,7 @@
       <c r="Q27" s="132"/>
       <c r="R27" s="50"/>
       <c r="S27" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T27" s="53"/>
       <c r="U27" s="132"/>
@@ -11109,7 +11118,7 @@
       <c r="K29" s="132"/>
       <c r="L29" s="50"/>
       <c r="M29" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N29" s="53"/>
       <c r="O29" s="132"/>
@@ -11117,7 +11126,7 @@
       <c r="Q29" s="132"/>
       <c r="R29" s="50"/>
       <c r="S29" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T29" s="53"/>
       <c r="U29" s="132"/>
@@ -11267,7 +11276,7 @@
       <c r="K31" s="132"/>
       <c r="L31" s="50"/>
       <c r="M31" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N31" s="53"/>
       <c r="O31" s="132"/>
@@ -11275,7 +11284,7 @@
       <c r="Q31" s="132"/>
       <c r="R31" s="50"/>
       <c r="S31" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T31" s="53"/>
       <c r="U31" s="132"/>
@@ -11425,7 +11434,7 @@
       <c r="K33" s="132"/>
       <c r="L33" s="50"/>
       <c r="M33" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N33" s="53"/>
       <c r="O33" s="132"/>
@@ -11433,7 +11442,7 @@
       <c r="Q33" s="132"/>
       <c r="R33" s="50"/>
       <c r="S33" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T33" s="53"/>
       <c r="U33" s="132"/>
@@ -11583,7 +11592,7 @@
       <c r="K35" s="132"/>
       <c r="L35" s="50"/>
       <c r="M35" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N35" s="53"/>
       <c r="O35" s="132"/>
@@ -11591,7 +11600,7 @@
       <c r="Q35" s="132"/>
       <c r="R35" s="50"/>
       <c r="S35" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T35" s="53"/>
       <c r="U35" s="132"/>
@@ -11741,7 +11750,7 @@
       <c r="K37" s="132"/>
       <c r="L37" s="50"/>
       <c r="M37" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N37" s="53"/>
       <c r="O37" s="132"/>
@@ -11749,7 +11758,7 @@
       <c r="Q37" s="132"/>
       <c r="R37" s="50"/>
       <c r="S37" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T37" s="53"/>
       <c r="U37" s="132"/>
@@ -11899,7 +11908,7 @@
       <c r="K39" s="132"/>
       <c r="L39" s="50"/>
       <c r="M39" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N39" s="53"/>
       <c r="O39" s="132"/>
@@ -11907,7 +11916,7 @@
       <c r="Q39" s="132"/>
       <c r="R39" s="50"/>
       <c r="S39" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T39" s="53"/>
       <c r="U39" s="132"/>
@@ -12057,7 +12066,7 @@
       <c r="K41" s="132"/>
       <c r="L41" s="50"/>
       <c r="M41" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N41" s="53"/>
       <c r="O41" s="132"/>
@@ -12065,7 +12074,7 @@
       <c r="Q41" s="132"/>
       <c r="R41" s="50"/>
       <c r="S41" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T41" s="53"/>
       <c r="U41" s="132"/>
@@ -12215,7 +12224,7 @@
       <c r="K43" s="132"/>
       <c r="L43" s="50"/>
       <c r="M43" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N43" s="53"/>
       <c r="O43" s="132"/>
@@ -12223,7 +12232,7 @@
       <c r="Q43" s="132"/>
       <c r="R43" s="50"/>
       <c r="S43" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T43" s="53"/>
       <c r="U43" s="132"/>
@@ -12373,7 +12382,7 @@
       <c r="K45" s="132"/>
       <c r="L45" s="50"/>
       <c r="M45" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N45" s="53"/>
       <c r="O45" s="132"/>
@@ -12381,7 +12390,7 @@
       <c r="Q45" s="132"/>
       <c r="R45" s="50"/>
       <c r="S45" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T45" s="53"/>
       <c r="U45" s="132"/>
@@ -12531,7 +12540,7 @@
       <c r="K47" s="132"/>
       <c r="L47" s="50"/>
       <c r="M47" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N47" s="53"/>
       <c r="O47" s="132"/>
@@ -12539,7 +12548,7 @@
       <c r="Q47" s="132"/>
       <c r="R47" s="50"/>
       <c r="S47" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T47" s="53"/>
       <c r="U47" s="132"/>
@@ -12689,7 +12698,7 @@
       <c r="K49" s="132"/>
       <c r="L49" s="50"/>
       <c r="M49" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N49" s="53"/>
       <c r="O49" s="132"/>
@@ -12697,7 +12706,7 @@
       <c r="Q49" s="132"/>
       <c r="R49" s="50"/>
       <c r="S49" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T49" s="53"/>
       <c r="U49" s="132"/>
@@ -12847,7 +12856,7 @@
       <c r="K51" s="132"/>
       <c r="L51" s="50"/>
       <c r="M51" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N51" s="53"/>
       <c r="O51" s="132"/>
@@ -12855,7 +12864,7 @@
       <c r="Q51" s="132"/>
       <c r="R51" s="50"/>
       <c r="S51" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T51" s="53"/>
       <c r="U51" s="132"/>
@@ -12993,7 +13002,7 @@
     </row>
     <row r="53" spans="1:75" ht="17.25" customHeight="1">
       <c r="A53" s="150" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B53" s="42"/>
       <c r="C53" s="42"/>
@@ -13226,7 +13235,7 @@
     </row>
     <row r="56" spans="1:75" ht="45" customHeight="1">
       <c r="A56" s="151" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B56" s="42"/>
       <c r="C56" s="42"/>
@@ -16111,7 +16120,7 @@
     </row>
     <row r="7" spans="1:41" ht="31.5" customHeight="1">
       <c r="A7" s="152" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -16158,7 +16167,7 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="42"/>
@@ -16175,7 +16184,7 @@
       <c r="P8" s="42"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="103" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S8" s="42"/>
       <c r="T8" s="42"/>
@@ -16183,7 +16192,7 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Y8" s="42"/>
       <c r="Z8" s="42"/>
@@ -16254,7 +16263,7 @@
     </row>
     <row r="10" spans="1:41" ht="17.25" customHeight="1">
       <c r="A10" s="62" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
@@ -16274,7 +16283,7 @@
       <c r="Q10" s="42"/>
       <c r="R10" s="3"/>
       <c r="S10" s="79" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T10" s="42"/>
       <c r="U10" s="3"/>
@@ -16430,7 +16439,7 @@
     </row>
     <row r="14" spans="1:41" ht="21" customHeight="1">
       <c r="A14" s="62" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -16450,7 +16459,7 @@
       <c r="Q14" s="42"/>
       <c r="R14" s="3"/>
       <c r="S14" s="79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T14" s="42"/>
       <c r="U14" s="16"/>
@@ -16520,7 +16529,7 @@
     </row>
     <row r="16" spans="1:41" ht="12.75">
       <c r="A16" s="62" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B16" s="42"/>
       <c r="C16" s="42"/>
@@ -16540,7 +16549,7 @@
       <c r="Q16" s="42"/>
       <c r="R16" s="42"/>
       <c r="S16" s="79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T16" s="42"/>
       <c r="U16" s="16"/>
@@ -16610,7 +16619,7 @@
     </row>
     <row r="18" spans="1:41" ht="21" customHeight="1">
       <c r="A18" s="62" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B18" s="42"/>
       <c r="C18" s="42"/>
@@ -16630,18 +16639,18 @@
       <c r="Q18" s="42"/>
       <c r="R18" s="42"/>
       <c r="S18" s="79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T18" s="42"/>
       <c r="U18" s="16"/>
       <c r="V18" s="16"/>
       <c r="W18" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X18" s="16"/>
       <c r="Y18" s="16"/>
       <c r="Z18" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA18" s="16"/>
       <c r="AB18" s="16"/>
@@ -16704,7 +16713,7 @@
     </row>
     <row r="20" spans="1:41" ht="21" customHeight="1">
       <c r="A20" s="62" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
@@ -16724,7 +16733,7 @@
       <c r="Q20" s="42"/>
       <c r="R20" s="42"/>
       <c r="S20" s="79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T20" s="42"/>
       <c r="U20" s="16"/>
@@ -16794,7 +16803,7 @@
     </row>
     <row r="22" spans="1:41" ht="27" customHeight="1">
       <c r="A22" s="92" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
@@ -16882,7 +16891,7 @@
     </row>
     <row r="24" spans="1:41" ht="18" customHeight="1">
       <c r="A24" s="63" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="42"/>
@@ -16902,7 +16911,7 @@
       <c r="Q24" s="42"/>
       <c r="R24" s="42"/>
       <c r="S24" s="79" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T24" s="42"/>
       <c r="U24" s="11"/>
@@ -17058,7 +17067,7 @@
     </row>
     <row r="28" spans="1:41" ht="17.25" customHeight="1">
       <c r="A28" s="63" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -17078,7 +17087,7 @@
       <c r="Q28" s="42"/>
       <c r="R28" s="42"/>
       <c r="S28" s="79" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="T28" s="42"/>
       <c r="U28" s="11"/>
@@ -17234,7 +17243,7 @@
     </row>
     <row r="32" spans="1:41" ht="18.75" customHeight="1">
       <c r="A32" s="63" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
@@ -17254,7 +17263,7 @@
       <c r="Q32" s="42"/>
       <c r="R32" s="42"/>
       <c r="S32" s="79" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="T32" s="42"/>
       <c r="U32" s="16"/>
@@ -17410,7 +17419,7 @@
     </row>
     <row r="36" spans="1:41" ht="17.25" customHeight="1">
       <c r="A36" s="63" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B36" s="42"/>
       <c r="C36" s="42"/>
@@ -17430,7 +17439,7 @@
       <c r="Q36" s="42"/>
       <c r="R36" s="42"/>
       <c r="S36" s="79" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="T36" s="42"/>
       <c r="U36" s="11"/>
@@ -17586,7 +17595,7 @@
     </row>
     <row r="40" spans="1:41" ht="19.5" customHeight="1">
       <c r="A40" s="63" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
@@ -17606,7 +17615,7 @@
       <c r="Q40" s="42"/>
       <c r="R40" s="42"/>
       <c r="S40" s="79" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="T40" s="42"/>
       <c r="U40" s="16"/>
@@ -18194,7 +18203,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="63" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="42"/>
@@ -19037,7 +19046,7 @@
     </row>
     <row r="8" spans="1:40" ht="43.5" customHeight="1">
       <c r="A8" s="102" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
@@ -19124,7 +19133,7 @@
     <row r="10" spans="1:40" ht="12.75">
       <c r="A10" s="3"/>
       <c r="B10" s="103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -19147,13 +19156,13 @@
       <c r="U10" s="42"/>
       <c r="V10" s="42"/>
       <c r="W10" s="103" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X10" s="42"/>
       <c r="Y10" s="42"/>
       <c r="Z10" s="42"/>
       <c r="AA10" s="103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AB10" s="42"/>
       <c r="AC10" s="42"/>
@@ -19261,7 +19270,7 @@
     </row>
     <row r="13" spans="1:40" ht="21">
       <c r="A13" s="91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
@@ -19286,7 +19295,7 @@
       <c r="V13" s="42"/>
       <c r="W13" s="42"/>
       <c r="X13" s="79" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y13" s="53"/>
       <c r="Z13" s="10"/>
@@ -19349,7 +19358,7 @@
     </row>
     <row r="15" spans="1:40" ht="21" customHeight="1">
       <c r="A15" s="92" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="42"/>
@@ -19374,21 +19383,21 @@
       <c r="V15" s="42"/>
       <c r="W15" s="42"/>
       <c r="X15" s="79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y15" s="53"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="11"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="11"/>
-      <c r="AJ15" s="11"/>
-      <c r="AK15" s="11"/>
+      <c r="Z15" s="153"/>
+      <c r="AA15" s="153"/>
+      <c r="AB15" s="153"/>
+      <c r="AC15" s="153"/>
+      <c r="AD15" s="153"/>
+      <c r="AE15" s="153"/>
+      <c r="AF15" s="153"/>
+      <c r="AG15" s="153"/>
+      <c r="AH15" s="153"/>
+      <c r="AI15" s="153"/>
+      <c r="AJ15" s="153"/>
+      <c r="AK15" s="153"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
@@ -19479,7 +19488,7 @@
     </row>
     <row r="18" spans="1:40" ht="21" customHeight="1">
       <c r="A18" s="91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="42"/>
       <c r="C18" s="42"/>
@@ -19504,20 +19513,20 @@
       <c r="V18" s="42"/>
       <c r="W18" s="42"/>
       <c r="X18" s="79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y18" s="53"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="11"/>
-      <c r="AG18" s="11"/>
-      <c r="AH18" s="11"/>
-      <c r="AI18" s="11"/>
-      <c r="AJ18" s="11"/>
+      <c r="Z18" s="153"/>
+      <c r="AA18" s="153"/>
+      <c r="AB18" s="153"/>
+      <c r="AC18" s="153"/>
+      <c r="AD18" s="153"/>
+      <c r="AE18" s="153"/>
+      <c r="AF18" s="153"/>
+      <c r="AG18" s="153"/>
+      <c r="AH18" s="153"/>
+      <c r="AI18" s="153"/>
+      <c r="AJ18" s="153"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
@@ -19567,7 +19576,7 @@
     </row>
     <row r="20" spans="1:40" ht="21" customHeight="1">
       <c r="A20" s="92" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
@@ -19592,21 +19601,21 @@
       <c r="V20" s="42"/>
       <c r="W20" s="42"/>
       <c r="X20" s="79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y20" s="53"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="11"/>
-      <c r="AG20" s="11"/>
-      <c r="AH20" s="11"/>
-      <c r="AI20" s="11"/>
-      <c r="AJ20" s="11"/>
-      <c r="AK20" s="11"/>
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="153"/>
+      <c r="AB20" s="153"/>
+      <c r="AC20" s="153"/>
+      <c r="AD20" s="153"/>
+      <c r="AE20" s="153"/>
+      <c r="AF20" s="153"/>
+      <c r="AG20" s="153"/>
+      <c r="AH20" s="153"/>
+      <c r="AI20" s="153"/>
+      <c r="AJ20" s="153"/>
+      <c r="AK20" s="153"/>
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
@@ -19697,7 +19706,7 @@
     </row>
     <row r="23" spans="1:40" ht="21" customHeight="1">
       <c r="A23" s="92" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
@@ -19722,21 +19731,21 @@
       <c r="V23" s="42"/>
       <c r="W23" s="42"/>
       <c r="X23" s="79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y23" s="53"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="11"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="11"/>
-      <c r="AG23" s="11"/>
-      <c r="AH23" s="11"/>
-      <c r="AI23" s="11"/>
-      <c r="AJ23" s="11"/>
-      <c r="AK23" s="11"/>
+      <c r="Z23" s="153"/>
+      <c r="AA23" s="153"/>
+      <c r="AB23" s="153"/>
+      <c r="AC23" s="153"/>
+      <c r="AD23" s="153"/>
+      <c r="AE23" s="153"/>
+      <c r="AF23" s="153"/>
+      <c r="AG23" s="153"/>
+      <c r="AH23" s="153"/>
+      <c r="AI23" s="153"/>
+      <c r="AJ23" s="153"/>
+      <c r="AK23" s="153"/>
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
@@ -19827,7 +19836,7 @@
     </row>
     <row r="26" spans="1:40" ht="21" customHeight="1">
       <c r="A26" s="91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -19852,20 +19861,20 @@
       <c r="V26" s="42"/>
       <c r="W26" s="42"/>
       <c r="X26" s="79" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y26" s="53"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="11"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="11"/>
-      <c r="AD26" s="11"/>
-      <c r="AE26" s="11"/>
-      <c r="AF26" s="11"/>
-      <c r="AG26" s="11"/>
-      <c r="AH26" s="11"/>
-      <c r="AI26" s="11"/>
-      <c r="AJ26" s="11"/>
+      <c r="Z26" s="153"/>
+      <c r="AA26" s="153"/>
+      <c r="AB26" s="153"/>
+      <c r="AC26" s="153"/>
+      <c r="AD26" s="153"/>
+      <c r="AE26" s="153"/>
+      <c r="AF26" s="153"/>
+      <c r="AG26" s="153"/>
+      <c r="AH26" s="153"/>
+      <c r="AI26" s="153"/>
+      <c r="AJ26" s="153"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
@@ -19915,7 +19924,7 @@
     </row>
     <row r="28" spans="1:40" ht="21" customHeight="1">
       <c r="A28" s="93" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -19940,21 +19949,21 @@
       <c r="V28" s="42"/>
       <c r="W28" s="42"/>
       <c r="X28" s="79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y28" s="53"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="11"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="11"/>
-      <c r="AD28" s="11"/>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="11"/>
-      <c r="AG28" s="11"/>
-      <c r="AH28" s="11"/>
-      <c r="AI28" s="11"/>
-      <c r="AJ28" s="11"/>
-      <c r="AK28" s="11"/>
+      <c r="Z28" s="153"/>
+      <c r="AA28" s="153"/>
+      <c r="AB28" s="153"/>
+      <c r="AC28" s="153"/>
+      <c r="AD28" s="153"/>
+      <c r="AE28" s="153"/>
+      <c r="AF28" s="153"/>
+      <c r="AG28" s="153"/>
+      <c r="AH28" s="153"/>
+      <c r="AI28" s="153"/>
+      <c r="AJ28" s="153"/>
+      <c r="AK28" s="153"/>
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
       <c r="AN28" s="3"/>
@@ -20045,7 +20054,7 @@
     </row>
     <row r="31" spans="1:40" ht="21" customHeight="1">
       <c r="A31" s="93" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
@@ -20070,21 +20079,21 @@
       <c r="V31" s="42"/>
       <c r="W31" s="42"/>
       <c r="X31" s="79" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y31" s="53"/>
-      <c r="Z31" s="11"/>
-      <c r="AA31" s="11"/>
-      <c r="AB31" s="11"/>
-      <c r="AC31" s="11"/>
-      <c r="AD31" s="11"/>
-      <c r="AE31" s="11"/>
-      <c r="AF31" s="11"/>
-      <c r="AG31" s="11"/>
-      <c r="AH31" s="11"/>
-      <c r="AI31" s="11"/>
-      <c r="AJ31" s="11"/>
-      <c r="AK31" s="11"/>
+      <c r="Z31" s="153"/>
+      <c r="AA31" s="153"/>
+      <c r="AB31" s="153"/>
+      <c r="AC31" s="153"/>
+      <c r="AD31" s="153"/>
+      <c r="AE31" s="153"/>
+      <c r="AF31" s="153"/>
+      <c r="AG31" s="153"/>
+      <c r="AH31" s="153"/>
+      <c r="AI31" s="153"/>
+      <c r="AJ31" s="153"/>
+      <c r="AK31" s="153"/>
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
@@ -20175,7 +20184,7 @@
     </row>
     <row r="34" spans="1:40" ht="21" customHeight="1">
       <c r="A34" s="94" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
@@ -20200,20 +20209,20 @@
       <c r="V34" s="42"/>
       <c r="W34" s="42"/>
       <c r="X34" s="79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y34" s="53"/>
-      <c r="Z34" s="11"/>
-      <c r="AA34" s="11"/>
-      <c r="AB34" s="11"/>
-      <c r="AC34" s="11"/>
-      <c r="AD34" s="11"/>
-      <c r="AE34" s="11"/>
-      <c r="AF34" s="11"/>
-      <c r="AG34" s="11"/>
-      <c r="AH34" s="11"/>
-      <c r="AI34" s="11"/>
-      <c r="AJ34" s="11"/>
+      <c r="Z34" s="153"/>
+      <c r="AA34" s="153"/>
+      <c r="AB34" s="153"/>
+      <c r="AC34" s="153"/>
+      <c r="AD34" s="153"/>
+      <c r="AE34" s="153"/>
+      <c r="AF34" s="153"/>
+      <c r="AG34" s="153"/>
+      <c r="AH34" s="153"/>
+      <c r="AI34" s="153"/>
+      <c r="AJ34" s="153"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
@@ -20263,7 +20272,7 @@
     </row>
     <row r="36" spans="1:40" ht="21" customHeight="1">
       <c r="A36" s="93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B36" s="42"/>
       <c r="C36" s="42"/>
@@ -20288,21 +20297,21 @@
       <c r="V36" s="42"/>
       <c r="W36" s="42"/>
       <c r="X36" s="79" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y36" s="53"/>
-      <c r="Z36" s="11"/>
-      <c r="AA36" s="11"/>
-      <c r="AB36" s="11"/>
-      <c r="AC36" s="11"/>
-      <c r="AD36" s="11"/>
-      <c r="AE36" s="11"/>
-      <c r="AF36" s="11"/>
-      <c r="AG36" s="11"/>
-      <c r="AH36" s="11"/>
-      <c r="AI36" s="11"/>
-      <c r="AJ36" s="11"/>
-      <c r="AK36" s="11"/>
+      <c r="Z36" s="153"/>
+      <c r="AA36" s="153"/>
+      <c r="AB36" s="153"/>
+      <c r="AC36" s="153"/>
+      <c r="AD36" s="153"/>
+      <c r="AE36" s="153"/>
+      <c r="AF36" s="153"/>
+      <c r="AG36" s="153"/>
+      <c r="AH36" s="153"/>
+      <c r="AI36" s="153"/>
+      <c r="AJ36" s="153"/>
+      <c r="AK36" s="153"/>
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
@@ -20393,7 +20402,7 @@
     </row>
     <row r="39" spans="1:40" ht="21" customHeight="1">
       <c r="A39" s="93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B39" s="42"/>
       <c r="C39" s="42"/>
@@ -20418,21 +20427,21 @@
       <c r="V39" s="42"/>
       <c r="W39" s="42"/>
       <c r="X39" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y39" s="53"/>
-      <c r="Z39" s="11"/>
-      <c r="AA39" s="11"/>
-      <c r="AB39" s="11"/>
-      <c r="AC39" s="11"/>
-      <c r="AD39" s="11"/>
-      <c r="AE39" s="11"/>
-      <c r="AF39" s="11"/>
-      <c r="AG39" s="11"/>
-      <c r="AH39" s="11"/>
-      <c r="AI39" s="11"/>
-      <c r="AJ39" s="11"/>
-      <c r="AK39" s="11"/>
+      <c r="Z39" s="153"/>
+      <c r="AA39" s="153"/>
+      <c r="AB39" s="153"/>
+      <c r="AC39" s="153"/>
+      <c r="AD39" s="153"/>
+      <c r="AE39" s="153"/>
+      <c r="AF39" s="153"/>
+      <c r="AG39" s="153"/>
+      <c r="AH39" s="153"/>
+      <c r="AI39" s="153"/>
+      <c r="AJ39" s="153"/>
+      <c r="AK39" s="153"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
@@ -20481,7 +20490,7 @@
     </row>
     <row r="41" spans="1:40" ht="21" customHeight="1">
       <c r="A41" s="93" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B41" s="42"/>
       <c r="C41" s="42"/>
@@ -20506,21 +20515,21 @@
       <c r="V41" s="42"/>
       <c r="W41" s="42"/>
       <c r="X41" s="79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y41" s="53"/>
-      <c r="Z41" s="11"/>
-      <c r="AA41" s="11"/>
-      <c r="AB41" s="11"/>
-      <c r="AC41" s="11"/>
-      <c r="AD41" s="11"/>
-      <c r="AE41" s="11"/>
-      <c r="AF41" s="11"/>
-      <c r="AG41" s="11"/>
-      <c r="AH41" s="11"/>
-      <c r="AI41" s="11"/>
-      <c r="AJ41" s="11"/>
-      <c r="AK41" s="11"/>
+      <c r="Z41" s="153"/>
+      <c r="AA41" s="153"/>
+      <c r="AB41" s="153"/>
+      <c r="AC41" s="153"/>
+      <c r="AD41" s="153"/>
+      <c r="AE41" s="153"/>
+      <c r="AF41" s="153"/>
+      <c r="AG41" s="153"/>
+      <c r="AH41" s="153"/>
+      <c r="AI41" s="153"/>
+      <c r="AJ41" s="153"/>
+      <c r="AK41" s="153"/>
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
@@ -20653,7 +20662,7 @@
     </row>
     <row r="45" spans="1:40" ht="25.5" customHeight="1">
       <c r="A45" s="63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B45" s="42"/>
       <c r="C45" s="42"/>
@@ -20823,7 +20832,7 @@
     </row>
     <row r="49" spans="1:40" ht="14.25" customHeight="1">
       <c r="A49" s="96" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B49" s="42"/>
       <c r="C49" s="42"/>
@@ -20875,9 +20884,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="97" t="s">
-        <v>43</v>
-      </c>
+      <c r="J50" s="97"/>
       <c r="K50" s="89"/>
       <c r="L50" s="89"/>
       <c r="M50" s="89"/>
@@ -20885,15 +20892,13 @@
       <c r="O50" s="89"/>
       <c r="P50" s="89"/>
       <c r="Q50" s="82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R50" s="42"/>
       <c r="S50" s="42"/>
       <c r="T50" s="41"/>
       <c r="U50" s="42"/>
-      <c r="V50" s="97" t="s">
-        <v>78</v>
-      </c>
+      <c r="V50" s="97"/>
       <c r="W50" s="89"/>
       <c r="X50" s="89"/>
       <c r="Y50" s="89"/>
@@ -20901,7 +20906,7 @@
       <c r="AA50" s="89"/>
       <c r="AB50" s="89"/>
       <c r="AC50" s="82" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD50" s="42"/>
       <c r="AE50" s="42"/>
@@ -21040,11 +21045,11 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="40" man="1"/>
   </colBreaks>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -21423,7 +21428,7 @@
     </row>
     <row r="8" spans="1:40" ht="42" customHeight="1">
       <c r="A8" s="109" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
@@ -21510,7 +21515,7 @@
     <row r="10" spans="1:40" ht="12.75">
       <c r="A10" s="8"/>
       <c r="B10" s="103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -21533,13 +21538,13 @@
       <c r="U10" s="42"/>
       <c r="V10" s="42"/>
       <c r="W10" s="103" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X10" s="42"/>
       <c r="Y10" s="42"/>
       <c r="Z10" s="42"/>
       <c r="AA10" s="103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AB10" s="42"/>
       <c r="AC10" s="42"/>
@@ -21605,7 +21610,7 @@
     </row>
     <row r="12" spans="1:40" ht="16.5" customHeight="1">
       <c r="A12" s="91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
@@ -21630,7 +21635,7 @@
       <c r="V12" s="42"/>
       <c r="W12" s="42"/>
       <c r="X12" s="79" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y12" s="53"/>
       <c r="Z12" s="16"/>
@@ -21693,7 +21698,7 @@
     </row>
     <row r="14" spans="1:40" ht="18.75" customHeight="1">
       <c r="A14" s="92" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -21718,7 +21723,7 @@
       <c r="V14" s="42"/>
       <c r="W14" s="42"/>
       <c r="X14" s="79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y14" s="53"/>
       <c r="Z14" s="16"/>
@@ -21823,7 +21828,7 @@
     </row>
     <row r="17" spans="1:40" ht="20.25" customHeight="1">
       <c r="A17" s="91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -21848,7 +21853,7 @@
       <c r="V17" s="42"/>
       <c r="W17" s="42"/>
       <c r="X17" s="79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y17" s="53"/>
       <c r="Z17" s="16"/>
@@ -21911,7 +21916,7 @@
     </row>
     <row r="19" spans="1:40" ht="19.5" customHeight="1">
       <c r="A19" s="92" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -21936,7 +21941,7 @@
       <c r="V19" s="42"/>
       <c r="W19" s="42"/>
       <c r="X19" s="79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y19" s="53"/>
       <c r="Z19" s="16"/>
@@ -22041,7 +22046,7 @@
     </row>
     <row r="22" spans="1:40" ht="17.25" customHeight="1">
       <c r="A22" s="92" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
@@ -22066,7 +22071,7 @@
       <c r="V22" s="42"/>
       <c r="W22" s="42"/>
       <c r="X22" s="79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y22" s="53"/>
       <c r="Z22" s="16"/>
@@ -22171,7 +22176,7 @@
     </row>
     <row r="25" spans="1:40" ht="18.75" customHeight="1">
       <c r="A25" s="91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="42"/>
       <c r="C25" s="42"/>
@@ -22196,7 +22201,7 @@
       <c r="V25" s="42"/>
       <c r="W25" s="42"/>
       <c r="X25" s="79" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y25" s="53"/>
       <c r="Z25" s="16"/>
@@ -22259,7 +22264,7 @@
     </row>
     <row r="27" spans="1:40" ht="20.25" customHeight="1">
       <c r="A27" s="92" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
@@ -22284,7 +22289,7 @@
       <c r="V27" s="42"/>
       <c r="W27" s="42"/>
       <c r="X27" s="79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y27" s="53"/>
       <c r="Z27" s="16"/>
@@ -22389,7 +22394,7 @@
     </row>
     <row r="30" spans="1:40" ht="17.25" customHeight="1">
       <c r="A30" s="92" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
@@ -22414,7 +22419,7 @@
       <c r="V30" s="42"/>
       <c r="W30" s="42"/>
       <c r="X30" s="79" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y30" s="53"/>
       <c r="Z30" s="16"/>
@@ -22519,7 +22524,7 @@
     </row>
     <row r="33" spans="1:40" ht="19.5" customHeight="1">
       <c r="A33" s="91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="42"/>
@@ -22544,7 +22549,7 @@
       <c r="V33" s="42"/>
       <c r="W33" s="42"/>
       <c r="X33" s="79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y33" s="53"/>
       <c r="Z33" s="16"/>
@@ -22607,7 +22612,7 @@
     </row>
     <row r="35" spans="1:40" ht="18.75" customHeight="1">
       <c r="A35" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B35" s="42"/>
       <c r="C35" s="42"/>
@@ -22632,7 +22637,7 @@
       <c r="V35" s="42"/>
       <c r="W35" s="42"/>
       <c r="X35" s="79" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y35" s="53"/>
       <c r="Z35" s="16"/>
@@ -22737,7 +22742,7 @@
     </row>
     <row r="38" spans="1:40" ht="17.25" customHeight="1">
       <c r="A38" s="93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B38" s="42"/>
       <c r="C38" s="42"/>
@@ -22762,7 +22767,7 @@
       <c r="V38" s="42"/>
       <c r="W38" s="42"/>
       <c r="X38" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y38" s="53"/>
       <c r="Z38" s="16"/>
@@ -22825,7 +22830,7 @@
     </row>
     <row r="40" spans="1:40" ht="17.25" customHeight="1">
       <c r="A40" s="93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
@@ -22850,7 +22855,7 @@
       <c r="V40" s="42"/>
       <c r="W40" s="42"/>
       <c r="X40" s="79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y40" s="53"/>
       <c r="Z40" s="16"/>
@@ -22955,7 +22960,7 @@
     </row>
     <row r="43" spans="1:40" ht="17.25" customHeight="1">
       <c r="A43" s="93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
@@ -22980,7 +22985,7 @@
       <c r="V43" s="42"/>
       <c r="W43" s="42"/>
       <c r="X43" s="79" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Y43" s="53"/>
       <c r="Z43" s="16"/>
@@ -23169,7 +23174,7 @@
     </row>
     <row r="48" spans="1:40" ht="25.5" customHeight="1">
       <c r="A48" s="63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -23255,7 +23260,7 @@
     </row>
     <row r="50" spans="1:40" ht="14.25" customHeight="1">
       <c r="A50" s="96" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B50" s="42"/>
       <c r="C50" s="42"/>
@@ -23315,7 +23320,7 @@
       <c r="O51" s="89"/>
       <c r="P51" s="89"/>
       <c r="Q51" s="82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R51" s="42"/>
       <c r="S51" s="42"/>
@@ -23329,7 +23334,7 @@
       <c r="AA51" s="89"/>
       <c r="AB51" s="89"/>
       <c r="AC51" s="82" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD51" s="42"/>
       <c r="AE51" s="42"/>
@@ -23834,7 +23839,7 @@
     </row>
     <row r="7" spans="1:41" ht="31.5" customHeight="1">
       <c r="A7" s="109" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -23881,7 +23886,7 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="42"/>
@@ -23906,13 +23911,13 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="103" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA8" s="42"/>
       <c r="AB8" s="42"/>
       <c r="AC8" s="42"/>
       <c r="AD8" s="103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AE8" s="42"/>
       <c r="AF8" s="42"/>
@@ -23977,7 +23982,7 @@
     </row>
     <row r="10" spans="1:41" ht="17.25" customHeight="1">
       <c r="A10" s="112" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
@@ -24022,11 +24027,11 @@
     </row>
     <row r="11" spans="1:41" ht="21">
       <c r="A11" s="63" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="63" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42"/>
@@ -24052,7 +24057,7 @@
       <c r="Y11" s="42"/>
       <c r="Z11" s="42"/>
       <c r="AA11" s="79" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AB11" s="53"/>
       <c r="AC11" s="10" t="s">
@@ -24116,11 +24121,11 @@
     </row>
     <row r="13" spans="1:41" ht="27" customHeight="1">
       <c r="A13" s="63" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B13" s="42"/>
       <c r="C13" s="63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="42"/>
@@ -24163,7 +24168,7 @@
     </row>
     <row r="14" spans="1:41" ht="28.5" customHeight="1">
       <c r="A14" s="111" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -24208,7 +24213,7 @@
     </row>
     <row r="15" spans="1:41" ht="19.5" customHeight="1">
       <c r="A15" s="92" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="42"/>
@@ -24236,7 +24241,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AB15" s="53"/>
       <c r="AC15" s="11"/>
@@ -24298,7 +24303,7 @@
     </row>
     <row r="17" spans="1:41" ht="19.5" customHeight="1">
       <c r="A17" s="92" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -24326,7 +24331,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AB17" s="53"/>
       <c r="AC17" s="11"/>
@@ -24388,7 +24393,7 @@
     </row>
     <row r="19" spans="1:41" ht="17.25" customHeight="1">
       <c r="A19" s="92" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -24416,7 +24421,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AB19" s="53"/>
       <c r="AC19" s="11"/>
@@ -24478,7 +24483,7 @@
     </row>
     <row r="21" spans="1:41" ht="17.25" customHeight="1">
       <c r="A21" s="92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
@@ -24506,7 +24511,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
       <c r="AA21" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AB21" s="53"/>
       <c r="AC21" s="11"/>
@@ -24525,7 +24530,7 @@
     </row>
     <row r="22" spans="1:41" ht="20.25" customHeight="1">
       <c r="A22" s="112" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
@@ -24570,7 +24575,7 @@
     </row>
     <row r="23" spans="1:41" ht="21">
       <c r="A23" s="113" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
@@ -24598,14 +24603,14 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="79" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AB23" s="53"/>
       <c r="AC23" s="10" t="s">
         <v>7</v>
       </c>
       <c r="AD23" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AE23" s="10" t="s">
         <v>10</v>
@@ -24666,7 +24671,7 @@
     </row>
     <row r="25" spans="1:41" ht="21">
       <c r="A25" s="113" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B25" s="42"/>
       <c r="C25" s="42"/>
@@ -24694,14 +24699,14 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
       <c r="AA25" s="79" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AB25" s="53"/>
       <c r="AC25" s="10" t="s">
         <v>7</v>
       </c>
       <c r="AD25" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AE25" s="10" t="s">
         <v>10</v>
@@ -24762,7 +24767,7 @@
     </row>
     <row r="27" spans="1:41" ht="21">
       <c r="A27" s="113" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
@@ -24790,14 +24795,14 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
       <c r="AA27" s="79" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AB27" s="53"/>
       <c r="AC27" s="10" t="s">
         <v>7</v>
       </c>
       <c r="AD27" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AE27" s="10" t="s">
         <v>10</v>
@@ -24858,7 +24863,7 @@
     </row>
     <row r="29" spans="1:41" ht="21">
       <c r="A29" s="113" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="42"/>
@@ -24886,14 +24891,14 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
       <c r="AA29" s="79" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AB29" s="53"/>
       <c r="AC29" s="10" t="s">
         <v>7</v>
       </c>
       <c r="AD29" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AE29" s="10" t="s">
         <v>10</v>
@@ -24954,7 +24959,7 @@
     </row>
     <row r="31" spans="1:41" ht="21">
       <c r="A31" s="92" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
@@ -24974,7 +24979,7 @@
       <c r="Q31" s="42"/>
       <c r="R31" s="42"/>
       <c r="S31" s="79" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T31" s="53"/>
       <c r="U31" s="11"/>
@@ -25046,7 +25051,7 @@
     </row>
     <row r="33" spans="1:41" ht="12.75">
       <c r="A33" s="111" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="42"/>
@@ -25091,7 +25096,7 @@
     </row>
     <row r="34" spans="1:41" ht="21" customHeight="1">
       <c r="A34" s="92" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
@@ -25119,7 +25124,7 @@
       <c r="Y34" s="42"/>
       <c r="Z34" s="42"/>
       <c r="AA34" s="79" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AB34" s="53"/>
       <c r="AC34" s="11"/>
@@ -25181,7 +25186,7 @@
     </row>
     <row r="36" spans="1:41" ht="20.25" customHeight="1">
       <c r="A36" s="92" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B36" s="42"/>
       <c r="C36" s="42"/>
@@ -25209,7 +25214,7 @@
       <c r="Y36" s="42"/>
       <c r="Z36" s="42"/>
       <c r="AA36" s="79" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AB36" s="53"/>
       <c r="AC36" s="11"/>
@@ -25271,7 +25276,7 @@
     </row>
     <row r="38" spans="1:41" ht="17.25" customHeight="1">
       <c r="A38" s="92" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B38" s="42"/>
       <c r="C38" s="42"/>
@@ -25299,7 +25304,7 @@
       <c r="Y38" s="42"/>
       <c r="Z38" s="42"/>
       <c r="AA38" s="79" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AB38" s="53"/>
       <c r="AC38" s="11"/>
@@ -25361,7 +25366,7 @@
     </row>
     <row r="40" spans="1:41" ht="17.25" customHeight="1">
       <c r="A40" s="92" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
@@ -25389,7 +25394,7 @@
       <c r="Y40" s="42"/>
       <c r="Z40" s="42"/>
       <c r="AA40" s="79" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AB40" s="53"/>
       <c r="AC40" s="11"/>
@@ -25709,7 +25714,7 @@
     </row>
     <row r="48" spans="1:41" ht="1.5" customHeight="1">
       <c r="A48" s="115" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -26398,7 +26403,7 @@
     </row>
     <row r="9" spans="1:40" ht="12.75">
       <c r="A9" s="117" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
@@ -26484,7 +26489,7 @@
     </row>
     <row r="11" spans="1:40" ht="18.75" customHeight="1">
       <c r="A11" s="92" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
@@ -26511,7 +26516,7 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="79" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AA11" s="53"/>
       <c r="AB11" s="24"/>
@@ -26614,7 +26619,7 @@
     </row>
     <row r="14" spans="1:40" ht="17.25" customHeight="1">
       <c r="A14" s="92" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -26641,7 +26646,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="79" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AA14" s="53"/>
       <c r="AB14" s="24"/>
@@ -26744,7 +26749,7 @@
     </row>
     <row r="17" spans="1:40" ht="17.25" customHeight="1">
       <c r="A17" s="92" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -26771,7 +26776,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="79" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AA17" s="53"/>
       <c r="AB17" s="24"/>
@@ -26874,7 +26879,7 @@
     </row>
     <row r="20" spans="1:40" ht="17.25" customHeight="1">
       <c r="A20" s="92" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
@@ -26901,7 +26906,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="79" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AA20" s="53"/>
       <c r="AB20" s="24"/>
@@ -27130,7 +27135,7 @@
     </row>
     <row r="26" spans="1:40" ht="12.75">
       <c r="A26" s="111" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -27216,7 +27221,7 @@
     </row>
     <row r="28" spans="1:40" ht="17.25" customHeight="1">
       <c r="A28" s="92" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -27243,7 +27248,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="79" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AA28" s="53"/>
       <c r="AB28" s="11"/>
@@ -27346,7 +27351,7 @@
     </row>
     <row r="31" spans="1:40" ht="16.5" customHeight="1">
       <c r="A31" s="92" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
@@ -27373,7 +27378,7 @@
       <c r="X31" s="42"/>
       <c r="Y31" s="42"/>
       <c r="Z31" s="79" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA31" s="53"/>
       <c r="AB31" s="11"/>
@@ -27477,7 +27482,7 @@
     <row r="34" spans="1:40" ht="17.25" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="92" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C34" s="42"/>
       <c r="D34" s="42"/>
@@ -27503,7 +27508,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="79" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AA34" s="53"/>
       <c r="AB34" s="11"/>
@@ -27607,7 +27612,7 @@
     <row r="37" spans="1:40" ht="17.25" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="92" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C37" s="42"/>
       <c r="D37" s="42"/>
@@ -27633,7 +27638,7 @@
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="79" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AA37" s="53"/>
       <c r="AB37" s="11"/>
@@ -29965,7 +29970,7 @@
         <v>11</v>
       </c>
       <c r="B93" s="85" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C93" s="42"/>
       <c r="D93" s="42"/>
@@ -30612,7 +30617,7 @@
     </row>
     <row r="8" spans="1:40" ht="42" customHeight="1">
       <c r="A8" s="128" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
@@ -30657,7 +30662,7 @@
     <row r="9" spans="1:40" ht="15" customHeight="1">
       <c r="A9" s="32"/>
       <c r="B9" s="129" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -30682,13 +30687,13 @@
       <c r="W9" s="33"/>
       <c r="X9" s="32"/>
       <c r="Y9" s="129" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Z9" s="42"/>
       <c r="AA9" s="42"/>
       <c r="AB9" s="42"/>
       <c r="AC9" s="129" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AD9" s="42"/>
       <c r="AE9" s="42"/>
@@ -30752,7 +30757,7 @@
     </row>
     <row r="11" spans="1:40" ht="27" customHeight="1">
       <c r="A11" s="118" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
@@ -30838,7 +30843,7 @@
     </row>
     <row r="13" spans="1:40" ht="17.25" customHeight="1">
       <c r="A13" s="119" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
@@ -30865,7 +30870,7 @@
       <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
       <c r="Z13" s="120" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AA13" s="53"/>
       <c r="AB13" s="29"/>
@@ -30926,7 +30931,7 @@
     </row>
     <row r="15" spans="1:40" ht="17.25" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="42"/>
@@ -30953,7 +30958,7 @@
       <c r="X15" s="21"/>
       <c r="Y15" s="21"/>
       <c r="Z15" s="120" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA15" s="53"/>
       <c r="AB15" s="29"/>
@@ -31014,7 +31019,7 @@
     </row>
     <row r="17" spans="1:40" ht="17.25" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -31041,7 +31046,7 @@
       <c r="X17" s="21"/>
       <c r="Y17" s="21"/>
       <c r="Z17" s="120" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AA17" s="53"/>
       <c r="AB17" s="29"/>
@@ -31102,7 +31107,7 @@
     </row>
     <row r="19" spans="1:40" ht="17.25" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -31129,7 +31134,7 @@
       <c r="X19" s="21"/>
       <c r="Y19" s="21"/>
       <c r="Z19" s="120" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AA19" s="53"/>
       <c r="AB19" s="29"/>
@@ -31190,7 +31195,7 @@
     </row>
     <row r="21" spans="1:40" ht="15.75" customHeight="1">
       <c r="A21" s="118" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
@@ -31276,7 +31281,7 @@
     </row>
     <row r="23" spans="1:40" ht="17.25" customHeight="1">
       <c r="A23" s="92" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
@@ -31303,7 +31308,7 @@
       <c r="X23" s="42"/>
       <c r="Y23" s="42"/>
       <c r="Z23" s="79" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AA23" s="53"/>
       <c r="AB23" s="11"/>
@@ -31406,7 +31411,7 @@
     </row>
     <row r="26" spans="1:40" ht="17.25" customHeight="1">
       <c r="A26" s="92" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -31433,7 +31438,7 @@
       <c r="X26" s="42"/>
       <c r="Y26" s="42"/>
       <c r="Z26" s="79" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AA26" s="53"/>
       <c r="AB26" s="11"/>
@@ -31536,7 +31541,7 @@
     </row>
     <row r="29" spans="1:40" ht="17.25" customHeight="1">
       <c r="A29" s="92" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="42"/>
@@ -31563,7 +31568,7 @@
       <c r="X29" s="42"/>
       <c r="Y29" s="42"/>
       <c r="Z29" s="79" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AA29" s="53"/>
       <c r="AB29" s="11"/>
@@ -31666,7 +31671,7 @@
     </row>
     <row r="32" spans="1:40" ht="17.25" customHeight="1">
       <c r="A32" s="92" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
@@ -31693,7 +31698,7 @@
       <c r="X32" s="42"/>
       <c r="Y32" s="42"/>
       <c r="Z32" s="79" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AA32" s="53"/>
       <c r="AB32" s="11"/>
@@ -31796,7 +31801,7 @@
     </row>
     <row r="35" spans="1:40" ht="20.25">
       <c r="A35" s="117" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B35" s="42"/>
       <c r="C35" s="42"/>
@@ -31882,7 +31887,7 @@
     </row>
     <row r="37" spans="1:40" ht="17.25" customHeight="1">
       <c r="A37" s="92" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B37" s="42"/>
       <c r="C37" s="42"/>
@@ -31909,7 +31914,7 @@
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="120" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AA37" s="53"/>
       <c r="AB37" s="29"/>
@@ -32012,7 +32017,7 @@
     </row>
     <row r="40" spans="1:40" ht="17.25" customHeight="1">
       <c r="A40" s="92" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
@@ -32039,7 +32044,7 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="120" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AA40" s="53"/>
       <c r="AB40" s="29"/>
@@ -32142,7 +32147,7 @@
     </row>
     <row r="43" spans="1:40" ht="17.25" customHeight="1">
       <c r="A43" s="92" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
@@ -32169,7 +32174,7 @@
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
       <c r="Z43" s="120" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AA43" s="53"/>
       <c r="AB43" s="29"/>
@@ -32272,7 +32277,7 @@
     </row>
     <row r="46" spans="1:40" ht="17.25" customHeight="1">
       <c r="A46" s="92" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B46" s="42"/>
       <c r="C46" s="42"/>
@@ -32299,7 +32304,7 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="120" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AA46" s="53"/>
       <c r="AB46" s="29"/>
@@ -32573,7 +32578,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="85" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C53" s="42"/>
       <c r="D53" s="42"/>
@@ -33326,7 +33331,7 @@
     </row>
     <row r="9" spans="1:40" ht="27" customHeight="1">
       <c r="A9" s="118" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
@@ -33412,7 +33417,7 @@
     </row>
     <row r="11" spans="1:40" ht="17.25" customHeight="1">
       <c r="A11" s="119" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
@@ -33439,7 +33444,7 @@
       <c r="X11" s="21"/>
       <c r="Y11" s="21"/>
       <c r="Z11" s="120" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AA11" s="53"/>
       <c r="AB11" s="29"/>
@@ -33500,7 +33505,7 @@
     </row>
     <row r="13" spans="1:40" ht="17.25" customHeight="1">
       <c r="A13" s="119" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
@@ -33527,7 +33532,7 @@
       <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
       <c r="Z13" s="120" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA13" s="53"/>
       <c r="AB13" s="29"/>
@@ -33588,7 +33593,7 @@
     </row>
     <row r="15" spans="1:40" ht="17.25" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="42"/>
@@ -33615,7 +33620,7 @@
       <c r="X15" s="21"/>
       <c r="Y15" s="21"/>
       <c r="Z15" s="120" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AA15" s="53"/>
       <c r="AB15" s="29"/>
@@ -33676,7 +33681,7 @@
     </row>
     <row r="17" spans="1:40" ht="17.25" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -33703,7 +33708,7 @@
       <c r="X17" s="21"/>
       <c r="Y17" s="21"/>
       <c r="Z17" s="120" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AA17" s="53"/>
       <c r="AB17" s="29"/>
@@ -33764,7 +33769,7 @@
     </row>
     <row r="19" spans="1:40" ht="37.5" customHeight="1">
       <c r="A19" s="112" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -33850,7 +33855,7 @@
     </row>
     <row r="21" spans="1:40" ht="17.25" customHeight="1">
       <c r="A21" s="92" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
@@ -33877,7 +33882,7 @@
       <c r="X21" s="42"/>
       <c r="Y21" s="42"/>
       <c r="Z21" s="120" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA21" s="53"/>
       <c r="AB21" s="29"/>
@@ -33980,7 +33985,7 @@
     </row>
     <row r="24" spans="1:40" ht="17.25" customHeight="1">
       <c r="A24" s="92" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="42"/>
@@ -34007,7 +34012,7 @@
       <c r="X24" s="42"/>
       <c r="Y24" s="42"/>
       <c r="Z24" s="120" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA24" s="53"/>
       <c r="AB24" s="29"/>
@@ -34110,7 +34115,7 @@
     </row>
     <row r="27" spans="1:40" ht="17.25" customHeight="1">
       <c r="A27" s="92" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
@@ -34137,7 +34142,7 @@
       <c r="X27" s="42"/>
       <c r="Y27" s="42"/>
       <c r="Z27" s="120" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AA27" s="53"/>
       <c r="AB27" s="29"/>
@@ -34240,7 +34245,7 @@
     </row>
     <row r="30" spans="1:40" ht="17.25" customHeight="1">
       <c r="A30" s="92" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
@@ -34267,7 +34272,7 @@
       <c r="X30" s="42"/>
       <c r="Y30" s="42"/>
       <c r="Z30" s="120" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AA30" s="53"/>
       <c r="AB30" s="29"/>
@@ -36167,7 +36172,7 @@
     </row>
     <row r="8" spans="1:41" ht="29.25" customHeight="1">
       <c r="A8" s="109" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
@@ -36214,7 +36219,7 @@
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="42"/>
@@ -36239,14 +36244,14 @@
       <c r="X9" s="42"/>
       <c r="Y9" s="42"/>
       <c r="Z9" s="103" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA9" s="42"/>
       <c r="AB9" s="42"/>
       <c r="AC9" s="42"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF9" s="42"/>
       <c r="AG9" s="42"/>
@@ -36310,7 +36315,7 @@
     </row>
     <row r="11" spans="1:41" ht="17.25" customHeight="1">
       <c r="A11" s="112" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
@@ -36355,7 +36360,7 @@
     </row>
     <row r="12" spans="1:41" ht="16.5" customHeight="1">
       <c r="A12" s="92" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
@@ -36383,7 +36388,7 @@
       <c r="Y12" s="42"/>
       <c r="Z12" s="42"/>
       <c r="AA12" s="79" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AB12" s="42"/>
       <c r="AC12" s="6"/>
@@ -36445,7 +36450,7 @@
     </row>
     <row r="14" spans="1:41" ht="12.75">
       <c r="A14" s="92" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -36473,7 +36478,7 @@
       <c r="Y14" s="42"/>
       <c r="Z14" s="42"/>
       <c r="AA14" s="79" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AB14" s="42"/>
       <c r="AC14" s="6"/>
@@ -36535,7 +36540,7 @@
     </row>
     <row r="16" spans="1:41" ht="17.25" customHeight="1">
       <c r="A16" s="92" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B16" s="42"/>
       <c r="C16" s="42"/>
@@ -36563,7 +36568,7 @@
       <c r="Y16" s="42"/>
       <c r="Z16" s="42"/>
       <c r="AA16" s="79" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AB16" s="42"/>
       <c r="AC16" s="6"/>
@@ -36625,7 +36630,7 @@
     </row>
     <row r="18" spans="1:41" ht="18" customHeight="1">
       <c r="A18" s="92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B18" s="42"/>
       <c r="C18" s="42"/>
@@ -36653,7 +36658,7 @@
       <c r="Y18" s="42"/>
       <c r="Z18" s="42"/>
       <c r="AA18" s="79" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AB18" s="42"/>
       <c r="AC18" s="6"/>
@@ -36672,7 +36677,7 @@
     </row>
     <row r="19" spans="1:41" ht="12.75">
       <c r="A19" s="130" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -36717,7 +36722,7 @@
     </row>
     <row r="20" spans="1:41" ht="18" customHeight="1">
       <c r="A20" s="92" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
@@ -36745,7 +36750,7 @@
       <c r="Y20" s="42"/>
       <c r="Z20" s="42"/>
       <c r="AA20" s="79" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AB20" s="42"/>
       <c r="AC20" s="6"/>
@@ -36807,7 +36812,7 @@
     </row>
     <row r="22" spans="1:41" ht="17.25" customHeight="1">
       <c r="A22" s="92" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
@@ -36835,7 +36840,7 @@
       <c r="Y22" s="42"/>
       <c r="Z22" s="42"/>
       <c r="AA22" s="79" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AB22" s="42"/>
       <c r="AC22" s="6"/>
@@ -36897,7 +36902,7 @@
     </row>
     <row r="24" spans="1:41" ht="18" customHeight="1">
       <c r="A24" s="92" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="42"/>
@@ -36925,7 +36930,7 @@
       <c r="Y24" s="42"/>
       <c r="Z24" s="42"/>
       <c r="AA24" s="79" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB24" s="42"/>
       <c r="AC24" s="6"/>
@@ -36987,7 +36992,7 @@
     </row>
     <row r="26" spans="1:41" ht="17.25" customHeight="1">
       <c r="A26" s="92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -37015,7 +37020,7 @@
       <c r="Y26" s="42"/>
       <c r="Z26" s="42"/>
       <c r="AA26" s="79" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AB26" s="42"/>
       <c r="AC26" s="6"/>
@@ -37077,7 +37082,7 @@
     </row>
     <row r="28" spans="1:41" ht="18.75" customHeight="1">
       <c r="A28" s="92" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -37105,7 +37110,7 @@
       <c r="Y28" s="42"/>
       <c r="Z28" s="42"/>
       <c r="AA28" s="79" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AB28" s="42"/>
       <c r="AC28" s="6"/>
@@ -37167,7 +37172,7 @@
     </row>
     <row r="30" spans="1:41" ht="19.5" customHeight="1">
       <c r="A30" s="130" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
@@ -37212,7 +37217,7 @@
     </row>
     <row r="31" spans="1:41" ht="16.5" customHeight="1">
       <c r="A31" s="92" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
@@ -37240,7 +37245,7 @@
       <c r="Y31" s="42"/>
       <c r="Z31" s="42"/>
       <c r="AA31" s="79" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AB31" s="42"/>
       <c r="AC31" s="6"/>
@@ -37302,7 +37307,7 @@
     </row>
     <row r="33" spans="1:41" ht="18.75" customHeight="1">
       <c r="A33" s="92" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="42"/>
@@ -37330,7 +37335,7 @@
       <c r="Y33" s="42"/>
       <c r="Z33" s="42"/>
       <c r="AA33" s="79" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AB33" s="42"/>
       <c r="AC33" s="6"/>
@@ -37392,7 +37397,7 @@
     </row>
     <row r="35" spans="1:41" ht="18" customHeight="1">
       <c r="A35" s="92" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B35" s="42"/>
       <c r="C35" s="42"/>
@@ -37420,7 +37425,7 @@
       <c r="Y35" s="42"/>
       <c r="Z35" s="42"/>
       <c r="AA35" s="79" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AB35" s="42"/>
       <c r="AC35" s="6"/>
@@ -37482,7 +37487,7 @@
     </row>
     <row r="37" spans="1:41" ht="16.5" customHeight="1">
       <c r="A37" s="92" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B37" s="42"/>
       <c r="C37" s="42"/>
@@ -37510,7 +37515,7 @@
       <c r="Y37" s="42"/>
       <c r="Z37" s="42"/>
       <c r="AA37" s="79" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AB37" s="42"/>
       <c r="AC37" s="6"/>
@@ -37572,7 +37577,7 @@
     </row>
     <row r="39" spans="1:41" ht="17.25" customHeight="1">
       <c r="A39" s="130" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B39" s="42"/>
       <c r="C39" s="42"/>
@@ -37617,7 +37622,7 @@
     </row>
     <row r="40" spans="1:41" ht="17.25" customHeight="1">
       <c r="A40" s="92" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
@@ -37645,7 +37650,7 @@
       <c r="Y40" s="42"/>
       <c r="Z40" s="42"/>
       <c r="AA40" s="79" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AB40" s="42"/>
       <c r="AC40" s="6"/>
@@ -37707,7 +37712,7 @@
     </row>
     <row r="42" spans="1:41" ht="18" customHeight="1">
       <c r="A42" s="92" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B42" s="42"/>
       <c r="C42" s="42"/>
@@ -37735,7 +37740,7 @@
       <c r="Y42" s="42"/>
       <c r="Z42" s="42"/>
       <c r="AA42" s="79" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AB42" s="42"/>
       <c r="AC42" s="6"/>
@@ -37797,7 +37802,7 @@
     </row>
     <row r="44" spans="1:41" ht="17.25" customHeight="1">
       <c r="A44" s="92" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="42"/>
@@ -37825,7 +37830,7 @@
       <c r="Y44" s="42"/>
       <c r="Z44" s="42"/>
       <c r="AA44" s="79" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AB44" s="42"/>
       <c r="AC44" s="6"/>
@@ -37887,7 +37892,7 @@
     </row>
     <row r="46" spans="1:41" ht="17.25" customHeight="1">
       <c r="A46" s="92" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B46" s="42"/>
       <c r="C46" s="42"/>
@@ -37915,7 +37920,7 @@
       <c r="Y46" s="42"/>
       <c r="Z46" s="42"/>
       <c r="AA46" s="79" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AB46" s="42"/>
       <c r="AC46" s="6"/>
@@ -37977,7 +37982,7 @@
     </row>
     <row r="48" spans="1:41" ht="17.25" customHeight="1">
       <c r="A48" s="112" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -38022,7 +38027,7 @@
     </row>
     <row r="49" spans="1:41" ht="21">
       <c r="A49" s="92" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B49" s="42"/>
       <c r="C49" s="42"/>
@@ -38050,14 +38055,14 @@
       <c r="Y49" s="42"/>
       <c r="Z49" s="42"/>
       <c r="AA49" s="79" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AB49" s="42"/>
       <c r="AC49" s="6"/>
       <c r="AD49" s="11"/>
       <c r="AE49" s="11"/>
       <c r="AF49" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG49" s="11"/>
       <c r="AH49" s="3"/>
@@ -38114,7 +38119,7 @@
     </row>
     <row r="51" spans="1:41" ht="21">
       <c r="A51" s="92" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
@@ -38142,14 +38147,14 @@
       <c r="Y51" s="42"/>
       <c r="Z51" s="42"/>
       <c r="AA51" s="79" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AB51" s="42"/>
       <c r="AC51" s="6"/>
       <c r="AD51" s="11"/>
       <c r="AE51" s="11"/>
       <c r="AF51" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG51" s="11"/>
       <c r="AH51" s="3"/>
@@ -38206,7 +38211,7 @@
     </row>
     <row r="53" spans="1:41" ht="21">
       <c r="A53" s="92" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B53" s="42"/>
       <c r="C53" s="42"/>
@@ -38234,14 +38239,14 @@
       <c r="Y53" s="42"/>
       <c r="Z53" s="42"/>
       <c r="AA53" s="79" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AB53" s="42"/>
       <c r="AC53" s="6"/>
       <c r="AD53" s="11"/>
       <c r="AE53" s="11"/>
       <c r="AF53" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG53" s="11"/>
       <c r="AH53" s="3"/>
@@ -38298,7 +38303,7 @@
     </row>
     <row r="55" spans="1:41" ht="21">
       <c r="A55" s="92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B55" s="42"/>
       <c r="C55" s="42"/>
@@ -38326,14 +38331,14 @@
       <c r="Y55" s="42"/>
       <c r="Z55" s="42"/>
       <c r="AA55" s="79" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AB55" s="42"/>
       <c r="AC55" s="6"/>
       <c r="AD55" s="11"/>
       <c r="AE55" s="11"/>
       <c r="AF55" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG55" s="11"/>
       <c r="AH55" s="3"/>
@@ -38390,7 +38395,7 @@
     </row>
     <row r="57" spans="1:41" ht="21">
       <c r="A57" s="92" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B57" s="42"/>
       <c r="C57" s="42"/>
@@ -38410,7 +38415,7 @@
       <c r="Q57" s="42"/>
       <c r="R57" s="42"/>
       <c r="S57" s="79" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="T57" s="53"/>
       <c r="U57" s="11"/>
@@ -39103,7 +39108,7 @@
     <row r="8" spans="1:40" ht="16.5" customHeight="1">
       <c r="A8" s="32"/>
       <c r="B8" s="129" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -39129,13 +39134,13 @@
       <c r="X8" s="42"/>
       <c r="Y8" s="21"/>
       <c r="Z8" s="129" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA8" s="42"/>
       <c r="AB8" s="42"/>
       <c r="AC8" s="42"/>
       <c r="AD8" s="129" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AE8" s="42"/>
       <c r="AF8" s="42"/>
@@ -39198,7 +39203,7 @@
     </row>
     <row r="10" spans="1:40" ht="17.25" customHeight="1">
       <c r="A10" s="130" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
@@ -39242,7 +39247,7 @@
     </row>
     <row r="11" spans="1:40" ht="18" customHeight="1">
       <c r="A11" s="92" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
@@ -39270,7 +39275,7 @@
       <c r="Y11" s="42"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="120" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AB11" s="42"/>
       <c r="AC11" s="29"/>
@@ -39330,7 +39335,7 @@
     </row>
     <row r="13" spans="1:40" ht="17.25" customHeight="1">
       <c r="A13" s="92" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
@@ -39358,7 +39363,7 @@
       <c r="Y13" s="42"/>
       <c r="Z13" s="3"/>
       <c r="AA13" s="120" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AB13" s="42"/>
       <c r="AC13" s="29"/>
@@ -39418,7 +39423,7 @@
     </row>
     <row r="15" spans="1:40" ht="18" customHeight="1">
       <c r="A15" s="92" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="42"/>
@@ -39446,7 +39451,7 @@
       <c r="Y15" s="42"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="120" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AB15" s="42"/>
       <c r="AC15" s="29"/>
@@ -39506,7 +39511,7 @@
     </row>
     <row r="17" spans="1:40" ht="17.25" customHeight="1">
       <c r="A17" s="92" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -39534,7 +39539,7 @@
       <c r="Y17" s="42"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="120" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AB17" s="42"/>
       <c r="AC17" s="11"/>
@@ -39594,7 +39599,7 @@
     </row>
     <row r="19" spans="1:40" ht="18" customHeight="1">
       <c r="A19" s="92" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -39622,7 +39627,7 @@
       <c r="Y19" s="42"/>
       <c r="Z19" s="42"/>
       <c r="AA19" s="120" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AB19" s="42"/>
       <c r="AC19" s="29"/>
@@ -39682,7 +39687,7 @@
     </row>
     <row r="21" spans="1:40" ht="21.75" customHeight="1">
       <c r="A21" s="111" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
@@ -39768,7 +39773,7 @@
     </row>
     <row r="23" spans="1:40" ht="21.75" customHeight="1">
       <c r="A23" s="92" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
@@ -39796,7 +39801,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="79" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AB23" s="42"/>
       <c r="AC23" s="11"/>
@@ -39898,7 +39903,7 @@
     </row>
     <row r="26" spans="1:40" ht="18.75" customHeight="1">
       <c r="A26" s="92" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -39926,7 +39931,7 @@
       <c r="Y26" s="42"/>
       <c r="Z26" s="3"/>
       <c r="AA26" s="79" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AB26" s="42"/>
       <c r="AC26" s="11"/>
@@ -39987,7 +39992,7 @@
     <row r="28" spans="1:40" ht="19.5" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="92" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C28" s="42"/>
       <c r="D28" s="42"/>
@@ -40014,7 +40019,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
       <c r="AA28" s="79" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AB28" s="42"/>
       <c r="AC28" s="11"/>
@@ -40075,7 +40080,7 @@
     <row r="30" spans="1:40" ht="18" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="92" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C30" s="42"/>
       <c r="D30" s="42"/>
@@ -40102,7 +40107,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
       <c r="AA30" s="79" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AB30" s="42"/>
       <c r="AC30" s="11"/>

--- a/templates/Declaration_template.xlsx
+++ b/templates/Declaration_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="540" windowWidth="13095" windowHeight="10935" activeTab="1"/>
+    <workbookView xWindow="270" yWindow="540" windowWidth="13095" windowHeight="10935" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Титул" sheetId="1" r:id="rId1"/>
@@ -1952,7 +1952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2329,6 +2329,8 @@
     <xf numFmtId="49" fontId="29" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -23560,11 +23562,11 @@
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="X1" s="116" t="str">
+      <c r="X1" s="154" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="Y1" s="116" t="str">
+      <c r="Y1" s="154" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
@@ -23608,9 +23610,9 @@
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
       <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="100"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
       <c r="Z2" s="98"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -26045,11 +26047,11 @@
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="W1" s="116" t="str">
+      <c r="W1" s="154" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="X1" s="116" t="str">
+      <c r="X1" s="154" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
@@ -26092,9 +26094,9 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
       <c r="Y2" s="98"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>

--- a/templates/Declaration_template.xlsx
+++ b/templates/Declaration_template.xlsx
@@ -1666,7 +1666,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1689,6 +1689,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1952,7 +1958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2192,7 +2198,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2329,8 +2334,10 @@
     <xf numFmtId="49" fontId="29" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -8832,9 +8839,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:75" ht="15.75">
-      <c r="A1" s="140"/>
+      <c r="A1" s="139"/>
       <c r="B1" s="75"/>
-      <c r="C1" s="141"/>
+      <c r="C1" s="140"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
@@ -8848,9 +8855,9 @@
       <c r="N1" s="42"/>
       <c r="O1" s="42"/>
       <c r="P1" s="42"/>
-      <c r="Q1" s="142"/>
+      <c r="Q1" s="141"/>
       <c r="R1" s="75"/>
-      <c r="S1" s="125" t="s">
+      <c r="S1" s="124" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="42"/>
@@ -8858,62 +8865,62 @@
       <c r="V1" s="42"/>
       <c r="W1" s="42"/>
       <c r="X1" s="53"/>
-      <c r="Y1" s="138" t="str">
+      <c r="Y1" s="137" t="str">
         <f>IF(Титул!Y1="","",Титул!Y1)</f>
         <v>1</v>
       </c>
       <c r="Z1" s="66"/>
-      <c r="AA1" s="138" t="str">
+      <c r="AA1" s="137" t="str">
         <f>IF(Титул!AA1="","",Титул!AA1)</f>
         <v>2</v>
       </c>
       <c r="AB1" s="66"/>
-      <c r="AC1" s="138" t="str">
+      <c r="AC1" s="137" t="str">
         <f>IF(Титул!AC1="","",Титул!AC1)</f>
         <v>3</v>
       </c>
       <c r="AD1" s="66"/>
-      <c r="AE1" s="138" t="str">
+      <c r="AE1" s="137" t="str">
         <f>IF(Титул!AE1="","",Титул!AE1)</f>
         <v>4</v>
       </c>
       <c r="AF1" s="66"/>
-      <c r="AG1" s="138" t="str">
+      <c r="AG1" s="137" t="str">
         <f>IF(Титул!AG1="","",Титул!AG1)</f>
         <v>5</v>
       </c>
       <c r="AH1" s="66"/>
-      <c r="AI1" s="138" t="str">
+      <c r="AI1" s="137" t="str">
         <f>IF(Титул!AI1="","",Титул!AI1)</f>
         <v>6</v>
       </c>
       <c r="AJ1" s="66"/>
-      <c r="AK1" s="138" t="str">
+      <c r="AK1" s="137" t="str">
         <f>IF(Титул!AK1="","",Титул!AK1)</f>
         <v>7</v>
       </c>
       <c r="AL1" s="66"/>
-      <c r="AM1" s="138" t="str">
+      <c r="AM1" s="137" t="str">
         <f>IF(Титул!AM1="","",Титул!AM1)</f>
         <v>8</v>
       </c>
       <c r="AN1" s="66"/>
-      <c r="AO1" s="138" t="str">
+      <c r="AO1" s="137" t="str">
         <f>IF(Титул!AO1="","",Титул!AO1)</f>
         <v>9</v>
       </c>
       <c r="AP1" s="66"/>
-      <c r="AQ1" s="138" t="str">
+      <c r="AQ1" s="137" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
       <c r="AR1" s="66"/>
-      <c r="AS1" s="136" t="str">
+      <c r="AS1" s="135" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
       <c r="AT1" s="66"/>
-      <c r="AU1" s="136" t="str">
+      <c r="AU1" s="135" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
@@ -8922,7 +8929,7 @@
       <c r="AX1" s="31"/>
       <c r="AY1" s="31"/>
       <c r="AZ1" s="31"/>
-      <c r="BA1" s="137"/>
+      <c r="BA1" s="136"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
       <c r="BD1" s="42"/>
@@ -8947,7 +8954,7 @@
       <c r="BW1" s="42"/>
     </row>
     <row r="2" spans="1:75" ht="2.25" customHeight="1">
-      <c r="A2" s="141"/>
+      <c r="A2" s="140"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
@@ -8963,7 +8970,7 @@
       <c r="N2" s="42"/>
       <c r="O2" s="42"/>
       <c r="P2" s="42"/>
-      <c r="Q2" s="114"/>
+      <c r="Q2" s="113"/>
       <c r="R2" s="42"/>
       <c r="S2" s="42"/>
       <c r="T2" s="42"/>
@@ -9024,7 +9031,7 @@
       <c r="BW2" s="42"/>
     </row>
     <row r="3" spans="1:75" ht="4.5" customHeight="1">
-      <c r="A3" s="141"/>
+      <c r="A3" s="140"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
@@ -9040,9 +9047,9 @@
       <c r="N3" s="42"/>
       <c r="O3" s="42"/>
       <c r="P3" s="42"/>
-      <c r="Q3" s="114"/>
+      <c r="Q3" s="113"/>
       <c r="R3" s="42"/>
-      <c r="S3" s="114"/>
+      <c r="S3" s="113"/>
       <c r="T3" s="42"/>
       <c r="U3" s="42"/>
       <c r="V3" s="42"/>
@@ -9062,7 +9069,7 @@
       <c r="AJ3" s="38"/>
       <c r="AK3" s="38"/>
       <c r="AL3" s="38"/>
-      <c r="AM3" s="139"/>
+      <c r="AM3" s="138"/>
       <c r="AN3" s="70"/>
       <c r="AO3" s="38"/>
       <c r="AP3" s="21"/>
@@ -9101,7 +9108,7 @@
       <c r="BW3" s="42"/>
     </row>
     <row r="4" spans="1:75" ht="21">
-      <c r="A4" s="143"/>
+      <c r="A4" s="142"/>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
@@ -9117,9 +9124,9 @@
       <c r="N4" s="42"/>
       <c r="O4" s="42"/>
       <c r="P4" s="42"/>
-      <c r="Q4" s="114"/>
+      <c r="Q4" s="113"/>
       <c r="R4" s="42"/>
-      <c r="S4" s="125" t="s">
+      <c r="S4" s="124" t="s">
         <v>9</v>
       </c>
       <c r="T4" s="42"/>
@@ -9127,62 +9134,62 @@
       <c r="V4" s="42"/>
       <c r="W4" s="42"/>
       <c r="X4" s="53"/>
-      <c r="Y4" s="144" t="str">
+      <c r="Y4" s="143" t="str">
         <f>IF(Титул!Y4="","",Титул!Y4)</f>
         <v/>
       </c>
       <c r="Z4" s="50"/>
-      <c r="AA4" s="144" t="str">
+      <c r="AA4" s="143" t="str">
         <f>IF(Титул!AA4="","",Титул!AA4)</f>
         <v/>
       </c>
       <c r="AB4" s="50"/>
-      <c r="AC4" s="144" t="str">
+      <c r="AC4" s="143" t="str">
         <f>IF(Титул!AC4="","",Титул!AC4)</f>
         <v/>
       </c>
       <c r="AD4" s="50"/>
-      <c r="AE4" s="144" t="str">
+      <c r="AE4" s="143" t="str">
         <f>IF(Титул!AE4="","",Титул!AE4)</f>
         <v/>
       </c>
       <c r="AF4" s="50"/>
-      <c r="AG4" s="144" t="str">
+      <c r="AG4" s="143" t="str">
         <f>IF(Титул!AG4="","",Титул!AG4)</f>
         <v/>
       </c>
       <c r="AH4" s="50"/>
-      <c r="AI4" s="144" t="str">
+      <c r="AI4" s="143" t="str">
         <f>IF(Титул!AI4="","",Титул!AI4)</f>
         <v/>
       </c>
       <c r="AJ4" s="50"/>
-      <c r="AK4" s="144" t="str">
+      <c r="AK4" s="143" t="str">
         <f>IF(Титул!AK4="","",Титул!AK4)</f>
         <v/>
       </c>
       <c r="AL4" s="50"/>
-      <c r="AM4" s="144" t="str">
+      <c r="AM4" s="143" t="str">
         <f>IF(Титул!AM4="","",Титул!AM4)</f>
         <v/>
       </c>
       <c r="AN4" s="50"/>
-      <c r="AO4" s="144" t="str">
+      <c r="AO4" s="143" t="str">
         <f>IF(Титул!AO4="","",Титул!AO4)</f>
         <v/>
       </c>
       <c r="AP4" s="50"/>
-      <c r="AQ4" s="149" t="s">
+      <c r="AQ4" s="148" t="s">
         <v>12</v>
       </c>
       <c r="AR4" s="42"/>
       <c r="AS4" s="42"/>
       <c r="AT4" s="53"/>
-      <c r="AU4" s="132"/>
+      <c r="AU4" s="131"/>
       <c r="AV4" s="50"/>
-      <c r="AW4" s="132"/>
+      <c r="AW4" s="131"/>
       <c r="AX4" s="50"/>
-      <c r="AY4" s="132"/>
+      <c r="AY4" s="131"/>
       <c r="AZ4" s="50"/>
       <c r="BA4" s="42"/>
       <c r="BB4" s="42"/>
@@ -9209,7 +9216,7 @@
       <c r="BW4" s="42"/>
     </row>
     <row r="5" spans="1:75" ht="4.5" customHeight="1">
-      <c r="A5" s="141"/>
+      <c r="A5" s="140"/>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
@@ -9225,9 +9232,9 @@
       <c r="N5" s="42"/>
       <c r="O5" s="42"/>
       <c r="P5" s="42"/>
-      <c r="Q5" s="114"/>
+      <c r="Q5" s="113"/>
       <c r="R5" s="42"/>
-      <c r="S5" s="114"/>
+      <c r="S5" s="113"/>
       <c r="T5" s="42"/>
       <c r="U5" s="42"/>
       <c r="V5" s="42"/>
@@ -9262,7 +9269,7 @@
       <c r="AY5" s="42"/>
       <c r="AZ5" s="42"/>
       <c r="BA5" s="21"/>
-      <c r="BB5" s="114"/>
+      <c r="BB5" s="113"/>
       <c r="BC5" s="42"/>
       <c r="BD5" s="42"/>
       <c r="BE5" s="42"/>
@@ -9286,7 +9293,7 @@
       <c r="BW5" s="42"/>
     </row>
     <row r="6" spans="1:75" ht="16.5" customHeight="1">
-      <c r="A6" s="141"/>
+      <c r="A6" s="140"/>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
@@ -9302,9 +9309,9 @@
       <c r="N6" s="42"/>
       <c r="O6" s="42"/>
       <c r="P6" s="42"/>
-      <c r="Q6" s="114"/>
+      <c r="Q6" s="113"/>
       <c r="R6" s="42"/>
-      <c r="S6" s="114"/>
+      <c r="S6" s="113"/>
       <c r="T6" s="42"/>
       <c r="U6" s="42"/>
       <c r="V6" s="42"/>
@@ -9339,7 +9346,7 @@
       <c r="AY6" s="42"/>
       <c r="AZ6" s="42"/>
       <c r="BA6" s="21"/>
-      <c r="BB6" s="114"/>
+      <c r="BB6" s="113"/>
       <c r="BC6" s="42"/>
       <c r="BD6" s="42"/>
       <c r="BE6" s="42"/>
@@ -9363,7 +9370,7 @@
       <c r="BW6" s="42"/>
     </row>
     <row r="7" spans="1:75" ht="5.25" customHeight="1">
-      <c r="A7" s="145"/>
+      <c r="A7" s="144"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -9440,7 +9447,7 @@
       <c r="BW7" s="42"/>
     </row>
     <row r="8" spans="1:75" ht="14.25" customHeight="1">
-      <c r="A8" s="146"/>
+      <c r="A8" s="145"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -9517,7 +9524,7 @@
       <c r="BW8" s="42"/>
     </row>
     <row r="9" spans="1:75" ht="48.75" customHeight="1">
-      <c r="A9" s="147" t="s">
+      <c r="A9" s="146" t="s">
         <v>212</v>
       </c>
       <c r="B9" s="42"/>
@@ -9596,7 +9603,7 @@
       <c r="BW9" s="42"/>
     </row>
     <row r="10" spans="1:75" ht="69.75" customHeight="1">
-      <c r="A10" s="129" t="s">
+      <c r="A10" s="128" t="s">
         <v>213</v>
       </c>
       <c r="B10" s="42"/>
@@ -9606,7 +9613,7 @@
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
-      <c r="I10" s="129" t="s">
+      <c r="I10" s="128" t="s">
         <v>214</v>
       </c>
       <c r="J10" s="42"/>
@@ -9628,7 +9635,7 @@
       <c r="Z10" s="42"/>
       <c r="AA10" s="42"/>
       <c r="AB10" s="42"/>
-      <c r="AC10" s="129" t="s">
+      <c r="AC10" s="128" t="s">
         <v>215</v>
       </c>
       <c r="AD10" s="42"/>
@@ -9656,7 +9663,7 @@
       <c r="AZ10" s="42"/>
       <c r="BA10" s="42"/>
       <c r="BB10" s="42"/>
-      <c r="BC10" s="129" t="s">
+      <c r="BC10" s="128" t="s">
         <v>216</v>
       </c>
       <c r="BD10" s="42"/>
@@ -9681,7 +9688,7 @@
       <c r="BW10" s="42"/>
     </row>
     <row r="11" spans="1:75" ht="14.25" customHeight="1">
-      <c r="A11" s="148" t="s">
+      <c r="A11" s="147" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="42"/>
@@ -9691,7 +9698,7 @@
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
-      <c r="I11" s="148" t="s">
+      <c r="I11" s="147" t="s">
         <v>217</v>
       </c>
       <c r="J11" s="42"/>
@@ -9713,7 +9720,7 @@
       <c r="Z11" s="42"/>
       <c r="AA11" s="42"/>
       <c r="AB11" s="42"/>
-      <c r="AC11" s="148" t="s">
+      <c r="AC11" s="147" t="s">
         <v>218</v>
       </c>
       <c r="AD11" s="42"/>
@@ -9741,7 +9748,7 @@
       <c r="AZ11" s="42"/>
       <c r="BA11" s="42"/>
       <c r="BB11" s="42"/>
-      <c r="BC11" s="148" t="s">
+      <c r="BC11" s="147" t="s">
         <v>219</v>
       </c>
       <c r="BD11" s="42"/>
@@ -9766,3244 +9773,3244 @@
       <c r="BW11" s="42"/>
     </row>
     <row r="12" spans="1:75" ht="6" customHeight="1">
-      <c r="A12" s="120"/>
+      <c r="A12" s="119"/>
       <c r="B12" s="42"/>
-      <c r="C12" s="120"/>
+      <c r="C12" s="119"/>
       <c r="D12" s="42"/>
-      <c r="E12" s="120"/>
+      <c r="E12" s="119"/>
       <c r="F12" s="42"/>
-      <c r="G12" s="120"/>
+      <c r="G12" s="119"/>
       <c r="H12" s="42"/>
-      <c r="I12" s="120"/>
+      <c r="I12" s="119"/>
       <c r="J12" s="42"/>
-      <c r="K12" s="120"/>
+      <c r="K12" s="119"/>
       <c r="L12" s="42"/>
-      <c r="M12" s="120"/>
+      <c r="M12" s="119"/>
       <c r="N12" s="42"/>
-      <c r="O12" s="120"/>
+      <c r="O12" s="119"/>
       <c r="P12" s="42"/>
-      <c r="Q12" s="120"/>
+      <c r="Q12" s="119"/>
       <c r="R12" s="42"/>
-      <c r="S12" s="120"/>
+      <c r="S12" s="119"/>
       <c r="T12" s="42"/>
-      <c r="U12" s="120"/>
+      <c r="U12" s="119"/>
       <c r="V12" s="42"/>
-      <c r="W12" s="120"/>
+      <c r="W12" s="119"/>
       <c r="X12" s="42"/>
-      <c r="Y12" s="120"/>
+      <c r="Y12" s="119"/>
       <c r="Z12" s="42"/>
-      <c r="AA12" s="120"/>
+      <c r="AA12" s="119"/>
       <c r="AB12" s="42"/>
-      <c r="AC12" s="120"/>
+      <c r="AC12" s="119"/>
       <c r="AD12" s="42"/>
-      <c r="AE12" s="120"/>
+      <c r="AE12" s="119"/>
       <c r="AF12" s="42"/>
-      <c r="AG12" s="120"/>
+      <c r="AG12" s="119"/>
       <c r="AH12" s="42"/>
-      <c r="AI12" s="120"/>
+      <c r="AI12" s="119"/>
       <c r="AJ12" s="42"/>
-      <c r="AK12" s="120"/>
+      <c r="AK12" s="119"/>
       <c r="AL12" s="42"/>
-      <c r="AM12" s="120"/>
+      <c r="AM12" s="119"/>
       <c r="AN12" s="42"/>
-      <c r="AO12" s="120"/>
+      <c r="AO12" s="119"/>
       <c r="AP12" s="42"/>
-      <c r="AQ12" s="120"/>
+      <c r="AQ12" s="119"/>
       <c r="AR12" s="42"/>
-      <c r="AS12" s="120"/>
+      <c r="AS12" s="119"/>
       <c r="AT12" s="42"/>
-      <c r="AU12" s="120"/>
+      <c r="AU12" s="119"/>
       <c r="AV12" s="42"/>
-      <c r="AW12" s="120"/>
+      <c r="AW12" s="119"/>
       <c r="AX12" s="42"/>
-      <c r="AY12" s="120"/>
+      <c r="AY12" s="119"/>
       <c r="AZ12" s="42"/>
-      <c r="BA12" s="120"/>
+      <c r="BA12" s="119"/>
       <c r="BB12" s="42"/>
-      <c r="BC12" s="120"/>
+      <c r="BC12" s="119"/>
       <c r="BD12" s="42"/>
-      <c r="BE12" s="120"/>
+      <c r="BE12" s="119"/>
       <c r="BF12" s="42"/>
-      <c r="BG12" s="120"/>
+      <c r="BG12" s="119"/>
       <c r="BH12" s="42"/>
-      <c r="BI12" s="120"/>
+      <c r="BI12" s="119"/>
       <c r="BJ12" s="42"/>
-      <c r="BK12" s="120"/>
+      <c r="BK12" s="119"/>
       <c r="BL12" s="42"/>
-      <c r="BM12" s="120"/>
+      <c r="BM12" s="119"/>
       <c r="BN12" s="42"/>
-      <c r="BO12" s="120"/>
+      <c r="BO12" s="119"/>
       <c r="BP12" s="42"/>
-      <c r="BQ12" s="120"/>
+      <c r="BQ12" s="119"/>
       <c r="BR12" s="42"/>
-      <c r="BS12" s="120"/>
+      <c r="BS12" s="119"/>
       <c r="BT12" s="42"/>
-      <c r="BU12" s="120"/>
+      <c r="BU12" s="119"/>
       <c r="BV12" s="42"/>
       <c r="BW12" s="36"/>
     </row>
     <row r="13" spans="1:75" ht="17.25" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="132"/>
+      <c r="B13" s="131"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="132"/>
+      <c r="D13" s="131"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="132"/>
+      <c r="F13" s="131"/>
       <c r="G13" s="50"/>
       <c r="H13" s="36"/>
-      <c r="I13" s="132"/>
+      <c r="I13" s="131"/>
       <c r="J13" s="50"/>
-      <c r="K13" s="132"/>
+      <c r="K13" s="131"/>
       <c r="L13" s="50"/>
-      <c r="M13" s="133" t="s">
+      <c r="M13" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N13" s="53"/>
-      <c r="O13" s="132"/>
+      <c r="O13" s="131"/>
       <c r="P13" s="50"/>
-      <c r="Q13" s="132"/>
+      <c r="Q13" s="131"/>
       <c r="R13" s="50"/>
-      <c r="S13" s="133" t="s">
+      <c r="S13" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T13" s="53"/>
-      <c r="U13" s="132"/>
+      <c r="U13" s="131"/>
       <c r="V13" s="50"/>
-      <c r="W13" s="132"/>
+      <c r="W13" s="131"/>
       <c r="X13" s="50"/>
-      <c r="Y13" s="132"/>
+      <c r="Y13" s="131"/>
       <c r="Z13" s="50"/>
-      <c r="AA13" s="132"/>
+      <c r="AA13" s="131"/>
       <c r="AB13" s="50"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="132"/>
+      <c r="AD13" s="131"/>
       <c r="AE13" s="50"/>
-      <c r="AF13" s="132"/>
+      <c r="AF13" s="131"/>
       <c r="AG13" s="50"/>
-      <c r="AH13" s="132"/>
+      <c r="AH13" s="131"/>
       <c r="AI13" s="50"/>
-      <c r="AJ13" s="132"/>
+      <c r="AJ13" s="131"/>
       <c r="AK13" s="50"/>
-      <c r="AL13" s="132"/>
+      <c r="AL13" s="131"/>
       <c r="AM13" s="50"/>
-      <c r="AN13" s="132"/>
+      <c r="AN13" s="131"/>
       <c r="AO13" s="50"/>
-      <c r="AP13" s="132"/>
+      <c r="AP13" s="131"/>
       <c r="AQ13" s="50"/>
-      <c r="AR13" s="132"/>
+      <c r="AR13" s="131"/>
       <c r="AS13" s="50"/>
-      <c r="AT13" s="132"/>
+      <c r="AT13" s="131"/>
       <c r="AU13" s="50"/>
-      <c r="AV13" s="132"/>
+      <c r="AV13" s="131"/>
       <c r="AW13" s="50"/>
-      <c r="AX13" s="132"/>
+      <c r="AX13" s="131"/>
       <c r="AY13" s="50"/>
-      <c r="AZ13" s="132"/>
+      <c r="AZ13" s="131"/>
       <c r="BA13" s="50"/>
       <c r="BB13" s="36"/>
       <c r="BC13" s="36"/>
-      <c r="BD13" s="132"/>
+      <c r="BD13" s="131"/>
       <c r="BE13" s="50"/>
-      <c r="BF13" s="132"/>
+      <c r="BF13" s="131"/>
       <c r="BG13" s="50"/>
-      <c r="BH13" s="132"/>
+      <c r="BH13" s="131"/>
       <c r="BI13" s="50"/>
-      <c r="BJ13" s="132"/>
+      <c r="BJ13" s="131"/>
       <c r="BK13" s="50"/>
-      <c r="BL13" s="132"/>
+      <c r="BL13" s="131"/>
       <c r="BM13" s="50"/>
-      <c r="BN13" s="132"/>
+      <c r="BN13" s="131"/>
       <c r="BO13" s="50"/>
-      <c r="BP13" s="132"/>
+      <c r="BP13" s="131"/>
       <c r="BQ13" s="50"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="131"/>
       <c r="BS13" s="50"/>
-      <c r="BT13" s="132"/>
+      <c r="BT13" s="131"/>
       <c r="BU13" s="50"/>
-      <c r="BV13" s="132"/>
+      <c r="BV13" s="131"/>
       <c r="BW13" s="50"/>
     </row>
     <row r="14" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A14" s="134"/>
+      <c r="A14" s="133"/>
       <c r="B14" s="42"/>
-      <c r="C14" s="134"/>
+      <c r="C14" s="133"/>
       <c r="D14" s="42"/>
-      <c r="E14" s="134"/>
+      <c r="E14" s="133"/>
       <c r="F14" s="42"/>
-      <c r="G14" s="134"/>
+      <c r="G14" s="133"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="134"/>
+      <c r="I14" s="133"/>
       <c r="J14" s="42"/>
-      <c r="K14" s="134"/>
+      <c r="K14" s="133"/>
       <c r="L14" s="42"/>
-      <c r="M14" s="134"/>
+      <c r="M14" s="133"/>
       <c r="N14" s="42"/>
-      <c r="O14" s="134"/>
+      <c r="O14" s="133"/>
       <c r="P14" s="42"/>
-      <c r="Q14" s="134"/>
+      <c r="Q14" s="133"/>
       <c r="R14" s="42"/>
-      <c r="S14" s="134"/>
+      <c r="S14" s="133"/>
       <c r="T14" s="42"/>
-      <c r="U14" s="134"/>
+      <c r="U14" s="133"/>
       <c r="V14" s="42"/>
-      <c r="W14" s="134"/>
+      <c r="W14" s="133"/>
       <c r="X14" s="42"/>
-      <c r="Y14" s="134"/>
+      <c r="Y14" s="133"/>
       <c r="Z14" s="42"/>
-      <c r="AA14" s="134"/>
+      <c r="AA14" s="133"/>
       <c r="AB14" s="42"/>
-      <c r="AC14" s="134"/>
+      <c r="AC14" s="133"/>
       <c r="AD14" s="42"/>
-      <c r="AE14" s="134"/>
+      <c r="AE14" s="133"/>
       <c r="AF14" s="42"/>
-      <c r="AG14" s="134"/>
+      <c r="AG14" s="133"/>
       <c r="AH14" s="42"/>
-      <c r="AI14" s="134"/>
+      <c r="AI14" s="133"/>
       <c r="AJ14" s="42"/>
-      <c r="AK14" s="134"/>
+      <c r="AK14" s="133"/>
       <c r="AL14" s="42"/>
-      <c r="AM14" s="134"/>
+      <c r="AM14" s="133"/>
       <c r="AN14" s="42"/>
-      <c r="AO14" s="134"/>
+      <c r="AO14" s="133"/>
       <c r="AP14" s="42"/>
-      <c r="AQ14" s="134"/>
+      <c r="AQ14" s="133"/>
       <c r="AR14" s="42"/>
-      <c r="AS14" s="134"/>
+      <c r="AS14" s="133"/>
       <c r="AT14" s="42"/>
-      <c r="AU14" s="134"/>
+      <c r="AU14" s="133"/>
       <c r="AV14" s="42"/>
-      <c r="AW14" s="134"/>
+      <c r="AW14" s="133"/>
       <c r="AX14" s="42"/>
-      <c r="AY14" s="134"/>
+      <c r="AY14" s="133"/>
       <c r="AZ14" s="42"/>
-      <c r="BA14" s="134"/>
+      <c r="BA14" s="133"/>
       <c r="BB14" s="42"/>
-      <c r="BC14" s="134"/>
+      <c r="BC14" s="133"/>
       <c r="BD14" s="42"/>
-      <c r="BE14" s="134"/>
+      <c r="BE14" s="133"/>
       <c r="BF14" s="42"/>
-      <c r="BG14" s="134"/>
+      <c r="BG14" s="133"/>
       <c r="BH14" s="42"/>
-      <c r="BI14" s="134"/>
+      <c r="BI14" s="133"/>
       <c r="BJ14" s="42"/>
-      <c r="BK14" s="134"/>
+      <c r="BK14" s="133"/>
       <c r="BL14" s="42"/>
-      <c r="BM14" s="134"/>
+      <c r="BM14" s="133"/>
       <c r="BN14" s="42"/>
-      <c r="BO14" s="134"/>
+      <c r="BO14" s="133"/>
       <c r="BP14" s="42"/>
-      <c r="BQ14" s="134"/>
+      <c r="BQ14" s="133"/>
       <c r="BR14" s="42"/>
-      <c r="BS14" s="134"/>
+      <c r="BS14" s="133"/>
       <c r="BT14" s="42"/>
-      <c r="BU14" s="134"/>
+      <c r="BU14" s="133"/>
       <c r="BV14" s="42"/>
       <c r="BW14" s="39"/>
     </row>
     <row r="15" spans="1:75" ht="17.25" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="135"/>
+      <c r="B15" s="134"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="135"/>
+      <c r="D15" s="134"/>
       <c r="E15" s="42"/>
-      <c r="F15" s="135"/>
+      <c r="F15" s="134"/>
       <c r="G15" s="42"/>
       <c r="H15" s="36"/>
-      <c r="I15" s="132"/>
+      <c r="I15" s="131"/>
       <c r="J15" s="50"/>
-      <c r="K15" s="132"/>
+      <c r="K15" s="131"/>
       <c r="L15" s="50"/>
-      <c r="M15" s="133" t="s">
+      <c r="M15" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N15" s="53"/>
-      <c r="O15" s="132"/>
+      <c r="O15" s="131"/>
       <c r="P15" s="50"/>
-      <c r="Q15" s="132"/>
+      <c r="Q15" s="131"/>
       <c r="R15" s="50"/>
-      <c r="S15" s="133" t="s">
+      <c r="S15" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T15" s="53"/>
-      <c r="U15" s="132"/>
+      <c r="U15" s="131"/>
       <c r="V15" s="50"/>
-      <c r="W15" s="132"/>
+      <c r="W15" s="131"/>
       <c r="X15" s="50"/>
-      <c r="Y15" s="132"/>
+      <c r="Y15" s="131"/>
       <c r="Z15" s="50"/>
-      <c r="AA15" s="132"/>
+      <c r="AA15" s="131"/>
       <c r="AB15" s="50"/>
       <c r="AC15" s="36"/>
-      <c r="AD15" s="132"/>
+      <c r="AD15" s="131"/>
       <c r="AE15" s="50"/>
-      <c r="AF15" s="132"/>
+      <c r="AF15" s="131"/>
       <c r="AG15" s="50"/>
-      <c r="AH15" s="132"/>
+      <c r="AH15" s="131"/>
       <c r="AI15" s="50"/>
-      <c r="AJ15" s="132"/>
+      <c r="AJ15" s="131"/>
       <c r="AK15" s="50"/>
-      <c r="AL15" s="132"/>
+      <c r="AL15" s="131"/>
       <c r="AM15" s="50"/>
-      <c r="AN15" s="132"/>
+      <c r="AN15" s="131"/>
       <c r="AO15" s="50"/>
-      <c r="AP15" s="132"/>
+      <c r="AP15" s="131"/>
       <c r="AQ15" s="50"/>
-      <c r="AR15" s="132"/>
+      <c r="AR15" s="131"/>
       <c r="AS15" s="50"/>
-      <c r="AT15" s="132"/>
+      <c r="AT15" s="131"/>
       <c r="AU15" s="50"/>
-      <c r="AV15" s="132"/>
+      <c r="AV15" s="131"/>
       <c r="AW15" s="50"/>
-      <c r="AX15" s="132"/>
+      <c r="AX15" s="131"/>
       <c r="AY15" s="50"/>
-      <c r="AZ15" s="132"/>
+      <c r="AZ15" s="131"/>
       <c r="BA15" s="50"/>
       <c r="BB15" s="36"/>
       <c r="BC15" s="36"/>
-      <c r="BD15" s="132"/>
+      <c r="BD15" s="131"/>
       <c r="BE15" s="50"/>
-      <c r="BF15" s="132"/>
+      <c r="BF15" s="131"/>
       <c r="BG15" s="50"/>
-      <c r="BH15" s="132"/>
+      <c r="BH15" s="131"/>
       <c r="BI15" s="50"/>
-      <c r="BJ15" s="132"/>
+      <c r="BJ15" s="131"/>
       <c r="BK15" s="50"/>
-      <c r="BL15" s="132"/>
+      <c r="BL15" s="131"/>
       <c r="BM15" s="50"/>
-      <c r="BN15" s="132"/>
+      <c r="BN15" s="131"/>
       <c r="BO15" s="50"/>
-      <c r="BP15" s="132"/>
+      <c r="BP15" s="131"/>
       <c r="BQ15" s="50"/>
-      <c r="BR15" s="132"/>
+      <c r="BR15" s="131"/>
       <c r="BS15" s="50"/>
-      <c r="BT15" s="132"/>
+      <c r="BT15" s="131"/>
       <c r="BU15" s="50"/>
-      <c r="BV15" s="132"/>
+      <c r="BV15" s="131"/>
       <c r="BW15" s="50"/>
     </row>
     <row r="16" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A16" s="120"/>
+      <c r="A16" s="119"/>
       <c r="B16" s="42"/>
-      <c r="C16" s="120"/>
+      <c r="C16" s="119"/>
       <c r="D16" s="42"/>
-      <c r="E16" s="120"/>
+      <c r="E16" s="119"/>
       <c r="F16" s="42"/>
-      <c r="G16" s="120"/>
+      <c r="G16" s="119"/>
       <c r="H16" s="42"/>
-      <c r="I16" s="120"/>
+      <c r="I16" s="119"/>
       <c r="J16" s="42"/>
-      <c r="K16" s="120"/>
+      <c r="K16" s="119"/>
       <c r="L16" s="42"/>
-      <c r="M16" s="120"/>
+      <c r="M16" s="119"/>
       <c r="N16" s="42"/>
-      <c r="O16" s="120"/>
+      <c r="O16" s="119"/>
       <c r="P16" s="42"/>
-      <c r="Q16" s="120"/>
+      <c r="Q16" s="119"/>
       <c r="R16" s="42"/>
-      <c r="S16" s="120"/>
+      <c r="S16" s="119"/>
       <c r="T16" s="42"/>
-      <c r="U16" s="120"/>
+      <c r="U16" s="119"/>
       <c r="V16" s="42"/>
-      <c r="W16" s="120"/>
+      <c r="W16" s="119"/>
       <c r="X16" s="42"/>
-      <c r="Y16" s="120"/>
+      <c r="Y16" s="119"/>
       <c r="Z16" s="42"/>
-      <c r="AA16" s="120"/>
+      <c r="AA16" s="119"/>
       <c r="AB16" s="42"/>
-      <c r="AC16" s="120"/>
+      <c r="AC16" s="119"/>
       <c r="AD16" s="42"/>
-      <c r="AE16" s="120"/>
+      <c r="AE16" s="119"/>
       <c r="AF16" s="42"/>
-      <c r="AG16" s="120"/>
+      <c r="AG16" s="119"/>
       <c r="AH16" s="42"/>
-      <c r="AI16" s="120"/>
+      <c r="AI16" s="119"/>
       <c r="AJ16" s="42"/>
-      <c r="AK16" s="120"/>
+      <c r="AK16" s="119"/>
       <c r="AL16" s="42"/>
-      <c r="AM16" s="120"/>
+      <c r="AM16" s="119"/>
       <c r="AN16" s="42"/>
-      <c r="AO16" s="120"/>
+      <c r="AO16" s="119"/>
       <c r="AP16" s="42"/>
-      <c r="AQ16" s="120"/>
+      <c r="AQ16" s="119"/>
       <c r="AR16" s="42"/>
-      <c r="AS16" s="120"/>
+      <c r="AS16" s="119"/>
       <c r="AT16" s="42"/>
-      <c r="AU16" s="120"/>
+      <c r="AU16" s="119"/>
       <c r="AV16" s="42"/>
-      <c r="AW16" s="120"/>
+      <c r="AW16" s="119"/>
       <c r="AX16" s="42"/>
-      <c r="AY16" s="120"/>
+      <c r="AY16" s="119"/>
       <c r="AZ16" s="42"/>
-      <c r="BA16" s="120"/>
+      <c r="BA16" s="119"/>
       <c r="BB16" s="42"/>
-      <c r="BC16" s="120"/>
+      <c r="BC16" s="119"/>
       <c r="BD16" s="42"/>
-      <c r="BE16" s="120"/>
+      <c r="BE16" s="119"/>
       <c r="BF16" s="42"/>
-      <c r="BG16" s="120"/>
+      <c r="BG16" s="119"/>
       <c r="BH16" s="42"/>
-      <c r="BI16" s="120"/>
+      <c r="BI16" s="119"/>
       <c r="BJ16" s="42"/>
-      <c r="BK16" s="120"/>
+      <c r="BK16" s="119"/>
       <c r="BL16" s="42"/>
-      <c r="BM16" s="120"/>
+      <c r="BM16" s="119"/>
       <c r="BN16" s="42"/>
-      <c r="BO16" s="120"/>
+      <c r="BO16" s="119"/>
       <c r="BP16" s="42"/>
-      <c r="BQ16" s="120"/>
+      <c r="BQ16" s="119"/>
       <c r="BR16" s="42"/>
-      <c r="BS16" s="120"/>
+      <c r="BS16" s="119"/>
       <c r="BT16" s="42"/>
-      <c r="BU16" s="120"/>
+      <c r="BU16" s="119"/>
       <c r="BV16" s="42"/>
       <c r="BW16" s="36"/>
     </row>
     <row r="17" spans="1:75" ht="17.25" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="132"/>
+      <c r="B17" s="131"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="132"/>
+      <c r="D17" s="131"/>
       <c r="E17" s="50"/>
-      <c r="F17" s="132"/>
+      <c r="F17" s="131"/>
       <c r="G17" s="50"/>
       <c r="H17" s="36"/>
-      <c r="I17" s="132"/>
+      <c r="I17" s="131"/>
       <c r="J17" s="50"/>
-      <c r="K17" s="132"/>
+      <c r="K17" s="131"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="133" t="s">
+      <c r="M17" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N17" s="53"/>
-      <c r="O17" s="132"/>
+      <c r="O17" s="131"/>
       <c r="P17" s="50"/>
-      <c r="Q17" s="132"/>
+      <c r="Q17" s="131"/>
       <c r="R17" s="50"/>
-      <c r="S17" s="133" t="s">
+      <c r="S17" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T17" s="53"/>
-      <c r="U17" s="132"/>
+      <c r="U17" s="131"/>
       <c r="V17" s="50"/>
-      <c r="W17" s="132"/>
+      <c r="W17" s="131"/>
       <c r="X17" s="50"/>
-      <c r="Y17" s="132"/>
+      <c r="Y17" s="131"/>
       <c r="Z17" s="50"/>
-      <c r="AA17" s="132"/>
+      <c r="AA17" s="131"/>
       <c r="AB17" s="50"/>
       <c r="AC17" s="36"/>
-      <c r="AD17" s="132"/>
+      <c r="AD17" s="131"/>
       <c r="AE17" s="50"/>
-      <c r="AF17" s="132"/>
+      <c r="AF17" s="131"/>
       <c r="AG17" s="50"/>
-      <c r="AH17" s="132"/>
+      <c r="AH17" s="131"/>
       <c r="AI17" s="50"/>
-      <c r="AJ17" s="132"/>
+      <c r="AJ17" s="131"/>
       <c r="AK17" s="50"/>
-      <c r="AL17" s="132"/>
+      <c r="AL17" s="131"/>
       <c r="AM17" s="50"/>
-      <c r="AN17" s="132"/>
+      <c r="AN17" s="131"/>
       <c r="AO17" s="50"/>
-      <c r="AP17" s="132"/>
+      <c r="AP17" s="131"/>
       <c r="AQ17" s="50"/>
-      <c r="AR17" s="132"/>
+      <c r="AR17" s="131"/>
       <c r="AS17" s="50"/>
-      <c r="AT17" s="132"/>
+      <c r="AT17" s="131"/>
       <c r="AU17" s="50"/>
-      <c r="AV17" s="132"/>
+      <c r="AV17" s="131"/>
       <c r="AW17" s="50"/>
-      <c r="AX17" s="132"/>
+      <c r="AX17" s="131"/>
       <c r="AY17" s="50"/>
-      <c r="AZ17" s="132"/>
+      <c r="AZ17" s="131"/>
       <c r="BA17" s="50"/>
       <c r="BB17" s="36"/>
       <c r="BC17" s="36"/>
-      <c r="BD17" s="132"/>
+      <c r="BD17" s="131"/>
       <c r="BE17" s="50"/>
-      <c r="BF17" s="132"/>
+      <c r="BF17" s="131"/>
       <c r="BG17" s="50"/>
-      <c r="BH17" s="132"/>
+      <c r="BH17" s="131"/>
       <c r="BI17" s="50"/>
-      <c r="BJ17" s="132"/>
+      <c r="BJ17" s="131"/>
       <c r="BK17" s="50"/>
-      <c r="BL17" s="132"/>
+      <c r="BL17" s="131"/>
       <c r="BM17" s="50"/>
-      <c r="BN17" s="132"/>
+      <c r="BN17" s="131"/>
       <c r="BO17" s="50"/>
-      <c r="BP17" s="132"/>
+      <c r="BP17" s="131"/>
       <c r="BQ17" s="50"/>
-      <c r="BR17" s="132"/>
+      <c r="BR17" s="131"/>
       <c r="BS17" s="50"/>
-      <c r="BT17" s="132"/>
+      <c r="BT17" s="131"/>
       <c r="BU17" s="50"/>
-      <c r="BV17" s="132"/>
+      <c r="BV17" s="131"/>
       <c r="BW17" s="50"/>
     </row>
     <row r="18" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A18" s="134"/>
+      <c r="A18" s="133"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="134"/>
+      <c r="C18" s="133"/>
       <c r="D18" s="42"/>
-      <c r="E18" s="134"/>
+      <c r="E18" s="133"/>
       <c r="F18" s="42"/>
-      <c r="G18" s="134"/>
+      <c r="G18" s="133"/>
       <c r="H18" s="42"/>
-      <c r="I18" s="134"/>
+      <c r="I18" s="133"/>
       <c r="J18" s="42"/>
-      <c r="K18" s="134"/>
+      <c r="K18" s="133"/>
       <c r="L18" s="42"/>
-      <c r="M18" s="134"/>
+      <c r="M18" s="133"/>
       <c r="N18" s="42"/>
-      <c r="O18" s="134"/>
+      <c r="O18" s="133"/>
       <c r="P18" s="42"/>
-      <c r="Q18" s="134"/>
+      <c r="Q18" s="133"/>
       <c r="R18" s="42"/>
-      <c r="S18" s="134"/>
+      <c r="S18" s="133"/>
       <c r="T18" s="42"/>
-      <c r="U18" s="134"/>
+      <c r="U18" s="133"/>
       <c r="V18" s="42"/>
-      <c r="W18" s="134"/>
+      <c r="W18" s="133"/>
       <c r="X18" s="42"/>
-      <c r="Y18" s="134"/>
+      <c r="Y18" s="133"/>
       <c r="Z18" s="42"/>
-      <c r="AA18" s="134"/>
+      <c r="AA18" s="133"/>
       <c r="AB18" s="42"/>
-      <c r="AC18" s="134"/>
+      <c r="AC18" s="133"/>
       <c r="AD18" s="42"/>
-      <c r="AE18" s="134"/>
+      <c r="AE18" s="133"/>
       <c r="AF18" s="42"/>
-      <c r="AG18" s="134"/>
+      <c r="AG18" s="133"/>
       <c r="AH18" s="42"/>
-      <c r="AI18" s="134"/>
+      <c r="AI18" s="133"/>
       <c r="AJ18" s="42"/>
-      <c r="AK18" s="134"/>
+      <c r="AK18" s="133"/>
       <c r="AL18" s="42"/>
-      <c r="AM18" s="134"/>
+      <c r="AM18" s="133"/>
       <c r="AN18" s="42"/>
-      <c r="AO18" s="134"/>
+      <c r="AO18" s="133"/>
       <c r="AP18" s="42"/>
-      <c r="AQ18" s="134"/>
+      <c r="AQ18" s="133"/>
       <c r="AR18" s="42"/>
-      <c r="AS18" s="134"/>
+      <c r="AS18" s="133"/>
       <c r="AT18" s="42"/>
-      <c r="AU18" s="134"/>
+      <c r="AU18" s="133"/>
       <c r="AV18" s="42"/>
-      <c r="AW18" s="134"/>
+      <c r="AW18" s="133"/>
       <c r="AX18" s="42"/>
-      <c r="AY18" s="134"/>
+      <c r="AY18" s="133"/>
       <c r="AZ18" s="42"/>
-      <c r="BA18" s="134"/>
+      <c r="BA18" s="133"/>
       <c r="BB18" s="42"/>
-      <c r="BC18" s="134"/>
+      <c r="BC18" s="133"/>
       <c r="BD18" s="42"/>
-      <c r="BE18" s="134"/>
+      <c r="BE18" s="133"/>
       <c r="BF18" s="42"/>
-      <c r="BG18" s="134"/>
+      <c r="BG18" s="133"/>
       <c r="BH18" s="42"/>
-      <c r="BI18" s="134"/>
+      <c r="BI18" s="133"/>
       <c r="BJ18" s="42"/>
-      <c r="BK18" s="134"/>
+      <c r="BK18" s="133"/>
       <c r="BL18" s="42"/>
-      <c r="BM18" s="134"/>
+      <c r="BM18" s="133"/>
       <c r="BN18" s="42"/>
-      <c r="BO18" s="134"/>
+      <c r="BO18" s="133"/>
       <c r="BP18" s="42"/>
-      <c r="BQ18" s="134"/>
+      <c r="BQ18" s="133"/>
       <c r="BR18" s="42"/>
-      <c r="BS18" s="134"/>
+      <c r="BS18" s="133"/>
       <c r="BT18" s="42"/>
-      <c r="BU18" s="134"/>
+      <c r="BU18" s="133"/>
       <c r="BV18" s="42"/>
       <c r="BW18" s="39"/>
     </row>
     <row r="19" spans="1:75" ht="17.25" customHeight="1">
       <c r="A19" s="36"/>
-      <c r="B19" s="135"/>
+      <c r="B19" s="134"/>
       <c r="C19" s="42"/>
-      <c r="D19" s="135"/>
+      <c r="D19" s="134"/>
       <c r="E19" s="42"/>
-      <c r="F19" s="135"/>
+      <c r="F19" s="134"/>
       <c r="G19" s="42"/>
       <c r="H19" s="36"/>
-      <c r="I19" s="132"/>
+      <c r="I19" s="131"/>
       <c r="J19" s="50"/>
-      <c r="K19" s="132"/>
+      <c r="K19" s="131"/>
       <c r="L19" s="50"/>
-      <c r="M19" s="133" t="s">
+      <c r="M19" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N19" s="53"/>
-      <c r="O19" s="132"/>
+      <c r="O19" s="131"/>
       <c r="P19" s="50"/>
-      <c r="Q19" s="132"/>
+      <c r="Q19" s="131"/>
       <c r="R19" s="50"/>
-      <c r="S19" s="133" t="s">
+      <c r="S19" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T19" s="53"/>
-      <c r="U19" s="132"/>
+      <c r="U19" s="131"/>
       <c r="V19" s="50"/>
-      <c r="W19" s="132"/>
+      <c r="W19" s="131"/>
       <c r="X19" s="50"/>
-      <c r="Y19" s="132"/>
+      <c r="Y19" s="131"/>
       <c r="Z19" s="50"/>
-      <c r="AA19" s="132"/>
+      <c r="AA19" s="131"/>
       <c r="AB19" s="50"/>
       <c r="AC19" s="36"/>
-      <c r="AD19" s="132"/>
+      <c r="AD19" s="131"/>
       <c r="AE19" s="50"/>
-      <c r="AF19" s="132"/>
+      <c r="AF19" s="131"/>
       <c r="AG19" s="50"/>
-      <c r="AH19" s="132"/>
+      <c r="AH19" s="131"/>
       <c r="AI19" s="50"/>
-      <c r="AJ19" s="132"/>
+      <c r="AJ19" s="131"/>
       <c r="AK19" s="50"/>
-      <c r="AL19" s="132"/>
+      <c r="AL19" s="131"/>
       <c r="AM19" s="50"/>
-      <c r="AN19" s="132"/>
+      <c r="AN19" s="131"/>
       <c r="AO19" s="50"/>
-      <c r="AP19" s="132"/>
+      <c r="AP19" s="131"/>
       <c r="AQ19" s="50"/>
-      <c r="AR19" s="132"/>
+      <c r="AR19" s="131"/>
       <c r="AS19" s="50"/>
-      <c r="AT19" s="132"/>
+      <c r="AT19" s="131"/>
       <c r="AU19" s="50"/>
-      <c r="AV19" s="132"/>
+      <c r="AV19" s="131"/>
       <c r="AW19" s="50"/>
-      <c r="AX19" s="132"/>
+      <c r="AX19" s="131"/>
       <c r="AY19" s="50"/>
-      <c r="AZ19" s="132"/>
+      <c r="AZ19" s="131"/>
       <c r="BA19" s="50"/>
       <c r="BB19" s="36"/>
       <c r="BC19" s="36"/>
-      <c r="BD19" s="132"/>
+      <c r="BD19" s="131"/>
       <c r="BE19" s="50"/>
-      <c r="BF19" s="132"/>
+      <c r="BF19" s="131"/>
       <c r="BG19" s="50"/>
-      <c r="BH19" s="132"/>
+      <c r="BH19" s="131"/>
       <c r="BI19" s="50"/>
-      <c r="BJ19" s="132"/>
+      <c r="BJ19" s="131"/>
       <c r="BK19" s="50"/>
-      <c r="BL19" s="132"/>
+      <c r="BL19" s="131"/>
       <c r="BM19" s="50"/>
-      <c r="BN19" s="132"/>
+      <c r="BN19" s="131"/>
       <c r="BO19" s="50"/>
-      <c r="BP19" s="132"/>
+      <c r="BP19" s="131"/>
       <c r="BQ19" s="50"/>
-      <c r="BR19" s="132"/>
+      <c r="BR19" s="131"/>
       <c r="BS19" s="50"/>
-      <c r="BT19" s="132"/>
+      <c r="BT19" s="131"/>
       <c r="BU19" s="50"/>
-      <c r="BV19" s="132"/>
+      <c r="BV19" s="131"/>
       <c r="BW19" s="50"/>
     </row>
     <row r="20" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A20" s="120"/>
+      <c r="A20" s="119"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="120"/>
+      <c r="C20" s="119"/>
       <c r="D20" s="42"/>
-      <c r="E20" s="120"/>
+      <c r="E20" s="119"/>
       <c r="F20" s="42"/>
-      <c r="G20" s="120"/>
+      <c r="G20" s="119"/>
       <c r="H20" s="42"/>
-      <c r="I20" s="120"/>
+      <c r="I20" s="119"/>
       <c r="J20" s="42"/>
-      <c r="K20" s="120"/>
+      <c r="K20" s="119"/>
       <c r="L20" s="42"/>
-      <c r="M20" s="120"/>
+      <c r="M20" s="119"/>
       <c r="N20" s="42"/>
-      <c r="O20" s="120"/>
+      <c r="O20" s="119"/>
       <c r="P20" s="42"/>
-      <c r="Q20" s="120"/>
+      <c r="Q20" s="119"/>
       <c r="R20" s="42"/>
-      <c r="S20" s="120"/>
+      <c r="S20" s="119"/>
       <c r="T20" s="42"/>
-      <c r="U20" s="120"/>
+      <c r="U20" s="119"/>
       <c r="V20" s="42"/>
-      <c r="W20" s="120"/>
+      <c r="W20" s="119"/>
       <c r="X20" s="42"/>
-      <c r="Y20" s="120"/>
+      <c r="Y20" s="119"/>
       <c r="Z20" s="42"/>
-      <c r="AA20" s="120"/>
+      <c r="AA20" s="119"/>
       <c r="AB20" s="42"/>
-      <c r="AC20" s="120"/>
+      <c r="AC20" s="119"/>
       <c r="AD20" s="42"/>
-      <c r="AE20" s="120"/>
+      <c r="AE20" s="119"/>
       <c r="AF20" s="42"/>
-      <c r="AG20" s="120"/>
+      <c r="AG20" s="119"/>
       <c r="AH20" s="42"/>
-      <c r="AI20" s="120"/>
+      <c r="AI20" s="119"/>
       <c r="AJ20" s="42"/>
-      <c r="AK20" s="120"/>
+      <c r="AK20" s="119"/>
       <c r="AL20" s="42"/>
-      <c r="AM20" s="120"/>
+      <c r="AM20" s="119"/>
       <c r="AN20" s="42"/>
-      <c r="AO20" s="120"/>
+      <c r="AO20" s="119"/>
       <c r="AP20" s="42"/>
-      <c r="AQ20" s="120"/>
+      <c r="AQ20" s="119"/>
       <c r="AR20" s="42"/>
-      <c r="AS20" s="120"/>
+      <c r="AS20" s="119"/>
       <c r="AT20" s="42"/>
-      <c r="AU20" s="120"/>
+      <c r="AU20" s="119"/>
       <c r="AV20" s="42"/>
-      <c r="AW20" s="120"/>
+      <c r="AW20" s="119"/>
       <c r="AX20" s="42"/>
-      <c r="AY20" s="120"/>
+      <c r="AY20" s="119"/>
       <c r="AZ20" s="42"/>
-      <c r="BA20" s="120"/>
+      <c r="BA20" s="119"/>
       <c r="BB20" s="42"/>
-      <c r="BC20" s="120"/>
+      <c r="BC20" s="119"/>
       <c r="BD20" s="42"/>
-      <c r="BE20" s="120"/>
+      <c r="BE20" s="119"/>
       <c r="BF20" s="42"/>
-      <c r="BG20" s="120"/>
+      <c r="BG20" s="119"/>
       <c r="BH20" s="42"/>
-      <c r="BI20" s="120"/>
+      <c r="BI20" s="119"/>
       <c r="BJ20" s="42"/>
-      <c r="BK20" s="120"/>
+      <c r="BK20" s="119"/>
       <c r="BL20" s="42"/>
-      <c r="BM20" s="120"/>
+      <c r="BM20" s="119"/>
       <c r="BN20" s="42"/>
-      <c r="BO20" s="120"/>
+      <c r="BO20" s="119"/>
       <c r="BP20" s="42"/>
-      <c r="BQ20" s="120"/>
+      <c r="BQ20" s="119"/>
       <c r="BR20" s="42"/>
-      <c r="BS20" s="120"/>
+      <c r="BS20" s="119"/>
       <c r="BT20" s="42"/>
-      <c r="BU20" s="120"/>
+      <c r="BU20" s="119"/>
       <c r="BV20" s="42"/>
       <c r="BW20" s="36"/>
     </row>
     <row r="21" spans="1:75" ht="17.25" customHeight="1">
       <c r="A21" s="36"/>
-      <c r="B21" s="132"/>
+      <c r="B21" s="131"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="132"/>
+      <c r="D21" s="131"/>
       <c r="E21" s="50"/>
-      <c r="F21" s="132"/>
+      <c r="F21" s="131"/>
       <c r="G21" s="50"/>
       <c r="H21" s="36"/>
-      <c r="I21" s="132"/>
+      <c r="I21" s="131"/>
       <c r="J21" s="50"/>
-      <c r="K21" s="132"/>
+      <c r="K21" s="131"/>
       <c r="L21" s="50"/>
-      <c r="M21" s="133" t="s">
+      <c r="M21" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N21" s="53"/>
-      <c r="O21" s="132"/>
+      <c r="O21" s="131"/>
       <c r="P21" s="50"/>
-      <c r="Q21" s="132"/>
+      <c r="Q21" s="131"/>
       <c r="R21" s="50"/>
-      <c r="S21" s="133" t="s">
+      <c r="S21" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T21" s="53"/>
-      <c r="U21" s="132"/>
+      <c r="U21" s="131"/>
       <c r="V21" s="50"/>
-      <c r="W21" s="132"/>
+      <c r="W21" s="131"/>
       <c r="X21" s="50"/>
-      <c r="Y21" s="132"/>
+      <c r="Y21" s="131"/>
       <c r="Z21" s="50"/>
-      <c r="AA21" s="132"/>
+      <c r="AA21" s="131"/>
       <c r="AB21" s="50"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="132"/>
+      <c r="AD21" s="131"/>
       <c r="AE21" s="50"/>
-      <c r="AF21" s="132"/>
+      <c r="AF21" s="131"/>
       <c r="AG21" s="50"/>
-      <c r="AH21" s="132"/>
+      <c r="AH21" s="131"/>
       <c r="AI21" s="50"/>
-      <c r="AJ21" s="132"/>
+      <c r="AJ21" s="131"/>
       <c r="AK21" s="50"/>
-      <c r="AL21" s="132"/>
+      <c r="AL21" s="131"/>
       <c r="AM21" s="50"/>
-      <c r="AN21" s="132"/>
+      <c r="AN21" s="131"/>
       <c r="AO21" s="50"/>
-      <c r="AP21" s="132"/>
+      <c r="AP21" s="131"/>
       <c r="AQ21" s="50"/>
-      <c r="AR21" s="132"/>
+      <c r="AR21" s="131"/>
       <c r="AS21" s="50"/>
-      <c r="AT21" s="132"/>
+      <c r="AT21" s="131"/>
       <c r="AU21" s="50"/>
-      <c r="AV21" s="132"/>
+      <c r="AV21" s="131"/>
       <c r="AW21" s="50"/>
-      <c r="AX21" s="132"/>
+      <c r="AX21" s="131"/>
       <c r="AY21" s="50"/>
-      <c r="AZ21" s="132"/>
+      <c r="AZ21" s="131"/>
       <c r="BA21" s="50"/>
       <c r="BB21" s="36"/>
       <c r="BC21" s="36"/>
-      <c r="BD21" s="132"/>
+      <c r="BD21" s="131"/>
       <c r="BE21" s="50"/>
-      <c r="BF21" s="132"/>
+      <c r="BF21" s="131"/>
       <c r="BG21" s="50"/>
-      <c r="BH21" s="132"/>
+      <c r="BH21" s="131"/>
       <c r="BI21" s="50"/>
-      <c r="BJ21" s="132"/>
+      <c r="BJ21" s="131"/>
       <c r="BK21" s="50"/>
-      <c r="BL21" s="132"/>
+      <c r="BL21" s="131"/>
       <c r="BM21" s="50"/>
-      <c r="BN21" s="132"/>
+      <c r="BN21" s="131"/>
       <c r="BO21" s="50"/>
-      <c r="BP21" s="132"/>
+      <c r="BP21" s="131"/>
       <c r="BQ21" s="50"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="131"/>
       <c r="BS21" s="50"/>
-      <c r="BT21" s="132"/>
+      <c r="BT21" s="131"/>
       <c r="BU21" s="50"/>
-      <c r="BV21" s="132"/>
+      <c r="BV21" s="131"/>
       <c r="BW21" s="50"/>
     </row>
     <row r="22" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A22" s="134"/>
+      <c r="A22" s="133"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="134"/>
+      <c r="C22" s="133"/>
       <c r="D22" s="42"/>
-      <c r="E22" s="134"/>
+      <c r="E22" s="133"/>
       <c r="F22" s="42"/>
-      <c r="G22" s="134"/>
+      <c r="G22" s="133"/>
       <c r="H22" s="42"/>
-      <c r="I22" s="134"/>
+      <c r="I22" s="133"/>
       <c r="J22" s="42"/>
-      <c r="K22" s="134"/>
+      <c r="K22" s="133"/>
       <c r="L22" s="42"/>
-      <c r="M22" s="134"/>
+      <c r="M22" s="133"/>
       <c r="N22" s="42"/>
-      <c r="O22" s="134"/>
+      <c r="O22" s="133"/>
       <c r="P22" s="42"/>
-      <c r="Q22" s="134"/>
+      <c r="Q22" s="133"/>
       <c r="R22" s="42"/>
-      <c r="S22" s="134"/>
+      <c r="S22" s="133"/>
       <c r="T22" s="42"/>
-      <c r="U22" s="134"/>
+      <c r="U22" s="133"/>
       <c r="V22" s="42"/>
-      <c r="W22" s="134"/>
+      <c r="W22" s="133"/>
       <c r="X22" s="42"/>
-      <c r="Y22" s="134"/>
+      <c r="Y22" s="133"/>
       <c r="Z22" s="42"/>
-      <c r="AA22" s="134"/>
+      <c r="AA22" s="133"/>
       <c r="AB22" s="42"/>
-      <c r="AC22" s="134"/>
+      <c r="AC22" s="133"/>
       <c r="AD22" s="42"/>
-      <c r="AE22" s="134"/>
+      <c r="AE22" s="133"/>
       <c r="AF22" s="42"/>
-      <c r="AG22" s="134"/>
+      <c r="AG22" s="133"/>
       <c r="AH22" s="42"/>
-      <c r="AI22" s="134"/>
+      <c r="AI22" s="133"/>
       <c r="AJ22" s="42"/>
-      <c r="AK22" s="134"/>
+      <c r="AK22" s="133"/>
       <c r="AL22" s="42"/>
-      <c r="AM22" s="134"/>
+      <c r="AM22" s="133"/>
       <c r="AN22" s="42"/>
-      <c r="AO22" s="134"/>
+      <c r="AO22" s="133"/>
       <c r="AP22" s="42"/>
-      <c r="AQ22" s="134"/>
+      <c r="AQ22" s="133"/>
       <c r="AR22" s="42"/>
-      <c r="AS22" s="134"/>
+      <c r="AS22" s="133"/>
       <c r="AT22" s="42"/>
-      <c r="AU22" s="134"/>
+      <c r="AU22" s="133"/>
       <c r="AV22" s="42"/>
-      <c r="AW22" s="134"/>
+      <c r="AW22" s="133"/>
       <c r="AX22" s="42"/>
-      <c r="AY22" s="134"/>
+      <c r="AY22" s="133"/>
       <c r="AZ22" s="42"/>
-      <c r="BA22" s="134"/>
+      <c r="BA22" s="133"/>
       <c r="BB22" s="42"/>
-      <c r="BC22" s="134"/>
+      <c r="BC22" s="133"/>
       <c r="BD22" s="42"/>
-      <c r="BE22" s="134"/>
+      <c r="BE22" s="133"/>
       <c r="BF22" s="42"/>
-      <c r="BG22" s="134"/>
+      <c r="BG22" s="133"/>
       <c r="BH22" s="42"/>
-      <c r="BI22" s="134"/>
+      <c r="BI22" s="133"/>
       <c r="BJ22" s="42"/>
-      <c r="BK22" s="134"/>
+      <c r="BK22" s="133"/>
       <c r="BL22" s="42"/>
-      <c r="BM22" s="134"/>
+      <c r="BM22" s="133"/>
       <c r="BN22" s="42"/>
-      <c r="BO22" s="134"/>
+      <c r="BO22" s="133"/>
       <c r="BP22" s="42"/>
-      <c r="BQ22" s="134"/>
+      <c r="BQ22" s="133"/>
       <c r="BR22" s="42"/>
-      <c r="BS22" s="134"/>
+      <c r="BS22" s="133"/>
       <c r="BT22" s="42"/>
-      <c r="BU22" s="134"/>
+      <c r="BU22" s="133"/>
       <c r="BV22" s="42"/>
       <c r="BW22" s="39"/>
     </row>
     <row r="23" spans="1:75" ht="17.25" customHeight="1">
       <c r="A23" s="36"/>
-      <c r="B23" s="135"/>
+      <c r="B23" s="134"/>
       <c r="C23" s="42"/>
-      <c r="D23" s="135"/>
+      <c r="D23" s="134"/>
       <c r="E23" s="42"/>
-      <c r="F23" s="135"/>
+      <c r="F23" s="134"/>
       <c r="G23" s="42"/>
       <c r="H23" s="36"/>
-      <c r="I23" s="132"/>
+      <c r="I23" s="131"/>
       <c r="J23" s="50"/>
-      <c r="K23" s="132"/>
+      <c r="K23" s="131"/>
       <c r="L23" s="50"/>
-      <c r="M23" s="133" t="s">
+      <c r="M23" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N23" s="53"/>
-      <c r="O23" s="132"/>
+      <c r="O23" s="131"/>
       <c r="P23" s="50"/>
-      <c r="Q23" s="132"/>
+      <c r="Q23" s="131"/>
       <c r="R23" s="50"/>
-      <c r="S23" s="133" t="s">
+      <c r="S23" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T23" s="53"/>
-      <c r="U23" s="132"/>
+      <c r="U23" s="131"/>
       <c r="V23" s="50"/>
-      <c r="W23" s="132"/>
+      <c r="W23" s="131"/>
       <c r="X23" s="50"/>
-      <c r="Y23" s="132"/>
+      <c r="Y23" s="131"/>
       <c r="Z23" s="50"/>
-      <c r="AA23" s="132"/>
+      <c r="AA23" s="131"/>
       <c r="AB23" s="50"/>
       <c r="AC23" s="36"/>
-      <c r="AD23" s="132"/>
+      <c r="AD23" s="131"/>
       <c r="AE23" s="50"/>
-      <c r="AF23" s="132"/>
+      <c r="AF23" s="131"/>
       <c r="AG23" s="50"/>
-      <c r="AH23" s="132"/>
+      <c r="AH23" s="131"/>
       <c r="AI23" s="50"/>
-      <c r="AJ23" s="132"/>
+      <c r="AJ23" s="131"/>
       <c r="AK23" s="50"/>
-      <c r="AL23" s="132"/>
+      <c r="AL23" s="131"/>
       <c r="AM23" s="50"/>
-      <c r="AN23" s="132"/>
+      <c r="AN23" s="131"/>
       <c r="AO23" s="50"/>
-      <c r="AP23" s="132"/>
+      <c r="AP23" s="131"/>
       <c r="AQ23" s="50"/>
-      <c r="AR23" s="132"/>
+      <c r="AR23" s="131"/>
       <c r="AS23" s="50"/>
-      <c r="AT23" s="132"/>
+      <c r="AT23" s="131"/>
       <c r="AU23" s="50"/>
-      <c r="AV23" s="132"/>
+      <c r="AV23" s="131"/>
       <c r="AW23" s="50"/>
-      <c r="AX23" s="132"/>
+      <c r="AX23" s="131"/>
       <c r="AY23" s="50"/>
-      <c r="AZ23" s="132"/>
+      <c r="AZ23" s="131"/>
       <c r="BA23" s="50"/>
       <c r="BB23" s="36"/>
       <c r="BC23" s="36"/>
-      <c r="BD23" s="132"/>
+      <c r="BD23" s="131"/>
       <c r="BE23" s="50"/>
-      <c r="BF23" s="132"/>
+      <c r="BF23" s="131"/>
       <c r="BG23" s="50"/>
-      <c r="BH23" s="132"/>
+      <c r="BH23" s="131"/>
       <c r="BI23" s="50"/>
-      <c r="BJ23" s="132"/>
+      <c r="BJ23" s="131"/>
       <c r="BK23" s="50"/>
-      <c r="BL23" s="132"/>
+      <c r="BL23" s="131"/>
       <c r="BM23" s="50"/>
-      <c r="BN23" s="132"/>
+      <c r="BN23" s="131"/>
       <c r="BO23" s="50"/>
-      <c r="BP23" s="132"/>
+      <c r="BP23" s="131"/>
       <c r="BQ23" s="50"/>
-      <c r="BR23" s="132"/>
+      <c r="BR23" s="131"/>
       <c r="BS23" s="50"/>
-      <c r="BT23" s="132"/>
+      <c r="BT23" s="131"/>
       <c r="BU23" s="50"/>
-      <c r="BV23" s="132"/>
+      <c r="BV23" s="131"/>
       <c r="BW23" s="50"/>
     </row>
     <row r="24" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A24" s="120"/>
+      <c r="A24" s="119"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="120"/>
+      <c r="C24" s="119"/>
       <c r="D24" s="42"/>
-      <c r="E24" s="120"/>
+      <c r="E24" s="119"/>
       <c r="F24" s="42"/>
-      <c r="G24" s="120"/>
+      <c r="G24" s="119"/>
       <c r="H24" s="42"/>
-      <c r="I24" s="120"/>
+      <c r="I24" s="119"/>
       <c r="J24" s="42"/>
-      <c r="K24" s="120"/>
+      <c r="K24" s="119"/>
       <c r="L24" s="42"/>
-      <c r="M24" s="120"/>
+      <c r="M24" s="119"/>
       <c r="N24" s="42"/>
-      <c r="O24" s="120"/>
+      <c r="O24" s="119"/>
       <c r="P24" s="42"/>
-      <c r="Q24" s="120"/>
+      <c r="Q24" s="119"/>
       <c r="R24" s="42"/>
-      <c r="S24" s="120"/>
+      <c r="S24" s="119"/>
       <c r="T24" s="42"/>
-      <c r="U24" s="120"/>
+      <c r="U24" s="119"/>
       <c r="V24" s="42"/>
-      <c r="W24" s="120"/>
+      <c r="W24" s="119"/>
       <c r="X24" s="42"/>
-      <c r="Y24" s="120"/>
+      <c r="Y24" s="119"/>
       <c r="Z24" s="42"/>
-      <c r="AA24" s="120"/>
+      <c r="AA24" s="119"/>
       <c r="AB24" s="42"/>
-      <c r="AC24" s="120"/>
+      <c r="AC24" s="119"/>
       <c r="AD24" s="42"/>
-      <c r="AE24" s="120"/>
+      <c r="AE24" s="119"/>
       <c r="AF24" s="42"/>
-      <c r="AG24" s="120"/>
+      <c r="AG24" s="119"/>
       <c r="AH24" s="42"/>
-      <c r="AI24" s="120"/>
+      <c r="AI24" s="119"/>
       <c r="AJ24" s="42"/>
-      <c r="AK24" s="120"/>
+      <c r="AK24" s="119"/>
       <c r="AL24" s="42"/>
-      <c r="AM24" s="120"/>
+      <c r="AM24" s="119"/>
       <c r="AN24" s="42"/>
-      <c r="AO24" s="120"/>
+      <c r="AO24" s="119"/>
       <c r="AP24" s="42"/>
-      <c r="AQ24" s="120"/>
+      <c r="AQ24" s="119"/>
       <c r="AR24" s="42"/>
-      <c r="AS24" s="120"/>
+      <c r="AS24" s="119"/>
       <c r="AT24" s="42"/>
-      <c r="AU24" s="120"/>
+      <c r="AU24" s="119"/>
       <c r="AV24" s="42"/>
-      <c r="AW24" s="120"/>
+      <c r="AW24" s="119"/>
       <c r="AX24" s="42"/>
-      <c r="AY24" s="120"/>
+      <c r="AY24" s="119"/>
       <c r="AZ24" s="42"/>
-      <c r="BA24" s="120"/>
+      <c r="BA24" s="119"/>
       <c r="BB24" s="42"/>
-      <c r="BC24" s="120"/>
+      <c r="BC24" s="119"/>
       <c r="BD24" s="42"/>
-      <c r="BE24" s="120"/>
+      <c r="BE24" s="119"/>
       <c r="BF24" s="42"/>
-      <c r="BG24" s="120"/>
+      <c r="BG24" s="119"/>
       <c r="BH24" s="42"/>
-      <c r="BI24" s="120"/>
+      <c r="BI24" s="119"/>
       <c r="BJ24" s="42"/>
-      <c r="BK24" s="120"/>
+      <c r="BK24" s="119"/>
       <c r="BL24" s="42"/>
-      <c r="BM24" s="120"/>
+      <c r="BM24" s="119"/>
       <c r="BN24" s="42"/>
-      <c r="BO24" s="120"/>
+      <c r="BO24" s="119"/>
       <c r="BP24" s="42"/>
-      <c r="BQ24" s="120"/>
+      <c r="BQ24" s="119"/>
       <c r="BR24" s="42"/>
-      <c r="BS24" s="120"/>
+      <c r="BS24" s="119"/>
       <c r="BT24" s="42"/>
-      <c r="BU24" s="120"/>
+      <c r="BU24" s="119"/>
       <c r="BV24" s="42"/>
       <c r="BW24" s="36"/>
     </row>
     <row r="25" spans="1:75" ht="17.25" customHeight="1">
       <c r="A25" s="36"/>
-      <c r="B25" s="132"/>
+      <c r="B25" s="131"/>
       <c r="C25" s="50"/>
-      <c r="D25" s="132"/>
+      <c r="D25" s="131"/>
       <c r="E25" s="50"/>
-      <c r="F25" s="132"/>
+      <c r="F25" s="131"/>
       <c r="G25" s="50"/>
       <c r="H25" s="36"/>
-      <c r="I25" s="132"/>
+      <c r="I25" s="131"/>
       <c r="J25" s="50"/>
-      <c r="K25" s="132"/>
+      <c r="K25" s="131"/>
       <c r="L25" s="50"/>
-      <c r="M25" s="133" t="s">
+      <c r="M25" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N25" s="53"/>
-      <c r="O25" s="132"/>
+      <c r="O25" s="131"/>
       <c r="P25" s="50"/>
-      <c r="Q25" s="132"/>
+      <c r="Q25" s="131"/>
       <c r="R25" s="50"/>
-      <c r="S25" s="133" t="s">
+      <c r="S25" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T25" s="53"/>
-      <c r="U25" s="132"/>
+      <c r="U25" s="131"/>
       <c r="V25" s="50"/>
-      <c r="W25" s="132"/>
+      <c r="W25" s="131"/>
       <c r="X25" s="50"/>
-      <c r="Y25" s="132"/>
+      <c r="Y25" s="131"/>
       <c r="Z25" s="50"/>
-      <c r="AA25" s="132"/>
+      <c r="AA25" s="131"/>
       <c r="AB25" s="50"/>
       <c r="AC25" s="36"/>
-      <c r="AD25" s="132"/>
+      <c r="AD25" s="131"/>
       <c r="AE25" s="50"/>
-      <c r="AF25" s="132"/>
+      <c r="AF25" s="131"/>
       <c r="AG25" s="50"/>
-      <c r="AH25" s="132"/>
+      <c r="AH25" s="131"/>
       <c r="AI25" s="50"/>
-      <c r="AJ25" s="132"/>
+      <c r="AJ25" s="131"/>
       <c r="AK25" s="50"/>
-      <c r="AL25" s="132"/>
+      <c r="AL25" s="131"/>
       <c r="AM25" s="50"/>
-      <c r="AN25" s="132"/>
+      <c r="AN25" s="131"/>
       <c r="AO25" s="50"/>
-      <c r="AP25" s="132"/>
+      <c r="AP25" s="131"/>
       <c r="AQ25" s="50"/>
-      <c r="AR25" s="132"/>
+      <c r="AR25" s="131"/>
       <c r="AS25" s="50"/>
-      <c r="AT25" s="132"/>
+      <c r="AT25" s="131"/>
       <c r="AU25" s="50"/>
-      <c r="AV25" s="132"/>
+      <c r="AV25" s="131"/>
       <c r="AW25" s="50"/>
-      <c r="AX25" s="132"/>
+      <c r="AX25" s="131"/>
       <c r="AY25" s="50"/>
-      <c r="AZ25" s="132"/>
+      <c r="AZ25" s="131"/>
       <c r="BA25" s="50"/>
       <c r="BB25" s="36"/>
       <c r="BC25" s="36"/>
-      <c r="BD25" s="132"/>
+      <c r="BD25" s="131"/>
       <c r="BE25" s="50"/>
-      <c r="BF25" s="132"/>
+      <c r="BF25" s="131"/>
       <c r="BG25" s="50"/>
-      <c r="BH25" s="132"/>
+      <c r="BH25" s="131"/>
       <c r="BI25" s="50"/>
-      <c r="BJ25" s="132"/>
+      <c r="BJ25" s="131"/>
       <c r="BK25" s="50"/>
-      <c r="BL25" s="132"/>
+      <c r="BL25" s="131"/>
       <c r="BM25" s="50"/>
-      <c r="BN25" s="132"/>
+      <c r="BN25" s="131"/>
       <c r="BO25" s="50"/>
-      <c r="BP25" s="132"/>
+      <c r="BP25" s="131"/>
       <c r="BQ25" s="50"/>
-      <c r="BR25" s="132"/>
+      <c r="BR25" s="131"/>
       <c r="BS25" s="50"/>
-      <c r="BT25" s="132"/>
+      <c r="BT25" s="131"/>
       <c r="BU25" s="50"/>
-      <c r="BV25" s="132"/>
+      <c r="BV25" s="131"/>
       <c r="BW25" s="50"/>
     </row>
     <row r="26" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A26" s="134"/>
+      <c r="A26" s="133"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="134"/>
+      <c r="C26" s="133"/>
       <c r="D26" s="42"/>
-      <c r="E26" s="134"/>
+      <c r="E26" s="133"/>
       <c r="F26" s="42"/>
-      <c r="G26" s="134"/>
+      <c r="G26" s="133"/>
       <c r="H26" s="42"/>
-      <c r="I26" s="134"/>
+      <c r="I26" s="133"/>
       <c r="J26" s="42"/>
-      <c r="K26" s="134"/>
+      <c r="K26" s="133"/>
       <c r="L26" s="42"/>
-      <c r="M26" s="134"/>
+      <c r="M26" s="133"/>
       <c r="N26" s="42"/>
-      <c r="O26" s="134"/>
+      <c r="O26" s="133"/>
       <c r="P26" s="42"/>
-      <c r="Q26" s="134"/>
+      <c r="Q26" s="133"/>
       <c r="R26" s="42"/>
-      <c r="S26" s="134"/>
+      <c r="S26" s="133"/>
       <c r="T26" s="42"/>
-      <c r="U26" s="134"/>
+      <c r="U26" s="133"/>
       <c r="V26" s="42"/>
-      <c r="W26" s="134"/>
+      <c r="W26" s="133"/>
       <c r="X26" s="42"/>
-      <c r="Y26" s="134"/>
+      <c r="Y26" s="133"/>
       <c r="Z26" s="42"/>
-      <c r="AA26" s="134"/>
+      <c r="AA26" s="133"/>
       <c r="AB26" s="42"/>
-      <c r="AC26" s="134"/>
+      <c r="AC26" s="133"/>
       <c r="AD26" s="42"/>
-      <c r="AE26" s="134"/>
+      <c r="AE26" s="133"/>
       <c r="AF26" s="42"/>
-      <c r="AG26" s="134"/>
+      <c r="AG26" s="133"/>
       <c r="AH26" s="42"/>
-      <c r="AI26" s="134"/>
+      <c r="AI26" s="133"/>
       <c r="AJ26" s="42"/>
-      <c r="AK26" s="134"/>
+      <c r="AK26" s="133"/>
       <c r="AL26" s="42"/>
-      <c r="AM26" s="134"/>
+      <c r="AM26" s="133"/>
       <c r="AN26" s="42"/>
-      <c r="AO26" s="134"/>
+      <c r="AO26" s="133"/>
       <c r="AP26" s="42"/>
-      <c r="AQ26" s="134"/>
+      <c r="AQ26" s="133"/>
       <c r="AR26" s="42"/>
-      <c r="AS26" s="134"/>
+      <c r="AS26" s="133"/>
       <c r="AT26" s="42"/>
-      <c r="AU26" s="134"/>
+      <c r="AU26" s="133"/>
       <c r="AV26" s="42"/>
-      <c r="AW26" s="134"/>
+      <c r="AW26" s="133"/>
       <c r="AX26" s="42"/>
-      <c r="AY26" s="134"/>
+      <c r="AY26" s="133"/>
       <c r="AZ26" s="42"/>
-      <c r="BA26" s="134"/>
+      <c r="BA26" s="133"/>
       <c r="BB26" s="42"/>
-      <c r="BC26" s="134"/>
+      <c r="BC26" s="133"/>
       <c r="BD26" s="42"/>
-      <c r="BE26" s="134"/>
+      <c r="BE26" s="133"/>
       <c r="BF26" s="42"/>
-      <c r="BG26" s="134"/>
+      <c r="BG26" s="133"/>
       <c r="BH26" s="42"/>
-      <c r="BI26" s="134"/>
+      <c r="BI26" s="133"/>
       <c r="BJ26" s="42"/>
-      <c r="BK26" s="134"/>
+      <c r="BK26" s="133"/>
       <c r="BL26" s="42"/>
-      <c r="BM26" s="134"/>
+      <c r="BM26" s="133"/>
       <c r="BN26" s="42"/>
-      <c r="BO26" s="134"/>
+      <c r="BO26" s="133"/>
       <c r="BP26" s="42"/>
-      <c r="BQ26" s="134"/>
+      <c r="BQ26" s="133"/>
       <c r="BR26" s="42"/>
-      <c r="BS26" s="134"/>
+      <c r="BS26" s="133"/>
       <c r="BT26" s="42"/>
-      <c r="BU26" s="134"/>
+      <c r="BU26" s="133"/>
       <c r="BV26" s="42"/>
       <c r="BW26" s="39"/>
     </row>
     <row r="27" spans="1:75" ht="17.25" customHeight="1">
       <c r="A27" s="36"/>
-      <c r="B27" s="135"/>
+      <c r="B27" s="134"/>
       <c r="C27" s="42"/>
-      <c r="D27" s="135"/>
+      <c r="D27" s="134"/>
       <c r="E27" s="42"/>
-      <c r="F27" s="135"/>
+      <c r="F27" s="134"/>
       <c r="G27" s="42"/>
       <c r="H27" s="36"/>
-      <c r="I27" s="132"/>
+      <c r="I27" s="131"/>
       <c r="J27" s="50"/>
-      <c r="K27" s="132"/>
+      <c r="K27" s="131"/>
       <c r="L27" s="50"/>
-      <c r="M27" s="133" t="s">
+      <c r="M27" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N27" s="53"/>
-      <c r="O27" s="132"/>
+      <c r="O27" s="131"/>
       <c r="P27" s="50"/>
-      <c r="Q27" s="132"/>
+      <c r="Q27" s="131"/>
       <c r="R27" s="50"/>
-      <c r="S27" s="133" t="s">
+      <c r="S27" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T27" s="53"/>
-      <c r="U27" s="132"/>
+      <c r="U27" s="131"/>
       <c r="V27" s="50"/>
-      <c r="W27" s="132"/>
+      <c r="W27" s="131"/>
       <c r="X27" s="50"/>
-      <c r="Y27" s="132"/>
+      <c r="Y27" s="131"/>
       <c r="Z27" s="50"/>
-      <c r="AA27" s="132"/>
+      <c r="AA27" s="131"/>
       <c r="AB27" s="50"/>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="132"/>
+      <c r="AD27" s="131"/>
       <c r="AE27" s="50"/>
-      <c r="AF27" s="132"/>
+      <c r="AF27" s="131"/>
       <c r="AG27" s="50"/>
-      <c r="AH27" s="132"/>
+      <c r="AH27" s="131"/>
       <c r="AI27" s="50"/>
-      <c r="AJ27" s="132"/>
+      <c r="AJ27" s="131"/>
       <c r="AK27" s="50"/>
-      <c r="AL27" s="132"/>
+      <c r="AL27" s="131"/>
       <c r="AM27" s="50"/>
-      <c r="AN27" s="132"/>
+      <c r="AN27" s="131"/>
       <c r="AO27" s="50"/>
-      <c r="AP27" s="132"/>
+      <c r="AP27" s="131"/>
       <c r="AQ27" s="50"/>
-      <c r="AR27" s="132"/>
+      <c r="AR27" s="131"/>
       <c r="AS27" s="50"/>
-      <c r="AT27" s="132"/>
+      <c r="AT27" s="131"/>
       <c r="AU27" s="50"/>
-      <c r="AV27" s="132"/>
+      <c r="AV27" s="131"/>
       <c r="AW27" s="50"/>
-      <c r="AX27" s="132"/>
+      <c r="AX27" s="131"/>
       <c r="AY27" s="50"/>
-      <c r="AZ27" s="132"/>
+      <c r="AZ27" s="131"/>
       <c r="BA27" s="50"/>
       <c r="BB27" s="36"/>
       <c r="BC27" s="36"/>
-      <c r="BD27" s="132"/>
+      <c r="BD27" s="131"/>
       <c r="BE27" s="50"/>
-      <c r="BF27" s="132"/>
+      <c r="BF27" s="131"/>
       <c r="BG27" s="50"/>
-      <c r="BH27" s="132"/>
+      <c r="BH27" s="131"/>
       <c r="BI27" s="50"/>
-      <c r="BJ27" s="132"/>
+      <c r="BJ27" s="131"/>
       <c r="BK27" s="50"/>
-      <c r="BL27" s="132"/>
+      <c r="BL27" s="131"/>
       <c r="BM27" s="50"/>
-      <c r="BN27" s="132"/>
+      <c r="BN27" s="131"/>
       <c r="BO27" s="50"/>
-      <c r="BP27" s="132"/>
+      <c r="BP27" s="131"/>
       <c r="BQ27" s="50"/>
-      <c r="BR27" s="132"/>
+      <c r="BR27" s="131"/>
       <c r="BS27" s="50"/>
-      <c r="BT27" s="132"/>
+      <c r="BT27" s="131"/>
       <c r="BU27" s="50"/>
-      <c r="BV27" s="132"/>
+      <c r="BV27" s="131"/>
       <c r="BW27" s="50"/>
     </row>
     <row r="28" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A28" s="120"/>
+      <c r="A28" s="119"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="120"/>
+      <c r="C28" s="119"/>
       <c r="D28" s="42"/>
-      <c r="E28" s="120"/>
+      <c r="E28" s="119"/>
       <c r="F28" s="42"/>
-      <c r="G28" s="120"/>
+      <c r="G28" s="119"/>
       <c r="H28" s="42"/>
-      <c r="I28" s="120"/>
+      <c r="I28" s="119"/>
       <c r="J28" s="42"/>
-      <c r="K28" s="120"/>
+      <c r="K28" s="119"/>
       <c r="L28" s="42"/>
-      <c r="M28" s="120"/>
+      <c r="M28" s="119"/>
       <c r="N28" s="42"/>
-      <c r="O28" s="120"/>
+      <c r="O28" s="119"/>
       <c r="P28" s="42"/>
-      <c r="Q28" s="120"/>
+      <c r="Q28" s="119"/>
       <c r="R28" s="42"/>
-      <c r="S28" s="120"/>
+      <c r="S28" s="119"/>
       <c r="T28" s="42"/>
-      <c r="U28" s="120"/>
+      <c r="U28" s="119"/>
       <c r="V28" s="42"/>
-      <c r="W28" s="120"/>
+      <c r="W28" s="119"/>
       <c r="X28" s="42"/>
-      <c r="Y28" s="120"/>
+      <c r="Y28" s="119"/>
       <c r="Z28" s="42"/>
-      <c r="AA28" s="120"/>
+      <c r="AA28" s="119"/>
       <c r="AB28" s="42"/>
-      <c r="AC28" s="120"/>
+      <c r="AC28" s="119"/>
       <c r="AD28" s="42"/>
-      <c r="AE28" s="120"/>
+      <c r="AE28" s="119"/>
       <c r="AF28" s="42"/>
-      <c r="AG28" s="120"/>
+      <c r="AG28" s="119"/>
       <c r="AH28" s="42"/>
-      <c r="AI28" s="120"/>
+      <c r="AI28" s="119"/>
       <c r="AJ28" s="42"/>
-      <c r="AK28" s="120"/>
+      <c r="AK28" s="119"/>
       <c r="AL28" s="42"/>
-      <c r="AM28" s="120"/>
+      <c r="AM28" s="119"/>
       <c r="AN28" s="42"/>
-      <c r="AO28" s="120"/>
+      <c r="AO28" s="119"/>
       <c r="AP28" s="42"/>
-      <c r="AQ28" s="120"/>
+      <c r="AQ28" s="119"/>
       <c r="AR28" s="42"/>
-      <c r="AS28" s="120"/>
+      <c r="AS28" s="119"/>
       <c r="AT28" s="42"/>
-      <c r="AU28" s="120"/>
+      <c r="AU28" s="119"/>
       <c r="AV28" s="42"/>
-      <c r="AW28" s="120"/>
+      <c r="AW28" s="119"/>
       <c r="AX28" s="42"/>
-      <c r="AY28" s="120"/>
+      <c r="AY28" s="119"/>
       <c r="AZ28" s="42"/>
-      <c r="BA28" s="120"/>
+      <c r="BA28" s="119"/>
       <c r="BB28" s="42"/>
-      <c r="BC28" s="120"/>
+      <c r="BC28" s="119"/>
       <c r="BD28" s="42"/>
-      <c r="BE28" s="120"/>
+      <c r="BE28" s="119"/>
       <c r="BF28" s="42"/>
-      <c r="BG28" s="120"/>
+      <c r="BG28" s="119"/>
       <c r="BH28" s="42"/>
-      <c r="BI28" s="120"/>
+      <c r="BI28" s="119"/>
       <c r="BJ28" s="42"/>
-      <c r="BK28" s="120"/>
+      <c r="BK28" s="119"/>
       <c r="BL28" s="42"/>
-      <c r="BM28" s="120"/>
+      <c r="BM28" s="119"/>
       <c r="BN28" s="42"/>
-      <c r="BO28" s="120"/>
+      <c r="BO28" s="119"/>
       <c r="BP28" s="42"/>
-      <c r="BQ28" s="120"/>
+      <c r="BQ28" s="119"/>
       <c r="BR28" s="42"/>
-      <c r="BS28" s="120"/>
+      <c r="BS28" s="119"/>
       <c r="BT28" s="42"/>
-      <c r="BU28" s="120"/>
+      <c r="BU28" s="119"/>
       <c r="BV28" s="42"/>
       <c r="BW28" s="36"/>
     </row>
     <row r="29" spans="1:75" ht="17.25" customHeight="1">
       <c r="A29" s="36"/>
-      <c r="B29" s="132"/>
+      <c r="B29" s="131"/>
       <c r="C29" s="50"/>
-      <c r="D29" s="132"/>
+      <c r="D29" s="131"/>
       <c r="E29" s="50"/>
-      <c r="F29" s="132"/>
+      <c r="F29" s="131"/>
       <c r="G29" s="50"/>
       <c r="H29" s="36"/>
-      <c r="I29" s="132"/>
+      <c r="I29" s="131"/>
       <c r="J29" s="50"/>
-      <c r="K29" s="132"/>
+      <c r="K29" s="131"/>
       <c r="L29" s="50"/>
-      <c r="M29" s="133" t="s">
+      <c r="M29" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N29" s="53"/>
-      <c r="O29" s="132"/>
+      <c r="O29" s="131"/>
       <c r="P29" s="50"/>
-      <c r="Q29" s="132"/>
+      <c r="Q29" s="131"/>
       <c r="R29" s="50"/>
-      <c r="S29" s="133" t="s">
+      <c r="S29" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T29" s="53"/>
-      <c r="U29" s="132"/>
+      <c r="U29" s="131"/>
       <c r="V29" s="50"/>
-      <c r="W29" s="132"/>
+      <c r="W29" s="131"/>
       <c r="X29" s="50"/>
-      <c r="Y29" s="132"/>
+      <c r="Y29" s="131"/>
       <c r="Z29" s="50"/>
-      <c r="AA29" s="132"/>
+      <c r="AA29" s="131"/>
       <c r="AB29" s="50"/>
       <c r="AC29" s="36"/>
-      <c r="AD29" s="132"/>
+      <c r="AD29" s="131"/>
       <c r="AE29" s="50"/>
-      <c r="AF29" s="132"/>
+      <c r="AF29" s="131"/>
       <c r="AG29" s="50"/>
-      <c r="AH29" s="132"/>
+      <c r="AH29" s="131"/>
       <c r="AI29" s="50"/>
-      <c r="AJ29" s="132"/>
+      <c r="AJ29" s="131"/>
       <c r="AK29" s="50"/>
-      <c r="AL29" s="132"/>
+      <c r="AL29" s="131"/>
       <c r="AM29" s="50"/>
-      <c r="AN29" s="132"/>
+      <c r="AN29" s="131"/>
       <c r="AO29" s="50"/>
-      <c r="AP29" s="132"/>
+      <c r="AP29" s="131"/>
       <c r="AQ29" s="50"/>
-      <c r="AR29" s="132"/>
+      <c r="AR29" s="131"/>
       <c r="AS29" s="50"/>
-      <c r="AT29" s="132"/>
+      <c r="AT29" s="131"/>
       <c r="AU29" s="50"/>
-      <c r="AV29" s="132"/>
+      <c r="AV29" s="131"/>
       <c r="AW29" s="50"/>
-      <c r="AX29" s="132"/>
+      <c r="AX29" s="131"/>
       <c r="AY29" s="50"/>
-      <c r="AZ29" s="132"/>
+      <c r="AZ29" s="131"/>
       <c r="BA29" s="50"/>
       <c r="BB29" s="36"/>
       <c r="BC29" s="36"/>
-      <c r="BD29" s="132"/>
+      <c r="BD29" s="131"/>
       <c r="BE29" s="50"/>
-      <c r="BF29" s="132"/>
+      <c r="BF29" s="131"/>
       <c r="BG29" s="50"/>
-      <c r="BH29" s="132"/>
+      <c r="BH29" s="131"/>
       <c r="BI29" s="50"/>
-      <c r="BJ29" s="132"/>
+      <c r="BJ29" s="131"/>
       <c r="BK29" s="50"/>
-      <c r="BL29" s="132"/>
+      <c r="BL29" s="131"/>
       <c r="BM29" s="50"/>
-      <c r="BN29" s="132"/>
+      <c r="BN29" s="131"/>
       <c r="BO29" s="50"/>
-      <c r="BP29" s="132"/>
+      <c r="BP29" s="131"/>
       <c r="BQ29" s="50"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="131"/>
       <c r="BS29" s="50"/>
-      <c r="BT29" s="132"/>
+      <c r="BT29" s="131"/>
       <c r="BU29" s="50"/>
-      <c r="BV29" s="132"/>
+      <c r="BV29" s="131"/>
       <c r="BW29" s="50"/>
     </row>
     <row r="30" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A30" s="134"/>
+      <c r="A30" s="133"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="134"/>
+      <c r="C30" s="133"/>
       <c r="D30" s="42"/>
-      <c r="E30" s="134"/>
+      <c r="E30" s="133"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="134"/>
+      <c r="G30" s="133"/>
       <c r="H30" s="42"/>
-      <c r="I30" s="134"/>
+      <c r="I30" s="133"/>
       <c r="J30" s="42"/>
-      <c r="K30" s="134"/>
+      <c r="K30" s="133"/>
       <c r="L30" s="42"/>
-      <c r="M30" s="134"/>
+      <c r="M30" s="133"/>
       <c r="N30" s="42"/>
-      <c r="O30" s="134"/>
+      <c r="O30" s="133"/>
       <c r="P30" s="42"/>
-      <c r="Q30" s="134"/>
+      <c r="Q30" s="133"/>
       <c r="R30" s="42"/>
-      <c r="S30" s="134"/>
+      <c r="S30" s="133"/>
       <c r="T30" s="42"/>
-      <c r="U30" s="134"/>
+      <c r="U30" s="133"/>
       <c r="V30" s="42"/>
-      <c r="W30" s="134"/>
+      <c r="W30" s="133"/>
       <c r="X30" s="42"/>
-      <c r="Y30" s="134"/>
+      <c r="Y30" s="133"/>
       <c r="Z30" s="42"/>
-      <c r="AA30" s="134"/>
+      <c r="AA30" s="133"/>
       <c r="AB30" s="42"/>
-      <c r="AC30" s="134"/>
+      <c r="AC30" s="133"/>
       <c r="AD30" s="42"/>
-      <c r="AE30" s="134"/>
+      <c r="AE30" s="133"/>
       <c r="AF30" s="42"/>
-      <c r="AG30" s="134"/>
+      <c r="AG30" s="133"/>
       <c r="AH30" s="42"/>
-      <c r="AI30" s="134"/>
+      <c r="AI30" s="133"/>
       <c r="AJ30" s="42"/>
-      <c r="AK30" s="134"/>
+      <c r="AK30" s="133"/>
       <c r="AL30" s="42"/>
-      <c r="AM30" s="134"/>
+      <c r="AM30" s="133"/>
       <c r="AN30" s="42"/>
-      <c r="AO30" s="134"/>
+      <c r="AO30" s="133"/>
       <c r="AP30" s="42"/>
-      <c r="AQ30" s="134"/>
+      <c r="AQ30" s="133"/>
       <c r="AR30" s="42"/>
-      <c r="AS30" s="134"/>
+      <c r="AS30" s="133"/>
       <c r="AT30" s="42"/>
-      <c r="AU30" s="134"/>
+      <c r="AU30" s="133"/>
       <c r="AV30" s="42"/>
-      <c r="AW30" s="134"/>
+      <c r="AW30" s="133"/>
       <c r="AX30" s="42"/>
-      <c r="AY30" s="134"/>
+      <c r="AY30" s="133"/>
       <c r="AZ30" s="42"/>
-      <c r="BA30" s="134"/>
+      <c r="BA30" s="133"/>
       <c r="BB30" s="42"/>
-      <c r="BC30" s="134"/>
+      <c r="BC30" s="133"/>
       <c r="BD30" s="42"/>
-      <c r="BE30" s="134"/>
+      <c r="BE30" s="133"/>
       <c r="BF30" s="42"/>
-      <c r="BG30" s="134"/>
+      <c r="BG30" s="133"/>
       <c r="BH30" s="42"/>
-      <c r="BI30" s="134"/>
+      <c r="BI30" s="133"/>
       <c r="BJ30" s="42"/>
-      <c r="BK30" s="134"/>
+      <c r="BK30" s="133"/>
       <c r="BL30" s="42"/>
-      <c r="BM30" s="134"/>
+      <c r="BM30" s="133"/>
       <c r="BN30" s="42"/>
-      <c r="BO30" s="134"/>
+      <c r="BO30" s="133"/>
       <c r="BP30" s="42"/>
-      <c r="BQ30" s="134"/>
+      <c r="BQ30" s="133"/>
       <c r="BR30" s="42"/>
-      <c r="BS30" s="134"/>
+      <c r="BS30" s="133"/>
       <c r="BT30" s="42"/>
-      <c r="BU30" s="134"/>
+      <c r="BU30" s="133"/>
       <c r="BV30" s="42"/>
       <c r="BW30" s="39"/>
     </row>
     <row r="31" spans="1:75" ht="17.25" customHeight="1">
       <c r="A31" s="36"/>
-      <c r="B31" s="135"/>
+      <c r="B31" s="134"/>
       <c r="C31" s="42"/>
-      <c r="D31" s="135"/>
+      <c r="D31" s="134"/>
       <c r="E31" s="42"/>
-      <c r="F31" s="135"/>
+      <c r="F31" s="134"/>
       <c r="G31" s="42"/>
       <c r="H31" s="36"/>
-      <c r="I31" s="132"/>
+      <c r="I31" s="131"/>
       <c r="J31" s="50"/>
-      <c r="K31" s="132"/>
+      <c r="K31" s="131"/>
       <c r="L31" s="50"/>
-      <c r="M31" s="133" t="s">
+      <c r="M31" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N31" s="53"/>
-      <c r="O31" s="132"/>
+      <c r="O31" s="131"/>
       <c r="P31" s="50"/>
-      <c r="Q31" s="132"/>
+      <c r="Q31" s="131"/>
       <c r="R31" s="50"/>
-      <c r="S31" s="133" t="s">
+      <c r="S31" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T31" s="53"/>
-      <c r="U31" s="132"/>
+      <c r="U31" s="131"/>
       <c r="V31" s="50"/>
-      <c r="W31" s="132"/>
+      <c r="W31" s="131"/>
       <c r="X31" s="50"/>
-      <c r="Y31" s="132"/>
+      <c r="Y31" s="131"/>
       <c r="Z31" s="50"/>
-      <c r="AA31" s="132"/>
+      <c r="AA31" s="131"/>
       <c r="AB31" s="50"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="132"/>
+      <c r="AD31" s="131"/>
       <c r="AE31" s="50"/>
-      <c r="AF31" s="132"/>
+      <c r="AF31" s="131"/>
       <c r="AG31" s="50"/>
-      <c r="AH31" s="132"/>
+      <c r="AH31" s="131"/>
       <c r="AI31" s="50"/>
-      <c r="AJ31" s="132"/>
+      <c r="AJ31" s="131"/>
       <c r="AK31" s="50"/>
-      <c r="AL31" s="132"/>
+      <c r="AL31" s="131"/>
       <c r="AM31" s="50"/>
-      <c r="AN31" s="132"/>
+      <c r="AN31" s="131"/>
       <c r="AO31" s="50"/>
-      <c r="AP31" s="132"/>
+      <c r="AP31" s="131"/>
       <c r="AQ31" s="50"/>
-      <c r="AR31" s="132"/>
+      <c r="AR31" s="131"/>
       <c r="AS31" s="50"/>
-      <c r="AT31" s="132"/>
+      <c r="AT31" s="131"/>
       <c r="AU31" s="50"/>
-      <c r="AV31" s="132"/>
+      <c r="AV31" s="131"/>
       <c r="AW31" s="50"/>
-      <c r="AX31" s="132"/>
+      <c r="AX31" s="131"/>
       <c r="AY31" s="50"/>
-      <c r="AZ31" s="132"/>
+      <c r="AZ31" s="131"/>
       <c r="BA31" s="50"/>
       <c r="BB31" s="36"/>
       <c r="BC31" s="36"/>
-      <c r="BD31" s="132"/>
+      <c r="BD31" s="131"/>
       <c r="BE31" s="50"/>
-      <c r="BF31" s="132"/>
+      <c r="BF31" s="131"/>
       <c r="BG31" s="50"/>
-      <c r="BH31" s="132"/>
+      <c r="BH31" s="131"/>
       <c r="BI31" s="50"/>
-      <c r="BJ31" s="132"/>
+      <c r="BJ31" s="131"/>
       <c r="BK31" s="50"/>
-      <c r="BL31" s="132"/>
+      <c r="BL31" s="131"/>
       <c r="BM31" s="50"/>
-      <c r="BN31" s="132"/>
+      <c r="BN31" s="131"/>
       <c r="BO31" s="50"/>
-      <c r="BP31" s="132"/>
+      <c r="BP31" s="131"/>
       <c r="BQ31" s="50"/>
-      <c r="BR31" s="132"/>
+      <c r="BR31" s="131"/>
       <c r="BS31" s="50"/>
-      <c r="BT31" s="132"/>
+      <c r="BT31" s="131"/>
       <c r="BU31" s="50"/>
-      <c r="BV31" s="132"/>
+      <c r="BV31" s="131"/>
       <c r="BW31" s="50"/>
     </row>
     <row r="32" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A32" s="120"/>
+      <c r="A32" s="119"/>
       <c r="B32" s="42"/>
-      <c r="C32" s="120"/>
+      <c r="C32" s="119"/>
       <c r="D32" s="42"/>
-      <c r="E32" s="120"/>
+      <c r="E32" s="119"/>
       <c r="F32" s="42"/>
-      <c r="G32" s="120"/>
+      <c r="G32" s="119"/>
       <c r="H32" s="42"/>
-      <c r="I32" s="120"/>
+      <c r="I32" s="119"/>
       <c r="J32" s="42"/>
-      <c r="K32" s="120"/>
+      <c r="K32" s="119"/>
       <c r="L32" s="42"/>
-      <c r="M32" s="120"/>
+      <c r="M32" s="119"/>
       <c r="N32" s="42"/>
-      <c r="O32" s="120"/>
+      <c r="O32" s="119"/>
       <c r="P32" s="42"/>
-      <c r="Q32" s="120"/>
+      <c r="Q32" s="119"/>
       <c r="R32" s="42"/>
-      <c r="S32" s="120"/>
+      <c r="S32" s="119"/>
       <c r="T32" s="42"/>
-      <c r="U32" s="120"/>
+      <c r="U32" s="119"/>
       <c r="V32" s="42"/>
-      <c r="W32" s="120"/>
+      <c r="W32" s="119"/>
       <c r="X32" s="42"/>
-      <c r="Y32" s="120"/>
+      <c r="Y32" s="119"/>
       <c r="Z32" s="42"/>
-      <c r="AA32" s="120"/>
+      <c r="AA32" s="119"/>
       <c r="AB32" s="42"/>
-      <c r="AC32" s="120"/>
+      <c r="AC32" s="119"/>
       <c r="AD32" s="42"/>
-      <c r="AE32" s="120"/>
+      <c r="AE32" s="119"/>
       <c r="AF32" s="42"/>
-      <c r="AG32" s="120"/>
+      <c r="AG32" s="119"/>
       <c r="AH32" s="42"/>
-      <c r="AI32" s="120"/>
+      <c r="AI32" s="119"/>
       <c r="AJ32" s="42"/>
-      <c r="AK32" s="120"/>
+      <c r="AK32" s="119"/>
       <c r="AL32" s="42"/>
-      <c r="AM32" s="120"/>
+      <c r="AM32" s="119"/>
       <c r="AN32" s="42"/>
-      <c r="AO32" s="120"/>
+      <c r="AO32" s="119"/>
       <c r="AP32" s="42"/>
-      <c r="AQ32" s="120"/>
+      <c r="AQ32" s="119"/>
       <c r="AR32" s="42"/>
-      <c r="AS32" s="120"/>
+      <c r="AS32" s="119"/>
       <c r="AT32" s="42"/>
-      <c r="AU32" s="120"/>
+      <c r="AU32" s="119"/>
       <c r="AV32" s="42"/>
-      <c r="AW32" s="120"/>
+      <c r="AW32" s="119"/>
       <c r="AX32" s="42"/>
-      <c r="AY32" s="120"/>
+      <c r="AY32" s="119"/>
       <c r="AZ32" s="42"/>
-      <c r="BA32" s="120"/>
+      <c r="BA32" s="119"/>
       <c r="BB32" s="42"/>
-      <c r="BC32" s="120"/>
+      <c r="BC32" s="119"/>
       <c r="BD32" s="42"/>
-      <c r="BE32" s="120"/>
+      <c r="BE32" s="119"/>
       <c r="BF32" s="42"/>
-      <c r="BG32" s="120"/>
+      <c r="BG32" s="119"/>
       <c r="BH32" s="42"/>
-      <c r="BI32" s="120"/>
+      <c r="BI32" s="119"/>
       <c r="BJ32" s="42"/>
-      <c r="BK32" s="120"/>
+      <c r="BK32" s="119"/>
       <c r="BL32" s="42"/>
-      <c r="BM32" s="120"/>
+      <c r="BM32" s="119"/>
       <c r="BN32" s="42"/>
-      <c r="BO32" s="120"/>
+      <c r="BO32" s="119"/>
       <c r="BP32" s="42"/>
-      <c r="BQ32" s="120"/>
+      <c r="BQ32" s="119"/>
       <c r="BR32" s="42"/>
-      <c r="BS32" s="120"/>
+      <c r="BS32" s="119"/>
       <c r="BT32" s="42"/>
-      <c r="BU32" s="120"/>
+      <c r="BU32" s="119"/>
       <c r="BV32" s="42"/>
       <c r="BW32" s="36"/>
     </row>
     <row r="33" spans="1:75" ht="17.25" customHeight="1">
       <c r="A33" s="36"/>
-      <c r="B33" s="132"/>
+      <c r="B33" s="131"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="132"/>
+      <c r="D33" s="131"/>
       <c r="E33" s="50"/>
-      <c r="F33" s="132"/>
+      <c r="F33" s="131"/>
       <c r="G33" s="50"/>
       <c r="H33" s="36"/>
-      <c r="I33" s="132"/>
+      <c r="I33" s="131"/>
       <c r="J33" s="50"/>
-      <c r="K33" s="132"/>
+      <c r="K33" s="131"/>
       <c r="L33" s="50"/>
-      <c r="M33" s="133" t="s">
+      <c r="M33" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N33" s="53"/>
-      <c r="O33" s="132"/>
+      <c r="O33" s="131"/>
       <c r="P33" s="50"/>
-      <c r="Q33" s="132"/>
+      <c r="Q33" s="131"/>
       <c r="R33" s="50"/>
-      <c r="S33" s="133" t="s">
+      <c r="S33" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T33" s="53"/>
-      <c r="U33" s="132"/>
+      <c r="U33" s="131"/>
       <c r="V33" s="50"/>
-      <c r="W33" s="132"/>
+      <c r="W33" s="131"/>
       <c r="X33" s="50"/>
-      <c r="Y33" s="132"/>
+      <c r="Y33" s="131"/>
       <c r="Z33" s="50"/>
-      <c r="AA33" s="132"/>
+      <c r="AA33" s="131"/>
       <c r="AB33" s="50"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="132"/>
+      <c r="AD33" s="131"/>
       <c r="AE33" s="50"/>
-      <c r="AF33" s="132"/>
+      <c r="AF33" s="131"/>
       <c r="AG33" s="50"/>
-      <c r="AH33" s="132"/>
+      <c r="AH33" s="131"/>
       <c r="AI33" s="50"/>
-      <c r="AJ33" s="132"/>
+      <c r="AJ33" s="131"/>
       <c r="AK33" s="50"/>
-      <c r="AL33" s="132"/>
+      <c r="AL33" s="131"/>
       <c r="AM33" s="50"/>
-      <c r="AN33" s="132"/>
+      <c r="AN33" s="131"/>
       <c r="AO33" s="50"/>
-      <c r="AP33" s="132"/>
+      <c r="AP33" s="131"/>
       <c r="AQ33" s="50"/>
-      <c r="AR33" s="132"/>
+      <c r="AR33" s="131"/>
       <c r="AS33" s="50"/>
-      <c r="AT33" s="132"/>
+      <c r="AT33" s="131"/>
       <c r="AU33" s="50"/>
-      <c r="AV33" s="132"/>
+      <c r="AV33" s="131"/>
       <c r="AW33" s="50"/>
-      <c r="AX33" s="132"/>
+      <c r="AX33" s="131"/>
       <c r="AY33" s="50"/>
-      <c r="AZ33" s="132"/>
+      <c r="AZ33" s="131"/>
       <c r="BA33" s="50"/>
       <c r="BB33" s="36"/>
       <c r="BC33" s="36"/>
-      <c r="BD33" s="132"/>
+      <c r="BD33" s="131"/>
       <c r="BE33" s="50"/>
-      <c r="BF33" s="132"/>
+      <c r="BF33" s="131"/>
       <c r="BG33" s="50"/>
-      <c r="BH33" s="132"/>
+      <c r="BH33" s="131"/>
       <c r="BI33" s="50"/>
-      <c r="BJ33" s="132"/>
+      <c r="BJ33" s="131"/>
       <c r="BK33" s="50"/>
-      <c r="BL33" s="132"/>
+      <c r="BL33" s="131"/>
       <c r="BM33" s="50"/>
-      <c r="BN33" s="132"/>
+      <c r="BN33" s="131"/>
       <c r="BO33" s="50"/>
-      <c r="BP33" s="132"/>
+      <c r="BP33" s="131"/>
       <c r="BQ33" s="50"/>
-      <c r="BR33" s="132"/>
+      <c r="BR33" s="131"/>
       <c r="BS33" s="50"/>
-      <c r="BT33" s="132"/>
+      <c r="BT33" s="131"/>
       <c r="BU33" s="50"/>
-      <c r="BV33" s="132"/>
+      <c r="BV33" s="131"/>
       <c r="BW33" s="50"/>
     </row>
     <row r="34" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A34" s="134"/>
+      <c r="A34" s="133"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="134"/>
+      <c r="C34" s="133"/>
       <c r="D34" s="42"/>
-      <c r="E34" s="134"/>
+      <c r="E34" s="133"/>
       <c r="F34" s="42"/>
-      <c r="G34" s="134"/>
+      <c r="G34" s="133"/>
       <c r="H34" s="42"/>
-      <c r="I34" s="134"/>
+      <c r="I34" s="133"/>
       <c r="J34" s="42"/>
-      <c r="K34" s="134"/>
+      <c r="K34" s="133"/>
       <c r="L34" s="42"/>
-      <c r="M34" s="134"/>
+      <c r="M34" s="133"/>
       <c r="N34" s="42"/>
-      <c r="O34" s="134"/>
+      <c r="O34" s="133"/>
       <c r="P34" s="42"/>
-      <c r="Q34" s="134"/>
+      <c r="Q34" s="133"/>
       <c r="R34" s="42"/>
-      <c r="S34" s="134"/>
+      <c r="S34" s="133"/>
       <c r="T34" s="42"/>
-      <c r="U34" s="134"/>
+      <c r="U34" s="133"/>
       <c r="V34" s="42"/>
-      <c r="W34" s="134"/>
+      <c r="W34" s="133"/>
       <c r="X34" s="42"/>
-      <c r="Y34" s="134"/>
+      <c r="Y34" s="133"/>
       <c r="Z34" s="42"/>
-      <c r="AA34" s="134"/>
+      <c r="AA34" s="133"/>
       <c r="AB34" s="42"/>
-      <c r="AC34" s="134"/>
+      <c r="AC34" s="133"/>
       <c r="AD34" s="42"/>
-      <c r="AE34" s="134"/>
+      <c r="AE34" s="133"/>
       <c r="AF34" s="42"/>
-      <c r="AG34" s="134"/>
+      <c r="AG34" s="133"/>
       <c r="AH34" s="42"/>
-      <c r="AI34" s="134"/>
+      <c r="AI34" s="133"/>
       <c r="AJ34" s="42"/>
-      <c r="AK34" s="134"/>
+      <c r="AK34" s="133"/>
       <c r="AL34" s="42"/>
-      <c r="AM34" s="134"/>
+      <c r="AM34" s="133"/>
       <c r="AN34" s="42"/>
-      <c r="AO34" s="134"/>
+      <c r="AO34" s="133"/>
       <c r="AP34" s="42"/>
-      <c r="AQ34" s="134"/>
+      <c r="AQ34" s="133"/>
       <c r="AR34" s="42"/>
-      <c r="AS34" s="134"/>
+      <c r="AS34" s="133"/>
       <c r="AT34" s="42"/>
-      <c r="AU34" s="134"/>
+      <c r="AU34" s="133"/>
       <c r="AV34" s="42"/>
-      <c r="AW34" s="134"/>
+      <c r="AW34" s="133"/>
       <c r="AX34" s="42"/>
-      <c r="AY34" s="134"/>
+      <c r="AY34" s="133"/>
       <c r="AZ34" s="42"/>
-      <c r="BA34" s="134"/>
+      <c r="BA34" s="133"/>
       <c r="BB34" s="42"/>
-      <c r="BC34" s="134"/>
+      <c r="BC34" s="133"/>
       <c r="BD34" s="42"/>
-      <c r="BE34" s="134"/>
+      <c r="BE34" s="133"/>
       <c r="BF34" s="42"/>
-      <c r="BG34" s="134"/>
+      <c r="BG34" s="133"/>
       <c r="BH34" s="42"/>
-      <c r="BI34" s="134"/>
+      <c r="BI34" s="133"/>
       <c r="BJ34" s="42"/>
-      <c r="BK34" s="134"/>
+      <c r="BK34" s="133"/>
       <c r="BL34" s="42"/>
-      <c r="BM34" s="134"/>
+      <c r="BM34" s="133"/>
       <c r="BN34" s="42"/>
-      <c r="BO34" s="134"/>
+      <c r="BO34" s="133"/>
       <c r="BP34" s="42"/>
-      <c r="BQ34" s="134"/>
+      <c r="BQ34" s="133"/>
       <c r="BR34" s="42"/>
-      <c r="BS34" s="134"/>
+      <c r="BS34" s="133"/>
       <c r="BT34" s="42"/>
-      <c r="BU34" s="134"/>
+      <c r="BU34" s="133"/>
       <c r="BV34" s="42"/>
       <c r="BW34" s="39"/>
     </row>
     <row r="35" spans="1:75" ht="17.25" customHeight="1">
       <c r="A35" s="36"/>
-      <c r="B35" s="135"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="42"/>
-      <c r="D35" s="135"/>
+      <c r="D35" s="134"/>
       <c r="E35" s="42"/>
-      <c r="F35" s="135"/>
+      <c r="F35" s="134"/>
       <c r="G35" s="42"/>
       <c r="H35" s="36"/>
-      <c r="I35" s="132"/>
+      <c r="I35" s="131"/>
       <c r="J35" s="50"/>
-      <c r="K35" s="132"/>
+      <c r="K35" s="131"/>
       <c r="L35" s="50"/>
-      <c r="M35" s="133" t="s">
+      <c r="M35" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N35" s="53"/>
-      <c r="O35" s="132"/>
+      <c r="O35" s="131"/>
       <c r="P35" s="50"/>
-      <c r="Q35" s="132"/>
+      <c r="Q35" s="131"/>
       <c r="R35" s="50"/>
-      <c r="S35" s="133" t="s">
+      <c r="S35" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T35" s="53"/>
-      <c r="U35" s="132"/>
+      <c r="U35" s="131"/>
       <c r="V35" s="50"/>
-      <c r="W35" s="132"/>
+      <c r="W35" s="131"/>
       <c r="X35" s="50"/>
-      <c r="Y35" s="132"/>
+      <c r="Y35" s="131"/>
       <c r="Z35" s="50"/>
-      <c r="AA35" s="132"/>
+      <c r="AA35" s="131"/>
       <c r="AB35" s="50"/>
       <c r="AC35" s="36"/>
-      <c r="AD35" s="132"/>
+      <c r="AD35" s="131"/>
       <c r="AE35" s="50"/>
-      <c r="AF35" s="132"/>
+      <c r="AF35" s="131"/>
       <c r="AG35" s="50"/>
-      <c r="AH35" s="132"/>
+      <c r="AH35" s="131"/>
       <c r="AI35" s="50"/>
-      <c r="AJ35" s="132"/>
+      <c r="AJ35" s="131"/>
       <c r="AK35" s="50"/>
-      <c r="AL35" s="132"/>
+      <c r="AL35" s="131"/>
       <c r="AM35" s="50"/>
-      <c r="AN35" s="132"/>
+      <c r="AN35" s="131"/>
       <c r="AO35" s="50"/>
-      <c r="AP35" s="132"/>
+      <c r="AP35" s="131"/>
       <c r="AQ35" s="50"/>
-      <c r="AR35" s="132"/>
+      <c r="AR35" s="131"/>
       <c r="AS35" s="50"/>
-      <c r="AT35" s="132"/>
+      <c r="AT35" s="131"/>
       <c r="AU35" s="50"/>
-      <c r="AV35" s="132"/>
+      <c r="AV35" s="131"/>
       <c r="AW35" s="50"/>
-      <c r="AX35" s="132"/>
+      <c r="AX35" s="131"/>
       <c r="AY35" s="50"/>
-      <c r="AZ35" s="132"/>
+      <c r="AZ35" s="131"/>
       <c r="BA35" s="50"/>
       <c r="BB35" s="36"/>
       <c r="BC35" s="36"/>
-      <c r="BD35" s="132"/>
+      <c r="BD35" s="131"/>
       <c r="BE35" s="50"/>
-      <c r="BF35" s="132"/>
+      <c r="BF35" s="131"/>
       <c r="BG35" s="50"/>
-      <c r="BH35" s="132"/>
+      <c r="BH35" s="131"/>
       <c r="BI35" s="50"/>
-      <c r="BJ35" s="132"/>
+      <c r="BJ35" s="131"/>
       <c r="BK35" s="50"/>
-      <c r="BL35" s="132"/>
+      <c r="BL35" s="131"/>
       <c r="BM35" s="50"/>
-      <c r="BN35" s="132"/>
+      <c r="BN35" s="131"/>
       <c r="BO35" s="50"/>
-      <c r="BP35" s="132"/>
+      <c r="BP35" s="131"/>
       <c r="BQ35" s="50"/>
-      <c r="BR35" s="132"/>
+      <c r="BR35" s="131"/>
       <c r="BS35" s="50"/>
-      <c r="BT35" s="132"/>
+      <c r="BT35" s="131"/>
       <c r="BU35" s="50"/>
-      <c r="BV35" s="132"/>
+      <c r="BV35" s="131"/>
       <c r="BW35" s="50"/>
     </row>
     <row r="36" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A36" s="120"/>
+      <c r="A36" s="119"/>
       <c r="B36" s="42"/>
-      <c r="C36" s="120"/>
+      <c r="C36" s="119"/>
       <c r="D36" s="42"/>
-      <c r="E36" s="120"/>
+      <c r="E36" s="119"/>
       <c r="F36" s="42"/>
-      <c r="G36" s="120"/>
+      <c r="G36" s="119"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="120"/>
+      <c r="I36" s="119"/>
       <c r="J36" s="42"/>
-      <c r="K36" s="120"/>
+      <c r="K36" s="119"/>
       <c r="L36" s="42"/>
-      <c r="M36" s="120"/>
+      <c r="M36" s="119"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="120"/>
+      <c r="O36" s="119"/>
       <c r="P36" s="42"/>
-      <c r="Q36" s="120"/>
+      <c r="Q36" s="119"/>
       <c r="R36" s="42"/>
-      <c r="S36" s="120"/>
+      <c r="S36" s="119"/>
       <c r="T36" s="42"/>
-      <c r="U36" s="120"/>
+      <c r="U36" s="119"/>
       <c r="V36" s="42"/>
-      <c r="W36" s="120"/>
+      <c r="W36" s="119"/>
       <c r="X36" s="42"/>
-      <c r="Y36" s="120"/>
+      <c r="Y36" s="119"/>
       <c r="Z36" s="42"/>
-      <c r="AA36" s="120"/>
+      <c r="AA36" s="119"/>
       <c r="AB36" s="42"/>
-      <c r="AC36" s="120"/>
+      <c r="AC36" s="119"/>
       <c r="AD36" s="42"/>
-      <c r="AE36" s="120"/>
+      <c r="AE36" s="119"/>
       <c r="AF36" s="42"/>
-      <c r="AG36" s="120"/>
+      <c r="AG36" s="119"/>
       <c r="AH36" s="42"/>
-      <c r="AI36" s="120"/>
+      <c r="AI36" s="119"/>
       <c r="AJ36" s="42"/>
-      <c r="AK36" s="120"/>
+      <c r="AK36" s="119"/>
       <c r="AL36" s="42"/>
-      <c r="AM36" s="120"/>
+      <c r="AM36" s="119"/>
       <c r="AN36" s="42"/>
-      <c r="AO36" s="120"/>
+      <c r="AO36" s="119"/>
       <c r="AP36" s="42"/>
-      <c r="AQ36" s="120"/>
+      <c r="AQ36" s="119"/>
       <c r="AR36" s="42"/>
-      <c r="AS36" s="120"/>
+      <c r="AS36" s="119"/>
       <c r="AT36" s="42"/>
-      <c r="AU36" s="120"/>
+      <c r="AU36" s="119"/>
       <c r="AV36" s="42"/>
-      <c r="AW36" s="120"/>
+      <c r="AW36" s="119"/>
       <c r="AX36" s="42"/>
-      <c r="AY36" s="120"/>
+      <c r="AY36" s="119"/>
       <c r="AZ36" s="42"/>
-      <c r="BA36" s="120"/>
+      <c r="BA36" s="119"/>
       <c r="BB36" s="42"/>
-      <c r="BC36" s="120"/>
+      <c r="BC36" s="119"/>
       <c r="BD36" s="42"/>
-      <c r="BE36" s="120"/>
+      <c r="BE36" s="119"/>
       <c r="BF36" s="42"/>
-      <c r="BG36" s="120"/>
+      <c r="BG36" s="119"/>
       <c r="BH36" s="42"/>
-      <c r="BI36" s="120"/>
+      <c r="BI36" s="119"/>
       <c r="BJ36" s="42"/>
-      <c r="BK36" s="120"/>
+      <c r="BK36" s="119"/>
       <c r="BL36" s="42"/>
-      <c r="BM36" s="120"/>
+      <c r="BM36" s="119"/>
       <c r="BN36" s="42"/>
-      <c r="BO36" s="120"/>
+      <c r="BO36" s="119"/>
       <c r="BP36" s="42"/>
-      <c r="BQ36" s="120"/>
+      <c r="BQ36" s="119"/>
       <c r="BR36" s="42"/>
-      <c r="BS36" s="120"/>
+      <c r="BS36" s="119"/>
       <c r="BT36" s="42"/>
-      <c r="BU36" s="120"/>
+      <c r="BU36" s="119"/>
       <c r="BV36" s="42"/>
       <c r="BW36" s="36"/>
     </row>
     <row r="37" spans="1:75" ht="17.25" customHeight="1">
       <c r="A37" s="36"/>
-      <c r="B37" s="132"/>
+      <c r="B37" s="131"/>
       <c r="C37" s="50"/>
-      <c r="D37" s="132"/>
+      <c r="D37" s="131"/>
       <c r="E37" s="50"/>
-      <c r="F37" s="132"/>
+      <c r="F37" s="131"/>
       <c r="G37" s="50"/>
       <c r="H37" s="36"/>
-      <c r="I37" s="132"/>
+      <c r="I37" s="131"/>
       <c r="J37" s="50"/>
-      <c r="K37" s="132"/>
+      <c r="K37" s="131"/>
       <c r="L37" s="50"/>
-      <c r="M37" s="133" t="s">
+      <c r="M37" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N37" s="53"/>
-      <c r="O37" s="132"/>
+      <c r="O37" s="131"/>
       <c r="P37" s="50"/>
-      <c r="Q37" s="132"/>
+      <c r="Q37" s="131"/>
       <c r="R37" s="50"/>
-      <c r="S37" s="133" t="s">
+      <c r="S37" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T37" s="53"/>
-      <c r="U37" s="132"/>
+      <c r="U37" s="131"/>
       <c r="V37" s="50"/>
-      <c r="W37" s="132"/>
+      <c r="W37" s="131"/>
       <c r="X37" s="50"/>
-      <c r="Y37" s="132"/>
+      <c r="Y37" s="131"/>
       <c r="Z37" s="50"/>
-      <c r="AA37" s="132"/>
+      <c r="AA37" s="131"/>
       <c r="AB37" s="50"/>
       <c r="AC37" s="36"/>
-      <c r="AD37" s="132"/>
+      <c r="AD37" s="131"/>
       <c r="AE37" s="50"/>
-      <c r="AF37" s="132"/>
+      <c r="AF37" s="131"/>
       <c r="AG37" s="50"/>
-      <c r="AH37" s="132"/>
+      <c r="AH37" s="131"/>
       <c r="AI37" s="50"/>
-      <c r="AJ37" s="132"/>
+      <c r="AJ37" s="131"/>
       <c r="AK37" s="50"/>
-      <c r="AL37" s="132"/>
+      <c r="AL37" s="131"/>
       <c r="AM37" s="50"/>
-      <c r="AN37" s="132"/>
+      <c r="AN37" s="131"/>
       <c r="AO37" s="50"/>
-      <c r="AP37" s="132"/>
+      <c r="AP37" s="131"/>
       <c r="AQ37" s="50"/>
-      <c r="AR37" s="132"/>
+      <c r="AR37" s="131"/>
       <c r="AS37" s="50"/>
-      <c r="AT37" s="132"/>
+      <c r="AT37" s="131"/>
       <c r="AU37" s="50"/>
-      <c r="AV37" s="132"/>
+      <c r="AV37" s="131"/>
       <c r="AW37" s="50"/>
-      <c r="AX37" s="132"/>
+      <c r="AX37" s="131"/>
       <c r="AY37" s="50"/>
-      <c r="AZ37" s="132"/>
+      <c r="AZ37" s="131"/>
       <c r="BA37" s="50"/>
       <c r="BB37" s="36"/>
       <c r="BC37" s="36"/>
-      <c r="BD37" s="132"/>
+      <c r="BD37" s="131"/>
       <c r="BE37" s="50"/>
-      <c r="BF37" s="132"/>
+      <c r="BF37" s="131"/>
       <c r="BG37" s="50"/>
-      <c r="BH37" s="132"/>
+      <c r="BH37" s="131"/>
       <c r="BI37" s="50"/>
-      <c r="BJ37" s="132"/>
+      <c r="BJ37" s="131"/>
       <c r="BK37" s="50"/>
-      <c r="BL37" s="132"/>
+      <c r="BL37" s="131"/>
       <c r="BM37" s="50"/>
-      <c r="BN37" s="132"/>
+      <c r="BN37" s="131"/>
       <c r="BO37" s="50"/>
-      <c r="BP37" s="132"/>
+      <c r="BP37" s="131"/>
       <c r="BQ37" s="50"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="131"/>
       <c r="BS37" s="50"/>
-      <c r="BT37" s="132"/>
+      <c r="BT37" s="131"/>
       <c r="BU37" s="50"/>
-      <c r="BV37" s="132"/>
+      <c r="BV37" s="131"/>
       <c r="BW37" s="50"/>
     </row>
     <row r="38" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A38" s="134"/>
+      <c r="A38" s="133"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="134"/>
+      <c r="C38" s="133"/>
       <c r="D38" s="42"/>
-      <c r="E38" s="134"/>
+      <c r="E38" s="133"/>
       <c r="F38" s="42"/>
-      <c r="G38" s="134"/>
+      <c r="G38" s="133"/>
       <c r="H38" s="42"/>
-      <c r="I38" s="134"/>
+      <c r="I38" s="133"/>
       <c r="J38" s="42"/>
-      <c r="K38" s="134"/>
+      <c r="K38" s="133"/>
       <c r="L38" s="42"/>
-      <c r="M38" s="134"/>
+      <c r="M38" s="133"/>
       <c r="N38" s="42"/>
-      <c r="O38" s="134"/>
+      <c r="O38" s="133"/>
       <c r="P38" s="42"/>
-      <c r="Q38" s="134"/>
+      <c r="Q38" s="133"/>
       <c r="R38" s="42"/>
-      <c r="S38" s="134"/>
+      <c r="S38" s="133"/>
       <c r="T38" s="42"/>
-      <c r="U38" s="134"/>
+      <c r="U38" s="133"/>
       <c r="V38" s="42"/>
-      <c r="W38" s="134"/>
+      <c r="W38" s="133"/>
       <c r="X38" s="42"/>
-      <c r="Y38" s="134"/>
+      <c r="Y38" s="133"/>
       <c r="Z38" s="42"/>
-      <c r="AA38" s="134"/>
+      <c r="AA38" s="133"/>
       <c r="AB38" s="42"/>
-      <c r="AC38" s="134"/>
+      <c r="AC38" s="133"/>
       <c r="AD38" s="42"/>
-      <c r="AE38" s="134"/>
+      <c r="AE38" s="133"/>
       <c r="AF38" s="42"/>
-      <c r="AG38" s="134"/>
+      <c r="AG38" s="133"/>
       <c r="AH38" s="42"/>
-      <c r="AI38" s="134"/>
+      <c r="AI38" s="133"/>
       <c r="AJ38" s="42"/>
-      <c r="AK38" s="134"/>
+      <c r="AK38" s="133"/>
       <c r="AL38" s="42"/>
-      <c r="AM38" s="134"/>
+      <c r="AM38" s="133"/>
       <c r="AN38" s="42"/>
-      <c r="AO38" s="134"/>
+      <c r="AO38" s="133"/>
       <c r="AP38" s="42"/>
-      <c r="AQ38" s="134"/>
+      <c r="AQ38" s="133"/>
       <c r="AR38" s="42"/>
-      <c r="AS38" s="134"/>
+      <c r="AS38" s="133"/>
       <c r="AT38" s="42"/>
-      <c r="AU38" s="134"/>
+      <c r="AU38" s="133"/>
       <c r="AV38" s="42"/>
-      <c r="AW38" s="134"/>
+      <c r="AW38" s="133"/>
       <c r="AX38" s="42"/>
-      <c r="AY38" s="134"/>
+      <c r="AY38" s="133"/>
       <c r="AZ38" s="42"/>
-      <c r="BA38" s="134"/>
+      <c r="BA38" s="133"/>
       <c r="BB38" s="42"/>
-      <c r="BC38" s="134"/>
+      <c r="BC38" s="133"/>
       <c r="BD38" s="42"/>
-      <c r="BE38" s="134"/>
+      <c r="BE38" s="133"/>
       <c r="BF38" s="42"/>
-      <c r="BG38" s="134"/>
+      <c r="BG38" s="133"/>
       <c r="BH38" s="42"/>
-      <c r="BI38" s="134"/>
+      <c r="BI38" s="133"/>
       <c r="BJ38" s="42"/>
-      <c r="BK38" s="134"/>
+      <c r="BK38" s="133"/>
       <c r="BL38" s="42"/>
-      <c r="BM38" s="134"/>
+      <c r="BM38" s="133"/>
       <c r="BN38" s="42"/>
-      <c r="BO38" s="134"/>
+      <c r="BO38" s="133"/>
       <c r="BP38" s="42"/>
-      <c r="BQ38" s="134"/>
+      <c r="BQ38" s="133"/>
       <c r="BR38" s="42"/>
-      <c r="BS38" s="134"/>
+      <c r="BS38" s="133"/>
       <c r="BT38" s="42"/>
-      <c r="BU38" s="134"/>
+      <c r="BU38" s="133"/>
       <c r="BV38" s="42"/>
       <c r="BW38" s="39"/>
     </row>
     <row r="39" spans="1:75" ht="17.25" customHeight="1">
       <c r="A39" s="36"/>
-      <c r="B39" s="135"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="42"/>
-      <c r="D39" s="135"/>
+      <c r="D39" s="134"/>
       <c r="E39" s="42"/>
-      <c r="F39" s="135"/>
+      <c r="F39" s="134"/>
       <c r="G39" s="42"/>
       <c r="H39" s="36"/>
-      <c r="I39" s="132"/>
+      <c r="I39" s="131"/>
       <c r="J39" s="50"/>
-      <c r="K39" s="132"/>
+      <c r="K39" s="131"/>
       <c r="L39" s="50"/>
-      <c r="M39" s="133" t="s">
+      <c r="M39" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N39" s="53"/>
-      <c r="O39" s="132"/>
+      <c r="O39" s="131"/>
       <c r="P39" s="50"/>
-      <c r="Q39" s="132"/>
+      <c r="Q39" s="131"/>
       <c r="R39" s="50"/>
-      <c r="S39" s="133" t="s">
+      <c r="S39" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T39" s="53"/>
-      <c r="U39" s="132"/>
+      <c r="U39" s="131"/>
       <c r="V39" s="50"/>
-      <c r="W39" s="132"/>
+      <c r="W39" s="131"/>
       <c r="X39" s="50"/>
-      <c r="Y39" s="132"/>
+      <c r="Y39" s="131"/>
       <c r="Z39" s="50"/>
-      <c r="AA39" s="132"/>
+      <c r="AA39" s="131"/>
       <c r="AB39" s="50"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="132"/>
+      <c r="AD39" s="131"/>
       <c r="AE39" s="50"/>
-      <c r="AF39" s="132"/>
+      <c r="AF39" s="131"/>
       <c r="AG39" s="50"/>
-      <c r="AH39" s="132"/>
+      <c r="AH39" s="131"/>
       <c r="AI39" s="50"/>
-      <c r="AJ39" s="132"/>
+      <c r="AJ39" s="131"/>
       <c r="AK39" s="50"/>
-      <c r="AL39" s="132"/>
+      <c r="AL39" s="131"/>
       <c r="AM39" s="50"/>
-      <c r="AN39" s="132"/>
+      <c r="AN39" s="131"/>
       <c r="AO39" s="50"/>
-      <c r="AP39" s="132"/>
+      <c r="AP39" s="131"/>
       <c r="AQ39" s="50"/>
-      <c r="AR39" s="132"/>
+      <c r="AR39" s="131"/>
       <c r="AS39" s="50"/>
-      <c r="AT39" s="132"/>
+      <c r="AT39" s="131"/>
       <c r="AU39" s="50"/>
-      <c r="AV39" s="132"/>
+      <c r="AV39" s="131"/>
       <c r="AW39" s="50"/>
-      <c r="AX39" s="132"/>
+      <c r="AX39" s="131"/>
       <c r="AY39" s="50"/>
-      <c r="AZ39" s="132"/>
+      <c r="AZ39" s="131"/>
       <c r="BA39" s="50"/>
       <c r="BB39" s="36"/>
       <c r="BC39" s="36"/>
-      <c r="BD39" s="132"/>
+      <c r="BD39" s="131"/>
       <c r="BE39" s="50"/>
-      <c r="BF39" s="132"/>
+      <c r="BF39" s="131"/>
       <c r="BG39" s="50"/>
-      <c r="BH39" s="132"/>
+      <c r="BH39" s="131"/>
       <c r="BI39" s="50"/>
-      <c r="BJ39" s="132"/>
+      <c r="BJ39" s="131"/>
       <c r="BK39" s="50"/>
-      <c r="BL39" s="132"/>
+      <c r="BL39" s="131"/>
       <c r="BM39" s="50"/>
-      <c r="BN39" s="132"/>
+      <c r="BN39" s="131"/>
       <c r="BO39" s="50"/>
-      <c r="BP39" s="132"/>
+      <c r="BP39" s="131"/>
       <c r="BQ39" s="50"/>
-      <c r="BR39" s="132"/>
+      <c r="BR39" s="131"/>
       <c r="BS39" s="50"/>
-      <c r="BT39" s="132"/>
+      <c r="BT39" s="131"/>
       <c r="BU39" s="50"/>
-      <c r="BV39" s="132"/>
+      <c r="BV39" s="131"/>
       <c r="BW39" s="50"/>
     </row>
     <row r="40" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A40" s="120"/>
+      <c r="A40" s="119"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="120"/>
+      <c r="C40" s="119"/>
       <c r="D40" s="42"/>
-      <c r="E40" s="120"/>
+      <c r="E40" s="119"/>
       <c r="F40" s="42"/>
-      <c r="G40" s="120"/>
+      <c r="G40" s="119"/>
       <c r="H40" s="42"/>
-      <c r="I40" s="120"/>
+      <c r="I40" s="119"/>
       <c r="J40" s="42"/>
-      <c r="K40" s="120"/>
+      <c r="K40" s="119"/>
       <c r="L40" s="42"/>
-      <c r="M40" s="120"/>
+      <c r="M40" s="119"/>
       <c r="N40" s="42"/>
-      <c r="O40" s="120"/>
+      <c r="O40" s="119"/>
       <c r="P40" s="42"/>
-      <c r="Q40" s="120"/>
+      <c r="Q40" s="119"/>
       <c r="R40" s="42"/>
-      <c r="S40" s="120"/>
+      <c r="S40" s="119"/>
       <c r="T40" s="42"/>
-      <c r="U40" s="120"/>
+      <c r="U40" s="119"/>
       <c r="V40" s="42"/>
-      <c r="W40" s="120"/>
+      <c r="W40" s="119"/>
       <c r="X40" s="42"/>
-      <c r="Y40" s="120"/>
+      <c r="Y40" s="119"/>
       <c r="Z40" s="42"/>
-      <c r="AA40" s="120"/>
+      <c r="AA40" s="119"/>
       <c r="AB40" s="42"/>
-      <c r="AC40" s="120"/>
+      <c r="AC40" s="119"/>
       <c r="AD40" s="42"/>
-      <c r="AE40" s="120"/>
+      <c r="AE40" s="119"/>
       <c r="AF40" s="42"/>
-      <c r="AG40" s="120"/>
+      <c r="AG40" s="119"/>
       <c r="AH40" s="42"/>
-      <c r="AI40" s="120"/>
+      <c r="AI40" s="119"/>
       <c r="AJ40" s="42"/>
-      <c r="AK40" s="120"/>
+      <c r="AK40" s="119"/>
       <c r="AL40" s="42"/>
-      <c r="AM40" s="120"/>
+      <c r="AM40" s="119"/>
       <c r="AN40" s="42"/>
-      <c r="AO40" s="120"/>
+      <c r="AO40" s="119"/>
       <c r="AP40" s="42"/>
-      <c r="AQ40" s="120"/>
+      <c r="AQ40" s="119"/>
       <c r="AR40" s="42"/>
-      <c r="AS40" s="120"/>
+      <c r="AS40" s="119"/>
       <c r="AT40" s="42"/>
-      <c r="AU40" s="120"/>
+      <c r="AU40" s="119"/>
       <c r="AV40" s="42"/>
-      <c r="AW40" s="120"/>
+      <c r="AW40" s="119"/>
       <c r="AX40" s="42"/>
-      <c r="AY40" s="120"/>
+      <c r="AY40" s="119"/>
       <c r="AZ40" s="42"/>
-      <c r="BA40" s="120"/>
+      <c r="BA40" s="119"/>
       <c r="BB40" s="42"/>
-      <c r="BC40" s="120"/>
+      <c r="BC40" s="119"/>
       <c r="BD40" s="42"/>
-      <c r="BE40" s="120"/>
+      <c r="BE40" s="119"/>
       <c r="BF40" s="42"/>
-      <c r="BG40" s="120"/>
+      <c r="BG40" s="119"/>
       <c r="BH40" s="42"/>
-      <c r="BI40" s="120"/>
+      <c r="BI40" s="119"/>
       <c r="BJ40" s="42"/>
-      <c r="BK40" s="120"/>
+      <c r="BK40" s="119"/>
       <c r="BL40" s="42"/>
-      <c r="BM40" s="120"/>
+      <c r="BM40" s="119"/>
       <c r="BN40" s="42"/>
-      <c r="BO40" s="120"/>
+      <c r="BO40" s="119"/>
       <c r="BP40" s="42"/>
-      <c r="BQ40" s="120"/>
+      <c r="BQ40" s="119"/>
       <c r="BR40" s="42"/>
-      <c r="BS40" s="120"/>
+      <c r="BS40" s="119"/>
       <c r="BT40" s="42"/>
-      <c r="BU40" s="120"/>
+      <c r="BU40" s="119"/>
       <c r="BV40" s="42"/>
       <c r="BW40" s="36"/>
     </row>
     <row r="41" spans="1:75" ht="17.25" customHeight="1">
       <c r="A41" s="36"/>
-      <c r="B41" s="132"/>
+      <c r="B41" s="131"/>
       <c r="C41" s="50"/>
-      <c r="D41" s="132"/>
+      <c r="D41" s="131"/>
       <c r="E41" s="50"/>
-      <c r="F41" s="132"/>
+      <c r="F41" s="131"/>
       <c r="G41" s="50"/>
       <c r="H41" s="36"/>
-      <c r="I41" s="132"/>
+      <c r="I41" s="131"/>
       <c r="J41" s="50"/>
-      <c r="K41" s="132"/>
+      <c r="K41" s="131"/>
       <c r="L41" s="50"/>
-      <c r="M41" s="133" t="s">
+      <c r="M41" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N41" s="53"/>
-      <c r="O41" s="132"/>
+      <c r="O41" s="131"/>
       <c r="P41" s="50"/>
-      <c r="Q41" s="132"/>
+      <c r="Q41" s="131"/>
       <c r="R41" s="50"/>
-      <c r="S41" s="133" t="s">
+      <c r="S41" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T41" s="53"/>
-      <c r="U41" s="132"/>
+      <c r="U41" s="131"/>
       <c r="V41" s="50"/>
-      <c r="W41" s="132"/>
+      <c r="W41" s="131"/>
       <c r="X41" s="50"/>
-      <c r="Y41" s="132"/>
+      <c r="Y41" s="131"/>
       <c r="Z41" s="50"/>
-      <c r="AA41" s="132"/>
+      <c r="AA41" s="131"/>
       <c r="AB41" s="50"/>
       <c r="AC41" s="36"/>
-      <c r="AD41" s="132"/>
+      <c r="AD41" s="131"/>
       <c r="AE41" s="50"/>
-      <c r="AF41" s="132"/>
+      <c r="AF41" s="131"/>
       <c r="AG41" s="50"/>
-      <c r="AH41" s="132"/>
+      <c r="AH41" s="131"/>
       <c r="AI41" s="50"/>
-      <c r="AJ41" s="132"/>
+      <c r="AJ41" s="131"/>
       <c r="AK41" s="50"/>
-      <c r="AL41" s="132"/>
+      <c r="AL41" s="131"/>
       <c r="AM41" s="50"/>
-      <c r="AN41" s="132"/>
+      <c r="AN41" s="131"/>
       <c r="AO41" s="50"/>
-      <c r="AP41" s="132"/>
+      <c r="AP41" s="131"/>
       <c r="AQ41" s="50"/>
-      <c r="AR41" s="132"/>
+      <c r="AR41" s="131"/>
       <c r="AS41" s="50"/>
-      <c r="AT41" s="132"/>
+      <c r="AT41" s="131"/>
       <c r="AU41" s="50"/>
-      <c r="AV41" s="132"/>
+      <c r="AV41" s="131"/>
       <c r="AW41" s="50"/>
-      <c r="AX41" s="132"/>
+      <c r="AX41" s="131"/>
       <c r="AY41" s="50"/>
-      <c r="AZ41" s="132"/>
+      <c r="AZ41" s="131"/>
       <c r="BA41" s="50"/>
       <c r="BB41" s="36"/>
       <c r="BC41" s="36"/>
-      <c r="BD41" s="132"/>
+      <c r="BD41" s="131"/>
       <c r="BE41" s="50"/>
-      <c r="BF41" s="132"/>
+      <c r="BF41" s="131"/>
       <c r="BG41" s="50"/>
-      <c r="BH41" s="132"/>
+      <c r="BH41" s="131"/>
       <c r="BI41" s="50"/>
-      <c r="BJ41" s="132"/>
+      <c r="BJ41" s="131"/>
       <c r="BK41" s="50"/>
-      <c r="BL41" s="132"/>
+      <c r="BL41" s="131"/>
       <c r="BM41" s="50"/>
-      <c r="BN41" s="132"/>
+      <c r="BN41" s="131"/>
       <c r="BO41" s="50"/>
-      <c r="BP41" s="132"/>
+      <c r="BP41" s="131"/>
       <c r="BQ41" s="50"/>
-      <c r="BR41" s="132"/>
+      <c r="BR41" s="131"/>
       <c r="BS41" s="50"/>
-      <c r="BT41" s="132"/>
+      <c r="BT41" s="131"/>
       <c r="BU41" s="50"/>
-      <c r="BV41" s="132"/>
+      <c r="BV41" s="131"/>
       <c r="BW41" s="50"/>
     </row>
     <row r="42" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A42" s="134"/>
+      <c r="A42" s="133"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="134"/>
+      <c r="C42" s="133"/>
       <c r="D42" s="42"/>
-      <c r="E42" s="134"/>
+      <c r="E42" s="133"/>
       <c r="F42" s="42"/>
-      <c r="G42" s="134"/>
+      <c r="G42" s="133"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="134"/>
+      <c r="I42" s="133"/>
       <c r="J42" s="42"/>
-      <c r="K42" s="134"/>
+      <c r="K42" s="133"/>
       <c r="L42" s="42"/>
-      <c r="M42" s="134"/>
+      <c r="M42" s="133"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="134"/>
+      <c r="O42" s="133"/>
       <c r="P42" s="42"/>
-      <c r="Q42" s="134"/>
+      <c r="Q42" s="133"/>
       <c r="R42" s="42"/>
-      <c r="S42" s="134"/>
+      <c r="S42" s="133"/>
       <c r="T42" s="42"/>
-      <c r="U42" s="134"/>
+      <c r="U42" s="133"/>
       <c r="V42" s="42"/>
-      <c r="W42" s="134"/>
+      <c r="W42" s="133"/>
       <c r="X42" s="42"/>
-      <c r="Y42" s="134"/>
+      <c r="Y42" s="133"/>
       <c r="Z42" s="42"/>
-      <c r="AA42" s="134"/>
+      <c r="AA42" s="133"/>
       <c r="AB42" s="42"/>
-      <c r="AC42" s="134"/>
+      <c r="AC42" s="133"/>
       <c r="AD42" s="42"/>
-      <c r="AE42" s="134"/>
+      <c r="AE42" s="133"/>
       <c r="AF42" s="42"/>
-      <c r="AG42" s="134"/>
+      <c r="AG42" s="133"/>
       <c r="AH42" s="42"/>
-      <c r="AI42" s="134"/>
+      <c r="AI42" s="133"/>
       <c r="AJ42" s="42"/>
-      <c r="AK42" s="134"/>
+      <c r="AK42" s="133"/>
       <c r="AL42" s="42"/>
-      <c r="AM42" s="134"/>
+      <c r="AM42" s="133"/>
       <c r="AN42" s="42"/>
-      <c r="AO42" s="134"/>
+      <c r="AO42" s="133"/>
       <c r="AP42" s="42"/>
-      <c r="AQ42" s="134"/>
+      <c r="AQ42" s="133"/>
       <c r="AR42" s="42"/>
-      <c r="AS42" s="134"/>
+      <c r="AS42" s="133"/>
       <c r="AT42" s="42"/>
-      <c r="AU42" s="134"/>
+      <c r="AU42" s="133"/>
       <c r="AV42" s="42"/>
-      <c r="AW42" s="134"/>
+      <c r="AW42" s="133"/>
       <c r="AX42" s="42"/>
-      <c r="AY42" s="134"/>
+      <c r="AY42" s="133"/>
       <c r="AZ42" s="42"/>
-      <c r="BA42" s="134"/>
+      <c r="BA42" s="133"/>
       <c r="BB42" s="42"/>
-      <c r="BC42" s="134"/>
+      <c r="BC42" s="133"/>
       <c r="BD42" s="42"/>
-      <c r="BE42" s="134"/>
+      <c r="BE42" s="133"/>
       <c r="BF42" s="42"/>
-      <c r="BG42" s="134"/>
+      <c r="BG42" s="133"/>
       <c r="BH42" s="42"/>
-      <c r="BI42" s="134"/>
+      <c r="BI42" s="133"/>
       <c r="BJ42" s="42"/>
-      <c r="BK42" s="134"/>
+      <c r="BK42" s="133"/>
       <c r="BL42" s="42"/>
-      <c r="BM42" s="134"/>
+      <c r="BM42" s="133"/>
       <c r="BN42" s="42"/>
-      <c r="BO42" s="134"/>
+      <c r="BO42" s="133"/>
       <c r="BP42" s="42"/>
-      <c r="BQ42" s="134"/>
+      <c r="BQ42" s="133"/>
       <c r="BR42" s="42"/>
-      <c r="BS42" s="134"/>
+      <c r="BS42" s="133"/>
       <c r="BT42" s="42"/>
-      <c r="BU42" s="134"/>
+      <c r="BU42" s="133"/>
       <c r="BV42" s="42"/>
       <c r="BW42" s="39"/>
     </row>
     <row r="43" spans="1:75" ht="17.25" customHeight="1">
       <c r="A43" s="36"/>
-      <c r="B43" s="135"/>
+      <c r="B43" s="134"/>
       <c r="C43" s="42"/>
-      <c r="D43" s="135"/>
+      <c r="D43" s="134"/>
       <c r="E43" s="42"/>
-      <c r="F43" s="135"/>
+      <c r="F43" s="134"/>
       <c r="G43" s="42"/>
       <c r="H43" s="36"/>
-      <c r="I43" s="132"/>
+      <c r="I43" s="131"/>
       <c r="J43" s="50"/>
-      <c r="K43" s="132"/>
+      <c r="K43" s="131"/>
       <c r="L43" s="50"/>
-      <c r="M43" s="133" t="s">
+      <c r="M43" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N43" s="53"/>
-      <c r="O43" s="132"/>
+      <c r="O43" s="131"/>
       <c r="P43" s="50"/>
-      <c r="Q43" s="132"/>
+      <c r="Q43" s="131"/>
       <c r="R43" s="50"/>
-      <c r="S43" s="133" t="s">
+      <c r="S43" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T43" s="53"/>
-      <c r="U43" s="132"/>
+      <c r="U43" s="131"/>
       <c r="V43" s="50"/>
-      <c r="W43" s="132"/>
+      <c r="W43" s="131"/>
       <c r="X43" s="50"/>
-      <c r="Y43" s="132"/>
+      <c r="Y43" s="131"/>
       <c r="Z43" s="50"/>
-      <c r="AA43" s="132"/>
+      <c r="AA43" s="131"/>
       <c r="AB43" s="50"/>
       <c r="AC43" s="36"/>
-      <c r="AD43" s="132"/>
+      <c r="AD43" s="131"/>
       <c r="AE43" s="50"/>
-      <c r="AF43" s="132"/>
+      <c r="AF43" s="131"/>
       <c r="AG43" s="50"/>
-      <c r="AH43" s="132"/>
+      <c r="AH43" s="131"/>
       <c r="AI43" s="50"/>
-      <c r="AJ43" s="132"/>
+      <c r="AJ43" s="131"/>
       <c r="AK43" s="50"/>
-      <c r="AL43" s="132"/>
+      <c r="AL43" s="131"/>
       <c r="AM43" s="50"/>
-      <c r="AN43" s="132"/>
+      <c r="AN43" s="131"/>
       <c r="AO43" s="50"/>
-      <c r="AP43" s="132"/>
+      <c r="AP43" s="131"/>
       <c r="AQ43" s="50"/>
-      <c r="AR43" s="132"/>
+      <c r="AR43" s="131"/>
       <c r="AS43" s="50"/>
-      <c r="AT43" s="132"/>
+      <c r="AT43" s="131"/>
       <c r="AU43" s="50"/>
-      <c r="AV43" s="132"/>
+      <c r="AV43" s="131"/>
       <c r="AW43" s="50"/>
-      <c r="AX43" s="132"/>
+      <c r="AX43" s="131"/>
       <c r="AY43" s="50"/>
-      <c r="AZ43" s="132"/>
+      <c r="AZ43" s="131"/>
       <c r="BA43" s="50"/>
       <c r="BB43" s="36"/>
       <c r="BC43" s="36"/>
-      <c r="BD43" s="132"/>
+      <c r="BD43" s="131"/>
       <c r="BE43" s="50"/>
-      <c r="BF43" s="132"/>
+      <c r="BF43" s="131"/>
       <c r="BG43" s="50"/>
-      <c r="BH43" s="132"/>
+      <c r="BH43" s="131"/>
       <c r="BI43" s="50"/>
-      <c r="BJ43" s="132"/>
+      <c r="BJ43" s="131"/>
       <c r="BK43" s="50"/>
-      <c r="BL43" s="132"/>
+      <c r="BL43" s="131"/>
       <c r="BM43" s="50"/>
-      <c r="BN43" s="132"/>
+      <c r="BN43" s="131"/>
       <c r="BO43" s="50"/>
-      <c r="BP43" s="132"/>
+      <c r="BP43" s="131"/>
       <c r="BQ43" s="50"/>
-      <c r="BR43" s="132"/>
+      <c r="BR43" s="131"/>
       <c r="BS43" s="50"/>
-      <c r="BT43" s="132"/>
+      <c r="BT43" s="131"/>
       <c r="BU43" s="50"/>
-      <c r="BV43" s="132"/>
+      <c r="BV43" s="131"/>
       <c r="BW43" s="50"/>
     </row>
     <row r="44" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A44" s="120"/>
+      <c r="A44" s="119"/>
       <c r="B44" s="42"/>
-      <c r="C44" s="120"/>
+      <c r="C44" s="119"/>
       <c r="D44" s="42"/>
-      <c r="E44" s="120"/>
+      <c r="E44" s="119"/>
       <c r="F44" s="42"/>
-      <c r="G44" s="120"/>
+      <c r="G44" s="119"/>
       <c r="H44" s="42"/>
-      <c r="I44" s="120"/>
+      <c r="I44" s="119"/>
       <c r="J44" s="42"/>
-      <c r="K44" s="120"/>
+      <c r="K44" s="119"/>
       <c r="L44" s="42"/>
-      <c r="M44" s="120"/>
+      <c r="M44" s="119"/>
       <c r="N44" s="42"/>
-      <c r="O44" s="120"/>
+      <c r="O44" s="119"/>
       <c r="P44" s="42"/>
-      <c r="Q44" s="120"/>
+      <c r="Q44" s="119"/>
       <c r="R44" s="42"/>
-      <c r="S44" s="120"/>
+      <c r="S44" s="119"/>
       <c r="T44" s="42"/>
-      <c r="U44" s="120"/>
+      <c r="U44" s="119"/>
       <c r="V44" s="42"/>
-      <c r="W44" s="120"/>
+      <c r="W44" s="119"/>
       <c r="X44" s="42"/>
-      <c r="Y44" s="120"/>
+      <c r="Y44" s="119"/>
       <c r="Z44" s="42"/>
-      <c r="AA44" s="120"/>
+      <c r="AA44" s="119"/>
       <c r="AB44" s="42"/>
-      <c r="AC44" s="120"/>
+      <c r="AC44" s="119"/>
       <c r="AD44" s="42"/>
-      <c r="AE44" s="120"/>
+      <c r="AE44" s="119"/>
       <c r="AF44" s="42"/>
-      <c r="AG44" s="120"/>
+      <c r="AG44" s="119"/>
       <c r="AH44" s="42"/>
-      <c r="AI44" s="120"/>
+      <c r="AI44" s="119"/>
       <c r="AJ44" s="42"/>
-      <c r="AK44" s="120"/>
+      <c r="AK44" s="119"/>
       <c r="AL44" s="42"/>
-      <c r="AM44" s="120"/>
+      <c r="AM44" s="119"/>
       <c r="AN44" s="42"/>
-      <c r="AO44" s="120"/>
+      <c r="AO44" s="119"/>
       <c r="AP44" s="42"/>
-      <c r="AQ44" s="120"/>
+      <c r="AQ44" s="119"/>
       <c r="AR44" s="42"/>
-      <c r="AS44" s="120"/>
+      <c r="AS44" s="119"/>
       <c r="AT44" s="42"/>
-      <c r="AU44" s="120"/>
+      <c r="AU44" s="119"/>
       <c r="AV44" s="42"/>
-      <c r="AW44" s="120"/>
+      <c r="AW44" s="119"/>
       <c r="AX44" s="42"/>
-      <c r="AY44" s="120"/>
+      <c r="AY44" s="119"/>
       <c r="AZ44" s="42"/>
-      <c r="BA44" s="120"/>
+      <c r="BA44" s="119"/>
       <c r="BB44" s="42"/>
-      <c r="BC44" s="120"/>
+      <c r="BC44" s="119"/>
       <c r="BD44" s="42"/>
-      <c r="BE44" s="120"/>
+      <c r="BE44" s="119"/>
       <c r="BF44" s="42"/>
-      <c r="BG44" s="120"/>
+      <c r="BG44" s="119"/>
       <c r="BH44" s="42"/>
-      <c r="BI44" s="120"/>
+      <c r="BI44" s="119"/>
       <c r="BJ44" s="42"/>
-      <c r="BK44" s="120"/>
+      <c r="BK44" s="119"/>
       <c r="BL44" s="42"/>
-      <c r="BM44" s="120"/>
+      <c r="BM44" s="119"/>
       <c r="BN44" s="42"/>
-      <c r="BO44" s="120"/>
+      <c r="BO44" s="119"/>
       <c r="BP44" s="42"/>
-      <c r="BQ44" s="120"/>
+      <c r="BQ44" s="119"/>
       <c r="BR44" s="42"/>
-      <c r="BS44" s="120"/>
+      <c r="BS44" s="119"/>
       <c r="BT44" s="42"/>
-      <c r="BU44" s="120"/>
+      <c r="BU44" s="119"/>
       <c r="BV44" s="42"/>
       <c r="BW44" s="36"/>
     </row>
     <row r="45" spans="1:75" ht="17.25" customHeight="1">
       <c r="A45" s="36"/>
-      <c r="B45" s="132"/>
+      <c r="B45" s="131"/>
       <c r="C45" s="50"/>
-      <c r="D45" s="132"/>
+      <c r="D45" s="131"/>
       <c r="E45" s="50"/>
-      <c r="F45" s="132"/>
+      <c r="F45" s="131"/>
       <c r="G45" s="50"/>
       <c r="H45" s="36"/>
-      <c r="I45" s="132"/>
+      <c r="I45" s="131"/>
       <c r="J45" s="50"/>
-      <c r="K45" s="132"/>
+      <c r="K45" s="131"/>
       <c r="L45" s="50"/>
-      <c r="M45" s="133" t="s">
+      <c r="M45" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N45" s="53"/>
-      <c r="O45" s="132"/>
+      <c r="O45" s="131"/>
       <c r="P45" s="50"/>
-      <c r="Q45" s="132"/>
+      <c r="Q45" s="131"/>
       <c r="R45" s="50"/>
-      <c r="S45" s="133" t="s">
+      <c r="S45" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T45" s="53"/>
-      <c r="U45" s="132"/>
+      <c r="U45" s="131"/>
       <c r="V45" s="50"/>
-      <c r="W45" s="132"/>
+      <c r="W45" s="131"/>
       <c r="X45" s="50"/>
-      <c r="Y45" s="132"/>
+      <c r="Y45" s="131"/>
       <c r="Z45" s="50"/>
-      <c r="AA45" s="132"/>
+      <c r="AA45" s="131"/>
       <c r="AB45" s="50"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="132"/>
+      <c r="AD45" s="131"/>
       <c r="AE45" s="50"/>
-      <c r="AF45" s="132"/>
+      <c r="AF45" s="131"/>
       <c r="AG45" s="50"/>
-      <c r="AH45" s="132"/>
+      <c r="AH45" s="131"/>
       <c r="AI45" s="50"/>
-      <c r="AJ45" s="132"/>
+      <c r="AJ45" s="131"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="132"/>
+      <c r="AL45" s="131"/>
       <c r="AM45" s="50"/>
-      <c r="AN45" s="132"/>
+      <c r="AN45" s="131"/>
       <c r="AO45" s="50"/>
-      <c r="AP45" s="132"/>
+      <c r="AP45" s="131"/>
       <c r="AQ45" s="50"/>
-      <c r="AR45" s="132"/>
+      <c r="AR45" s="131"/>
       <c r="AS45" s="50"/>
-      <c r="AT45" s="132"/>
+      <c r="AT45" s="131"/>
       <c r="AU45" s="50"/>
-      <c r="AV45" s="132"/>
+      <c r="AV45" s="131"/>
       <c r="AW45" s="50"/>
-      <c r="AX45" s="132"/>
+      <c r="AX45" s="131"/>
       <c r="AY45" s="50"/>
-      <c r="AZ45" s="132"/>
+      <c r="AZ45" s="131"/>
       <c r="BA45" s="50"/>
       <c r="BB45" s="36"/>
       <c r="BC45" s="36"/>
-      <c r="BD45" s="132"/>
+      <c r="BD45" s="131"/>
       <c r="BE45" s="50"/>
-      <c r="BF45" s="132"/>
+      <c r="BF45" s="131"/>
       <c r="BG45" s="50"/>
-      <c r="BH45" s="132"/>
+      <c r="BH45" s="131"/>
       <c r="BI45" s="50"/>
-      <c r="BJ45" s="132"/>
+      <c r="BJ45" s="131"/>
       <c r="BK45" s="50"/>
-      <c r="BL45" s="132"/>
+      <c r="BL45" s="131"/>
       <c r="BM45" s="50"/>
-      <c r="BN45" s="132"/>
+      <c r="BN45" s="131"/>
       <c r="BO45" s="50"/>
-      <c r="BP45" s="132"/>
+      <c r="BP45" s="131"/>
       <c r="BQ45" s="50"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="131"/>
       <c r="BS45" s="50"/>
-      <c r="BT45" s="132"/>
+      <c r="BT45" s="131"/>
       <c r="BU45" s="50"/>
-      <c r="BV45" s="132"/>
+      <c r="BV45" s="131"/>
       <c r="BW45" s="50"/>
     </row>
     <row r="46" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A46" s="134"/>
+      <c r="A46" s="133"/>
       <c r="B46" s="42"/>
-      <c r="C46" s="134"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="42"/>
-      <c r="E46" s="134"/>
+      <c r="E46" s="133"/>
       <c r="F46" s="42"/>
-      <c r="G46" s="134"/>
+      <c r="G46" s="133"/>
       <c r="H46" s="42"/>
-      <c r="I46" s="134"/>
+      <c r="I46" s="133"/>
       <c r="J46" s="42"/>
-      <c r="K46" s="134"/>
+      <c r="K46" s="133"/>
       <c r="L46" s="42"/>
-      <c r="M46" s="134"/>
+      <c r="M46" s="133"/>
       <c r="N46" s="42"/>
-      <c r="O46" s="134"/>
+      <c r="O46" s="133"/>
       <c r="P46" s="42"/>
-      <c r="Q46" s="134"/>
+      <c r="Q46" s="133"/>
       <c r="R46" s="42"/>
-      <c r="S46" s="134"/>
+      <c r="S46" s="133"/>
       <c r="T46" s="42"/>
-      <c r="U46" s="134"/>
+      <c r="U46" s="133"/>
       <c r="V46" s="42"/>
-      <c r="W46" s="134"/>
+      <c r="W46" s="133"/>
       <c r="X46" s="42"/>
-      <c r="Y46" s="134"/>
+      <c r="Y46" s="133"/>
       <c r="Z46" s="42"/>
-      <c r="AA46" s="134"/>
+      <c r="AA46" s="133"/>
       <c r="AB46" s="42"/>
-      <c r="AC46" s="134"/>
+      <c r="AC46" s="133"/>
       <c r="AD46" s="42"/>
-      <c r="AE46" s="134"/>
+      <c r="AE46" s="133"/>
       <c r="AF46" s="42"/>
-      <c r="AG46" s="134"/>
+      <c r="AG46" s="133"/>
       <c r="AH46" s="42"/>
-      <c r="AI46" s="134"/>
+      <c r="AI46" s="133"/>
       <c r="AJ46" s="42"/>
-      <c r="AK46" s="134"/>
+      <c r="AK46" s="133"/>
       <c r="AL46" s="42"/>
-      <c r="AM46" s="134"/>
+      <c r="AM46" s="133"/>
       <c r="AN46" s="42"/>
-      <c r="AO46" s="134"/>
+      <c r="AO46" s="133"/>
       <c r="AP46" s="42"/>
-      <c r="AQ46" s="134"/>
+      <c r="AQ46" s="133"/>
       <c r="AR46" s="42"/>
-      <c r="AS46" s="134"/>
+      <c r="AS46" s="133"/>
       <c r="AT46" s="42"/>
-      <c r="AU46" s="134"/>
+      <c r="AU46" s="133"/>
       <c r="AV46" s="42"/>
-      <c r="AW46" s="134"/>
+      <c r="AW46" s="133"/>
       <c r="AX46" s="42"/>
-      <c r="AY46" s="134"/>
+      <c r="AY46" s="133"/>
       <c r="AZ46" s="42"/>
-      <c r="BA46" s="134"/>
+      <c r="BA46" s="133"/>
       <c r="BB46" s="42"/>
-      <c r="BC46" s="134"/>
+      <c r="BC46" s="133"/>
       <c r="BD46" s="42"/>
-      <c r="BE46" s="134"/>
+      <c r="BE46" s="133"/>
       <c r="BF46" s="42"/>
-      <c r="BG46" s="134"/>
+      <c r="BG46" s="133"/>
       <c r="BH46" s="42"/>
-      <c r="BI46" s="134"/>
+      <c r="BI46" s="133"/>
       <c r="BJ46" s="42"/>
-      <c r="BK46" s="134"/>
+      <c r="BK46" s="133"/>
       <c r="BL46" s="42"/>
-      <c r="BM46" s="134"/>
+      <c r="BM46" s="133"/>
       <c r="BN46" s="42"/>
-      <c r="BO46" s="134"/>
+      <c r="BO46" s="133"/>
       <c r="BP46" s="42"/>
-      <c r="BQ46" s="134"/>
+      <c r="BQ46" s="133"/>
       <c r="BR46" s="42"/>
-      <c r="BS46" s="134"/>
+      <c r="BS46" s="133"/>
       <c r="BT46" s="42"/>
-      <c r="BU46" s="134"/>
+      <c r="BU46" s="133"/>
       <c r="BV46" s="42"/>
       <c r="BW46" s="39"/>
     </row>
     <row r="47" spans="1:75" ht="17.25" customHeight="1">
       <c r="A47" s="36"/>
-      <c r="B47" s="135"/>
+      <c r="B47" s="134"/>
       <c r="C47" s="42"/>
-      <c r="D47" s="135"/>
+      <c r="D47" s="134"/>
       <c r="E47" s="42"/>
-      <c r="F47" s="135"/>
+      <c r="F47" s="134"/>
       <c r="G47" s="42"/>
       <c r="H47" s="36"/>
-      <c r="I47" s="132"/>
+      <c r="I47" s="131"/>
       <c r="J47" s="50"/>
-      <c r="K47" s="132"/>
+      <c r="K47" s="131"/>
       <c r="L47" s="50"/>
-      <c r="M47" s="133" t="s">
+      <c r="M47" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N47" s="53"/>
-      <c r="O47" s="132"/>
+      <c r="O47" s="131"/>
       <c r="P47" s="50"/>
-      <c r="Q47" s="132"/>
+      <c r="Q47" s="131"/>
       <c r="R47" s="50"/>
-      <c r="S47" s="133" t="s">
+      <c r="S47" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T47" s="53"/>
-      <c r="U47" s="132"/>
+      <c r="U47" s="131"/>
       <c r="V47" s="50"/>
-      <c r="W47" s="132"/>
+      <c r="W47" s="131"/>
       <c r="X47" s="50"/>
-      <c r="Y47" s="132"/>
+      <c r="Y47" s="131"/>
       <c r="Z47" s="50"/>
-      <c r="AA47" s="132"/>
+      <c r="AA47" s="131"/>
       <c r="AB47" s="50"/>
       <c r="AC47" s="36"/>
-      <c r="AD47" s="132"/>
+      <c r="AD47" s="131"/>
       <c r="AE47" s="50"/>
-      <c r="AF47" s="132"/>
+      <c r="AF47" s="131"/>
       <c r="AG47" s="50"/>
-      <c r="AH47" s="132"/>
+      <c r="AH47" s="131"/>
       <c r="AI47" s="50"/>
-      <c r="AJ47" s="132"/>
+      <c r="AJ47" s="131"/>
       <c r="AK47" s="50"/>
-      <c r="AL47" s="132"/>
+      <c r="AL47" s="131"/>
       <c r="AM47" s="50"/>
-      <c r="AN47" s="132"/>
+      <c r="AN47" s="131"/>
       <c r="AO47" s="50"/>
-      <c r="AP47" s="132"/>
+      <c r="AP47" s="131"/>
       <c r="AQ47" s="50"/>
-      <c r="AR47" s="132"/>
+      <c r="AR47" s="131"/>
       <c r="AS47" s="50"/>
-      <c r="AT47" s="132"/>
+      <c r="AT47" s="131"/>
       <c r="AU47" s="50"/>
-      <c r="AV47" s="132"/>
+      <c r="AV47" s="131"/>
       <c r="AW47" s="50"/>
-      <c r="AX47" s="132"/>
+      <c r="AX47" s="131"/>
       <c r="AY47" s="50"/>
-      <c r="AZ47" s="132"/>
+      <c r="AZ47" s="131"/>
       <c r="BA47" s="50"/>
       <c r="BB47" s="36"/>
       <c r="BC47" s="36"/>
-      <c r="BD47" s="132"/>
+      <c r="BD47" s="131"/>
       <c r="BE47" s="50"/>
-      <c r="BF47" s="132"/>
+      <c r="BF47" s="131"/>
       <c r="BG47" s="50"/>
-      <c r="BH47" s="132"/>
+      <c r="BH47" s="131"/>
       <c r="BI47" s="50"/>
-      <c r="BJ47" s="132"/>
+      <c r="BJ47" s="131"/>
       <c r="BK47" s="50"/>
-      <c r="BL47" s="132"/>
+      <c r="BL47" s="131"/>
       <c r="BM47" s="50"/>
-      <c r="BN47" s="132"/>
+      <c r="BN47" s="131"/>
       <c r="BO47" s="50"/>
-      <c r="BP47" s="132"/>
+      <c r="BP47" s="131"/>
       <c r="BQ47" s="50"/>
-      <c r="BR47" s="132"/>
+      <c r="BR47" s="131"/>
       <c r="BS47" s="50"/>
-      <c r="BT47" s="132"/>
+      <c r="BT47" s="131"/>
       <c r="BU47" s="50"/>
-      <c r="BV47" s="132"/>
+      <c r="BV47" s="131"/>
       <c r="BW47" s="50"/>
     </row>
     <row r="48" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A48" s="120"/>
+      <c r="A48" s="119"/>
       <c r="B48" s="42"/>
-      <c r="C48" s="120"/>
+      <c r="C48" s="119"/>
       <c r="D48" s="42"/>
-      <c r="E48" s="120"/>
+      <c r="E48" s="119"/>
       <c r="F48" s="42"/>
-      <c r="G48" s="120"/>
+      <c r="G48" s="119"/>
       <c r="H48" s="42"/>
-      <c r="I48" s="120"/>
+      <c r="I48" s="119"/>
       <c r="J48" s="42"/>
-      <c r="K48" s="120"/>
+      <c r="K48" s="119"/>
       <c r="L48" s="42"/>
-      <c r="M48" s="120"/>
+      <c r="M48" s="119"/>
       <c r="N48" s="42"/>
-      <c r="O48" s="120"/>
+      <c r="O48" s="119"/>
       <c r="P48" s="42"/>
-      <c r="Q48" s="120"/>
+      <c r="Q48" s="119"/>
       <c r="R48" s="42"/>
-      <c r="S48" s="120"/>
+      <c r="S48" s="119"/>
       <c r="T48" s="42"/>
-      <c r="U48" s="120"/>
+      <c r="U48" s="119"/>
       <c r="V48" s="42"/>
-      <c r="W48" s="120"/>
+      <c r="W48" s="119"/>
       <c r="X48" s="42"/>
-      <c r="Y48" s="120"/>
+      <c r="Y48" s="119"/>
       <c r="Z48" s="42"/>
-      <c r="AA48" s="120"/>
+      <c r="AA48" s="119"/>
       <c r="AB48" s="42"/>
-      <c r="AC48" s="120"/>
+      <c r="AC48" s="119"/>
       <c r="AD48" s="42"/>
-      <c r="AE48" s="120"/>
+      <c r="AE48" s="119"/>
       <c r="AF48" s="42"/>
-      <c r="AG48" s="120"/>
+      <c r="AG48" s="119"/>
       <c r="AH48" s="42"/>
-      <c r="AI48" s="120"/>
+      <c r="AI48" s="119"/>
       <c r="AJ48" s="42"/>
-      <c r="AK48" s="120"/>
+      <c r="AK48" s="119"/>
       <c r="AL48" s="42"/>
-      <c r="AM48" s="120"/>
+      <c r="AM48" s="119"/>
       <c r="AN48" s="42"/>
-      <c r="AO48" s="120"/>
+      <c r="AO48" s="119"/>
       <c r="AP48" s="42"/>
-      <c r="AQ48" s="120"/>
+      <c r="AQ48" s="119"/>
       <c r="AR48" s="42"/>
-      <c r="AS48" s="120"/>
+      <c r="AS48" s="119"/>
       <c r="AT48" s="42"/>
-      <c r="AU48" s="120"/>
+      <c r="AU48" s="119"/>
       <c r="AV48" s="42"/>
-      <c r="AW48" s="120"/>
+      <c r="AW48" s="119"/>
       <c r="AX48" s="42"/>
-      <c r="AY48" s="120"/>
+      <c r="AY48" s="119"/>
       <c r="AZ48" s="42"/>
-      <c r="BA48" s="120"/>
+      <c r="BA48" s="119"/>
       <c r="BB48" s="42"/>
-      <c r="BC48" s="120"/>
+      <c r="BC48" s="119"/>
       <c r="BD48" s="42"/>
-      <c r="BE48" s="120"/>
+      <c r="BE48" s="119"/>
       <c r="BF48" s="42"/>
-      <c r="BG48" s="120"/>
+      <c r="BG48" s="119"/>
       <c r="BH48" s="42"/>
-      <c r="BI48" s="120"/>
+      <c r="BI48" s="119"/>
       <c r="BJ48" s="42"/>
-      <c r="BK48" s="120"/>
+      <c r="BK48" s="119"/>
       <c r="BL48" s="42"/>
-      <c r="BM48" s="120"/>
+      <c r="BM48" s="119"/>
       <c r="BN48" s="42"/>
-      <c r="BO48" s="120"/>
+      <c r="BO48" s="119"/>
       <c r="BP48" s="42"/>
-      <c r="BQ48" s="120"/>
+      <c r="BQ48" s="119"/>
       <c r="BR48" s="42"/>
-      <c r="BS48" s="120"/>
+      <c r="BS48" s="119"/>
       <c r="BT48" s="42"/>
-      <c r="BU48" s="120"/>
+      <c r="BU48" s="119"/>
       <c r="BV48" s="42"/>
       <c r="BW48" s="36"/>
     </row>
     <row r="49" spans="1:75" ht="17.25" customHeight="1">
       <c r="A49" s="36"/>
-      <c r="B49" s="132"/>
+      <c r="B49" s="131"/>
       <c r="C49" s="50"/>
-      <c r="D49" s="132"/>
+      <c r="D49" s="131"/>
       <c r="E49" s="50"/>
-      <c r="F49" s="132"/>
+      <c r="F49" s="131"/>
       <c r="G49" s="50"/>
       <c r="H49" s="36"/>
-      <c r="I49" s="132"/>
+      <c r="I49" s="131"/>
       <c r="J49" s="50"/>
-      <c r="K49" s="132"/>
+      <c r="K49" s="131"/>
       <c r="L49" s="50"/>
-      <c r="M49" s="133" t="s">
+      <c r="M49" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N49" s="53"/>
-      <c r="O49" s="132"/>
+      <c r="O49" s="131"/>
       <c r="P49" s="50"/>
-      <c r="Q49" s="132"/>
+      <c r="Q49" s="131"/>
       <c r="R49" s="50"/>
-      <c r="S49" s="133" t="s">
+      <c r="S49" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T49" s="53"/>
-      <c r="U49" s="132"/>
+      <c r="U49" s="131"/>
       <c r="V49" s="50"/>
-      <c r="W49" s="132"/>
+      <c r="W49" s="131"/>
       <c r="X49" s="50"/>
-      <c r="Y49" s="132"/>
+      <c r="Y49" s="131"/>
       <c r="Z49" s="50"/>
-      <c r="AA49" s="132"/>
+      <c r="AA49" s="131"/>
       <c r="AB49" s="50"/>
       <c r="AC49" s="36"/>
-      <c r="AD49" s="132"/>
+      <c r="AD49" s="131"/>
       <c r="AE49" s="50"/>
-      <c r="AF49" s="132"/>
+      <c r="AF49" s="131"/>
       <c r="AG49" s="50"/>
-      <c r="AH49" s="132"/>
+      <c r="AH49" s="131"/>
       <c r="AI49" s="50"/>
-      <c r="AJ49" s="132"/>
+      <c r="AJ49" s="131"/>
       <c r="AK49" s="50"/>
-      <c r="AL49" s="132"/>
+      <c r="AL49" s="131"/>
       <c r="AM49" s="50"/>
-      <c r="AN49" s="132"/>
+      <c r="AN49" s="131"/>
       <c r="AO49" s="50"/>
-      <c r="AP49" s="132"/>
+      <c r="AP49" s="131"/>
       <c r="AQ49" s="50"/>
-      <c r="AR49" s="132"/>
+      <c r="AR49" s="131"/>
       <c r="AS49" s="50"/>
-      <c r="AT49" s="132"/>
+      <c r="AT49" s="131"/>
       <c r="AU49" s="50"/>
-      <c r="AV49" s="132"/>
+      <c r="AV49" s="131"/>
       <c r="AW49" s="50"/>
-      <c r="AX49" s="132"/>
+      <c r="AX49" s="131"/>
       <c r="AY49" s="50"/>
-      <c r="AZ49" s="132"/>
+      <c r="AZ49" s="131"/>
       <c r="BA49" s="50"/>
       <c r="BB49" s="36"/>
       <c r="BC49" s="36"/>
-      <c r="BD49" s="132"/>
+      <c r="BD49" s="131"/>
       <c r="BE49" s="50"/>
-      <c r="BF49" s="132"/>
+      <c r="BF49" s="131"/>
       <c r="BG49" s="50"/>
-      <c r="BH49" s="132"/>
+      <c r="BH49" s="131"/>
       <c r="BI49" s="50"/>
-      <c r="BJ49" s="132"/>
+      <c r="BJ49" s="131"/>
       <c r="BK49" s="50"/>
-      <c r="BL49" s="132"/>
+      <c r="BL49" s="131"/>
       <c r="BM49" s="50"/>
-      <c r="BN49" s="132"/>
+      <c r="BN49" s="131"/>
       <c r="BO49" s="50"/>
-      <c r="BP49" s="132"/>
+      <c r="BP49" s="131"/>
       <c r="BQ49" s="50"/>
-      <c r="BR49" s="132"/>
+      <c r="BR49" s="131"/>
       <c r="BS49" s="50"/>
-      <c r="BT49" s="132"/>
+      <c r="BT49" s="131"/>
       <c r="BU49" s="50"/>
-      <c r="BV49" s="132"/>
+      <c r="BV49" s="131"/>
       <c r="BW49" s="50"/>
     </row>
     <row r="50" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A50" s="134"/>
+      <c r="A50" s="133"/>
       <c r="B50" s="42"/>
-      <c r="C50" s="134"/>
+      <c r="C50" s="133"/>
       <c r="D50" s="42"/>
-      <c r="E50" s="134"/>
+      <c r="E50" s="133"/>
       <c r="F50" s="42"/>
-      <c r="G50" s="134"/>
+      <c r="G50" s="133"/>
       <c r="H50" s="42"/>
-      <c r="I50" s="134"/>
+      <c r="I50" s="133"/>
       <c r="J50" s="42"/>
-      <c r="K50" s="134"/>
+      <c r="K50" s="133"/>
       <c r="L50" s="42"/>
-      <c r="M50" s="134"/>
+      <c r="M50" s="133"/>
       <c r="N50" s="42"/>
-      <c r="O50" s="134"/>
+      <c r="O50" s="133"/>
       <c r="P50" s="42"/>
-      <c r="Q50" s="134"/>
+      <c r="Q50" s="133"/>
       <c r="R50" s="42"/>
-      <c r="S50" s="134"/>
+      <c r="S50" s="133"/>
       <c r="T50" s="42"/>
-      <c r="U50" s="134"/>
+      <c r="U50" s="133"/>
       <c r="V50" s="42"/>
-      <c r="W50" s="134"/>
+      <c r="W50" s="133"/>
       <c r="X50" s="42"/>
-      <c r="Y50" s="134"/>
+      <c r="Y50" s="133"/>
       <c r="Z50" s="42"/>
-      <c r="AA50" s="134"/>
+      <c r="AA50" s="133"/>
       <c r="AB50" s="42"/>
-      <c r="AC50" s="134"/>
+      <c r="AC50" s="133"/>
       <c r="AD50" s="42"/>
-      <c r="AE50" s="134"/>
+      <c r="AE50" s="133"/>
       <c r="AF50" s="42"/>
-      <c r="AG50" s="134"/>
+      <c r="AG50" s="133"/>
       <c r="AH50" s="42"/>
-      <c r="AI50" s="134"/>
+      <c r="AI50" s="133"/>
       <c r="AJ50" s="42"/>
-      <c r="AK50" s="134"/>
+      <c r="AK50" s="133"/>
       <c r="AL50" s="42"/>
-      <c r="AM50" s="134"/>
+      <c r="AM50" s="133"/>
       <c r="AN50" s="42"/>
-      <c r="AO50" s="134"/>
+      <c r="AO50" s="133"/>
       <c r="AP50" s="42"/>
-      <c r="AQ50" s="134"/>
+      <c r="AQ50" s="133"/>
       <c r="AR50" s="42"/>
-      <c r="AS50" s="134"/>
+      <c r="AS50" s="133"/>
       <c r="AT50" s="42"/>
-      <c r="AU50" s="134"/>
+      <c r="AU50" s="133"/>
       <c r="AV50" s="42"/>
-      <c r="AW50" s="134"/>
+      <c r="AW50" s="133"/>
       <c r="AX50" s="42"/>
-      <c r="AY50" s="134"/>
+      <c r="AY50" s="133"/>
       <c r="AZ50" s="42"/>
-      <c r="BA50" s="134"/>
+      <c r="BA50" s="133"/>
       <c r="BB50" s="42"/>
-      <c r="BC50" s="134"/>
+      <c r="BC50" s="133"/>
       <c r="BD50" s="42"/>
-      <c r="BE50" s="134"/>
+      <c r="BE50" s="133"/>
       <c r="BF50" s="42"/>
-      <c r="BG50" s="134"/>
+      <c r="BG50" s="133"/>
       <c r="BH50" s="42"/>
-      <c r="BI50" s="134"/>
+      <c r="BI50" s="133"/>
       <c r="BJ50" s="42"/>
-      <c r="BK50" s="134"/>
+      <c r="BK50" s="133"/>
       <c r="BL50" s="42"/>
-      <c r="BM50" s="134"/>
+      <c r="BM50" s="133"/>
       <c r="BN50" s="42"/>
-      <c r="BO50" s="134"/>
+      <c r="BO50" s="133"/>
       <c r="BP50" s="42"/>
-      <c r="BQ50" s="134"/>
+      <c r="BQ50" s="133"/>
       <c r="BR50" s="42"/>
-      <c r="BS50" s="134"/>
+      <c r="BS50" s="133"/>
       <c r="BT50" s="42"/>
-      <c r="BU50" s="134"/>
+      <c r="BU50" s="133"/>
       <c r="BV50" s="42"/>
       <c r="BW50" s="39"/>
     </row>
     <row r="51" spans="1:75" ht="17.25" customHeight="1">
       <c r="A51" s="36"/>
-      <c r="B51" s="135"/>
+      <c r="B51" s="134"/>
       <c r="C51" s="42"/>
-      <c r="D51" s="135"/>
+      <c r="D51" s="134"/>
       <c r="E51" s="42"/>
-      <c r="F51" s="135"/>
+      <c r="F51" s="134"/>
       <c r="G51" s="42"/>
       <c r="H51" s="36"/>
-      <c r="I51" s="132"/>
+      <c r="I51" s="131"/>
       <c r="J51" s="50"/>
-      <c r="K51" s="132"/>
+      <c r="K51" s="131"/>
       <c r="L51" s="50"/>
-      <c r="M51" s="133" t="s">
+      <c r="M51" s="132" t="s">
         <v>44</v>
       </c>
       <c r="N51" s="53"/>
-      <c r="O51" s="132"/>
+      <c r="O51" s="131"/>
       <c r="P51" s="50"/>
-      <c r="Q51" s="132"/>
+      <c r="Q51" s="131"/>
       <c r="R51" s="50"/>
-      <c r="S51" s="133" t="s">
+      <c r="S51" s="132" t="s">
         <v>44</v>
       </c>
       <c r="T51" s="53"/>
-      <c r="U51" s="132"/>
+      <c r="U51" s="131"/>
       <c r="V51" s="50"/>
-      <c r="W51" s="132"/>
+      <c r="W51" s="131"/>
       <c r="X51" s="50"/>
-      <c r="Y51" s="132"/>
+      <c r="Y51" s="131"/>
       <c r="Z51" s="50"/>
-      <c r="AA51" s="132"/>
+      <c r="AA51" s="131"/>
       <c r="AB51" s="50"/>
       <c r="AC51" s="36"/>
-      <c r="AD51" s="132"/>
+      <c r="AD51" s="131"/>
       <c r="AE51" s="50"/>
-      <c r="AF51" s="132"/>
+      <c r="AF51" s="131"/>
       <c r="AG51" s="50"/>
-      <c r="AH51" s="132"/>
+      <c r="AH51" s="131"/>
       <c r="AI51" s="50"/>
-      <c r="AJ51" s="132"/>
+      <c r="AJ51" s="131"/>
       <c r="AK51" s="50"/>
-      <c r="AL51" s="132"/>
+      <c r="AL51" s="131"/>
       <c r="AM51" s="50"/>
-      <c r="AN51" s="132"/>
+      <c r="AN51" s="131"/>
       <c r="AO51" s="50"/>
-      <c r="AP51" s="132"/>
+      <c r="AP51" s="131"/>
       <c r="AQ51" s="50"/>
-      <c r="AR51" s="132"/>
+      <c r="AR51" s="131"/>
       <c r="AS51" s="50"/>
-      <c r="AT51" s="132"/>
+      <c r="AT51" s="131"/>
       <c r="AU51" s="50"/>
-      <c r="AV51" s="132"/>
+      <c r="AV51" s="131"/>
       <c r="AW51" s="50"/>
-      <c r="AX51" s="132"/>
+      <c r="AX51" s="131"/>
       <c r="AY51" s="50"/>
-      <c r="AZ51" s="132"/>
+      <c r="AZ51" s="131"/>
       <c r="BA51" s="50"/>
       <c r="BB51" s="36"/>
       <c r="BC51" s="36"/>
-      <c r="BD51" s="132"/>
+      <c r="BD51" s="131"/>
       <c r="BE51" s="50"/>
-      <c r="BF51" s="132"/>
+      <c r="BF51" s="131"/>
       <c r="BG51" s="50"/>
-      <c r="BH51" s="132"/>
+      <c r="BH51" s="131"/>
       <c r="BI51" s="50"/>
-      <c r="BJ51" s="132"/>
+      <c r="BJ51" s="131"/>
       <c r="BK51" s="50"/>
-      <c r="BL51" s="132"/>
+      <c r="BL51" s="131"/>
       <c r="BM51" s="50"/>
-      <c r="BN51" s="132"/>
+      <c r="BN51" s="131"/>
       <c r="BO51" s="50"/>
-      <c r="BP51" s="132"/>
+      <c r="BP51" s="131"/>
       <c r="BQ51" s="50"/>
-      <c r="BR51" s="132"/>
+      <c r="BR51" s="131"/>
       <c r="BS51" s="50"/>
-      <c r="BT51" s="132"/>
+      <c r="BT51" s="131"/>
       <c r="BU51" s="50"/>
-      <c r="BV51" s="132"/>
+      <c r="BV51" s="131"/>
       <c r="BW51" s="50"/>
     </row>
     <row r="52" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A52" s="120"/>
+      <c r="A52" s="119"/>
       <c r="B52" s="42"/>
-      <c r="C52" s="120"/>
+      <c r="C52" s="119"/>
       <c r="D52" s="42"/>
-      <c r="E52" s="120"/>
+      <c r="E52" s="119"/>
       <c r="F52" s="42"/>
-      <c r="G52" s="120"/>
+      <c r="G52" s="119"/>
       <c r="H52" s="42"/>
-      <c r="I52" s="120"/>
+      <c r="I52" s="119"/>
       <c r="J52" s="42"/>
-      <c r="K52" s="120"/>
+      <c r="K52" s="119"/>
       <c r="L52" s="42"/>
-      <c r="M52" s="120"/>
+      <c r="M52" s="119"/>
       <c r="N52" s="42"/>
-      <c r="O52" s="120"/>
+      <c r="O52" s="119"/>
       <c r="P52" s="42"/>
-      <c r="Q52" s="120"/>
+      <c r="Q52" s="119"/>
       <c r="R52" s="42"/>
-      <c r="S52" s="120"/>
+      <c r="S52" s="119"/>
       <c r="T52" s="42"/>
-      <c r="U52" s="120"/>
+      <c r="U52" s="119"/>
       <c r="V52" s="42"/>
-      <c r="W52" s="120"/>
+      <c r="W52" s="119"/>
       <c r="X52" s="42"/>
-      <c r="Y52" s="120"/>
+      <c r="Y52" s="119"/>
       <c r="Z52" s="42"/>
-      <c r="AA52" s="120"/>
+      <c r="AA52" s="119"/>
       <c r="AB52" s="42"/>
-      <c r="AC52" s="120"/>
+      <c r="AC52" s="119"/>
       <c r="AD52" s="42"/>
-      <c r="AE52" s="120"/>
+      <c r="AE52" s="119"/>
       <c r="AF52" s="42"/>
-      <c r="AG52" s="120"/>
+      <c r="AG52" s="119"/>
       <c r="AH52" s="42"/>
-      <c r="AI52" s="120"/>
+      <c r="AI52" s="119"/>
       <c r="AJ52" s="42"/>
-      <c r="AK52" s="120"/>
+      <c r="AK52" s="119"/>
       <c r="AL52" s="42"/>
-      <c r="AM52" s="120"/>
+      <c r="AM52" s="119"/>
       <c r="AN52" s="42"/>
-      <c r="AO52" s="120"/>
+      <c r="AO52" s="119"/>
       <c r="AP52" s="42"/>
-      <c r="AQ52" s="120"/>
+      <c r="AQ52" s="119"/>
       <c r="AR52" s="42"/>
-      <c r="AS52" s="120"/>
+      <c r="AS52" s="119"/>
       <c r="AT52" s="42"/>
-      <c r="AU52" s="120"/>
+      <c r="AU52" s="119"/>
       <c r="AV52" s="42"/>
-      <c r="AW52" s="120"/>
+      <c r="AW52" s="119"/>
       <c r="AX52" s="42"/>
-      <c r="AY52" s="120"/>
+      <c r="AY52" s="119"/>
       <c r="AZ52" s="42"/>
-      <c r="BA52" s="120"/>
+      <c r="BA52" s="119"/>
       <c r="BB52" s="42"/>
-      <c r="BC52" s="120"/>
+      <c r="BC52" s="119"/>
       <c r="BD52" s="42"/>
-      <c r="BE52" s="120"/>
+      <c r="BE52" s="119"/>
       <c r="BF52" s="42"/>
-      <c r="BG52" s="120"/>
+      <c r="BG52" s="119"/>
       <c r="BH52" s="42"/>
-      <c r="BI52" s="120"/>
+      <c r="BI52" s="119"/>
       <c r="BJ52" s="42"/>
-      <c r="BK52" s="120"/>
+      <c r="BK52" s="119"/>
       <c r="BL52" s="42"/>
-      <c r="BM52" s="120"/>
+      <c r="BM52" s="119"/>
       <c r="BN52" s="42"/>
-      <c r="BO52" s="120"/>
+      <c r="BO52" s="119"/>
       <c r="BP52" s="42"/>
-      <c r="BQ52" s="120"/>
+      <c r="BQ52" s="119"/>
       <c r="BR52" s="42"/>
-      <c r="BS52" s="120"/>
+      <c r="BS52" s="119"/>
       <c r="BT52" s="42"/>
-      <c r="BU52" s="120"/>
+      <c r="BU52" s="119"/>
       <c r="BV52" s="42"/>
       <c r="BW52" s="36"/>
     </row>
     <row r="53" spans="1:75" ht="17.25" customHeight="1">
-      <c r="A53" s="150" t="s">
+      <c r="A53" s="149" t="s">
         <v>220</v>
       </c>
       <c r="B53" s="42"/>
@@ -13034,51 +13041,51 @@
       <c r="AA53" s="42"/>
       <c r="AB53" s="42"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="132"/>
+      <c r="AD53" s="131"/>
       <c r="AE53" s="50"/>
-      <c r="AF53" s="132"/>
+      <c r="AF53" s="131"/>
       <c r="AG53" s="50"/>
-      <c r="AH53" s="132"/>
+      <c r="AH53" s="131"/>
       <c r="AI53" s="50"/>
-      <c r="AJ53" s="132"/>
+      <c r="AJ53" s="131"/>
       <c r="AK53" s="50"/>
-      <c r="AL53" s="132"/>
+      <c r="AL53" s="131"/>
       <c r="AM53" s="50"/>
-      <c r="AN53" s="132"/>
+      <c r="AN53" s="131"/>
       <c r="AO53" s="50"/>
-      <c r="AP53" s="132"/>
+      <c r="AP53" s="131"/>
       <c r="AQ53" s="50"/>
-      <c r="AR53" s="132"/>
+      <c r="AR53" s="131"/>
       <c r="AS53" s="50"/>
-      <c r="AT53" s="132"/>
+      <c r="AT53" s="131"/>
       <c r="AU53" s="50"/>
-      <c r="AV53" s="132"/>
+      <c r="AV53" s="131"/>
       <c r="AW53" s="50"/>
-      <c r="AX53" s="132"/>
+      <c r="AX53" s="131"/>
       <c r="AY53" s="50"/>
-      <c r="AZ53" s="132"/>
+      <c r="AZ53" s="131"/>
       <c r="BA53" s="50"/>
       <c r="BB53" s="36"/>
       <c r="BC53" s="36"/>
-      <c r="BD53" s="132"/>
+      <c r="BD53" s="131"/>
       <c r="BE53" s="50"/>
-      <c r="BF53" s="132"/>
+      <c r="BF53" s="131"/>
       <c r="BG53" s="50"/>
-      <c r="BH53" s="132"/>
+      <c r="BH53" s="131"/>
       <c r="BI53" s="50"/>
-      <c r="BJ53" s="132"/>
+      <c r="BJ53" s="131"/>
       <c r="BK53" s="50"/>
-      <c r="BL53" s="132"/>
+      <c r="BL53" s="131"/>
       <c r="BM53" s="50"/>
-      <c r="BN53" s="132"/>
+      <c r="BN53" s="131"/>
       <c r="BO53" s="50"/>
-      <c r="BP53" s="132"/>
+      <c r="BP53" s="131"/>
       <c r="BQ53" s="50"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="131"/>
       <c r="BS53" s="50"/>
-      <c r="BT53" s="132"/>
+      <c r="BT53" s="131"/>
       <c r="BU53" s="50"/>
-      <c r="BV53" s="132"/>
+      <c r="BV53" s="131"/>
       <c r="BW53" s="50"/>
     </row>
     <row r="54" spans="1:75" ht="7.5" customHeight="1">
@@ -13110,51 +13117,51 @@
       <c r="Z54" s="39"/>
       <c r="AA54" s="39"/>
       <c r="AB54" s="39"/>
-      <c r="AC54" s="134"/>
+      <c r="AC54" s="133"/>
       <c r="AD54" s="42"/>
-      <c r="AE54" s="134"/>
+      <c r="AE54" s="133"/>
       <c r="AF54" s="42"/>
-      <c r="AG54" s="134"/>
+      <c r="AG54" s="133"/>
       <c r="AH54" s="42"/>
-      <c r="AI54" s="134"/>
+      <c r="AI54" s="133"/>
       <c r="AJ54" s="42"/>
-      <c r="AK54" s="134"/>
+      <c r="AK54" s="133"/>
       <c r="AL54" s="42"/>
-      <c r="AM54" s="134"/>
+      <c r="AM54" s="133"/>
       <c r="AN54" s="42"/>
-      <c r="AO54" s="134"/>
+      <c r="AO54" s="133"/>
       <c r="AP54" s="42"/>
-      <c r="AQ54" s="134"/>
+      <c r="AQ54" s="133"/>
       <c r="AR54" s="42"/>
-      <c r="AS54" s="134"/>
+      <c r="AS54" s="133"/>
       <c r="AT54" s="42"/>
-      <c r="AU54" s="134"/>
+      <c r="AU54" s="133"/>
       <c r="AV54" s="42"/>
-      <c r="AW54" s="134"/>
+      <c r="AW54" s="133"/>
       <c r="AX54" s="42"/>
-      <c r="AY54" s="134"/>
+      <c r="AY54" s="133"/>
       <c r="AZ54" s="42"/>
-      <c r="BA54" s="134"/>
+      <c r="BA54" s="133"/>
       <c r="BB54" s="42"/>
-      <c r="BC54" s="134"/>
+      <c r="BC54" s="133"/>
       <c r="BD54" s="42"/>
-      <c r="BE54" s="134"/>
+      <c r="BE54" s="133"/>
       <c r="BF54" s="42"/>
-      <c r="BG54" s="134"/>
+      <c r="BG54" s="133"/>
       <c r="BH54" s="42"/>
-      <c r="BI54" s="134"/>
+      <c r="BI54" s="133"/>
       <c r="BJ54" s="42"/>
-      <c r="BK54" s="134"/>
+      <c r="BK54" s="133"/>
       <c r="BL54" s="42"/>
-      <c r="BM54" s="134"/>
+      <c r="BM54" s="133"/>
       <c r="BN54" s="42"/>
-      <c r="BO54" s="134"/>
+      <c r="BO54" s="133"/>
       <c r="BP54" s="42"/>
-      <c r="BQ54" s="134"/>
+      <c r="BQ54" s="133"/>
       <c r="BR54" s="42"/>
-      <c r="BS54" s="134"/>
+      <c r="BS54" s="133"/>
       <c r="BT54" s="42"/>
-      <c r="BU54" s="134"/>
+      <c r="BU54" s="133"/>
       <c r="BV54" s="42"/>
       <c r="BW54" s="39"/>
     </row>
@@ -13188,55 +13195,55 @@
       <c r="AA55" s="40"/>
       <c r="AB55" s="40"/>
       <c r="AC55" s="36"/>
-      <c r="AD55" s="132"/>
+      <c r="AD55" s="131"/>
       <c r="AE55" s="50"/>
-      <c r="AF55" s="132"/>
+      <c r="AF55" s="131"/>
       <c r="AG55" s="50"/>
-      <c r="AH55" s="132"/>
+      <c r="AH55" s="131"/>
       <c r="AI55" s="50"/>
-      <c r="AJ55" s="132"/>
+      <c r="AJ55" s="131"/>
       <c r="AK55" s="50"/>
-      <c r="AL55" s="132"/>
+      <c r="AL55" s="131"/>
       <c r="AM55" s="50"/>
-      <c r="AN55" s="132"/>
+      <c r="AN55" s="131"/>
       <c r="AO55" s="50"/>
-      <c r="AP55" s="132"/>
+      <c r="AP55" s="131"/>
       <c r="AQ55" s="50"/>
-      <c r="AR55" s="132"/>
+      <c r="AR55" s="131"/>
       <c r="AS55" s="50"/>
-      <c r="AT55" s="132"/>
+      <c r="AT55" s="131"/>
       <c r="AU55" s="50"/>
-      <c r="AV55" s="132"/>
+      <c r="AV55" s="131"/>
       <c r="AW55" s="50"/>
-      <c r="AX55" s="132"/>
+      <c r="AX55" s="131"/>
       <c r="AY55" s="50"/>
-      <c r="AZ55" s="132"/>
+      <c r="AZ55" s="131"/>
       <c r="BA55" s="50"/>
       <c r="BB55" s="36"/>
       <c r="BC55" s="36"/>
-      <c r="BD55" s="132"/>
+      <c r="BD55" s="131"/>
       <c r="BE55" s="50"/>
-      <c r="BF55" s="132"/>
+      <c r="BF55" s="131"/>
       <c r="BG55" s="50"/>
-      <c r="BH55" s="132"/>
+      <c r="BH55" s="131"/>
       <c r="BI55" s="50"/>
-      <c r="BJ55" s="132"/>
+      <c r="BJ55" s="131"/>
       <c r="BK55" s="50"/>
-      <c r="BL55" s="132"/>
+      <c r="BL55" s="131"/>
       <c r="BM55" s="50"/>
-      <c r="BN55" s="132"/>
+      <c r="BN55" s="131"/>
       <c r="BO55" s="50"/>
-      <c r="BP55" s="132"/>
+      <c r="BP55" s="131"/>
       <c r="BQ55" s="50"/>
-      <c r="BR55" s="132"/>
+      <c r="BR55" s="131"/>
       <c r="BS55" s="50"/>
-      <c r="BT55" s="132"/>
+      <c r="BT55" s="131"/>
       <c r="BU55" s="50"/>
-      <c r="BV55" s="132"/>
+      <c r="BV55" s="131"/>
       <c r="BW55" s="50"/>
     </row>
     <row r="56" spans="1:75" ht="45" customHeight="1">
-      <c r="A56" s="151" t="s">
+      <c r="A56" s="150" t="s">
         <v>221</v>
       </c>
       <c r="B56" s="42"/>
@@ -13931,7 +13938,7 @@
       <c r="BW64" s="33"/>
     </row>
     <row r="65" spans="1:75" ht="14.25" customHeight="1">
-      <c r="A65" s="142"/>
+      <c r="A65" s="141"/>
       <c r="B65" s="75"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
@@ -14085,7 +14092,7 @@
       <c r="BW66" s="21"/>
     </row>
     <row r="67" spans="1:75" ht="16.5" customHeight="1">
-      <c r="A67" s="131"/>
+      <c r="A67" s="130"/>
       <c r="B67" s="42"/>
       <c r="C67" s="42"/>
       <c r="D67" s="42"/>
@@ -15795,7 +15802,7 @@
   <sheetData>
     <row r="1" spans="1:41" ht="12.75">
       <c r="A1" s="17"/>
-      <c r="B1" s="108"/>
+      <c r="B1" s="107"/>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
@@ -15849,11 +15856,11 @@
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="X1" s="116" t="str">
+      <c r="X1" s="115" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="Y1" s="116" t="str">
+      <c r="Y1" s="115" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
@@ -16121,7 +16128,7 @@
       <c r="AO6" s="42"/>
     </row>
     <row r="7" spans="1:41" ht="31.5" customHeight="1">
-      <c r="A7" s="152" t="s">
+      <c r="A7" s="151" t="s">
         <v>222</v>
       </c>
       <c r="B7" s="42"/>
@@ -18548,7 +18555,7 @@
       <c r="AO61" s="3"/>
     </row>
     <row r="62" spans="1:41" ht="16.5" customHeight="1">
-      <c r="A62" s="131"/>
+      <c r="A62" s="130"/>
       <c r="B62" s="42"/>
       <c r="C62" s="42"/>
       <c r="D62" s="42"/>
@@ -19388,18 +19395,18 @@
         <v>56</v>
       </c>
       <c r="Y15" s="53"/>
-      <c r="Z15" s="153"/>
-      <c r="AA15" s="153"/>
-      <c r="AB15" s="153"/>
-      <c r="AC15" s="153"/>
-      <c r="AD15" s="153"/>
-      <c r="AE15" s="153"/>
-      <c r="AF15" s="153"/>
-      <c r="AG15" s="153"/>
-      <c r="AH15" s="153"/>
-      <c r="AI15" s="153"/>
-      <c r="AJ15" s="153"/>
-      <c r="AK15" s="153"/>
+      <c r="Z15" s="152"/>
+      <c r="AA15" s="152"/>
+      <c r="AB15" s="152"/>
+      <c r="AC15" s="152"/>
+      <c r="AD15" s="152"/>
+      <c r="AE15" s="152"/>
+      <c r="AF15" s="152"/>
+      <c r="AG15" s="152"/>
+      <c r="AH15" s="152"/>
+      <c r="AI15" s="152"/>
+      <c r="AJ15" s="152"/>
+      <c r="AK15" s="152"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
@@ -19518,17 +19525,17 @@
         <v>57</v>
       </c>
       <c r="Y18" s="53"/>
-      <c r="Z18" s="153"/>
-      <c r="AA18" s="153"/>
-      <c r="AB18" s="153"/>
-      <c r="AC18" s="153"/>
-      <c r="AD18" s="153"/>
-      <c r="AE18" s="153"/>
-      <c r="AF18" s="153"/>
-      <c r="AG18" s="153"/>
-      <c r="AH18" s="153"/>
-      <c r="AI18" s="153"/>
-      <c r="AJ18" s="153"/>
+      <c r="Z18" s="152"/>
+      <c r="AA18" s="152"/>
+      <c r="AB18" s="152"/>
+      <c r="AC18" s="152"/>
+      <c r="AD18" s="152"/>
+      <c r="AE18" s="152"/>
+      <c r="AF18" s="152"/>
+      <c r="AG18" s="152"/>
+      <c r="AH18" s="152"/>
+      <c r="AI18" s="152"/>
+      <c r="AJ18" s="152"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
@@ -19606,18 +19613,18 @@
         <v>59</v>
       </c>
       <c r="Y20" s="53"/>
-      <c r="Z20" s="153"/>
-      <c r="AA20" s="153"/>
-      <c r="AB20" s="153"/>
-      <c r="AC20" s="153"/>
-      <c r="AD20" s="153"/>
-      <c r="AE20" s="153"/>
-      <c r="AF20" s="153"/>
-      <c r="AG20" s="153"/>
-      <c r="AH20" s="153"/>
-      <c r="AI20" s="153"/>
-      <c r="AJ20" s="153"/>
-      <c r="AK20" s="153"/>
+      <c r="Z20" s="152"/>
+      <c r="AA20" s="152"/>
+      <c r="AB20" s="152"/>
+      <c r="AC20" s="152"/>
+      <c r="AD20" s="152"/>
+      <c r="AE20" s="152"/>
+      <c r="AF20" s="152"/>
+      <c r="AG20" s="152"/>
+      <c r="AH20" s="152"/>
+      <c r="AI20" s="152"/>
+      <c r="AJ20" s="152"/>
+      <c r="AK20" s="152"/>
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
@@ -19736,18 +19743,18 @@
         <v>61</v>
       </c>
       <c r="Y23" s="53"/>
-      <c r="Z23" s="153"/>
-      <c r="AA23" s="153"/>
-      <c r="AB23" s="153"/>
-      <c r="AC23" s="153"/>
-      <c r="AD23" s="153"/>
-      <c r="AE23" s="153"/>
-      <c r="AF23" s="153"/>
-      <c r="AG23" s="153"/>
-      <c r="AH23" s="153"/>
-      <c r="AI23" s="153"/>
-      <c r="AJ23" s="153"/>
-      <c r="AK23" s="153"/>
+      <c r="Z23" s="152"/>
+      <c r="AA23" s="152"/>
+      <c r="AB23" s="152"/>
+      <c r="AC23" s="152"/>
+      <c r="AD23" s="152"/>
+      <c r="AE23" s="152"/>
+      <c r="AF23" s="152"/>
+      <c r="AG23" s="152"/>
+      <c r="AH23" s="152"/>
+      <c r="AI23" s="152"/>
+      <c r="AJ23" s="152"/>
+      <c r="AK23" s="152"/>
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
@@ -19866,17 +19873,17 @@
         <v>62</v>
       </c>
       <c r="Y26" s="53"/>
-      <c r="Z26" s="153"/>
-      <c r="AA26" s="153"/>
-      <c r="AB26" s="153"/>
-      <c r="AC26" s="153"/>
-      <c r="AD26" s="153"/>
-      <c r="AE26" s="153"/>
-      <c r="AF26" s="153"/>
-      <c r="AG26" s="153"/>
-      <c r="AH26" s="153"/>
-      <c r="AI26" s="153"/>
-      <c r="AJ26" s="153"/>
+      <c r="Z26" s="152"/>
+      <c r="AA26" s="152"/>
+      <c r="AB26" s="152"/>
+      <c r="AC26" s="152"/>
+      <c r="AD26" s="152"/>
+      <c r="AE26" s="152"/>
+      <c r="AF26" s="152"/>
+      <c r="AG26" s="152"/>
+      <c r="AH26" s="152"/>
+      <c r="AI26" s="152"/>
+      <c r="AJ26" s="152"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
@@ -19954,18 +19961,18 @@
         <v>64</v>
       </c>
       <c r="Y28" s="53"/>
-      <c r="Z28" s="153"/>
-      <c r="AA28" s="153"/>
-      <c r="AB28" s="153"/>
-      <c r="AC28" s="153"/>
-      <c r="AD28" s="153"/>
-      <c r="AE28" s="153"/>
-      <c r="AF28" s="153"/>
-      <c r="AG28" s="153"/>
-      <c r="AH28" s="153"/>
-      <c r="AI28" s="153"/>
-      <c r="AJ28" s="153"/>
-      <c r="AK28" s="153"/>
+      <c r="Z28" s="152"/>
+      <c r="AA28" s="152"/>
+      <c r="AB28" s="152"/>
+      <c r="AC28" s="152"/>
+      <c r="AD28" s="152"/>
+      <c r="AE28" s="152"/>
+      <c r="AF28" s="152"/>
+      <c r="AG28" s="152"/>
+      <c r="AH28" s="152"/>
+      <c r="AI28" s="152"/>
+      <c r="AJ28" s="152"/>
+      <c r="AK28" s="152"/>
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
       <c r="AN28" s="3"/>
@@ -20084,18 +20091,18 @@
         <v>66</v>
       </c>
       <c r="Y31" s="53"/>
-      <c r="Z31" s="153"/>
-      <c r="AA31" s="153"/>
-      <c r="AB31" s="153"/>
-      <c r="AC31" s="153"/>
-      <c r="AD31" s="153"/>
-      <c r="AE31" s="153"/>
-      <c r="AF31" s="153"/>
-      <c r="AG31" s="153"/>
-      <c r="AH31" s="153"/>
-      <c r="AI31" s="153"/>
-      <c r="AJ31" s="153"/>
-      <c r="AK31" s="153"/>
+      <c r="Z31" s="152"/>
+      <c r="AA31" s="152"/>
+      <c r="AB31" s="152"/>
+      <c r="AC31" s="152"/>
+      <c r="AD31" s="152"/>
+      <c r="AE31" s="152"/>
+      <c r="AF31" s="152"/>
+      <c r="AG31" s="152"/>
+      <c r="AH31" s="152"/>
+      <c r="AI31" s="152"/>
+      <c r="AJ31" s="152"/>
+      <c r="AK31" s="152"/>
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
@@ -20214,17 +20221,17 @@
         <v>67</v>
       </c>
       <c r="Y34" s="53"/>
-      <c r="Z34" s="153"/>
-      <c r="AA34" s="153"/>
-      <c r="AB34" s="153"/>
-      <c r="AC34" s="153"/>
-      <c r="AD34" s="153"/>
-      <c r="AE34" s="153"/>
-      <c r="AF34" s="153"/>
-      <c r="AG34" s="153"/>
-      <c r="AH34" s="153"/>
-      <c r="AI34" s="153"/>
-      <c r="AJ34" s="153"/>
+      <c r="Z34" s="152"/>
+      <c r="AA34" s="152"/>
+      <c r="AB34" s="152"/>
+      <c r="AC34" s="152"/>
+      <c r="AD34" s="152"/>
+      <c r="AE34" s="152"/>
+      <c r="AF34" s="152"/>
+      <c r="AG34" s="152"/>
+      <c r="AH34" s="152"/>
+      <c r="AI34" s="152"/>
+      <c r="AJ34" s="152"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
@@ -20302,18 +20309,18 @@
         <v>69</v>
       </c>
       <c r="Y36" s="53"/>
-      <c r="Z36" s="153"/>
-      <c r="AA36" s="153"/>
-      <c r="AB36" s="153"/>
-      <c r="AC36" s="153"/>
-      <c r="AD36" s="153"/>
-      <c r="AE36" s="153"/>
-      <c r="AF36" s="153"/>
-      <c r="AG36" s="153"/>
-      <c r="AH36" s="153"/>
-      <c r="AI36" s="153"/>
-      <c r="AJ36" s="153"/>
-      <c r="AK36" s="153"/>
+      <c r="Z36" s="152"/>
+      <c r="AA36" s="152"/>
+      <c r="AB36" s="152"/>
+      <c r="AC36" s="152"/>
+      <c r="AD36" s="152"/>
+      <c r="AE36" s="152"/>
+      <c r="AF36" s="152"/>
+      <c r="AG36" s="152"/>
+      <c r="AH36" s="152"/>
+      <c r="AI36" s="152"/>
+      <c r="AJ36" s="152"/>
+      <c r="AK36" s="152"/>
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
@@ -20432,18 +20439,18 @@
         <v>71</v>
       </c>
       <c r="Y39" s="53"/>
-      <c r="Z39" s="153"/>
-      <c r="AA39" s="153"/>
-      <c r="AB39" s="153"/>
-      <c r="AC39" s="153"/>
-      <c r="AD39" s="153"/>
-      <c r="AE39" s="153"/>
-      <c r="AF39" s="153"/>
-      <c r="AG39" s="153"/>
-      <c r="AH39" s="153"/>
-      <c r="AI39" s="153"/>
-      <c r="AJ39" s="153"/>
-      <c r="AK39" s="153"/>
+      <c r="Z39" s="152"/>
+      <c r="AA39" s="152"/>
+      <c r="AB39" s="152"/>
+      <c r="AC39" s="152"/>
+      <c r="AD39" s="152"/>
+      <c r="AE39" s="152"/>
+      <c r="AF39" s="152"/>
+      <c r="AG39" s="152"/>
+      <c r="AH39" s="152"/>
+      <c r="AI39" s="152"/>
+      <c r="AJ39" s="152"/>
+      <c r="AK39" s="152"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
@@ -20520,18 +20527,18 @@
         <v>73</v>
       </c>
       <c r="Y41" s="53"/>
-      <c r="Z41" s="153"/>
-      <c r="AA41" s="153"/>
-      <c r="AB41" s="153"/>
-      <c r="AC41" s="153"/>
-      <c r="AD41" s="153"/>
-      <c r="AE41" s="153"/>
-      <c r="AF41" s="153"/>
-      <c r="AG41" s="153"/>
-      <c r="AH41" s="153"/>
-      <c r="AI41" s="153"/>
-      <c r="AJ41" s="153"/>
-      <c r="AK41" s="153"/>
+      <c r="Z41" s="152"/>
+      <c r="AA41" s="152"/>
+      <c r="AB41" s="152"/>
+      <c r="AC41" s="152"/>
+      <c r="AD41" s="152"/>
+      <c r="AE41" s="152"/>
+      <c r="AF41" s="152"/>
+      <c r="AG41" s="152"/>
+      <c r="AH41" s="152"/>
+      <c r="AI41" s="152"/>
+      <c r="AJ41" s="152"/>
+      <c r="AK41" s="152"/>
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
@@ -21067,7 +21074,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="12.75">
       <c r="A1" s="14"/>
-      <c r="B1" s="108"/>
+      <c r="B1" s="107"/>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
@@ -21120,11 +21127,11 @@
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="W1" s="107" t="str">
+      <c r="W1" s="153" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="X1" s="107" t="str">
+      <c r="X1" s="153" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
@@ -21167,9 +21174,9 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
       <c r="Y2" s="106"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
@@ -21429,7 +21436,7 @@
       <c r="AN7" s="42"/>
     </row>
     <row r="8" spans="1:40" ht="42" customHeight="1">
-      <c r="A8" s="109" t="s">
+      <c r="A8" s="108" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="42"/>
@@ -21564,7 +21571,7 @@
     </row>
     <row r="11" spans="1:40" ht="15" customHeight="1">
       <c r="A11" s="3"/>
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="109" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="42"/>
@@ -21587,13 +21594,13 @@
       <c r="T11" s="42"/>
       <c r="U11" s="42"/>
       <c r="V11" s="42"/>
-      <c r="W11" s="110" t="s">
+      <c r="W11" s="109" t="s">
         <v>2</v>
       </c>
       <c r="X11" s="42"/>
       <c r="Y11" s="42"/>
       <c r="Z11" s="42"/>
-      <c r="AA11" s="110" t="s">
+      <c r="AA11" s="109" t="s">
         <v>3</v>
       </c>
       <c r="AB11" s="42"/>
@@ -23562,11 +23569,11 @@
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="X1" s="154" t="str">
+      <c r="X1" s="155" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="Y1" s="154" t="str">
+      <c r="Y1" s="155" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
@@ -23610,9 +23617,9 @@
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
       <c r="V2" s="100"/>
-      <c r="W2" s="155"/>
-      <c r="X2" s="155"/>
-      <c r="Y2" s="155"/>
+      <c r="W2" s="156"/>
+      <c r="X2" s="156"/>
+      <c r="Y2" s="156"/>
       <c r="Z2" s="98"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -23840,7 +23847,7 @@
       <c r="AO6" s="42"/>
     </row>
     <row r="7" spans="1:41" ht="31.5" customHeight="1">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="108" t="s">
         <v>88</v>
       </c>
       <c r="B7" s="42"/>
@@ -23983,7 +23990,7 @@
       <c r="AO9" s="42"/>
     </row>
     <row r="10" spans="1:41" ht="17.25" customHeight="1">
-      <c r="A10" s="112" t="s">
+      <c r="A10" s="111" t="s">
         <v>89</v>
       </c>
       <c r="B10" s="42"/>
@@ -24169,7 +24176,7 @@
       <c r="AO13" s="3"/>
     </row>
     <row r="14" spans="1:41" ht="28.5" customHeight="1">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="110" t="s">
         <v>95</v>
       </c>
       <c r="B14" s="42"/>
@@ -24531,7 +24538,7 @@
       <c r="AO21" s="3"/>
     </row>
     <row r="22" spans="1:41" ht="20.25" customHeight="1">
-      <c r="A22" s="112" t="s">
+      <c r="A22" s="111" t="s">
         <v>103</v>
       </c>
       <c r="B22" s="42"/>
@@ -24576,7 +24583,7 @@
       <c r="AO22" s="3"/>
     </row>
     <row r="23" spans="1:41" ht="21">
-      <c r="A23" s="113" t="s">
+      <c r="A23" s="112" t="s">
         <v>96</v>
       </c>
       <c r="B23" s="42"/>
@@ -24672,7 +24679,7 @@
       <c r="AO24" s="3"/>
     </row>
     <row r="25" spans="1:41" ht="21">
-      <c r="A25" s="113" t="s">
+      <c r="A25" s="112" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="42"/>
@@ -24768,7 +24775,7 @@
       <c r="AO26" s="3"/>
     </row>
     <row r="27" spans="1:41" ht="21">
-      <c r="A27" s="113" t="s">
+      <c r="A27" s="112" t="s">
         <v>99</v>
       </c>
       <c r="B27" s="42"/>
@@ -24864,7 +24871,7 @@
       <c r="AO28" s="3"/>
     </row>
     <row r="29" spans="1:41" ht="21">
-      <c r="A29" s="113" t="s">
+      <c r="A29" s="112" t="s">
         <v>101</v>
       </c>
       <c r="B29" s="42"/>
@@ -25052,7 +25059,7 @@
       <c r="AO32" s="3"/>
     </row>
     <row r="33" spans="1:41" ht="12.75">
-      <c r="A33" s="111" t="s">
+      <c r="A33" s="110" t="s">
         <v>109</v>
       </c>
       <c r="B33" s="42"/>
@@ -25715,7 +25722,7 @@
       <c r="AO47" s="3"/>
     </row>
     <row r="48" spans="1:41" ht="1.5" customHeight="1">
-      <c r="A48" s="115" t="s">
+      <c r="A48" s="114" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="42"/>
@@ -25762,7 +25769,7 @@
     <row r="49" spans="1:41" ht="6" customHeight="1">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
-      <c r="C49" s="114"/>
+      <c r="C49" s="113"/>
       <c r="D49" s="42"/>
       <c r="E49" s="42"/>
       <c r="F49" s="42"/>
@@ -25804,7 +25811,7 @@
     </row>
     <row r="50" spans="1:41" ht="14.25" customHeight="1">
       <c r="A50" s="22"/>
-      <c r="B50" s="114"/>
+      <c r="B50" s="113"/>
       <c r="C50" s="42"/>
       <c r="D50" s="42"/>
       <c r="E50" s="42"/>
@@ -26047,11 +26054,11 @@
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="W1" s="154" t="str">
+      <c r="W1" s="155" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="X1" s="154" t="str">
+      <c r="X1" s="155" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
@@ -26094,9 +26101,9 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="155"/>
-      <c r="W2" s="155"/>
-      <c r="X2" s="155"/>
+      <c r="V2" s="156"/>
+      <c r="W2" s="156"/>
+      <c r="X2" s="156"/>
       <c r="Y2" s="98"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
@@ -26404,7 +26411,7 @@
       <c r="AN8" s="3"/>
     </row>
     <row r="9" spans="1:40" ht="12.75">
-      <c r="A9" s="117" t="s">
+      <c r="A9" s="116" t="s">
         <v>118</v>
       </c>
       <c r="B9" s="42"/>
@@ -27136,7 +27143,7 @@
       <c r="AN25" s="3"/>
     </row>
     <row r="26" spans="1:40" ht="12.75">
-      <c r="A26" s="111" t="s">
+      <c r="A26" s="110" t="s">
         <v>127</v>
       </c>
       <c r="B26" s="42"/>
@@ -30256,7 +30263,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="14.25" customHeight="1">
       <c r="A1" s="26"/>
-      <c r="B1" s="126"/>
+      <c r="B1" s="125"/>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
@@ -30264,60 +30271,60 @@
       <c r="G1" s="42"/>
       <c r="H1" s="42"/>
       <c r="I1" s="23"/>
-      <c r="J1" s="125" t="s">
+      <c r="J1" s="124" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="42"/>
       <c r="L1" s="53"/>
-      <c r="M1" s="127" t="str">
+      <c r="M1" s="126" t="str">
         <f>IF(Титул!Y1="","",Титул!Y1)</f>
         <v>1</v>
       </c>
-      <c r="N1" s="127" t="str">
+      <c r="N1" s="126" t="str">
         <f>IF(Титул!AA1="","",Титул!AA1)</f>
         <v>2</v>
       </c>
-      <c r="O1" s="127" t="str">
+      <c r="O1" s="126" t="str">
         <f>IF(Титул!AC1="","",Титул!AC1)</f>
         <v>3</v>
       </c>
-      <c r="P1" s="127" t="str">
+      <c r="P1" s="126" t="str">
         <f>IF(Титул!AE1="","",Титул!AE1)</f>
         <v>4</v>
       </c>
-      <c r="Q1" s="127" t="str">
+      <c r="Q1" s="126" t="str">
         <f>IF(Титул!AG1="","",Титул!AG1)</f>
         <v>5</v>
       </c>
-      <c r="R1" s="127" t="str">
+      <c r="R1" s="126" t="str">
         <f>IF(Титул!AI1="","",Титул!AI1)</f>
         <v>6</v>
       </c>
-      <c r="S1" s="127" t="str">
+      <c r="S1" s="126" t="str">
         <f>IF(Титул!AK1="","",Титул!AK1)</f>
         <v>7</v>
       </c>
-      <c r="T1" s="127" t="str">
+      <c r="T1" s="126" t="str">
         <f>IF(Титул!AM1="","",Титул!AM1)</f>
         <v>8</v>
       </c>
-      <c r="U1" s="127" t="str">
+      <c r="U1" s="126" t="str">
         <f>IF(Титул!AO1="","",Титул!AO1)</f>
         <v>9</v>
       </c>
-      <c r="V1" s="127" t="str">
+      <c r="V1" s="126" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="W1" s="124" t="str">
+      <c r="W1" s="123" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="X1" s="124" t="str">
+      <c r="X1" s="123" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
-      <c r="Y1" s="122"/>
+      <c r="Y1" s="121"/>
       <c r="Z1" s="42"/>
       <c r="AA1" s="42"/>
       <c r="AB1" s="42"/>
@@ -30359,7 +30366,7 @@
       <c r="V2" s="100"/>
       <c r="W2" s="100"/>
       <c r="X2" s="100"/>
-      <c r="Y2" s="122"/>
+      <c r="Y2" s="121"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -30386,7 +30393,7 @@
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="21"/>
-      <c r="J3" s="114"/>
+      <c r="J3" s="113"/>
       <c r="K3" s="42"/>
       <c r="L3" s="42"/>
       <c r="M3" s="21"/>
@@ -30401,7 +30408,7 @@
       <c r="V3" s="21"/>
       <c r="W3" s="21"/>
       <c r="X3" s="21"/>
-      <c r="Y3" s="114"/>
+      <c r="Y3" s="113"/>
       <c r="Z3" s="42"/>
       <c r="AA3" s="42"/>
       <c r="AB3" s="42"/>
@@ -30428,7 +30435,7 @@
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="21"/>
-      <c r="J4" s="125" t="s">
+      <c r="J4" s="124" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="42"/>
@@ -30469,14 +30476,14 @@
         <f>IF(Титул!AO4="","",Титул!AO4)</f>
         <v/>
       </c>
-      <c r="V4" s="125" t="s">
+      <c r="V4" s="124" t="s">
         <v>12</v>
       </c>
       <c r="W4" s="53"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="29"/>
       <c r="Z4" s="29"/>
-      <c r="AA4" s="123"/>
+      <c r="AA4" s="122"/>
       <c r="AB4" s="42"/>
       <c r="AC4" s="42"/>
       <c r="AD4" s="42"/>
@@ -30501,7 +30508,7 @@
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
       <c r="I5" s="21"/>
-      <c r="J5" s="114"/>
+      <c r="J5" s="113"/>
       <c r="K5" s="42"/>
       <c r="L5" s="42"/>
       <c r="M5" s="31"/>
@@ -30543,7 +30550,7 @@
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
       <c r="I6" s="21"/>
-      <c r="J6" s="114"/>
+      <c r="J6" s="113"/>
       <c r="K6" s="42"/>
       <c r="L6" s="42"/>
       <c r="M6" s="31"/>
@@ -30555,12 +30562,12 @@
       <c r="S6" s="31"/>
       <c r="T6" s="31"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="114"/>
+      <c r="V6" s="113"/>
       <c r="W6" s="42"/>
       <c r="X6" s="42"/>
       <c r="Y6" s="42"/>
       <c r="Z6" s="42"/>
-      <c r="AA6" s="114"/>
+      <c r="AA6" s="113"/>
       <c r="AB6" s="42"/>
       <c r="AC6" s="42"/>
       <c r="AD6" s="42"/>
@@ -30576,7 +30583,7 @@
       <c r="AN6" s="42"/>
     </row>
     <row r="7" spans="1:40" ht="6" customHeight="1">
-      <c r="A7" s="126"/>
+      <c r="A7" s="125"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -30618,7 +30625,7 @@
       <c r="AN7" s="42"/>
     </row>
     <row r="8" spans="1:40" ht="42" customHeight="1">
-      <c r="A8" s="128" t="s">
+      <c r="A8" s="127" t="s">
         <v>137</v>
       </c>
       <c r="B8" s="42"/>
@@ -30663,7 +30670,7 @@
     </row>
     <row r="9" spans="1:40" ht="15" customHeight="1">
       <c r="A9" s="32"/>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="128" t="s">
         <v>50</v>
       </c>
       <c r="C9" s="42"/>
@@ -30688,13 +30695,13 @@
       <c r="V9" s="33"/>
       <c r="W9" s="33"/>
       <c r="X9" s="32"/>
-      <c r="Y9" s="129" t="s">
+      <c r="Y9" s="128" t="s">
         <v>51</v>
       </c>
       <c r="Z9" s="42"/>
       <c r="AA9" s="42"/>
       <c r="AB9" s="42"/>
-      <c r="AC9" s="129" t="s">
+      <c r="AC9" s="128" t="s">
         <v>52</v>
       </c>
       <c r="AD9" s="42"/>
@@ -30711,7 +30718,7 @@
     </row>
     <row r="10" spans="1:40" ht="11.25" customHeight="1">
       <c r="A10" s="32"/>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="109" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="42"/>
@@ -30736,13 +30743,13 @@
       <c r="V10" s="21"/>
       <c r="W10" s="21"/>
       <c r="X10" s="21"/>
-      <c r="Y10" s="110" t="s">
+      <c r="Y10" s="109" t="s">
         <v>2</v>
       </c>
       <c r="Z10" s="42"/>
       <c r="AA10" s="42"/>
       <c r="AB10" s="42"/>
-      <c r="AC10" s="110" t="s">
+      <c r="AC10" s="109" t="s">
         <v>3</v>
       </c>
       <c r="AD10" s="42"/>
@@ -30758,7 +30765,7 @@
       <c r="AN10" s="42"/>
     </row>
     <row r="11" spans="1:40" ht="27" customHeight="1">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="117" t="s">
         <v>95</v>
       </c>
       <c r="B11" s="42"/>
@@ -30844,7 +30851,7 @@
       <c r="AN12" s="21"/>
     </row>
     <row r="13" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A13" s="119" t="s">
+      <c r="A13" s="118" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="42"/>
@@ -30871,7 +30878,7 @@
       <c r="W13" s="21"/>
       <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
-      <c r="Z13" s="120" t="s">
+      <c r="Z13" s="119" t="s">
         <v>73</v>
       </c>
       <c r="AA13" s="53"/>
@@ -30920,7 +30927,7 @@
       <c r="AB14" s="35"/>
       <c r="AC14" s="35"/>
       <c r="AD14" s="35"/>
-      <c r="AE14" s="120"/>
+      <c r="AE14" s="119"/>
       <c r="AF14" s="42"/>
       <c r="AG14" s="34"/>
       <c r="AH14" s="34"/>
@@ -30932,7 +30939,7 @@
       <c r="AN14" s="34"/>
     </row>
     <row r="15" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A15" s="119" t="s">
+      <c r="A15" s="118" t="s">
         <v>97</v>
       </c>
       <c r="B15" s="42"/>
@@ -30959,7 +30966,7 @@
       <c r="W15" s="21"/>
       <c r="X15" s="21"/>
       <c r="Y15" s="21"/>
-      <c r="Z15" s="120" t="s">
+      <c r="Z15" s="119" t="s">
         <v>98</v>
       </c>
       <c r="AA15" s="53"/>
@@ -31008,7 +31015,7 @@
       <c r="AB16" s="35"/>
       <c r="AC16" s="35"/>
       <c r="AD16" s="35"/>
-      <c r="AE16" s="120"/>
+      <c r="AE16" s="119"/>
       <c r="AF16" s="42"/>
       <c r="AG16" s="34"/>
       <c r="AH16" s="34"/>
@@ -31020,7 +31027,7 @@
       <c r="AN16" s="34"/>
     </row>
     <row r="17" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A17" s="119" t="s">
+      <c r="A17" s="118" t="s">
         <v>99</v>
       </c>
       <c r="B17" s="42"/>
@@ -31047,7 +31054,7 @@
       <c r="W17" s="21"/>
       <c r="X17" s="21"/>
       <c r="Y17" s="21"/>
-      <c r="Z17" s="120" t="s">
+      <c r="Z17" s="119" t="s">
         <v>100</v>
       </c>
       <c r="AA17" s="53"/>
@@ -31096,7 +31103,7 @@
       <c r="AB18" s="35"/>
       <c r="AC18" s="35"/>
       <c r="AD18" s="35"/>
-      <c r="AE18" s="120"/>
+      <c r="AE18" s="119"/>
       <c r="AF18" s="42"/>
       <c r="AG18" s="34"/>
       <c r="AH18" s="34"/>
@@ -31108,7 +31115,7 @@
       <c r="AN18" s="34"/>
     </row>
     <row r="19" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A19" s="119" t="s">
+      <c r="A19" s="118" t="s">
         <v>101</v>
       </c>
       <c r="B19" s="42"/>
@@ -31135,7 +31142,7 @@
       <c r="W19" s="21"/>
       <c r="X19" s="21"/>
       <c r="Y19" s="21"/>
-      <c r="Z19" s="120" t="s">
+      <c r="Z19" s="119" t="s">
         <v>102</v>
       </c>
       <c r="AA19" s="53"/>
@@ -31184,7 +31191,7 @@
       <c r="AB20" s="35"/>
       <c r="AC20" s="35"/>
       <c r="AD20" s="35"/>
-      <c r="AE20" s="120"/>
+      <c r="AE20" s="119"/>
       <c r="AF20" s="42"/>
       <c r="AG20" s="34"/>
       <c r="AH20" s="34"/>
@@ -31196,7 +31203,7 @@
       <c r="AN20" s="34"/>
     </row>
     <row r="21" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A21" s="118" t="s">
+      <c r="A21" s="117" t="s">
         <v>109</v>
       </c>
       <c r="B21" s="42"/>
@@ -31240,7 +31247,7 @@
       <c r="AN21" s="21"/>
     </row>
     <row r="22" spans="1:40" ht="7.5" customHeight="1">
-      <c r="A22" s="121"/>
+      <c r="A22" s="120"/>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -31760,7 +31767,7 @@
       <c r="AN33" s="34"/>
     </row>
     <row r="34" spans="1:40" ht="7.5" customHeight="1">
-      <c r="A34" s="119"/>
+      <c r="A34" s="118"/>
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
       <c r="D34" s="42"/>
@@ -31802,7 +31809,7 @@
       <c r="AN34" s="34"/>
     </row>
     <row r="35" spans="1:40" ht="20.25">
-      <c r="A35" s="117" t="s">
+      <c r="A35" s="116" t="s">
         <v>142</v>
       </c>
       <c r="B35" s="42"/>
@@ -31915,7 +31922,7 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
-      <c r="Z37" s="120" t="s">
+      <c r="Z37" s="119" t="s">
         <v>120</v>
       </c>
       <c r="AA37" s="53"/>
@@ -32045,7 +32052,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-      <c r="Z40" s="120" t="s">
+      <c r="Z40" s="119" t="s">
         <v>122</v>
       </c>
       <c r="AA40" s="53"/>
@@ -32175,7 +32182,7 @@
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
-      <c r="Z43" s="120" t="s">
+      <c r="Z43" s="119" t="s">
         <v>124</v>
       </c>
       <c r="AA43" s="53"/>
@@ -32305,7 +32312,7 @@
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
-      <c r="Z46" s="120" t="s">
+      <c r="Z46" s="119" t="s">
         <v>126</v>
       </c>
       <c r="AA46" s="53"/>
@@ -32749,7 +32756,7 @@
     </row>
     <row r="57" spans="1:40" ht="14.25" customHeight="1">
       <c r="A57" s="23"/>
-      <c r="B57" s="114"/>
+      <c r="B57" s="113"/>
       <c r="C57" s="42"/>
       <c r="D57" s="42"/>
       <c r="E57" s="42"/>
@@ -32928,7 +32935,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="14.25" customHeight="1">
       <c r="A1" s="26"/>
-      <c r="B1" s="126"/>
+      <c r="B1" s="125"/>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
@@ -32936,60 +32943,60 @@
       <c r="G1" s="42"/>
       <c r="H1" s="42"/>
       <c r="I1" s="23"/>
-      <c r="J1" s="125" t="s">
+      <c r="J1" s="124" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="42"/>
       <c r="L1" s="53"/>
-      <c r="M1" s="127" t="str">
+      <c r="M1" s="126" t="str">
         <f>IF(Титул!Y1="","",Титул!Y1)</f>
         <v>1</v>
       </c>
-      <c r="N1" s="127" t="str">
+      <c r="N1" s="126" t="str">
         <f>IF(Титул!AA1="","",Титул!AA1)</f>
         <v>2</v>
       </c>
-      <c r="O1" s="127" t="str">
+      <c r="O1" s="126" t="str">
         <f>IF(Титул!AC1="","",Титул!AC1)</f>
         <v>3</v>
       </c>
-      <c r="P1" s="127" t="str">
+      <c r="P1" s="126" t="str">
         <f>IF(Титул!AE1="","",Титул!AE1)</f>
         <v>4</v>
       </c>
-      <c r="Q1" s="127" t="str">
+      <c r="Q1" s="126" t="str">
         <f>IF(Титул!AG1="","",Титул!AG1)</f>
         <v>5</v>
       </c>
-      <c r="R1" s="127" t="str">
+      <c r="R1" s="126" t="str">
         <f>IF(Титул!AI1="","",Титул!AI1)</f>
         <v>6</v>
       </c>
-      <c r="S1" s="127" t="str">
+      <c r="S1" s="126" t="str">
         <f>IF(Титул!AK1="","",Титул!AK1)</f>
         <v>7</v>
       </c>
-      <c r="T1" s="127" t="str">
+      <c r="T1" s="126" t="str">
         <f>IF(Титул!AM1="","",Титул!AM1)</f>
         <v>8</v>
       </c>
-      <c r="U1" s="127" t="str">
+      <c r="U1" s="126" t="str">
         <f>IF(Титул!AO1="","",Титул!AO1)</f>
         <v>9</v>
       </c>
-      <c r="V1" s="127" t="str">
+      <c r="V1" s="126" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="W1" s="124" t="str">
+      <c r="W1" s="123" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="X1" s="124" t="str">
+      <c r="X1" s="123" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
-      <c r="Y1" s="122"/>
+      <c r="Y1" s="121"/>
       <c r="Z1" s="42"/>
       <c r="AA1" s="42"/>
       <c r="AB1" s="42"/>
@@ -33031,7 +33038,7 @@
       <c r="V2" s="100"/>
       <c r="W2" s="100"/>
       <c r="X2" s="100"/>
-      <c r="Y2" s="122"/>
+      <c r="Y2" s="121"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -33058,7 +33065,7 @@
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="21"/>
-      <c r="J3" s="114"/>
+      <c r="J3" s="113"/>
       <c r="K3" s="42"/>
       <c r="L3" s="42"/>
       <c r="M3" s="21"/>
@@ -33073,7 +33080,7 @@
       <c r="V3" s="21"/>
       <c r="W3" s="21"/>
       <c r="X3" s="21"/>
-      <c r="Y3" s="114"/>
+      <c r="Y3" s="113"/>
       <c r="Z3" s="42"/>
       <c r="AA3" s="42"/>
       <c r="AB3" s="42"/>
@@ -33100,7 +33107,7 @@
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="21"/>
-      <c r="J4" s="125" t="s">
+      <c r="J4" s="124" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="42"/>
@@ -33141,14 +33148,14 @@
         <f>IF(Титул!AO4="","",Титул!AO4)</f>
         <v/>
       </c>
-      <c r="V4" s="125" t="s">
+      <c r="V4" s="124" t="s">
         <v>12</v>
       </c>
       <c r="W4" s="53"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="29"/>
       <c r="Z4" s="29"/>
-      <c r="AA4" s="123"/>
+      <c r="AA4" s="122"/>
       <c r="AB4" s="42"/>
       <c r="AC4" s="42"/>
       <c r="AD4" s="42"/>
@@ -33173,7 +33180,7 @@
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
       <c r="I5" s="21"/>
-      <c r="J5" s="114"/>
+      <c r="J5" s="113"/>
       <c r="K5" s="42"/>
       <c r="L5" s="42"/>
       <c r="M5" s="31"/>
@@ -33215,7 +33222,7 @@
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
       <c r="I6" s="21"/>
-      <c r="J6" s="114"/>
+      <c r="J6" s="113"/>
       <c r="K6" s="42"/>
       <c r="L6" s="42"/>
       <c r="M6" s="31"/>
@@ -33227,12 +33234,12 @@
       <c r="S6" s="31"/>
       <c r="T6" s="31"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="114"/>
+      <c r="V6" s="113"/>
       <c r="W6" s="42"/>
       <c r="X6" s="42"/>
       <c r="Y6" s="42"/>
       <c r="Z6" s="42"/>
-      <c r="AA6" s="114"/>
+      <c r="AA6" s="113"/>
       <c r="AB6" s="42"/>
       <c r="AC6" s="42"/>
       <c r="AD6" s="42"/>
@@ -33248,7 +33255,7 @@
       <c r="AN6" s="42"/>
     </row>
     <row r="7" spans="1:40" ht="6" customHeight="1">
-      <c r="A7" s="126"/>
+      <c r="A7" s="125"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -33332,7 +33339,7 @@
       <c r="AN8" s="21"/>
     </row>
     <row r="9" spans="1:40" ht="27" customHeight="1">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="117" t="s">
         <v>147</v>
       </c>
       <c r="B9" s="42"/>
@@ -33418,7 +33425,7 @@
       <c r="AN10" s="21"/>
     </row>
     <row r="11" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A11" s="119" t="s">
+      <c r="A11" s="118" t="s">
         <v>148</v>
       </c>
       <c r="B11" s="42"/>
@@ -33445,7 +33452,7 @@
       <c r="W11" s="21"/>
       <c r="X11" s="21"/>
       <c r="Y11" s="21"/>
-      <c r="Z11" s="120" t="s">
+      <c r="Z11" s="119" t="s">
         <v>129</v>
       </c>
       <c r="AA11" s="53"/>
@@ -33494,7 +33501,7 @@
       <c r="AB12" s="35"/>
       <c r="AC12" s="35"/>
       <c r="AD12" s="35"/>
-      <c r="AE12" s="120"/>
+      <c r="AE12" s="119"/>
       <c r="AF12" s="42"/>
       <c r="AG12" s="34"/>
       <c r="AH12" s="34"/>
@@ -33506,7 +33513,7 @@
       <c r="AN12" s="34"/>
     </row>
     <row r="13" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A13" s="119" t="s">
+      <c r="A13" s="118" t="s">
         <v>149</v>
       </c>
       <c r="B13" s="42"/>
@@ -33533,7 +33540,7 @@
       <c r="W13" s="21"/>
       <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
-      <c r="Z13" s="120" t="s">
+      <c r="Z13" s="119" t="s">
         <v>131</v>
       </c>
       <c r="AA13" s="53"/>
@@ -33582,7 +33589,7 @@
       <c r="AB14" s="35"/>
       <c r="AC14" s="35"/>
       <c r="AD14" s="35"/>
-      <c r="AE14" s="120"/>
+      <c r="AE14" s="119"/>
       <c r="AF14" s="42"/>
       <c r="AG14" s="34"/>
       <c r="AH14" s="34"/>
@@ -33594,7 +33601,7 @@
       <c r="AN14" s="34"/>
     </row>
     <row r="15" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A15" s="119" t="s">
+      <c r="A15" s="118" t="s">
         <v>150</v>
       </c>
       <c r="B15" s="42"/>
@@ -33621,7 +33628,7 @@
       <c r="W15" s="21"/>
       <c r="X15" s="21"/>
       <c r="Y15" s="21"/>
-      <c r="Z15" s="120" t="s">
+      <c r="Z15" s="119" t="s">
         <v>133</v>
       </c>
       <c r="AA15" s="53"/>
@@ -33670,7 +33677,7 @@
       <c r="AB16" s="35"/>
       <c r="AC16" s="35"/>
       <c r="AD16" s="35"/>
-      <c r="AE16" s="120"/>
+      <c r="AE16" s="119"/>
       <c r="AF16" s="42"/>
       <c r="AG16" s="34"/>
       <c r="AH16" s="34"/>
@@ -33682,7 +33689,7 @@
       <c r="AN16" s="34"/>
     </row>
     <row r="17" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A17" s="119" t="s">
+      <c r="A17" s="118" t="s">
         <v>151</v>
       </c>
       <c r="B17" s="42"/>
@@ -33709,7 +33716,7 @@
       <c r="W17" s="21"/>
       <c r="X17" s="21"/>
       <c r="Y17" s="21"/>
-      <c r="Z17" s="120" t="s">
+      <c r="Z17" s="119" t="s">
         <v>135</v>
       </c>
       <c r="AA17" s="53"/>
@@ -33758,7 +33765,7 @@
       <c r="AB18" s="35"/>
       <c r="AC18" s="35"/>
       <c r="AD18" s="35"/>
-      <c r="AE18" s="120"/>
+      <c r="AE18" s="119"/>
       <c r="AF18" s="42"/>
       <c r="AG18" s="34"/>
       <c r="AH18" s="34"/>
@@ -33770,7 +33777,7 @@
       <c r="AN18" s="34"/>
     </row>
     <row r="19" spans="1:40" ht="37.5" customHeight="1">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="111" t="s">
         <v>152</v>
       </c>
       <c r="B19" s="42"/>
@@ -33883,7 +33890,7 @@
       <c r="W21" s="42"/>
       <c r="X21" s="42"/>
       <c r="Y21" s="42"/>
-      <c r="Z21" s="120" t="s">
+      <c r="Z21" s="119" t="s">
         <v>154</v>
       </c>
       <c r="AA21" s="53"/>
@@ -34013,7 +34020,7 @@
       <c r="W24" s="42"/>
       <c r="X24" s="42"/>
       <c r="Y24" s="42"/>
-      <c r="Z24" s="120" t="s">
+      <c r="Z24" s="119" t="s">
         <v>156</v>
       </c>
       <c r="AA24" s="53"/>
@@ -34143,7 +34150,7 @@
       <c r="W27" s="42"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="42"/>
-      <c r="Z27" s="120" t="s">
+      <c r="Z27" s="119" t="s">
         <v>158</v>
       </c>
       <c r="AA27" s="53"/>
@@ -34273,7 +34280,7 @@
       <c r="W30" s="42"/>
       <c r="X30" s="42"/>
       <c r="Y30" s="42"/>
-      <c r="Z30" s="120" t="s">
+      <c r="Z30" s="119" t="s">
         <v>160</v>
       </c>
       <c r="AA30" s="53"/>
@@ -34334,7 +34341,7 @@
       <c r="AN31" s="34"/>
     </row>
     <row r="32" spans="1:40" ht="13.5" customHeight="1">
-      <c r="A32" s="119"/>
+      <c r="A32" s="118"/>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
       <c r="D32" s="42"/>
@@ -35595,7 +35602,7 @@
     </row>
     <row r="62" spans="1:40" ht="6" customHeight="1">
       <c r="A62" s="21"/>
-      <c r="B62" s="114"/>
+      <c r="B62" s="113"/>
       <c r="C62" s="42"/>
       <c r="D62" s="42"/>
       <c r="E62" s="42"/>
@@ -35637,7 +35644,7 @@
     </row>
     <row r="63" spans="1:40" ht="14.25" customHeight="1">
       <c r="A63" s="23"/>
-      <c r="B63" s="114"/>
+      <c r="B63" s="113"/>
       <c r="C63" s="42"/>
       <c r="D63" s="42"/>
       <c r="E63" s="42"/>
@@ -35858,11 +35865,11 @@
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="X1" s="116" t="str">
+      <c r="X1" s="115" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="Y1" s="116" t="str">
+      <c r="Y1" s="115" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
@@ -36173,7 +36180,7 @@
       <c r="AO7" s="42"/>
     </row>
     <row r="8" spans="1:41" ht="29.25" customHeight="1">
-      <c r="A8" s="109" t="s">
+      <c r="A8" s="108" t="s">
         <v>161</v>
       </c>
       <c r="B8" s="42"/>
@@ -36316,7 +36323,7 @@
       <c r="AO10" s="42"/>
     </row>
     <row r="11" spans="1:41" ht="17.25" customHeight="1">
-      <c r="A11" s="112" t="s">
+      <c r="A11" s="111" t="s">
         <v>162</v>
       </c>
       <c r="B11" s="42"/>
@@ -36678,7 +36685,7 @@
       <c r="AO18" s="11"/>
     </row>
     <row r="19" spans="1:41" ht="12.75">
-      <c r="A19" s="130" t="s">
+      <c r="A19" s="129" t="s">
         <v>167</v>
       </c>
       <c r="B19" s="42"/>
@@ -37173,7 +37180,7 @@
       <c r="AO29" s="3"/>
     </row>
     <row r="30" spans="1:41" ht="19.5" customHeight="1">
-      <c r="A30" s="130" t="s">
+      <c r="A30" s="129" t="s">
         <v>174</v>
       </c>
       <c r="B30" s="42"/>
@@ -37578,7 +37585,7 @@
       <c r="AO38" s="3"/>
     </row>
     <row r="39" spans="1:41" ht="17.25" customHeight="1">
-      <c r="A39" s="130" t="s">
+      <c r="A39" s="129" t="s">
         <v>183</v>
       </c>
       <c r="B39" s="42"/>
@@ -37983,7 +37990,7 @@
       <c r="AO47" s="3"/>
     </row>
     <row r="48" spans="1:41" ht="17.25" customHeight="1">
-      <c r="A48" s="112" t="s">
+      <c r="A48" s="111" t="s">
         <v>103</v>
       </c>
       <c r="B48" s="42"/>
@@ -38574,7 +38581,7 @@
       <c r="AO60" s="3"/>
     </row>
     <row r="61" spans="1:41" ht="17.25" customHeight="1">
-      <c r="A61" s="115"/>
+      <c r="A61" s="114"/>
       <c r="B61" s="42"/>
       <c r="C61" s="42"/>
       <c r="D61" s="42"/>
@@ -38746,7 +38753,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="12.75">
       <c r="A1" s="26"/>
-      <c r="B1" s="126"/>
+      <c r="B1" s="125"/>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
@@ -38754,60 +38761,60 @@
       <c r="G1" s="42"/>
       <c r="H1" s="42"/>
       <c r="I1" s="23"/>
-      <c r="J1" s="125" t="s">
+      <c r="J1" s="124" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="42"/>
       <c r="L1" s="53"/>
-      <c r="M1" s="127" t="str">
+      <c r="M1" s="126" t="str">
         <f>IF(Титул!Y1="","",Титул!Y1)</f>
         <v>1</v>
       </c>
-      <c r="N1" s="127" t="str">
+      <c r="N1" s="126" t="str">
         <f>IF(Титул!AA1="","",Титул!AA1)</f>
         <v>2</v>
       </c>
-      <c r="O1" s="127" t="str">
+      <c r="O1" s="126" t="str">
         <f>IF(Титул!AC1="","",Титул!AC1)</f>
         <v>3</v>
       </c>
-      <c r="P1" s="127" t="str">
+      <c r="P1" s="126" t="str">
         <f>IF(Титул!AE1="","",Титул!AE1)</f>
         <v>4</v>
       </c>
-      <c r="Q1" s="127" t="str">
+      <c r="Q1" s="126" t="str">
         <f>IF(Титул!AG1="","",Титул!AG1)</f>
         <v>5</v>
       </c>
-      <c r="R1" s="127" t="str">
+      <c r="R1" s="126" t="str">
         <f>IF(Титул!AI1="","",Титул!AI1)</f>
         <v>6</v>
       </c>
-      <c r="S1" s="127" t="str">
+      <c r="S1" s="126" t="str">
         <f>IF(Титул!AK1="","",Титул!AK1)</f>
         <v>7</v>
       </c>
-      <c r="T1" s="127" t="str">
+      <c r="T1" s="126" t="str">
         <f>IF(Титул!AM1="","",Титул!AM1)</f>
         <v>8</v>
       </c>
-      <c r="U1" s="127" t="str">
+      <c r="U1" s="126" t="str">
         <f>IF(Титул!AO1="","",Титул!AO1)</f>
         <v>9</v>
       </c>
-      <c r="V1" s="127" t="str">
+      <c r="V1" s="126" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
         <v/>
       </c>
-      <c r="W1" s="124" t="str">
+      <c r="W1" s="123" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
         <v/>
       </c>
-      <c r="X1" s="124" t="str">
+      <c r="X1" s="123" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
         <v/>
       </c>
-      <c r="Y1" s="122"/>
+      <c r="Y1" s="121"/>
       <c r="Z1" s="42"/>
       <c r="AA1" s="42"/>
       <c r="AB1" s="42"/>
@@ -38849,7 +38856,7 @@
       <c r="V2" s="100"/>
       <c r="W2" s="100"/>
       <c r="X2" s="100"/>
-      <c r="Y2" s="122"/>
+      <c r="Y2" s="121"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -38876,7 +38883,7 @@
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="21"/>
-      <c r="J3" s="114"/>
+      <c r="J3" s="113"/>
       <c r="K3" s="42"/>
       <c r="L3" s="42"/>
       <c r="M3" s="21"/>
@@ -38891,7 +38898,7 @@
       <c r="V3" s="21"/>
       <c r="W3" s="21"/>
       <c r="X3" s="21"/>
-      <c r="Y3" s="114"/>
+      <c r="Y3" s="113"/>
       <c r="Z3" s="42"/>
       <c r="AA3" s="42"/>
       <c r="AB3" s="42"/>
@@ -38918,7 +38925,7 @@
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="21"/>
-      <c r="J4" s="125" t="s">
+      <c r="J4" s="124" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="42"/>
@@ -38959,14 +38966,14 @@
         <f>IF(Титул!AO4="","",Титул!AO4)</f>
         <v/>
       </c>
-      <c r="V4" s="125" t="s">
+      <c r="V4" s="124" t="s">
         <v>12</v>
       </c>
       <c r="W4" s="53"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="29"/>
       <c r="Z4" s="29"/>
-      <c r="AA4" s="123"/>
+      <c r="AA4" s="122"/>
       <c r="AB4" s="42"/>
       <c r="AC4" s="42"/>
       <c r="AD4" s="42"/>
@@ -38991,7 +38998,7 @@
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
       <c r="I5" s="21"/>
-      <c r="J5" s="114"/>
+      <c r="J5" s="113"/>
       <c r="K5" s="42"/>
       <c r="L5" s="42"/>
       <c r="M5" s="31"/>
@@ -39033,7 +39040,7 @@
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
       <c r="I6" s="21"/>
-      <c r="J6" s="114"/>
+      <c r="J6" s="113"/>
       <c r="K6" s="42"/>
       <c r="L6" s="42"/>
       <c r="M6" s="31"/>
@@ -39045,12 +39052,12 @@
       <c r="S6" s="31"/>
       <c r="T6" s="31"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="114"/>
+      <c r="V6" s="113"/>
       <c r="W6" s="42"/>
       <c r="X6" s="42"/>
       <c r="Y6" s="42"/>
       <c r="Z6" s="42"/>
-      <c r="AA6" s="114"/>
+      <c r="AA6" s="113"/>
       <c r="AB6" s="42"/>
       <c r="AC6" s="42"/>
       <c r="AD6" s="42"/>
@@ -39066,7 +39073,7 @@
       <c r="AN6" s="42"/>
     </row>
     <row r="7" spans="1:40" ht="6" customHeight="1">
-      <c r="A7" s="126"/>
+      <c r="A7" s="125"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -39109,7 +39116,7 @@
     </row>
     <row r="8" spans="1:40" ht="16.5" customHeight="1">
       <c r="A8" s="32"/>
-      <c r="B8" s="129" t="s">
+      <c r="B8" s="128" t="s">
         <v>50</v>
       </c>
       <c r="C8" s="42"/>
@@ -39135,13 +39142,13 @@
       <c r="W8" s="42"/>
       <c r="X8" s="42"/>
       <c r="Y8" s="21"/>
-      <c r="Z8" s="129" t="s">
+      <c r="Z8" s="128" t="s">
         <v>51</v>
       </c>
       <c r="AA8" s="42"/>
       <c r="AB8" s="42"/>
       <c r="AC8" s="42"/>
-      <c r="AD8" s="129" t="s">
+      <c r="AD8" s="128" t="s">
         <v>52</v>
       </c>
       <c r="AE8" s="42"/>
@@ -39157,7 +39164,7 @@
     </row>
     <row r="9" spans="1:40" ht="14.25" customHeight="1">
       <c r="A9" s="32"/>
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="109" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="42"/>
@@ -39183,13 +39190,13 @@
       <c r="W9" s="42"/>
       <c r="X9" s="42"/>
       <c r="Y9" s="21"/>
-      <c r="Z9" s="110" t="s">
+      <c r="Z9" s="109" t="s">
         <v>2</v>
       </c>
       <c r="AA9" s="42"/>
       <c r="AB9" s="42"/>
       <c r="AC9" s="42"/>
-      <c r="AD9" s="110" t="s">
+      <c r="AD9" s="109" t="s">
         <v>3</v>
       </c>
       <c r="AE9" s="42"/>
@@ -39204,7 +39211,7 @@
       <c r="AN9" s="42"/>
     </row>
     <row r="10" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A10" s="130" t="s">
+      <c r="A10" s="129" t="s">
         <v>109</v>
       </c>
       <c r="B10" s="42"/>
@@ -39276,7 +39283,7 @@
       <c r="X11" s="42"/>
       <c r="Y11" s="42"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="120" t="s">
+      <c r="AA11" s="119" t="s">
         <v>199</v>
       </c>
       <c r="AB11" s="42"/>
@@ -39364,7 +39371,7 @@
       <c r="X13" s="42"/>
       <c r="Y13" s="42"/>
       <c r="Z13" s="3"/>
-      <c r="AA13" s="120" t="s">
+      <c r="AA13" s="119" t="s">
         <v>201</v>
       </c>
       <c r="AB13" s="42"/>
@@ -39452,7 +39459,7 @@
       <c r="X15" s="42"/>
       <c r="Y15" s="42"/>
       <c r="Z15" s="3"/>
-      <c r="AA15" s="120" t="s">
+      <c r="AA15" s="119" t="s">
         <v>203</v>
       </c>
       <c r="AB15" s="42"/>
@@ -39540,7 +39547,7 @@
       <c r="X17" s="42"/>
       <c r="Y17" s="42"/>
       <c r="Z17" s="3"/>
-      <c r="AA17" s="120" t="s">
+      <c r="AA17" s="119" t="s">
         <v>205</v>
       </c>
       <c r="AB17" s="42"/>
@@ -39628,7 +39635,7 @@
       <c r="X19" s="42"/>
       <c r="Y19" s="42"/>
       <c r="Z19" s="42"/>
-      <c r="AA19" s="120" t="s">
+      <c r="AA19" s="119" t="s">
         <v>207</v>
       </c>
       <c r="AB19" s="42"/>
@@ -39688,7 +39695,7 @@
       <c r="AN20" s="34"/>
     </row>
     <row r="21" spans="1:40" ht="21.75" customHeight="1">
-      <c r="A21" s="111" t="s">
+      <c r="A21" s="110" t="s">
         <v>127</v>
       </c>
       <c r="B21" s="42"/>
@@ -40631,7 +40638,7 @@
     </row>
     <row r="43" spans="1:40" ht="14.25" customHeight="1">
       <c r="A43" s="23"/>
-      <c r="B43" s="114"/>
+      <c r="B43" s="113"/>
       <c r="C43" s="42"/>
       <c r="D43" s="42"/>
       <c r="E43" s="42"/>
@@ -40714,7 +40721,7 @@
       <c r="AN44" s="21"/>
     </row>
     <row r="45" spans="1:40" ht="16.5" customHeight="1">
-      <c r="A45" s="131"/>
+      <c r="A45" s="130"/>
       <c r="B45" s="42"/>
       <c r="C45" s="42"/>
       <c r="D45" s="42"/>

--- a/templates/Declaration_template.xlsx
+++ b/templates/Declaration_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="540" windowWidth="13095" windowHeight="10935" activeTab="4"/>
+    <workbookView xWindow="270" yWindow="540" windowWidth="13095" windowHeight="10935"/>
   </bookViews>
   <sheets>
     <sheet name="Титул" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="239">
   <si>
     <t>ИНН</t>
   </si>
@@ -1958,7 +1958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2222,7 +2222,6 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2242,9 +2241,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2278,9 +2274,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2334,10 +2327,19 @@
     <xf numFmtId="49" fontId="29" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2980,11 +2982,17 @@
         <v>6</v>
       </c>
       <c r="AP1" s="66"/>
-      <c r="AQ1" s="65"/>
+      <c r="AQ1" s="65" t="s">
+        <v>10</v>
+      </c>
       <c r="AR1" s="66"/>
-      <c r="AS1" s="65"/>
+      <c r="AS1" s="65" t="s">
+        <v>11</v>
+      </c>
       <c r="AT1" s="66"/>
-      <c r="AU1" s="65"/>
+      <c r="AU1" s="65" t="s">
+        <v>2</v>
+      </c>
       <c r="AV1" s="66"/>
       <c r="AW1" s="2"/>
       <c r="AX1" s="3"/>
@@ -8839,9 +8847,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:75" ht="15.75">
-      <c r="A1" s="139"/>
+      <c r="A1" s="136"/>
       <c r="B1" s="75"/>
-      <c r="C1" s="140"/>
+      <c r="C1" s="137"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
@@ -8855,9 +8863,9 @@
       <c r="N1" s="42"/>
       <c r="O1" s="42"/>
       <c r="P1" s="42"/>
-      <c r="Q1" s="141"/>
+      <c r="Q1" s="138"/>
       <c r="R1" s="75"/>
-      <c r="S1" s="124" t="s">
+      <c r="S1" s="122" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="42"/>
@@ -8865,71 +8873,71 @@
       <c r="V1" s="42"/>
       <c r="W1" s="42"/>
       <c r="X1" s="53"/>
-      <c r="Y1" s="137" t="str">
+      <c r="Y1" s="134" t="str">
         <f>IF(Титул!Y1="","",Титул!Y1)</f>
         <v>1</v>
       </c>
       <c r="Z1" s="66"/>
-      <c r="AA1" s="137" t="str">
+      <c r="AA1" s="134" t="str">
         <f>IF(Титул!AA1="","",Титул!AA1)</f>
         <v>2</v>
       </c>
       <c r="AB1" s="66"/>
-      <c r="AC1" s="137" t="str">
+      <c r="AC1" s="134" t="str">
         <f>IF(Титул!AC1="","",Титул!AC1)</f>
         <v>3</v>
       </c>
       <c r="AD1" s="66"/>
-      <c r="AE1" s="137" t="str">
+      <c r="AE1" s="134" t="str">
         <f>IF(Титул!AE1="","",Титул!AE1)</f>
         <v>4</v>
       </c>
       <c r="AF1" s="66"/>
-      <c r="AG1" s="137" t="str">
+      <c r="AG1" s="134" t="str">
         <f>IF(Титул!AG1="","",Титул!AG1)</f>
         <v>5</v>
       </c>
       <c r="AH1" s="66"/>
-      <c r="AI1" s="137" t="str">
+      <c r="AI1" s="134" t="str">
         <f>IF(Титул!AI1="","",Титул!AI1)</f>
         <v>6</v>
       </c>
       <c r="AJ1" s="66"/>
-      <c r="AK1" s="137" t="str">
+      <c r="AK1" s="134" t="str">
         <f>IF(Титул!AK1="","",Титул!AK1)</f>
         <v>7</v>
       </c>
       <c r="AL1" s="66"/>
-      <c r="AM1" s="137" t="str">
+      <c r="AM1" s="134" t="str">
         <f>IF(Титул!AM1="","",Титул!AM1)</f>
         <v>8</v>
       </c>
       <c r="AN1" s="66"/>
-      <c r="AO1" s="137" t="str">
+      <c r="AO1" s="134" t="str">
         <f>IF(Титул!AO1="","",Титул!AO1)</f>
         <v>9</v>
       </c>
       <c r="AP1" s="66"/>
-      <c r="AQ1" s="137" t="str">
+      <c r="AQ1" s="134" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="AR1" s="66"/>
-      <c r="AS1" s="135" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR1" s="155"/>
+      <c r="AS1" s="156" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
-      </c>
-      <c r="AT1" s="66"/>
-      <c r="AU1" s="135" t="str">
+        <v>1</v>
+      </c>
+      <c r="AT1" s="155"/>
+      <c r="AU1" s="156" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
-      </c>
-      <c r="AV1" s="66"/>
+        <v>2</v>
+      </c>
+      <c r="AV1" s="155"/>
       <c r="AW1" s="30"/>
       <c r="AX1" s="31"/>
       <c r="AY1" s="31"/>
       <c r="AZ1" s="31"/>
-      <c r="BA1" s="136"/>
+      <c r="BA1" s="133"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
       <c r="BD1" s="42"/>
@@ -8954,7 +8962,7 @@
       <c r="BW1" s="42"/>
     </row>
     <row r="2" spans="1:75" ht="2.25" customHeight="1">
-      <c r="A2" s="140"/>
+      <c r="A2" s="137"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
@@ -8996,12 +9004,12 @@
       <c r="AN2" s="68"/>
       <c r="AO2" s="67"/>
       <c r="AP2" s="68"/>
-      <c r="AQ2" s="67"/>
-      <c r="AR2" s="68"/>
-      <c r="AS2" s="67"/>
-      <c r="AT2" s="68"/>
-      <c r="AU2" s="67"/>
-      <c r="AV2" s="68"/>
+      <c r="AQ2" s="157"/>
+      <c r="AR2" s="158"/>
+      <c r="AS2" s="157"/>
+      <c r="AT2" s="158"/>
+      <c r="AU2" s="157"/>
+      <c r="AV2" s="158"/>
       <c r="AW2" s="30"/>
       <c r="AX2" s="31"/>
       <c r="AY2" s="31"/>
@@ -9031,7 +9039,7 @@
       <c r="BW2" s="42"/>
     </row>
     <row r="3" spans="1:75" ht="4.5" customHeight="1">
-      <c r="A3" s="140"/>
+      <c r="A3" s="137"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
@@ -9069,7 +9077,7 @@
       <c r="AJ3" s="38"/>
       <c r="AK3" s="38"/>
       <c r="AL3" s="38"/>
-      <c r="AM3" s="138"/>
+      <c r="AM3" s="135"/>
       <c r="AN3" s="70"/>
       <c r="AO3" s="38"/>
       <c r="AP3" s="21"/>
@@ -9108,7 +9116,7 @@
       <c r="BW3" s="42"/>
     </row>
     <row r="4" spans="1:75" ht="21">
-      <c r="A4" s="142"/>
+      <c r="A4" s="139"/>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
@@ -9126,7 +9134,7 @@
       <c r="P4" s="42"/>
       <c r="Q4" s="113"/>
       <c r="R4" s="42"/>
-      <c r="S4" s="124" t="s">
+      <c r="S4" s="122" t="s">
         <v>9</v>
       </c>
       <c r="T4" s="42"/>
@@ -9134,62 +9142,62 @@
       <c r="V4" s="42"/>
       <c r="W4" s="42"/>
       <c r="X4" s="53"/>
-      <c r="Y4" s="143" t="str">
+      <c r="Y4" s="140" t="str">
         <f>IF(Титул!Y4="","",Титул!Y4)</f>
         <v/>
       </c>
       <c r="Z4" s="50"/>
-      <c r="AA4" s="143" t="str">
+      <c r="AA4" s="140" t="str">
         <f>IF(Титул!AA4="","",Титул!AA4)</f>
         <v/>
       </c>
       <c r="AB4" s="50"/>
-      <c r="AC4" s="143" t="str">
+      <c r="AC4" s="140" t="str">
         <f>IF(Титул!AC4="","",Титул!AC4)</f>
         <v/>
       </c>
       <c r="AD4" s="50"/>
-      <c r="AE4" s="143" t="str">
+      <c r="AE4" s="140" t="str">
         <f>IF(Титул!AE4="","",Титул!AE4)</f>
         <v/>
       </c>
       <c r="AF4" s="50"/>
-      <c r="AG4" s="143" t="str">
+      <c r="AG4" s="140" t="str">
         <f>IF(Титул!AG4="","",Титул!AG4)</f>
         <v/>
       </c>
       <c r="AH4" s="50"/>
-      <c r="AI4" s="143" t="str">
+      <c r="AI4" s="140" t="str">
         <f>IF(Титул!AI4="","",Титул!AI4)</f>
         <v/>
       </c>
       <c r="AJ4" s="50"/>
-      <c r="AK4" s="143" t="str">
+      <c r="AK4" s="140" t="str">
         <f>IF(Титул!AK4="","",Титул!AK4)</f>
         <v/>
       </c>
       <c r="AL4" s="50"/>
-      <c r="AM4" s="143" t="str">
+      <c r="AM4" s="140" t="str">
         <f>IF(Титул!AM4="","",Титул!AM4)</f>
         <v/>
       </c>
       <c r="AN4" s="50"/>
-      <c r="AO4" s="143" t="str">
+      <c r="AO4" s="140" t="str">
         <f>IF(Титул!AO4="","",Титул!AO4)</f>
         <v/>
       </c>
       <c r="AP4" s="50"/>
-      <c r="AQ4" s="148" t="s">
+      <c r="AQ4" s="145" t="s">
         <v>12</v>
       </c>
       <c r="AR4" s="42"/>
       <c r="AS4" s="42"/>
       <c r="AT4" s="53"/>
-      <c r="AU4" s="131"/>
+      <c r="AU4" s="129"/>
       <c r="AV4" s="50"/>
-      <c r="AW4" s="131"/>
+      <c r="AW4" s="129"/>
       <c r="AX4" s="50"/>
-      <c r="AY4" s="131"/>
+      <c r="AY4" s="129"/>
       <c r="AZ4" s="50"/>
       <c r="BA4" s="42"/>
       <c r="BB4" s="42"/>
@@ -9216,7 +9224,7 @@
       <c r="BW4" s="42"/>
     </row>
     <row r="5" spans="1:75" ht="4.5" customHeight="1">
-      <c r="A5" s="140"/>
+      <c r="A5" s="137"/>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
@@ -9293,7 +9301,7 @@
       <c r="BW5" s="42"/>
     </row>
     <row r="6" spans="1:75" ht="16.5" customHeight="1">
-      <c r="A6" s="140"/>
+      <c r="A6" s="137"/>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
@@ -9370,7 +9378,7 @@
       <c r="BW6" s="42"/>
     </row>
     <row r="7" spans="1:75" ht="5.25" customHeight="1">
-      <c r="A7" s="144"/>
+      <c r="A7" s="141"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -9447,7 +9455,7 @@
       <c r="BW7" s="42"/>
     </row>
     <row r="8" spans="1:75" ht="14.25" customHeight="1">
-      <c r="A8" s="145"/>
+      <c r="A8" s="142"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -9524,7 +9532,7 @@
       <c r="BW8" s="42"/>
     </row>
     <row r="9" spans="1:75" ht="48.75" customHeight="1">
-      <c r="A9" s="146" t="s">
+      <c r="A9" s="143" t="s">
         <v>212</v>
       </c>
       <c r="B9" s="42"/>
@@ -9603,7 +9611,7 @@
       <c r="BW9" s="42"/>
     </row>
     <row r="10" spans="1:75" ht="69.75" customHeight="1">
-      <c r="A10" s="128" t="s">
+      <c r="A10" s="126" t="s">
         <v>213</v>
       </c>
       <c r="B10" s="42"/>
@@ -9613,7 +9621,7 @@
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
-      <c r="I10" s="128" t="s">
+      <c r="I10" s="126" t="s">
         <v>214</v>
       </c>
       <c r="J10" s="42"/>
@@ -9635,7 +9643,7 @@
       <c r="Z10" s="42"/>
       <c r="AA10" s="42"/>
       <c r="AB10" s="42"/>
-      <c r="AC10" s="128" t="s">
+      <c r="AC10" s="126" t="s">
         <v>215</v>
       </c>
       <c r="AD10" s="42"/>
@@ -9663,7 +9671,7 @@
       <c r="AZ10" s="42"/>
       <c r="BA10" s="42"/>
       <c r="BB10" s="42"/>
-      <c r="BC10" s="128" t="s">
+      <c r="BC10" s="126" t="s">
         <v>216</v>
       </c>
       <c r="BD10" s="42"/>
@@ -9688,7 +9696,7 @@
       <c r="BW10" s="42"/>
     </row>
     <row r="11" spans="1:75" ht="14.25" customHeight="1">
-      <c r="A11" s="147" t="s">
+      <c r="A11" s="144" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="42"/>
@@ -9698,7 +9706,7 @@
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
-      <c r="I11" s="147" t="s">
+      <c r="I11" s="144" t="s">
         <v>217</v>
       </c>
       <c r="J11" s="42"/>
@@ -9720,7 +9728,7 @@
       <c r="Z11" s="42"/>
       <c r="AA11" s="42"/>
       <c r="AB11" s="42"/>
-      <c r="AC11" s="147" t="s">
+      <c r="AC11" s="144" t="s">
         <v>218</v>
       </c>
       <c r="AD11" s="42"/>
@@ -9748,7 +9756,7 @@
       <c r="AZ11" s="42"/>
       <c r="BA11" s="42"/>
       <c r="BB11" s="42"/>
-      <c r="BC11" s="147" t="s">
+      <c r="BC11" s="144" t="s">
         <v>219</v>
       </c>
       <c r="BD11" s="42"/>
@@ -9773,3244 +9781,3244 @@
       <c r="BW11" s="42"/>
     </row>
     <row r="12" spans="1:75" ht="6" customHeight="1">
-      <c r="A12" s="119"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="42"/>
-      <c r="C12" s="119"/>
+      <c r="C12" s="118"/>
       <c r="D12" s="42"/>
-      <c r="E12" s="119"/>
+      <c r="E12" s="118"/>
       <c r="F12" s="42"/>
-      <c r="G12" s="119"/>
+      <c r="G12" s="118"/>
       <c r="H12" s="42"/>
-      <c r="I12" s="119"/>
+      <c r="I12" s="118"/>
       <c r="J12" s="42"/>
-      <c r="K12" s="119"/>
+      <c r="K12" s="118"/>
       <c r="L12" s="42"/>
-      <c r="M12" s="119"/>
+      <c r="M12" s="118"/>
       <c r="N12" s="42"/>
-      <c r="O12" s="119"/>
+      <c r="O12" s="118"/>
       <c r="P12" s="42"/>
-      <c r="Q12" s="119"/>
+      <c r="Q12" s="118"/>
       <c r="R12" s="42"/>
-      <c r="S12" s="119"/>
+      <c r="S12" s="118"/>
       <c r="T12" s="42"/>
-      <c r="U12" s="119"/>
+      <c r="U12" s="118"/>
       <c r="V12" s="42"/>
-      <c r="W12" s="119"/>
+      <c r="W12" s="118"/>
       <c r="X12" s="42"/>
-      <c r="Y12" s="119"/>
+      <c r="Y12" s="118"/>
       <c r="Z12" s="42"/>
-      <c r="AA12" s="119"/>
+      <c r="AA12" s="118"/>
       <c r="AB12" s="42"/>
-      <c r="AC12" s="119"/>
+      <c r="AC12" s="118"/>
       <c r="AD12" s="42"/>
-      <c r="AE12" s="119"/>
+      <c r="AE12" s="118"/>
       <c r="AF12" s="42"/>
-      <c r="AG12" s="119"/>
+      <c r="AG12" s="118"/>
       <c r="AH12" s="42"/>
-      <c r="AI12" s="119"/>
+      <c r="AI12" s="118"/>
       <c r="AJ12" s="42"/>
-      <c r="AK12" s="119"/>
+      <c r="AK12" s="118"/>
       <c r="AL12" s="42"/>
-      <c r="AM12" s="119"/>
+      <c r="AM12" s="118"/>
       <c r="AN12" s="42"/>
-      <c r="AO12" s="119"/>
+      <c r="AO12" s="118"/>
       <c r="AP12" s="42"/>
-      <c r="AQ12" s="119"/>
+      <c r="AQ12" s="118"/>
       <c r="AR12" s="42"/>
-      <c r="AS12" s="119"/>
+      <c r="AS12" s="118"/>
       <c r="AT12" s="42"/>
-      <c r="AU12" s="119"/>
+      <c r="AU12" s="118"/>
       <c r="AV12" s="42"/>
-      <c r="AW12" s="119"/>
+      <c r="AW12" s="118"/>
       <c r="AX12" s="42"/>
-      <c r="AY12" s="119"/>
+      <c r="AY12" s="118"/>
       <c r="AZ12" s="42"/>
-      <c r="BA12" s="119"/>
+      <c r="BA12" s="118"/>
       <c r="BB12" s="42"/>
-      <c r="BC12" s="119"/>
+      <c r="BC12" s="118"/>
       <c r="BD12" s="42"/>
-      <c r="BE12" s="119"/>
+      <c r="BE12" s="118"/>
       <c r="BF12" s="42"/>
-      <c r="BG12" s="119"/>
+      <c r="BG12" s="118"/>
       <c r="BH12" s="42"/>
-      <c r="BI12" s="119"/>
+      <c r="BI12" s="118"/>
       <c r="BJ12" s="42"/>
-      <c r="BK12" s="119"/>
+      <c r="BK12" s="118"/>
       <c r="BL12" s="42"/>
-      <c r="BM12" s="119"/>
+      <c r="BM12" s="118"/>
       <c r="BN12" s="42"/>
-      <c r="BO12" s="119"/>
+      <c r="BO12" s="118"/>
       <c r="BP12" s="42"/>
-      <c r="BQ12" s="119"/>
+      <c r="BQ12" s="118"/>
       <c r="BR12" s="42"/>
-      <c r="BS12" s="119"/>
+      <c r="BS12" s="118"/>
       <c r="BT12" s="42"/>
-      <c r="BU12" s="119"/>
+      <c r="BU12" s="118"/>
       <c r="BV12" s="42"/>
       <c r="BW12" s="36"/>
     </row>
     <row r="13" spans="1:75" ht="17.25" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="131"/>
+      <c r="B13" s="129"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="131"/>
+      <c r="D13" s="129"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="131"/>
+      <c r="F13" s="129"/>
       <c r="G13" s="50"/>
       <c r="H13" s="36"/>
-      <c r="I13" s="131"/>
+      <c r="I13" s="129"/>
       <c r="J13" s="50"/>
-      <c r="K13" s="131"/>
+      <c r="K13" s="129"/>
       <c r="L13" s="50"/>
-      <c r="M13" s="132" t="s">
+      <c r="M13" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N13" s="53"/>
-      <c r="O13" s="131"/>
+      <c r="O13" s="129"/>
       <c r="P13" s="50"/>
-      <c r="Q13" s="131"/>
+      <c r="Q13" s="129"/>
       <c r="R13" s="50"/>
-      <c r="S13" s="132" t="s">
+      <c r="S13" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T13" s="53"/>
-      <c r="U13" s="131"/>
+      <c r="U13" s="129"/>
       <c r="V13" s="50"/>
-      <c r="W13" s="131"/>
+      <c r="W13" s="129"/>
       <c r="X13" s="50"/>
-      <c r="Y13" s="131"/>
+      <c r="Y13" s="129"/>
       <c r="Z13" s="50"/>
-      <c r="AA13" s="131"/>
+      <c r="AA13" s="129"/>
       <c r="AB13" s="50"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="131"/>
+      <c r="AD13" s="129"/>
       <c r="AE13" s="50"/>
-      <c r="AF13" s="131"/>
+      <c r="AF13" s="129"/>
       <c r="AG13" s="50"/>
-      <c r="AH13" s="131"/>
+      <c r="AH13" s="129"/>
       <c r="AI13" s="50"/>
-      <c r="AJ13" s="131"/>
+      <c r="AJ13" s="129"/>
       <c r="AK13" s="50"/>
-      <c r="AL13" s="131"/>
+      <c r="AL13" s="129"/>
       <c r="AM13" s="50"/>
-      <c r="AN13" s="131"/>
+      <c r="AN13" s="129"/>
       <c r="AO13" s="50"/>
-      <c r="AP13" s="131"/>
+      <c r="AP13" s="129"/>
       <c r="AQ13" s="50"/>
-      <c r="AR13" s="131"/>
+      <c r="AR13" s="129"/>
       <c r="AS13" s="50"/>
-      <c r="AT13" s="131"/>
+      <c r="AT13" s="129"/>
       <c r="AU13" s="50"/>
-      <c r="AV13" s="131"/>
+      <c r="AV13" s="129"/>
       <c r="AW13" s="50"/>
-      <c r="AX13" s="131"/>
+      <c r="AX13" s="129"/>
       <c r="AY13" s="50"/>
-      <c r="AZ13" s="131"/>
+      <c r="AZ13" s="129"/>
       <c r="BA13" s="50"/>
       <c r="BB13" s="36"/>
       <c r="BC13" s="36"/>
-      <c r="BD13" s="131"/>
+      <c r="BD13" s="129"/>
       <c r="BE13" s="50"/>
-      <c r="BF13" s="131"/>
+      <c r="BF13" s="129"/>
       <c r="BG13" s="50"/>
-      <c r="BH13" s="131"/>
+      <c r="BH13" s="129"/>
       <c r="BI13" s="50"/>
-      <c r="BJ13" s="131"/>
+      <c r="BJ13" s="129"/>
       <c r="BK13" s="50"/>
-      <c r="BL13" s="131"/>
+      <c r="BL13" s="129"/>
       <c r="BM13" s="50"/>
-      <c r="BN13" s="131"/>
+      <c r="BN13" s="129"/>
       <c r="BO13" s="50"/>
-      <c r="BP13" s="131"/>
+      <c r="BP13" s="129"/>
       <c r="BQ13" s="50"/>
-      <c r="BR13" s="131"/>
+      <c r="BR13" s="129"/>
       <c r="BS13" s="50"/>
-      <c r="BT13" s="131"/>
+      <c r="BT13" s="129"/>
       <c r="BU13" s="50"/>
-      <c r="BV13" s="131"/>
+      <c r="BV13" s="129"/>
       <c r="BW13" s="50"/>
     </row>
     <row r="14" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A14" s="133"/>
+      <c r="A14" s="131"/>
       <c r="B14" s="42"/>
-      <c r="C14" s="133"/>
+      <c r="C14" s="131"/>
       <c r="D14" s="42"/>
-      <c r="E14" s="133"/>
+      <c r="E14" s="131"/>
       <c r="F14" s="42"/>
-      <c r="G14" s="133"/>
+      <c r="G14" s="131"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="133"/>
+      <c r="I14" s="131"/>
       <c r="J14" s="42"/>
-      <c r="K14" s="133"/>
+      <c r="K14" s="131"/>
       <c r="L14" s="42"/>
-      <c r="M14" s="133"/>
+      <c r="M14" s="131"/>
       <c r="N14" s="42"/>
-      <c r="O14" s="133"/>
+      <c r="O14" s="131"/>
       <c r="P14" s="42"/>
-      <c r="Q14" s="133"/>
+      <c r="Q14" s="131"/>
       <c r="R14" s="42"/>
-      <c r="S14" s="133"/>
+      <c r="S14" s="131"/>
       <c r="T14" s="42"/>
-      <c r="U14" s="133"/>
+      <c r="U14" s="131"/>
       <c r="V14" s="42"/>
-      <c r="W14" s="133"/>
+      <c r="W14" s="131"/>
       <c r="X14" s="42"/>
-      <c r="Y14" s="133"/>
+      <c r="Y14" s="131"/>
       <c r="Z14" s="42"/>
-      <c r="AA14" s="133"/>
+      <c r="AA14" s="131"/>
       <c r="AB14" s="42"/>
-      <c r="AC14" s="133"/>
+      <c r="AC14" s="131"/>
       <c r="AD14" s="42"/>
-      <c r="AE14" s="133"/>
+      <c r="AE14" s="131"/>
       <c r="AF14" s="42"/>
-      <c r="AG14" s="133"/>
+      <c r="AG14" s="131"/>
       <c r="AH14" s="42"/>
-      <c r="AI14" s="133"/>
+      <c r="AI14" s="131"/>
       <c r="AJ14" s="42"/>
-      <c r="AK14" s="133"/>
+      <c r="AK14" s="131"/>
       <c r="AL14" s="42"/>
-      <c r="AM14" s="133"/>
+      <c r="AM14" s="131"/>
       <c r="AN14" s="42"/>
-      <c r="AO14" s="133"/>
+      <c r="AO14" s="131"/>
       <c r="AP14" s="42"/>
-      <c r="AQ14" s="133"/>
+      <c r="AQ14" s="131"/>
       <c r="AR14" s="42"/>
-      <c r="AS14" s="133"/>
+      <c r="AS14" s="131"/>
       <c r="AT14" s="42"/>
-      <c r="AU14" s="133"/>
+      <c r="AU14" s="131"/>
       <c r="AV14" s="42"/>
-      <c r="AW14" s="133"/>
+      <c r="AW14" s="131"/>
       <c r="AX14" s="42"/>
-      <c r="AY14" s="133"/>
+      <c r="AY14" s="131"/>
       <c r="AZ14" s="42"/>
-      <c r="BA14" s="133"/>
+      <c r="BA14" s="131"/>
       <c r="BB14" s="42"/>
-      <c r="BC14" s="133"/>
+      <c r="BC14" s="131"/>
       <c r="BD14" s="42"/>
-      <c r="BE14" s="133"/>
+      <c r="BE14" s="131"/>
       <c r="BF14" s="42"/>
-      <c r="BG14" s="133"/>
+      <c r="BG14" s="131"/>
       <c r="BH14" s="42"/>
-      <c r="BI14" s="133"/>
+      <c r="BI14" s="131"/>
       <c r="BJ14" s="42"/>
-      <c r="BK14" s="133"/>
+      <c r="BK14" s="131"/>
       <c r="BL14" s="42"/>
-      <c r="BM14" s="133"/>
+      <c r="BM14" s="131"/>
       <c r="BN14" s="42"/>
-      <c r="BO14" s="133"/>
+      <c r="BO14" s="131"/>
       <c r="BP14" s="42"/>
-      <c r="BQ14" s="133"/>
+      <c r="BQ14" s="131"/>
       <c r="BR14" s="42"/>
-      <c r="BS14" s="133"/>
+      <c r="BS14" s="131"/>
       <c r="BT14" s="42"/>
-      <c r="BU14" s="133"/>
+      <c r="BU14" s="131"/>
       <c r="BV14" s="42"/>
       <c r="BW14" s="39"/>
     </row>
     <row r="15" spans="1:75" ht="17.25" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="134"/>
+      <c r="B15" s="132"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="134"/>
+      <c r="D15" s="132"/>
       <c r="E15" s="42"/>
-      <c r="F15" s="134"/>
+      <c r="F15" s="132"/>
       <c r="G15" s="42"/>
       <c r="H15" s="36"/>
-      <c r="I15" s="131"/>
+      <c r="I15" s="129"/>
       <c r="J15" s="50"/>
-      <c r="K15" s="131"/>
+      <c r="K15" s="129"/>
       <c r="L15" s="50"/>
-      <c r="M15" s="132" t="s">
+      <c r="M15" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N15" s="53"/>
-      <c r="O15" s="131"/>
+      <c r="O15" s="129"/>
       <c r="P15" s="50"/>
-      <c r="Q15" s="131"/>
+      <c r="Q15" s="129"/>
       <c r="R15" s="50"/>
-      <c r="S15" s="132" t="s">
+      <c r="S15" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T15" s="53"/>
-      <c r="U15" s="131"/>
+      <c r="U15" s="129"/>
       <c r="V15" s="50"/>
-      <c r="W15" s="131"/>
+      <c r="W15" s="129"/>
       <c r="X15" s="50"/>
-      <c r="Y15" s="131"/>
+      <c r="Y15" s="129"/>
       <c r="Z15" s="50"/>
-      <c r="AA15" s="131"/>
+      <c r="AA15" s="129"/>
       <c r="AB15" s="50"/>
       <c r="AC15" s="36"/>
-      <c r="AD15" s="131"/>
+      <c r="AD15" s="129"/>
       <c r="AE15" s="50"/>
-      <c r="AF15" s="131"/>
+      <c r="AF15" s="129"/>
       <c r="AG15" s="50"/>
-      <c r="AH15" s="131"/>
+      <c r="AH15" s="129"/>
       <c r="AI15" s="50"/>
-      <c r="AJ15" s="131"/>
+      <c r="AJ15" s="129"/>
       <c r="AK15" s="50"/>
-      <c r="AL15" s="131"/>
+      <c r="AL15" s="129"/>
       <c r="AM15" s="50"/>
-      <c r="AN15" s="131"/>
+      <c r="AN15" s="129"/>
       <c r="AO15" s="50"/>
-      <c r="AP15" s="131"/>
+      <c r="AP15" s="129"/>
       <c r="AQ15" s="50"/>
-      <c r="AR15" s="131"/>
+      <c r="AR15" s="129"/>
       <c r="AS15" s="50"/>
-      <c r="AT15" s="131"/>
+      <c r="AT15" s="129"/>
       <c r="AU15" s="50"/>
-      <c r="AV15" s="131"/>
+      <c r="AV15" s="129"/>
       <c r="AW15" s="50"/>
-      <c r="AX15" s="131"/>
+      <c r="AX15" s="129"/>
       <c r="AY15" s="50"/>
-      <c r="AZ15" s="131"/>
+      <c r="AZ15" s="129"/>
       <c r="BA15" s="50"/>
       <c r="BB15" s="36"/>
       <c r="BC15" s="36"/>
-      <c r="BD15" s="131"/>
+      <c r="BD15" s="129"/>
       <c r="BE15" s="50"/>
-      <c r="BF15" s="131"/>
+      <c r="BF15" s="129"/>
       <c r="BG15" s="50"/>
-      <c r="BH15" s="131"/>
+      <c r="BH15" s="129"/>
       <c r="BI15" s="50"/>
-      <c r="BJ15" s="131"/>
+      <c r="BJ15" s="129"/>
       <c r="BK15" s="50"/>
-      <c r="BL15" s="131"/>
+      <c r="BL15" s="129"/>
       <c r="BM15" s="50"/>
-      <c r="BN15" s="131"/>
+      <c r="BN15" s="129"/>
       <c r="BO15" s="50"/>
-      <c r="BP15" s="131"/>
+      <c r="BP15" s="129"/>
       <c r="BQ15" s="50"/>
-      <c r="BR15" s="131"/>
+      <c r="BR15" s="129"/>
       <c r="BS15" s="50"/>
-      <c r="BT15" s="131"/>
+      <c r="BT15" s="129"/>
       <c r="BU15" s="50"/>
-      <c r="BV15" s="131"/>
+      <c r="BV15" s="129"/>
       <c r="BW15" s="50"/>
     </row>
     <row r="16" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A16" s="119"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="42"/>
-      <c r="C16" s="119"/>
+      <c r="C16" s="118"/>
       <c r="D16" s="42"/>
-      <c r="E16" s="119"/>
+      <c r="E16" s="118"/>
       <c r="F16" s="42"/>
-      <c r="G16" s="119"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="42"/>
-      <c r="I16" s="119"/>
+      <c r="I16" s="118"/>
       <c r="J16" s="42"/>
-      <c r="K16" s="119"/>
+      <c r="K16" s="118"/>
       <c r="L16" s="42"/>
-      <c r="M16" s="119"/>
+      <c r="M16" s="118"/>
       <c r="N16" s="42"/>
-      <c r="O16" s="119"/>
+      <c r="O16" s="118"/>
       <c r="P16" s="42"/>
-      <c r="Q16" s="119"/>
+      <c r="Q16" s="118"/>
       <c r="R16" s="42"/>
-      <c r="S16" s="119"/>
+      <c r="S16" s="118"/>
       <c r="T16" s="42"/>
-      <c r="U16" s="119"/>
+      <c r="U16" s="118"/>
       <c r="V16" s="42"/>
-      <c r="W16" s="119"/>
+      <c r="W16" s="118"/>
       <c r="X16" s="42"/>
-      <c r="Y16" s="119"/>
+      <c r="Y16" s="118"/>
       <c r="Z16" s="42"/>
-      <c r="AA16" s="119"/>
+      <c r="AA16" s="118"/>
       <c r="AB16" s="42"/>
-      <c r="AC16" s="119"/>
+      <c r="AC16" s="118"/>
       <c r="AD16" s="42"/>
-      <c r="AE16" s="119"/>
+      <c r="AE16" s="118"/>
       <c r="AF16" s="42"/>
-      <c r="AG16" s="119"/>
+      <c r="AG16" s="118"/>
       <c r="AH16" s="42"/>
-      <c r="AI16" s="119"/>
+      <c r="AI16" s="118"/>
       <c r="AJ16" s="42"/>
-      <c r="AK16" s="119"/>
+      <c r="AK16" s="118"/>
       <c r="AL16" s="42"/>
-      <c r="AM16" s="119"/>
+      <c r="AM16" s="118"/>
       <c r="AN16" s="42"/>
-      <c r="AO16" s="119"/>
+      <c r="AO16" s="118"/>
       <c r="AP16" s="42"/>
-      <c r="AQ16" s="119"/>
+      <c r="AQ16" s="118"/>
       <c r="AR16" s="42"/>
-      <c r="AS16" s="119"/>
+      <c r="AS16" s="118"/>
       <c r="AT16" s="42"/>
-      <c r="AU16" s="119"/>
+      <c r="AU16" s="118"/>
       <c r="AV16" s="42"/>
-      <c r="AW16" s="119"/>
+      <c r="AW16" s="118"/>
       <c r="AX16" s="42"/>
-      <c r="AY16" s="119"/>
+      <c r="AY16" s="118"/>
       <c r="AZ16" s="42"/>
-      <c r="BA16" s="119"/>
+      <c r="BA16" s="118"/>
       <c r="BB16" s="42"/>
-      <c r="BC16" s="119"/>
+      <c r="BC16" s="118"/>
       <c r="BD16" s="42"/>
-      <c r="BE16" s="119"/>
+      <c r="BE16" s="118"/>
       <c r="BF16" s="42"/>
-      <c r="BG16" s="119"/>
+      <c r="BG16" s="118"/>
       <c r="BH16" s="42"/>
-      <c r="BI16" s="119"/>
+      <c r="BI16" s="118"/>
       <c r="BJ16" s="42"/>
-      <c r="BK16" s="119"/>
+      <c r="BK16" s="118"/>
       <c r="BL16" s="42"/>
-      <c r="BM16" s="119"/>
+      <c r="BM16" s="118"/>
       <c r="BN16" s="42"/>
-      <c r="BO16" s="119"/>
+      <c r="BO16" s="118"/>
       <c r="BP16" s="42"/>
-      <c r="BQ16" s="119"/>
+      <c r="BQ16" s="118"/>
       <c r="BR16" s="42"/>
-      <c r="BS16" s="119"/>
+      <c r="BS16" s="118"/>
       <c r="BT16" s="42"/>
-      <c r="BU16" s="119"/>
+      <c r="BU16" s="118"/>
       <c r="BV16" s="42"/>
       <c r="BW16" s="36"/>
     </row>
     <row r="17" spans="1:75" ht="17.25" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="131"/>
+      <c r="B17" s="129"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="131"/>
+      <c r="D17" s="129"/>
       <c r="E17" s="50"/>
-      <c r="F17" s="131"/>
+      <c r="F17" s="129"/>
       <c r="G17" s="50"/>
       <c r="H17" s="36"/>
-      <c r="I17" s="131"/>
+      <c r="I17" s="129"/>
       <c r="J17" s="50"/>
-      <c r="K17" s="131"/>
+      <c r="K17" s="129"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="132" t="s">
+      <c r="M17" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N17" s="53"/>
-      <c r="O17" s="131"/>
+      <c r="O17" s="129"/>
       <c r="P17" s="50"/>
-      <c r="Q17" s="131"/>
+      <c r="Q17" s="129"/>
       <c r="R17" s="50"/>
-      <c r="S17" s="132" t="s">
+      <c r="S17" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T17" s="53"/>
-      <c r="U17" s="131"/>
+      <c r="U17" s="129"/>
       <c r="V17" s="50"/>
-      <c r="W17" s="131"/>
+      <c r="W17" s="129"/>
       <c r="X17" s="50"/>
-      <c r="Y17" s="131"/>
+      <c r="Y17" s="129"/>
       <c r="Z17" s="50"/>
-      <c r="AA17" s="131"/>
+      <c r="AA17" s="129"/>
       <c r="AB17" s="50"/>
       <c r="AC17" s="36"/>
-      <c r="AD17" s="131"/>
+      <c r="AD17" s="129"/>
       <c r="AE17" s="50"/>
-      <c r="AF17" s="131"/>
+      <c r="AF17" s="129"/>
       <c r="AG17" s="50"/>
-      <c r="AH17" s="131"/>
+      <c r="AH17" s="129"/>
       <c r="AI17" s="50"/>
-      <c r="AJ17" s="131"/>
+      <c r="AJ17" s="129"/>
       <c r="AK17" s="50"/>
-      <c r="AL17" s="131"/>
+      <c r="AL17" s="129"/>
       <c r="AM17" s="50"/>
-      <c r="AN17" s="131"/>
+      <c r="AN17" s="129"/>
       <c r="AO17" s="50"/>
-      <c r="AP17" s="131"/>
+      <c r="AP17" s="129"/>
       <c r="AQ17" s="50"/>
-      <c r="AR17" s="131"/>
+      <c r="AR17" s="129"/>
       <c r="AS17" s="50"/>
-      <c r="AT17" s="131"/>
+      <c r="AT17" s="129"/>
       <c r="AU17" s="50"/>
-      <c r="AV17" s="131"/>
+      <c r="AV17" s="129"/>
       <c r="AW17" s="50"/>
-      <c r="AX17" s="131"/>
+      <c r="AX17" s="129"/>
       <c r="AY17" s="50"/>
-      <c r="AZ17" s="131"/>
+      <c r="AZ17" s="129"/>
       <c r="BA17" s="50"/>
       <c r="BB17" s="36"/>
       <c r="BC17" s="36"/>
-      <c r="BD17" s="131"/>
+      <c r="BD17" s="129"/>
       <c r="BE17" s="50"/>
-      <c r="BF17" s="131"/>
+      <c r="BF17" s="129"/>
       <c r="BG17" s="50"/>
-      <c r="BH17" s="131"/>
+      <c r="BH17" s="129"/>
       <c r="BI17" s="50"/>
-      <c r="BJ17" s="131"/>
+      <c r="BJ17" s="129"/>
       <c r="BK17" s="50"/>
-      <c r="BL17" s="131"/>
+      <c r="BL17" s="129"/>
       <c r="BM17" s="50"/>
-      <c r="BN17" s="131"/>
+      <c r="BN17" s="129"/>
       <c r="BO17" s="50"/>
-      <c r="BP17" s="131"/>
+      <c r="BP17" s="129"/>
       <c r="BQ17" s="50"/>
-      <c r="BR17" s="131"/>
+      <c r="BR17" s="129"/>
       <c r="BS17" s="50"/>
-      <c r="BT17" s="131"/>
+      <c r="BT17" s="129"/>
       <c r="BU17" s="50"/>
-      <c r="BV17" s="131"/>
+      <c r="BV17" s="129"/>
       <c r="BW17" s="50"/>
     </row>
     <row r="18" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A18" s="133"/>
+      <c r="A18" s="131"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="133"/>
+      <c r="C18" s="131"/>
       <c r="D18" s="42"/>
-      <c r="E18" s="133"/>
+      <c r="E18" s="131"/>
       <c r="F18" s="42"/>
-      <c r="G18" s="133"/>
+      <c r="G18" s="131"/>
       <c r="H18" s="42"/>
-      <c r="I18" s="133"/>
+      <c r="I18" s="131"/>
       <c r="J18" s="42"/>
-      <c r="K18" s="133"/>
+      <c r="K18" s="131"/>
       <c r="L18" s="42"/>
-      <c r="M18" s="133"/>
+      <c r="M18" s="131"/>
       <c r="N18" s="42"/>
-      <c r="O18" s="133"/>
+      <c r="O18" s="131"/>
       <c r="P18" s="42"/>
-      <c r="Q18" s="133"/>
+      <c r="Q18" s="131"/>
       <c r="R18" s="42"/>
-      <c r="S18" s="133"/>
+      <c r="S18" s="131"/>
       <c r="T18" s="42"/>
-      <c r="U18" s="133"/>
+      <c r="U18" s="131"/>
       <c r="V18" s="42"/>
-      <c r="W18" s="133"/>
+      <c r="W18" s="131"/>
       <c r="X18" s="42"/>
-      <c r="Y18" s="133"/>
+      <c r="Y18" s="131"/>
       <c r="Z18" s="42"/>
-      <c r="AA18" s="133"/>
+      <c r="AA18" s="131"/>
       <c r="AB18" s="42"/>
-      <c r="AC18" s="133"/>
+      <c r="AC18" s="131"/>
       <c r="AD18" s="42"/>
-      <c r="AE18" s="133"/>
+      <c r="AE18" s="131"/>
       <c r="AF18" s="42"/>
-      <c r="AG18" s="133"/>
+      <c r="AG18" s="131"/>
       <c r="AH18" s="42"/>
-      <c r="AI18" s="133"/>
+      <c r="AI18" s="131"/>
       <c r="AJ18" s="42"/>
-      <c r="AK18" s="133"/>
+      <c r="AK18" s="131"/>
       <c r="AL18" s="42"/>
-      <c r="AM18" s="133"/>
+      <c r="AM18" s="131"/>
       <c r="AN18" s="42"/>
-      <c r="AO18" s="133"/>
+      <c r="AO18" s="131"/>
       <c r="AP18" s="42"/>
-      <c r="AQ18" s="133"/>
+      <c r="AQ18" s="131"/>
       <c r="AR18" s="42"/>
-      <c r="AS18" s="133"/>
+      <c r="AS18" s="131"/>
       <c r="AT18" s="42"/>
-      <c r="AU18" s="133"/>
+      <c r="AU18" s="131"/>
       <c r="AV18" s="42"/>
-      <c r="AW18" s="133"/>
+      <c r="AW18" s="131"/>
       <c r="AX18" s="42"/>
-      <c r="AY18" s="133"/>
+      <c r="AY18" s="131"/>
       <c r="AZ18" s="42"/>
-      <c r="BA18" s="133"/>
+      <c r="BA18" s="131"/>
       <c r="BB18" s="42"/>
-      <c r="BC18" s="133"/>
+      <c r="BC18" s="131"/>
       <c r="BD18" s="42"/>
-      <c r="BE18" s="133"/>
+      <c r="BE18" s="131"/>
       <c r="BF18" s="42"/>
-      <c r="BG18" s="133"/>
+      <c r="BG18" s="131"/>
       <c r="BH18" s="42"/>
-      <c r="BI18" s="133"/>
+      <c r="BI18" s="131"/>
       <c r="BJ18" s="42"/>
-      <c r="BK18" s="133"/>
+      <c r="BK18" s="131"/>
       <c r="BL18" s="42"/>
-      <c r="BM18" s="133"/>
+      <c r="BM18" s="131"/>
       <c r="BN18" s="42"/>
-      <c r="BO18" s="133"/>
+      <c r="BO18" s="131"/>
       <c r="BP18" s="42"/>
-      <c r="BQ18" s="133"/>
+      <c r="BQ18" s="131"/>
       <c r="BR18" s="42"/>
-      <c r="BS18" s="133"/>
+      <c r="BS18" s="131"/>
       <c r="BT18" s="42"/>
-      <c r="BU18" s="133"/>
+      <c r="BU18" s="131"/>
       <c r="BV18" s="42"/>
       <c r="BW18" s="39"/>
     </row>
     <row r="19" spans="1:75" ht="17.25" customHeight="1">
       <c r="A19" s="36"/>
-      <c r="B19" s="134"/>
+      <c r="B19" s="132"/>
       <c r="C19" s="42"/>
-      <c r="D19" s="134"/>
+      <c r="D19" s="132"/>
       <c r="E19" s="42"/>
-      <c r="F19" s="134"/>
+      <c r="F19" s="132"/>
       <c r="G19" s="42"/>
       <c r="H19" s="36"/>
-      <c r="I19" s="131"/>
+      <c r="I19" s="129"/>
       <c r="J19" s="50"/>
-      <c r="K19" s="131"/>
+      <c r="K19" s="129"/>
       <c r="L19" s="50"/>
-      <c r="M19" s="132" t="s">
+      <c r="M19" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N19" s="53"/>
-      <c r="O19" s="131"/>
+      <c r="O19" s="129"/>
       <c r="P19" s="50"/>
-      <c r="Q19" s="131"/>
+      <c r="Q19" s="129"/>
       <c r="R19" s="50"/>
-      <c r="S19" s="132" t="s">
+      <c r="S19" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T19" s="53"/>
-      <c r="U19" s="131"/>
+      <c r="U19" s="129"/>
       <c r="V19" s="50"/>
-      <c r="W19" s="131"/>
+      <c r="W19" s="129"/>
       <c r="X19" s="50"/>
-      <c r="Y19" s="131"/>
+      <c r="Y19" s="129"/>
       <c r="Z19" s="50"/>
-      <c r="AA19" s="131"/>
+      <c r="AA19" s="129"/>
       <c r="AB19" s="50"/>
       <c r="AC19" s="36"/>
-      <c r="AD19" s="131"/>
+      <c r="AD19" s="129"/>
       <c r="AE19" s="50"/>
-      <c r="AF19" s="131"/>
+      <c r="AF19" s="129"/>
       <c r="AG19" s="50"/>
-      <c r="AH19" s="131"/>
+      <c r="AH19" s="129"/>
       <c r="AI19" s="50"/>
-      <c r="AJ19" s="131"/>
+      <c r="AJ19" s="129"/>
       <c r="AK19" s="50"/>
-      <c r="AL19" s="131"/>
+      <c r="AL19" s="129"/>
       <c r="AM19" s="50"/>
-      <c r="AN19" s="131"/>
+      <c r="AN19" s="129"/>
       <c r="AO19" s="50"/>
-      <c r="AP19" s="131"/>
+      <c r="AP19" s="129"/>
       <c r="AQ19" s="50"/>
-      <c r="AR19" s="131"/>
+      <c r="AR19" s="129"/>
       <c r="AS19" s="50"/>
-      <c r="AT19" s="131"/>
+      <c r="AT19" s="129"/>
       <c r="AU19" s="50"/>
-      <c r="AV19" s="131"/>
+      <c r="AV19" s="129"/>
       <c r="AW19" s="50"/>
-      <c r="AX19" s="131"/>
+      <c r="AX19" s="129"/>
       <c r="AY19" s="50"/>
-      <c r="AZ19" s="131"/>
+      <c r="AZ19" s="129"/>
       <c r="BA19" s="50"/>
       <c r="BB19" s="36"/>
       <c r="BC19" s="36"/>
-      <c r="BD19" s="131"/>
+      <c r="BD19" s="129"/>
       <c r="BE19" s="50"/>
-      <c r="BF19" s="131"/>
+      <c r="BF19" s="129"/>
       <c r="BG19" s="50"/>
-      <c r="BH19" s="131"/>
+      <c r="BH19" s="129"/>
       <c r="BI19" s="50"/>
-      <c r="BJ19" s="131"/>
+      <c r="BJ19" s="129"/>
       <c r="BK19" s="50"/>
-      <c r="BL19" s="131"/>
+      <c r="BL19" s="129"/>
       <c r="BM19" s="50"/>
-      <c r="BN19" s="131"/>
+      <c r="BN19" s="129"/>
       <c r="BO19" s="50"/>
-      <c r="BP19" s="131"/>
+      <c r="BP19" s="129"/>
       <c r="BQ19" s="50"/>
-      <c r="BR19" s="131"/>
+      <c r="BR19" s="129"/>
       <c r="BS19" s="50"/>
-      <c r="BT19" s="131"/>
+      <c r="BT19" s="129"/>
       <c r="BU19" s="50"/>
-      <c r="BV19" s="131"/>
+      <c r="BV19" s="129"/>
       <c r="BW19" s="50"/>
     </row>
     <row r="20" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A20" s="119"/>
+      <c r="A20" s="118"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="119"/>
+      <c r="C20" s="118"/>
       <c r="D20" s="42"/>
-      <c r="E20" s="119"/>
+      <c r="E20" s="118"/>
       <c r="F20" s="42"/>
-      <c r="G20" s="119"/>
+      <c r="G20" s="118"/>
       <c r="H20" s="42"/>
-      <c r="I20" s="119"/>
+      <c r="I20" s="118"/>
       <c r="J20" s="42"/>
-      <c r="K20" s="119"/>
+      <c r="K20" s="118"/>
       <c r="L20" s="42"/>
-      <c r="M20" s="119"/>
+      <c r="M20" s="118"/>
       <c r="N20" s="42"/>
-      <c r="O20" s="119"/>
+      <c r="O20" s="118"/>
       <c r="P20" s="42"/>
-      <c r="Q20" s="119"/>
+      <c r="Q20" s="118"/>
       <c r="R20" s="42"/>
-      <c r="S20" s="119"/>
+      <c r="S20" s="118"/>
       <c r="T20" s="42"/>
-      <c r="U20" s="119"/>
+      <c r="U20" s="118"/>
       <c r="V20" s="42"/>
-      <c r="W20" s="119"/>
+      <c r="W20" s="118"/>
       <c r="X20" s="42"/>
-      <c r="Y20" s="119"/>
+      <c r="Y20" s="118"/>
       <c r="Z20" s="42"/>
-      <c r="AA20" s="119"/>
+      <c r="AA20" s="118"/>
       <c r="AB20" s="42"/>
-      <c r="AC20" s="119"/>
+      <c r="AC20" s="118"/>
       <c r="AD20" s="42"/>
-      <c r="AE20" s="119"/>
+      <c r="AE20" s="118"/>
       <c r="AF20" s="42"/>
-      <c r="AG20" s="119"/>
+      <c r="AG20" s="118"/>
       <c r="AH20" s="42"/>
-      <c r="AI20" s="119"/>
+      <c r="AI20" s="118"/>
       <c r="AJ20" s="42"/>
-      <c r="AK20" s="119"/>
+      <c r="AK20" s="118"/>
       <c r="AL20" s="42"/>
-      <c r="AM20" s="119"/>
+      <c r="AM20" s="118"/>
       <c r="AN20" s="42"/>
-      <c r="AO20" s="119"/>
+      <c r="AO20" s="118"/>
       <c r="AP20" s="42"/>
-      <c r="AQ20" s="119"/>
+      <c r="AQ20" s="118"/>
       <c r="AR20" s="42"/>
-      <c r="AS20" s="119"/>
+      <c r="AS20" s="118"/>
       <c r="AT20" s="42"/>
-      <c r="AU20" s="119"/>
+      <c r="AU20" s="118"/>
       <c r="AV20" s="42"/>
-      <c r="AW20" s="119"/>
+      <c r="AW20" s="118"/>
       <c r="AX20" s="42"/>
-      <c r="AY20" s="119"/>
+      <c r="AY20" s="118"/>
       <c r="AZ20" s="42"/>
-      <c r="BA20" s="119"/>
+      <c r="BA20" s="118"/>
       <c r="BB20" s="42"/>
-      <c r="BC20" s="119"/>
+      <c r="BC20" s="118"/>
       <c r="BD20" s="42"/>
-      <c r="BE20" s="119"/>
+      <c r="BE20" s="118"/>
       <c r="BF20" s="42"/>
-      <c r="BG20" s="119"/>
+      <c r="BG20" s="118"/>
       <c r="BH20" s="42"/>
-      <c r="BI20" s="119"/>
+      <c r="BI20" s="118"/>
       <c r="BJ20" s="42"/>
-      <c r="BK20" s="119"/>
+      <c r="BK20" s="118"/>
       <c r="BL20" s="42"/>
-      <c r="BM20" s="119"/>
+      <c r="BM20" s="118"/>
       <c r="BN20" s="42"/>
-      <c r="BO20" s="119"/>
+      <c r="BO20" s="118"/>
       <c r="BP20" s="42"/>
-      <c r="BQ20" s="119"/>
+      <c r="BQ20" s="118"/>
       <c r="BR20" s="42"/>
-      <c r="BS20" s="119"/>
+      <c r="BS20" s="118"/>
       <c r="BT20" s="42"/>
-      <c r="BU20" s="119"/>
+      <c r="BU20" s="118"/>
       <c r="BV20" s="42"/>
       <c r="BW20" s="36"/>
     </row>
     <row r="21" spans="1:75" ht="17.25" customHeight="1">
       <c r="A21" s="36"/>
-      <c r="B21" s="131"/>
+      <c r="B21" s="129"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="131"/>
+      <c r="D21" s="129"/>
       <c r="E21" s="50"/>
-      <c r="F21" s="131"/>
+      <c r="F21" s="129"/>
       <c r="G21" s="50"/>
       <c r="H21" s="36"/>
-      <c r="I21" s="131"/>
+      <c r="I21" s="129"/>
       <c r="J21" s="50"/>
-      <c r="K21" s="131"/>
+      <c r="K21" s="129"/>
       <c r="L21" s="50"/>
-      <c r="M21" s="132" t="s">
+      <c r="M21" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N21" s="53"/>
-      <c r="O21" s="131"/>
+      <c r="O21" s="129"/>
       <c r="P21" s="50"/>
-      <c r="Q21" s="131"/>
+      <c r="Q21" s="129"/>
       <c r="R21" s="50"/>
-      <c r="S21" s="132" t="s">
+      <c r="S21" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T21" s="53"/>
-      <c r="U21" s="131"/>
+      <c r="U21" s="129"/>
       <c r="V21" s="50"/>
-      <c r="W21" s="131"/>
+      <c r="W21" s="129"/>
       <c r="X21" s="50"/>
-      <c r="Y21" s="131"/>
+      <c r="Y21" s="129"/>
       <c r="Z21" s="50"/>
-      <c r="AA21" s="131"/>
+      <c r="AA21" s="129"/>
       <c r="AB21" s="50"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="131"/>
+      <c r="AD21" s="129"/>
       <c r="AE21" s="50"/>
-      <c r="AF21" s="131"/>
+      <c r="AF21" s="129"/>
       <c r="AG21" s="50"/>
-      <c r="AH21" s="131"/>
+      <c r="AH21" s="129"/>
       <c r="AI21" s="50"/>
-      <c r="AJ21" s="131"/>
+      <c r="AJ21" s="129"/>
       <c r="AK21" s="50"/>
-      <c r="AL21" s="131"/>
+      <c r="AL21" s="129"/>
       <c r="AM21" s="50"/>
-      <c r="AN21" s="131"/>
+      <c r="AN21" s="129"/>
       <c r="AO21" s="50"/>
-      <c r="AP21" s="131"/>
+      <c r="AP21" s="129"/>
       <c r="AQ21" s="50"/>
-      <c r="AR21" s="131"/>
+      <c r="AR21" s="129"/>
       <c r="AS21" s="50"/>
-      <c r="AT21" s="131"/>
+      <c r="AT21" s="129"/>
       <c r="AU21" s="50"/>
-      <c r="AV21" s="131"/>
+      <c r="AV21" s="129"/>
       <c r="AW21" s="50"/>
-      <c r="AX21" s="131"/>
+      <c r="AX21" s="129"/>
       <c r="AY21" s="50"/>
-      <c r="AZ21" s="131"/>
+      <c r="AZ21" s="129"/>
       <c r="BA21" s="50"/>
       <c r="BB21" s="36"/>
       <c r="BC21" s="36"/>
-      <c r="BD21" s="131"/>
+      <c r="BD21" s="129"/>
       <c r="BE21" s="50"/>
-      <c r="BF21" s="131"/>
+      <c r="BF21" s="129"/>
       <c r="BG21" s="50"/>
-      <c r="BH21" s="131"/>
+      <c r="BH21" s="129"/>
       <c r="BI21" s="50"/>
-      <c r="BJ21" s="131"/>
+      <c r="BJ21" s="129"/>
       <c r="BK21" s="50"/>
-      <c r="BL21" s="131"/>
+      <c r="BL21" s="129"/>
       <c r="BM21" s="50"/>
-      <c r="BN21" s="131"/>
+      <c r="BN21" s="129"/>
       <c r="BO21" s="50"/>
-      <c r="BP21" s="131"/>
+      <c r="BP21" s="129"/>
       <c r="BQ21" s="50"/>
-      <c r="BR21" s="131"/>
+      <c r="BR21" s="129"/>
       <c r="BS21" s="50"/>
-      <c r="BT21" s="131"/>
+      <c r="BT21" s="129"/>
       <c r="BU21" s="50"/>
-      <c r="BV21" s="131"/>
+      <c r="BV21" s="129"/>
       <c r="BW21" s="50"/>
     </row>
     <row r="22" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A22" s="133"/>
+      <c r="A22" s="131"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="133"/>
+      <c r="C22" s="131"/>
       <c r="D22" s="42"/>
-      <c r="E22" s="133"/>
+      <c r="E22" s="131"/>
       <c r="F22" s="42"/>
-      <c r="G22" s="133"/>
+      <c r="G22" s="131"/>
       <c r="H22" s="42"/>
-      <c r="I22" s="133"/>
+      <c r="I22" s="131"/>
       <c r="J22" s="42"/>
-      <c r="K22" s="133"/>
+      <c r="K22" s="131"/>
       <c r="L22" s="42"/>
-      <c r="M22" s="133"/>
+      <c r="M22" s="131"/>
       <c r="N22" s="42"/>
-      <c r="O22" s="133"/>
+      <c r="O22" s="131"/>
       <c r="P22" s="42"/>
-      <c r="Q22" s="133"/>
+      <c r="Q22" s="131"/>
       <c r="R22" s="42"/>
-      <c r="S22" s="133"/>
+      <c r="S22" s="131"/>
       <c r="T22" s="42"/>
-      <c r="U22" s="133"/>
+      <c r="U22" s="131"/>
       <c r="V22" s="42"/>
-      <c r="W22" s="133"/>
+      <c r="W22" s="131"/>
       <c r="X22" s="42"/>
-      <c r="Y22" s="133"/>
+      <c r="Y22" s="131"/>
       <c r="Z22" s="42"/>
-      <c r="AA22" s="133"/>
+      <c r="AA22" s="131"/>
       <c r="AB22" s="42"/>
-      <c r="AC22" s="133"/>
+      <c r="AC22" s="131"/>
       <c r="AD22" s="42"/>
-      <c r="AE22" s="133"/>
+      <c r="AE22" s="131"/>
       <c r="AF22" s="42"/>
-      <c r="AG22" s="133"/>
+      <c r="AG22" s="131"/>
       <c r="AH22" s="42"/>
-      <c r="AI22" s="133"/>
+      <c r="AI22" s="131"/>
       <c r="AJ22" s="42"/>
-      <c r="AK22" s="133"/>
+      <c r="AK22" s="131"/>
       <c r="AL22" s="42"/>
-      <c r="AM22" s="133"/>
+      <c r="AM22" s="131"/>
       <c r="AN22" s="42"/>
-      <c r="AO22" s="133"/>
+      <c r="AO22" s="131"/>
       <c r="AP22" s="42"/>
-      <c r="AQ22" s="133"/>
+      <c r="AQ22" s="131"/>
       <c r="AR22" s="42"/>
-      <c r="AS22" s="133"/>
+      <c r="AS22" s="131"/>
       <c r="AT22" s="42"/>
-      <c r="AU22" s="133"/>
+      <c r="AU22" s="131"/>
       <c r="AV22" s="42"/>
-      <c r="AW22" s="133"/>
+      <c r="AW22" s="131"/>
       <c r="AX22" s="42"/>
-      <c r="AY22" s="133"/>
+      <c r="AY22" s="131"/>
       <c r="AZ22" s="42"/>
-      <c r="BA22" s="133"/>
+      <c r="BA22" s="131"/>
       <c r="BB22" s="42"/>
-      <c r="BC22" s="133"/>
+      <c r="BC22" s="131"/>
       <c r="BD22" s="42"/>
-      <c r="BE22" s="133"/>
+      <c r="BE22" s="131"/>
       <c r="BF22" s="42"/>
-      <c r="BG22" s="133"/>
+      <c r="BG22" s="131"/>
       <c r="BH22" s="42"/>
-      <c r="BI22" s="133"/>
+      <c r="BI22" s="131"/>
       <c r="BJ22" s="42"/>
-      <c r="BK22" s="133"/>
+      <c r="BK22" s="131"/>
       <c r="BL22" s="42"/>
-      <c r="BM22" s="133"/>
+      <c r="BM22" s="131"/>
       <c r="BN22" s="42"/>
-      <c r="BO22" s="133"/>
+      <c r="BO22" s="131"/>
       <c r="BP22" s="42"/>
-      <c r="BQ22" s="133"/>
+      <c r="BQ22" s="131"/>
       <c r="BR22" s="42"/>
-      <c r="BS22" s="133"/>
+      <c r="BS22" s="131"/>
       <c r="BT22" s="42"/>
-      <c r="BU22" s="133"/>
+      <c r="BU22" s="131"/>
       <c r="BV22" s="42"/>
       <c r="BW22" s="39"/>
     </row>
     <row r="23" spans="1:75" ht="17.25" customHeight="1">
       <c r="A23" s="36"/>
-      <c r="B23" s="134"/>
+      <c r="B23" s="132"/>
       <c r="C23" s="42"/>
-      <c r="D23" s="134"/>
+      <c r="D23" s="132"/>
       <c r="E23" s="42"/>
-      <c r="F23" s="134"/>
+      <c r="F23" s="132"/>
       <c r="G23" s="42"/>
       <c r="H23" s="36"/>
-      <c r="I23" s="131"/>
+      <c r="I23" s="129"/>
       <c r="J23" s="50"/>
-      <c r="K23" s="131"/>
+      <c r="K23" s="129"/>
       <c r="L23" s="50"/>
-      <c r="M23" s="132" t="s">
+      <c r="M23" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N23" s="53"/>
-      <c r="O23" s="131"/>
+      <c r="O23" s="129"/>
       <c r="P23" s="50"/>
-      <c r="Q23" s="131"/>
+      <c r="Q23" s="129"/>
       <c r="R23" s="50"/>
-      <c r="S23" s="132" t="s">
+      <c r="S23" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T23" s="53"/>
-      <c r="U23" s="131"/>
+      <c r="U23" s="129"/>
       <c r="V23" s="50"/>
-      <c r="W23" s="131"/>
+      <c r="W23" s="129"/>
       <c r="X23" s="50"/>
-      <c r="Y23" s="131"/>
+      <c r="Y23" s="129"/>
       <c r="Z23" s="50"/>
-      <c r="AA23" s="131"/>
+      <c r="AA23" s="129"/>
       <c r="AB23" s="50"/>
       <c r="AC23" s="36"/>
-      <c r="AD23" s="131"/>
+      <c r="AD23" s="129"/>
       <c r="AE23" s="50"/>
-      <c r="AF23" s="131"/>
+      <c r="AF23" s="129"/>
       <c r="AG23" s="50"/>
-      <c r="AH23" s="131"/>
+      <c r="AH23" s="129"/>
       <c r="AI23" s="50"/>
-      <c r="AJ23" s="131"/>
+      <c r="AJ23" s="129"/>
       <c r="AK23" s="50"/>
-      <c r="AL23" s="131"/>
+      <c r="AL23" s="129"/>
       <c r="AM23" s="50"/>
-      <c r="AN23" s="131"/>
+      <c r="AN23" s="129"/>
       <c r="AO23" s="50"/>
-      <c r="AP23" s="131"/>
+      <c r="AP23" s="129"/>
       <c r="AQ23" s="50"/>
-      <c r="AR23" s="131"/>
+      <c r="AR23" s="129"/>
       <c r="AS23" s="50"/>
-      <c r="AT23" s="131"/>
+      <c r="AT23" s="129"/>
       <c r="AU23" s="50"/>
-      <c r="AV23" s="131"/>
+      <c r="AV23" s="129"/>
       <c r="AW23" s="50"/>
-      <c r="AX23" s="131"/>
+      <c r="AX23" s="129"/>
       <c r="AY23" s="50"/>
-      <c r="AZ23" s="131"/>
+      <c r="AZ23" s="129"/>
       <c r="BA23" s="50"/>
       <c r="BB23" s="36"/>
       <c r="BC23" s="36"/>
-      <c r="BD23" s="131"/>
+      <c r="BD23" s="129"/>
       <c r="BE23" s="50"/>
-      <c r="BF23" s="131"/>
+      <c r="BF23" s="129"/>
       <c r="BG23" s="50"/>
-      <c r="BH23" s="131"/>
+      <c r="BH23" s="129"/>
       <c r="BI23" s="50"/>
-      <c r="BJ23" s="131"/>
+      <c r="BJ23" s="129"/>
       <c r="BK23" s="50"/>
-      <c r="BL23" s="131"/>
+      <c r="BL23" s="129"/>
       <c r="BM23" s="50"/>
-      <c r="BN23" s="131"/>
+      <c r="BN23" s="129"/>
       <c r="BO23" s="50"/>
-      <c r="BP23" s="131"/>
+      <c r="BP23" s="129"/>
       <c r="BQ23" s="50"/>
-      <c r="BR23" s="131"/>
+      <c r="BR23" s="129"/>
       <c r="BS23" s="50"/>
-      <c r="BT23" s="131"/>
+      <c r="BT23" s="129"/>
       <c r="BU23" s="50"/>
-      <c r="BV23" s="131"/>
+      <c r="BV23" s="129"/>
       <c r="BW23" s="50"/>
     </row>
     <row r="24" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A24" s="119"/>
+      <c r="A24" s="118"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="119"/>
+      <c r="C24" s="118"/>
       <c r="D24" s="42"/>
-      <c r="E24" s="119"/>
+      <c r="E24" s="118"/>
       <c r="F24" s="42"/>
-      <c r="G24" s="119"/>
+      <c r="G24" s="118"/>
       <c r="H24" s="42"/>
-      <c r="I24" s="119"/>
+      <c r="I24" s="118"/>
       <c r="J24" s="42"/>
-      <c r="K24" s="119"/>
+      <c r="K24" s="118"/>
       <c r="L24" s="42"/>
-      <c r="M24" s="119"/>
+      <c r="M24" s="118"/>
       <c r="N24" s="42"/>
-      <c r="O24" s="119"/>
+      <c r="O24" s="118"/>
       <c r="P24" s="42"/>
-      <c r="Q24" s="119"/>
+      <c r="Q24" s="118"/>
       <c r="R24" s="42"/>
-      <c r="S24" s="119"/>
+      <c r="S24" s="118"/>
       <c r="T24" s="42"/>
-      <c r="U24" s="119"/>
+      <c r="U24" s="118"/>
       <c r="V24" s="42"/>
-      <c r="W24" s="119"/>
+      <c r="W24" s="118"/>
       <c r="X24" s="42"/>
-      <c r="Y24" s="119"/>
+      <c r="Y24" s="118"/>
       <c r="Z24" s="42"/>
-      <c r="AA24" s="119"/>
+      <c r="AA24" s="118"/>
       <c r="AB24" s="42"/>
-      <c r="AC24" s="119"/>
+      <c r="AC24" s="118"/>
       <c r="AD24" s="42"/>
-      <c r="AE24" s="119"/>
+      <c r="AE24" s="118"/>
       <c r="AF24" s="42"/>
-      <c r="AG24" s="119"/>
+      <c r="AG24" s="118"/>
       <c r="AH24" s="42"/>
-      <c r="AI24" s="119"/>
+      <c r="AI24" s="118"/>
       <c r="AJ24" s="42"/>
-      <c r="AK24" s="119"/>
+      <c r="AK24" s="118"/>
       <c r="AL24" s="42"/>
-      <c r="AM24" s="119"/>
+      <c r="AM24" s="118"/>
       <c r="AN24" s="42"/>
-      <c r="AO24" s="119"/>
+      <c r="AO24" s="118"/>
       <c r="AP24" s="42"/>
-      <c r="AQ24" s="119"/>
+      <c r="AQ24" s="118"/>
       <c r="AR24" s="42"/>
-      <c r="AS24" s="119"/>
+      <c r="AS24" s="118"/>
       <c r="AT24" s="42"/>
-      <c r="AU24" s="119"/>
+      <c r="AU24" s="118"/>
       <c r="AV24" s="42"/>
-      <c r="AW24" s="119"/>
+      <c r="AW24" s="118"/>
       <c r="AX24" s="42"/>
-      <c r="AY24" s="119"/>
+      <c r="AY24" s="118"/>
       <c r="AZ24" s="42"/>
-      <c r="BA24" s="119"/>
+      <c r="BA24" s="118"/>
       <c r="BB24" s="42"/>
-      <c r="BC24" s="119"/>
+      <c r="BC24" s="118"/>
       <c r="BD24" s="42"/>
-      <c r="BE24" s="119"/>
+      <c r="BE24" s="118"/>
       <c r="BF24" s="42"/>
-      <c r="BG24" s="119"/>
+      <c r="BG24" s="118"/>
       <c r="BH24" s="42"/>
-      <c r="BI24" s="119"/>
+      <c r="BI24" s="118"/>
       <c r="BJ24" s="42"/>
-      <c r="BK24" s="119"/>
+      <c r="BK24" s="118"/>
       <c r="BL24" s="42"/>
-      <c r="BM24" s="119"/>
+      <c r="BM24" s="118"/>
       <c r="BN24" s="42"/>
-      <c r="BO24" s="119"/>
+      <c r="BO24" s="118"/>
       <c r="BP24" s="42"/>
-      <c r="BQ24" s="119"/>
+      <c r="BQ24" s="118"/>
       <c r="BR24" s="42"/>
-      <c r="BS24" s="119"/>
+      <c r="BS24" s="118"/>
       <c r="BT24" s="42"/>
-      <c r="BU24" s="119"/>
+      <c r="BU24" s="118"/>
       <c r="BV24" s="42"/>
       <c r="BW24" s="36"/>
     </row>
     <row r="25" spans="1:75" ht="17.25" customHeight="1">
       <c r="A25" s="36"/>
-      <c r="B25" s="131"/>
+      <c r="B25" s="129"/>
       <c r="C25" s="50"/>
-      <c r="D25" s="131"/>
+      <c r="D25" s="129"/>
       <c r="E25" s="50"/>
-      <c r="F25" s="131"/>
+      <c r="F25" s="129"/>
       <c r="G25" s="50"/>
       <c r="H25" s="36"/>
-      <c r="I25" s="131"/>
+      <c r="I25" s="129"/>
       <c r="J25" s="50"/>
-      <c r="K25" s="131"/>
+      <c r="K25" s="129"/>
       <c r="L25" s="50"/>
-      <c r="M25" s="132" t="s">
+      <c r="M25" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N25" s="53"/>
-      <c r="O25" s="131"/>
+      <c r="O25" s="129"/>
       <c r="P25" s="50"/>
-      <c r="Q25" s="131"/>
+      <c r="Q25" s="129"/>
       <c r="R25" s="50"/>
-      <c r="S25" s="132" t="s">
+      <c r="S25" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T25" s="53"/>
-      <c r="U25" s="131"/>
+      <c r="U25" s="129"/>
       <c r="V25" s="50"/>
-      <c r="W25" s="131"/>
+      <c r="W25" s="129"/>
       <c r="X25" s="50"/>
-      <c r="Y25" s="131"/>
+      <c r="Y25" s="129"/>
       <c r="Z25" s="50"/>
-      <c r="AA25" s="131"/>
+      <c r="AA25" s="129"/>
       <c r="AB25" s="50"/>
       <c r="AC25" s="36"/>
-      <c r="AD25" s="131"/>
+      <c r="AD25" s="129"/>
       <c r="AE25" s="50"/>
-      <c r="AF25" s="131"/>
+      <c r="AF25" s="129"/>
       <c r="AG25" s="50"/>
-      <c r="AH25" s="131"/>
+      <c r="AH25" s="129"/>
       <c r="AI25" s="50"/>
-      <c r="AJ25" s="131"/>
+      <c r="AJ25" s="129"/>
       <c r="AK25" s="50"/>
-      <c r="AL25" s="131"/>
+      <c r="AL25" s="129"/>
       <c r="AM25" s="50"/>
-      <c r="AN25" s="131"/>
+      <c r="AN25" s="129"/>
       <c r="AO25" s="50"/>
-      <c r="AP25" s="131"/>
+      <c r="AP25" s="129"/>
       <c r="AQ25" s="50"/>
-      <c r="AR25" s="131"/>
+      <c r="AR25" s="129"/>
       <c r="AS25" s="50"/>
-      <c r="AT25" s="131"/>
+      <c r="AT25" s="129"/>
       <c r="AU25" s="50"/>
-      <c r="AV25" s="131"/>
+      <c r="AV25" s="129"/>
       <c r="AW25" s="50"/>
-      <c r="AX25" s="131"/>
+      <c r="AX25" s="129"/>
       <c r="AY25" s="50"/>
-      <c r="AZ25" s="131"/>
+      <c r="AZ25" s="129"/>
       <c r="BA25" s="50"/>
       <c r="BB25" s="36"/>
       <c r="BC25" s="36"/>
-      <c r="BD25" s="131"/>
+      <c r="BD25" s="129"/>
       <c r="BE25" s="50"/>
-      <c r="BF25" s="131"/>
+      <c r="BF25" s="129"/>
       <c r="BG25" s="50"/>
-      <c r="BH25" s="131"/>
+      <c r="BH25" s="129"/>
       <c r="BI25" s="50"/>
-      <c r="BJ25" s="131"/>
+      <c r="BJ25" s="129"/>
       <c r="BK25" s="50"/>
-      <c r="BL25" s="131"/>
+      <c r="BL25" s="129"/>
       <c r="BM25" s="50"/>
-      <c r="BN25" s="131"/>
+      <c r="BN25" s="129"/>
       <c r="BO25" s="50"/>
-      <c r="BP25" s="131"/>
+      <c r="BP25" s="129"/>
       <c r="BQ25" s="50"/>
-      <c r="BR25" s="131"/>
+      <c r="BR25" s="129"/>
       <c r="BS25" s="50"/>
-      <c r="BT25" s="131"/>
+      <c r="BT25" s="129"/>
       <c r="BU25" s="50"/>
-      <c r="BV25" s="131"/>
+      <c r="BV25" s="129"/>
       <c r="BW25" s="50"/>
     </row>
     <row r="26" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A26" s="133"/>
+      <c r="A26" s="131"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="133"/>
+      <c r="C26" s="131"/>
       <c r="D26" s="42"/>
-      <c r="E26" s="133"/>
+      <c r="E26" s="131"/>
       <c r="F26" s="42"/>
-      <c r="G26" s="133"/>
+      <c r="G26" s="131"/>
       <c r="H26" s="42"/>
-      <c r="I26" s="133"/>
+      <c r="I26" s="131"/>
       <c r="J26" s="42"/>
-      <c r="K26" s="133"/>
+      <c r="K26" s="131"/>
       <c r="L26" s="42"/>
-      <c r="M26" s="133"/>
+      <c r="M26" s="131"/>
       <c r="N26" s="42"/>
-      <c r="O26" s="133"/>
+      <c r="O26" s="131"/>
       <c r="P26" s="42"/>
-      <c r="Q26" s="133"/>
+      <c r="Q26" s="131"/>
       <c r="R26" s="42"/>
-      <c r="S26" s="133"/>
+      <c r="S26" s="131"/>
       <c r="T26" s="42"/>
-      <c r="U26" s="133"/>
+      <c r="U26" s="131"/>
       <c r="V26" s="42"/>
-      <c r="W26" s="133"/>
+      <c r="W26" s="131"/>
       <c r="X26" s="42"/>
-      <c r="Y26" s="133"/>
+      <c r="Y26" s="131"/>
       <c r="Z26" s="42"/>
-      <c r="AA26" s="133"/>
+      <c r="AA26" s="131"/>
       <c r="AB26" s="42"/>
-      <c r="AC26" s="133"/>
+      <c r="AC26" s="131"/>
       <c r="AD26" s="42"/>
-      <c r="AE26" s="133"/>
+      <c r="AE26" s="131"/>
       <c r="AF26" s="42"/>
-      <c r="AG26" s="133"/>
+      <c r="AG26" s="131"/>
       <c r="AH26" s="42"/>
-      <c r="AI26" s="133"/>
+      <c r="AI26" s="131"/>
       <c r="AJ26" s="42"/>
-      <c r="AK26" s="133"/>
+      <c r="AK26" s="131"/>
       <c r="AL26" s="42"/>
-      <c r="AM26" s="133"/>
+      <c r="AM26" s="131"/>
       <c r="AN26" s="42"/>
-      <c r="AO26" s="133"/>
+      <c r="AO26" s="131"/>
       <c r="AP26" s="42"/>
-      <c r="AQ26" s="133"/>
+      <c r="AQ26" s="131"/>
       <c r="AR26" s="42"/>
-      <c r="AS26" s="133"/>
+      <c r="AS26" s="131"/>
       <c r="AT26" s="42"/>
-      <c r="AU26" s="133"/>
+      <c r="AU26" s="131"/>
       <c r="AV26" s="42"/>
-      <c r="AW26" s="133"/>
+      <c r="AW26" s="131"/>
       <c r="AX26" s="42"/>
-      <c r="AY26" s="133"/>
+      <c r="AY26" s="131"/>
       <c r="AZ26" s="42"/>
-      <c r="BA26" s="133"/>
+      <c r="BA26" s="131"/>
       <c r="BB26" s="42"/>
-      <c r="BC26" s="133"/>
+      <c r="BC26" s="131"/>
       <c r="BD26" s="42"/>
-      <c r="BE26" s="133"/>
+      <c r="BE26" s="131"/>
       <c r="BF26" s="42"/>
-      <c r="BG26" s="133"/>
+      <c r="BG26" s="131"/>
       <c r="BH26" s="42"/>
-      <c r="BI26" s="133"/>
+      <c r="BI26" s="131"/>
       <c r="BJ26" s="42"/>
-      <c r="BK26" s="133"/>
+      <c r="BK26" s="131"/>
       <c r="BL26" s="42"/>
-      <c r="BM26" s="133"/>
+      <c r="BM26" s="131"/>
       <c r="BN26" s="42"/>
-      <c r="BO26" s="133"/>
+      <c r="BO26" s="131"/>
       <c r="BP26" s="42"/>
-      <c r="BQ26" s="133"/>
+      <c r="BQ26" s="131"/>
       <c r="BR26" s="42"/>
-      <c r="BS26" s="133"/>
+      <c r="BS26" s="131"/>
       <c r="BT26" s="42"/>
-      <c r="BU26" s="133"/>
+      <c r="BU26" s="131"/>
       <c r="BV26" s="42"/>
       <c r="BW26" s="39"/>
     </row>
     <row r="27" spans="1:75" ht="17.25" customHeight="1">
       <c r="A27" s="36"/>
-      <c r="B27" s="134"/>
+      <c r="B27" s="132"/>
       <c r="C27" s="42"/>
-      <c r="D27" s="134"/>
+      <c r="D27" s="132"/>
       <c r="E27" s="42"/>
-      <c r="F27" s="134"/>
+      <c r="F27" s="132"/>
       <c r="G27" s="42"/>
       <c r="H27" s="36"/>
-      <c r="I27" s="131"/>
+      <c r="I27" s="129"/>
       <c r="J27" s="50"/>
-      <c r="K27" s="131"/>
+      <c r="K27" s="129"/>
       <c r="L27" s="50"/>
-      <c r="M27" s="132" t="s">
+      <c r="M27" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N27" s="53"/>
-      <c r="O27" s="131"/>
+      <c r="O27" s="129"/>
       <c r="P27" s="50"/>
-      <c r="Q27" s="131"/>
+      <c r="Q27" s="129"/>
       <c r="R27" s="50"/>
-      <c r="S27" s="132" t="s">
+      <c r="S27" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T27" s="53"/>
-      <c r="U27" s="131"/>
+      <c r="U27" s="129"/>
       <c r="V27" s="50"/>
-      <c r="W27" s="131"/>
+      <c r="W27" s="129"/>
       <c r="X27" s="50"/>
-      <c r="Y27" s="131"/>
+      <c r="Y27" s="129"/>
       <c r="Z27" s="50"/>
-      <c r="AA27" s="131"/>
+      <c r="AA27" s="129"/>
       <c r="AB27" s="50"/>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="131"/>
+      <c r="AD27" s="129"/>
       <c r="AE27" s="50"/>
-      <c r="AF27" s="131"/>
+      <c r="AF27" s="129"/>
       <c r="AG27" s="50"/>
-      <c r="AH27" s="131"/>
+      <c r="AH27" s="129"/>
       <c r="AI27" s="50"/>
-      <c r="AJ27" s="131"/>
+      <c r="AJ27" s="129"/>
       <c r="AK27" s="50"/>
-      <c r="AL27" s="131"/>
+      <c r="AL27" s="129"/>
       <c r="AM27" s="50"/>
-      <c r="AN27" s="131"/>
+      <c r="AN27" s="129"/>
       <c r="AO27" s="50"/>
-      <c r="AP27" s="131"/>
+      <c r="AP27" s="129"/>
       <c r="AQ27" s="50"/>
-      <c r="AR27" s="131"/>
+      <c r="AR27" s="129"/>
       <c r="AS27" s="50"/>
-      <c r="AT27" s="131"/>
+      <c r="AT27" s="129"/>
       <c r="AU27" s="50"/>
-      <c r="AV27" s="131"/>
+      <c r="AV27" s="129"/>
       <c r="AW27" s="50"/>
-      <c r="AX27" s="131"/>
+      <c r="AX27" s="129"/>
       <c r="AY27" s="50"/>
-      <c r="AZ27" s="131"/>
+      <c r="AZ27" s="129"/>
       <c r="BA27" s="50"/>
       <c r="BB27" s="36"/>
       <c r="BC27" s="36"/>
-      <c r="BD27" s="131"/>
+      <c r="BD27" s="129"/>
       <c r="BE27" s="50"/>
-      <c r="BF27" s="131"/>
+      <c r="BF27" s="129"/>
       <c r="BG27" s="50"/>
-      <c r="BH27" s="131"/>
+      <c r="BH27" s="129"/>
       <c r="BI27" s="50"/>
-      <c r="BJ27" s="131"/>
+      <c r="BJ27" s="129"/>
       <c r="BK27" s="50"/>
-      <c r="BL27" s="131"/>
+      <c r="BL27" s="129"/>
       <c r="BM27" s="50"/>
-      <c r="BN27" s="131"/>
+      <c r="BN27" s="129"/>
       <c r="BO27" s="50"/>
-      <c r="BP27" s="131"/>
+      <c r="BP27" s="129"/>
       <c r="BQ27" s="50"/>
-      <c r="BR27" s="131"/>
+      <c r="BR27" s="129"/>
       <c r="BS27" s="50"/>
-      <c r="BT27" s="131"/>
+      <c r="BT27" s="129"/>
       <c r="BU27" s="50"/>
-      <c r="BV27" s="131"/>
+      <c r="BV27" s="129"/>
       <c r="BW27" s="50"/>
     </row>
     <row r="28" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A28" s="119"/>
+      <c r="A28" s="118"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="119"/>
+      <c r="C28" s="118"/>
       <c r="D28" s="42"/>
-      <c r="E28" s="119"/>
+      <c r="E28" s="118"/>
       <c r="F28" s="42"/>
-      <c r="G28" s="119"/>
+      <c r="G28" s="118"/>
       <c r="H28" s="42"/>
-      <c r="I28" s="119"/>
+      <c r="I28" s="118"/>
       <c r="J28" s="42"/>
-      <c r="K28" s="119"/>
+      <c r="K28" s="118"/>
       <c r="L28" s="42"/>
-      <c r="M28" s="119"/>
+      <c r="M28" s="118"/>
       <c r="N28" s="42"/>
-      <c r="O28" s="119"/>
+      <c r="O28" s="118"/>
       <c r="P28" s="42"/>
-      <c r="Q28" s="119"/>
+      <c r="Q28" s="118"/>
       <c r="R28" s="42"/>
-      <c r="S28" s="119"/>
+      <c r="S28" s="118"/>
       <c r="T28" s="42"/>
-      <c r="U28" s="119"/>
+      <c r="U28" s="118"/>
       <c r="V28" s="42"/>
-      <c r="W28" s="119"/>
+      <c r="W28" s="118"/>
       <c r="X28" s="42"/>
-      <c r="Y28" s="119"/>
+      <c r="Y28" s="118"/>
       <c r="Z28" s="42"/>
-      <c r="AA28" s="119"/>
+      <c r="AA28" s="118"/>
       <c r="AB28" s="42"/>
-      <c r="AC28" s="119"/>
+      <c r="AC28" s="118"/>
       <c r="AD28" s="42"/>
-      <c r="AE28" s="119"/>
+      <c r="AE28" s="118"/>
       <c r="AF28" s="42"/>
-      <c r="AG28" s="119"/>
+      <c r="AG28" s="118"/>
       <c r="AH28" s="42"/>
-      <c r="AI28" s="119"/>
+      <c r="AI28" s="118"/>
       <c r="AJ28" s="42"/>
-      <c r="AK28" s="119"/>
+      <c r="AK28" s="118"/>
       <c r="AL28" s="42"/>
-      <c r="AM28" s="119"/>
+      <c r="AM28" s="118"/>
       <c r="AN28" s="42"/>
-      <c r="AO28" s="119"/>
+      <c r="AO28" s="118"/>
       <c r="AP28" s="42"/>
-      <c r="AQ28" s="119"/>
+      <c r="AQ28" s="118"/>
       <c r="AR28" s="42"/>
-      <c r="AS28" s="119"/>
+      <c r="AS28" s="118"/>
       <c r="AT28" s="42"/>
-      <c r="AU28" s="119"/>
+      <c r="AU28" s="118"/>
       <c r="AV28" s="42"/>
-      <c r="AW28" s="119"/>
+      <c r="AW28" s="118"/>
       <c r="AX28" s="42"/>
-      <c r="AY28" s="119"/>
+      <c r="AY28" s="118"/>
       <c r="AZ28" s="42"/>
-      <c r="BA28" s="119"/>
+      <c r="BA28" s="118"/>
       <c r="BB28" s="42"/>
-      <c r="BC28" s="119"/>
+      <c r="BC28" s="118"/>
       <c r="BD28" s="42"/>
-      <c r="BE28" s="119"/>
+      <c r="BE28" s="118"/>
       <c r="BF28" s="42"/>
-      <c r="BG28" s="119"/>
+      <c r="BG28" s="118"/>
       <c r="BH28" s="42"/>
-      <c r="BI28" s="119"/>
+      <c r="BI28" s="118"/>
       <c r="BJ28" s="42"/>
-      <c r="BK28" s="119"/>
+      <c r="BK28" s="118"/>
       <c r="BL28" s="42"/>
-      <c r="BM28" s="119"/>
+      <c r="BM28" s="118"/>
       <c r="BN28" s="42"/>
-      <c r="BO28" s="119"/>
+      <c r="BO28" s="118"/>
       <c r="BP28" s="42"/>
-      <c r="BQ28" s="119"/>
+      <c r="BQ28" s="118"/>
       <c r="BR28" s="42"/>
-      <c r="BS28" s="119"/>
+      <c r="BS28" s="118"/>
       <c r="BT28" s="42"/>
-      <c r="BU28" s="119"/>
+      <c r="BU28" s="118"/>
       <c r="BV28" s="42"/>
       <c r="BW28" s="36"/>
     </row>
     <row r="29" spans="1:75" ht="17.25" customHeight="1">
       <c r="A29" s="36"/>
-      <c r="B29" s="131"/>
+      <c r="B29" s="129"/>
       <c r="C29" s="50"/>
-      <c r="D29" s="131"/>
+      <c r="D29" s="129"/>
       <c r="E29" s="50"/>
-      <c r="F29" s="131"/>
+      <c r="F29" s="129"/>
       <c r="G29" s="50"/>
       <c r="H29" s="36"/>
-      <c r="I29" s="131"/>
+      <c r="I29" s="129"/>
       <c r="J29" s="50"/>
-      <c r="K29" s="131"/>
+      <c r="K29" s="129"/>
       <c r="L29" s="50"/>
-      <c r="M29" s="132" t="s">
+      <c r="M29" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N29" s="53"/>
-      <c r="O29" s="131"/>
+      <c r="O29" s="129"/>
       <c r="P29" s="50"/>
-      <c r="Q29" s="131"/>
+      <c r="Q29" s="129"/>
       <c r="R29" s="50"/>
-      <c r="S29" s="132" t="s">
+      <c r="S29" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T29" s="53"/>
-      <c r="U29" s="131"/>
+      <c r="U29" s="129"/>
       <c r="V29" s="50"/>
-      <c r="W29" s="131"/>
+      <c r="W29" s="129"/>
       <c r="X29" s="50"/>
-      <c r="Y29" s="131"/>
+      <c r="Y29" s="129"/>
       <c r="Z29" s="50"/>
-      <c r="AA29" s="131"/>
+      <c r="AA29" s="129"/>
       <c r="AB29" s="50"/>
       <c r="AC29" s="36"/>
-      <c r="AD29" s="131"/>
+      <c r="AD29" s="129"/>
       <c r="AE29" s="50"/>
-      <c r="AF29" s="131"/>
+      <c r="AF29" s="129"/>
       <c r="AG29" s="50"/>
-      <c r="AH29" s="131"/>
+      <c r="AH29" s="129"/>
       <c r="AI29" s="50"/>
-      <c r="AJ29" s="131"/>
+      <c r="AJ29" s="129"/>
       <c r="AK29" s="50"/>
-      <c r="AL29" s="131"/>
+      <c r="AL29" s="129"/>
       <c r="AM29" s="50"/>
-      <c r="AN29" s="131"/>
+      <c r="AN29" s="129"/>
       <c r="AO29" s="50"/>
-      <c r="AP29" s="131"/>
+      <c r="AP29" s="129"/>
       <c r="AQ29" s="50"/>
-      <c r="AR29" s="131"/>
+      <c r="AR29" s="129"/>
       <c r="AS29" s="50"/>
-      <c r="AT29" s="131"/>
+      <c r="AT29" s="129"/>
       <c r="AU29" s="50"/>
-      <c r="AV29" s="131"/>
+      <c r="AV29" s="129"/>
       <c r="AW29" s="50"/>
-      <c r="AX29" s="131"/>
+      <c r="AX29" s="129"/>
       <c r="AY29" s="50"/>
-      <c r="AZ29" s="131"/>
+      <c r="AZ29" s="129"/>
       <c r="BA29" s="50"/>
       <c r="BB29" s="36"/>
       <c r="BC29" s="36"/>
-      <c r="BD29" s="131"/>
+      <c r="BD29" s="129"/>
       <c r="BE29" s="50"/>
-      <c r="BF29" s="131"/>
+      <c r="BF29" s="129"/>
       <c r="BG29" s="50"/>
-      <c r="BH29" s="131"/>
+      <c r="BH29" s="129"/>
       <c r="BI29" s="50"/>
-      <c r="BJ29" s="131"/>
+      <c r="BJ29" s="129"/>
       <c r="BK29" s="50"/>
-      <c r="BL29" s="131"/>
+      <c r="BL29" s="129"/>
       <c r="BM29" s="50"/>
-      <c r="BN29" s="131"/>
+      <c r="BN29" s="129"/>
       <c r="BO29" s="50"/>
-      <c r="BP29" s="131"/>
+      <c r="BP29" s="129"/>
       <c r="BQ29" s="50"/>
-      <c r="BR29" s="131"/>
+      <c r="BR29" s="129"/>
       <c r="BS29" s="50"/>
-      <c r="BT29" s="131"/>
+      <c r="BT29" s="129"/>
       <c r="BU29" s="50"/>
-      <c r="BV29" s="131"/>
+      <c r="BV29" s="129"/>
       <c r="BW29" s="50"/>
     </row>
     <row r="30" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A30" s="133"/>
+      <c r="A30" s="131"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="133"/>
+      <c r="C30" s="131"/>
       <c r="D30" s="42"/>
-      <c r="E30" s="133"/>
+      <c r="E30" s="131"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="133"/>
+      <c r="G30" s="131"/>
       <c r="H30" s="42"/>
-      <c r="I30" s="133"/>
+      <c r="I30" s="131"/>
       <c r="J30" s="42"/>
-      <c r="K30" s="133"/>
+      <c r="K30" s="131"/>
       <c r="L30" s="42"/>
-      <c r="M30" s="133"/>
+      <c r="M30" s="131"/>
       <c r="N30" s="42"/>
-      <c r="O30" s="133"/>
+      <c r="O30" s="131"/>
       <c r="P30" s="42"/>
-      <c r="Q30" s="133"/>
+      <c r="Q30" s="131"/>
       <c r="R30" s="42"/>
-      <c r="S30" s="133"/>
+      <c r="S30" s="131"/>
       <c r="T30" s="42"/>
-      <c r="U30" s="133"/>
+      <c r="U30" s="131"/>
       <c r="V30" s="42"/>
-      <c r="W30" s="133"/>
+      <c r="W30" s="131"/>
       <c r="X30" s="42"/>
-      <c r="Y30" s="133"/>
+      <c r="Y30" s="131"/>
       <c r="Z30" s="42"/>
-      <c r="AA30" s="133"/>
+      <c r="AA30" s="131"/>
       <c r="AB30" s="42"/>
-      <c r="AC30" s="133"/>
+      <c r="AC30" s="131"/>
       <c r="AD30" s="42"/>
-      <c r="AE30" s="133"/>
+      <c r="AE30" s="131"/>
       <c r="AF30" s="42"/>
-      <c r="AG30" s="133"/>
+      <c r="AG30" s="131"/>
       <c r="AH30" s="42"/>
-      <c r="AI30" s="133"/>
+      <c r="AI30" s="131"/>
       <c r="AJ30" s="42"/>
-      <c r="AK30" s="133"/>
+      <c r="AK30" s="131"/>
       <c r="AL30" s="42"/>
-      <c r="AM30" s="133"/>
+      <c r="AM30" s="131"/>
       <c r="AN30" s="42"/>
-      <c r="AO30" s="133"/>
+      <c r="AO30" s="131"/>
       <c r="AP30" s="42"/>
-      <c r="AQ30" s="133"/>
+      <c r="AQ30" s="131"/>
       <c r="AR30" s="42"/>
-      <c r="AS30" s="133"/>
+      <c r="AS30" s="131"/>
       <c r="AT30" s="42"/>
-      <c r="AU30" s="133"/>
+      <c r="AU30" s="131"/>
       <c r="AV30" s="42"/>
-      <c r="AW30" s="133"/>
+      <c r="AW30" s="131"/>
       <c r="AX30" s="42"/>
-      <c r="AY30" s="133"/>
+      <c r="AY30" s="131"/>
       <c r="AZ30" s="42"/>
-      <c r="BA30" s="133"/>
+      <c r="BA30" s="131"/>
       <c r="BB30" s="42"/>
-      <c r="BC30" s="133"/>
+      <c r="BC30" s="131"/>
       <c r="BD30" s="42"/>
-      <c r="BE30" s="133"/>
+      <c r="BE30" s="131"/>
       <c r="BF30" s="42"/>
-      <c r="BG30" s="133"/>
+      <c r="BG30" s="131"/>
       <c r="BH30" s="42"/>
-      <c r="BI30" s="133"/>
+      <c r="BI30" s="131"/>
       <c r="BJ30" s="42"/>
-      <c r="BK30" s="133"/>
+      <c r="BK30" s="131"/>
       <c r="BL30" s="42"/>
-      <c r="BM30" s="133"/>
+      <c r="BM30" s="131"/>
       <c r="BN30" s="42"/>
-      <c r="BO30" s="133"/>
+      <c r="BO30" s="131"/>
       <c r="BP30" s="42"/>
-      <c r="BQ30" s="133"/>
+      <c r="BQ30" s="131"/>
       <c r="BR30" s="42"/>
-      <c r="BS30" s="133"/>
+      <c r="BS30" s="131"/>
       <c r="BT30" s="42"/>
-      <c r="BU30" s="133"/>
+      <c r="BU30" s="131"/>
       <c r="BV30" s="42"/>
       <c r="BW30" s="39"/>
     </row>
     <row r="31" spans="1:75" ht="17.25" customHeight="1">
       <c r="A31" s="36"/>
-      <c r="B31" s="134"/>
+      <c r="B31" s="132"/>
       <c r="C31" s="42"/>
-      <c r="D31" s="134"/>
+      <c r="D31" s="132"/>
       <c r="E31" s="42"/>
-      <c r="F31" s="134"/>
+      <c r="F31" s="132"/>
       <c r="G31" s="42"/>
       <c r="H31" s="36"/>
-      <c r="I31" s="131"/>
+      <c r="I31" s="129"/>
       <c r="J31" s="50"/>
-      <c r="K31" s="131"/>
+      <c r="K31" s="129"/>
       <c r="L31" s="50"/>
-      <c r="M31" s="132" t="s">
+      <c r="M31" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N31" s="53"/>
-      <c r="O31" s="131"/>
+      <c r="O31" s="129"/>
       <c r="P31" s="50"/>
-      <c r="Q31" s="131"/>
+      <c r="Q31" s="129"/>
       <c r="R31" s="50"/>
-      <c r="S31" s="132" t="s">
+      <c r="S31" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T31" s="53"/>
-      <c r="U31" s="131"/>
+      <c r="U31" s="129"/>
       <c r="V31" s="50"/>
-      <c r="W31" s="131"/>
+      <c r="W31" s="129"/>
       <c r="X31" s="50"/>
-      <c r="Y31" s="131"/>
+      <c r="Y31" s="129"/>
       <c r="Z31" s="50"/>
-      <c r="AA31" s="131"/>
+      <c r="AA31" s="129"/>
       <c r="AB31" s="50"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="131"/>
+      <c r="AD31" s="129"/>
       <c r="AE31" s="50"/>
-      <c r="AF31" s="131"/>
+      <c r="AF31" s="129"/>
       <c r="AG31" s="50"/>
-      <c r="AH31" s="131"/>
+      <c r="AH31" s="129"/>
       <c r="AI31" s="50"/>
-      <c r="AJ31" s="131"/>
+      <c r="AJ31" s="129"/>
       <c r="AK31" s="50"/>
-      <c r="AL31" s="131"/>
+      <c r="AL31" s="129"/>
       <c r="AM31" s="50"/>
-      <c r="AN31" s="131"/>
+      <c r="AN31" s="129"/>
       <c r="AO31" s="50"/>
-      <c r="AP31" s="131"/>
+      <c r="AP31" s="129"/>
       <c r="AQ31" s="50"/>
-      <c r="AR31" s="131"/>
+      <c r="AR31" s="129"/>
       <c r="AS31" s="50"/>
-      <c r="AT31" s="131"/>
+      <c r="AT31" s="129"/>
       <c r="AU31" s="50"/>
-      <c r="AV31" s="131"/>
+      <c r="AV31" s="129"/>
       <c r="AW31" s="50"/>
-      <c r="AX31" s="131"/>
+      <c r="AX31" s="129"/>
       <c r="AY31" s="50"/>
-      <c r="AZ31" s="131"/>
+      <c r="AZ31" s="129"/>
       <c r="BA31" s="50"/>
       <c r="BB31" s="36"/>
       <c r="BC31" s="36"/>
-      <c r="BD31" s="131"/>
+      <c r="BD31" s="129"/>
       <c r="BE31" s="50"/>
-      <c r="BF31" s="131"/>
+      <c r="BF31" s="129"/>
       <c r="BG31" s="50"/>
-      <c r="BH31" s="131"/>
+      <c r="BH31" s="129"/>
       <c r="BI31" s="50"/>
-      <c r="BJ31" s="131"/>
+      <c r="BJ31" s="129"/>
       <c r="BK31" s="50"/>
-      <c r="BL31" s="131"/>
+      <c r="BL31" s="129"/>
       <c r="BM31" s="50"/>
-      <c r="BN31" s="131"/>
+      <c r="BN31" s="129"/>
       <c r="BO31" s="50"/>
-      <c r="BP31" s="131"/>
+      <c r="BP31" s="129"/>
       <c r="BQ31" s="50"/>
-      <c r="BR31" s="131"/>
+      <c r="BR31" s="129"/>
       <c r="BS31" s="50"/>
-      <c r="BT31" s="131"/>
+      <c r="BT31" s="129"/>
       <c r="BU31" s="50"/>
-      <c r="BV31" s="131"/>
+      <c r="BV31" s="129"/>
       <c r="BW31" s="50"/>
     </row>
     <row r="32" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A32" s="119"/>
+      <c r="A32" s="118"/>
       <c r="B32" s="42"/>
-      <c r="C32" s="119"/>
+      <c r="C32" s="118"/>
       <c r="D32" s="42"/>
-      <c r="E32" s="119"/>
+      <c r="E32" s="118"/>
       <c r="F32" s="42"/>
-      <c r="G32" s="119"/>
+      <c r="G32" s="118"/>
       <c r="H32" s="42"/>
-      <c r="I32" s="119"/>
+      <c r="I32" s="118"/>
       <c r="J32" s="42"/>
-      <c r="K32" s="119"/>
+      <c r="K32" s="118"/>
       <c r="L32" s="42"/>
-      <c r="M32" s="119"/>
+      <c r="M32" s="118"/>
       <c r="N32" s="42"/>
-      <c r="O32" s="119"/>
+      <c r="O32" s="118"/>
       <c r="P32" s="42"/>
-      <c r="Q32" s="119"/>
+      <c r="Q32" s="118"/>
       <c r="R32" s="42"/>
-      <c r="S32" s="119"/>
+      <c r="S32" s="118"/>
       <c r="T32" s="42"/>
-      <c r="U32" s="119"/>
+      <c r="U32" s="118"/>
       <c r="V32" s="42"/>
-      <c r="W32" s="119"/>
+      <c r="W32" s="118"/>
       <c r="X32" s="42"/>
-      <c r="Y32" s="119"/>
+      <c r="Y32" s="118"/>
       <c r="Z32" s="42"/>
-      <c r="AA32" s="119"/>
+      <c r="AA32" s="118"/>
       <c r="AB32" s="42"/>
-      <c r="AC32" s="119"/>
+      <c r="AC32" s="118"/>
       <c r="AD32" s="42"/>
-      <c r="AE32" s="119"/>
+      <c r="AE32" s="118"/>
       <c r="AF32" s="42"/>
-      <c r="AG32" s="119"/>
+      <c r="AG32" s="118"/>
       <c r="AH32" s="42"/>
-      <c r="AI32" s="119"/>
+      <c r="AI32" s="118"/>
       <c r="AJ32" s="42"/>
-      <c r="AK32" s="119"/>
+      <c r="AK32" s="118"/>
       <c r="AL32" s="42"/>
-      <c r="AM32" s="119"/>
+      <c r="AM32" s="118"/>
       <c r="AN32" s="42"/>
-      <c r="AO32" s="119"/>
+      <c r="AO32" s="118"/>
       <c r="AP32" s="42"/>
-      <c r="AQ32" s="119"/>
+      <c r="AQ32" s="118"/>
       <c r="AR32" s="42"/>
-      <c r="AS32" s="119"/>
+      <c r="AS32" s="118"/>
       <c r="AT32" s="42"/>
-      <c r="AU32" s="119"/>
+      <c r="AU32" s="118"/>
       <c r="AV32" s="42"/>
-      <c r="AW32" s="119"/>
+      <c r="AW32" s="118"/>
       <c r="AX32" s="42"/>
-      <c r="AY32" s="119"/>
+      <c r="AY32" s="118"/>
       <c r="AZ32" s="42"/>
-      <c r="BA32" s="119"/>
+      <c r="BA32" s="118"/>
       <c r="BB32" s="42"/>
-      <c r="BC32" s="119"/>
+      <c r="BC32" s="118"/>
       <c r="BD32" s="42"/>
-      <c r="BE32" s="119"/>
+      <c r="BE32" s="118"/>
       <c r="BF32" s="42"/>
-      <c r="BG32" s="119"/>
+      <c r="BG32" s="118"/>
       <c r="BH32" s="42"/>
-      <c r="BI32" s="119"/>
+      <c r="BI32" s="118"/>
       <c r="BJ32" s="42"/>
-      <c r="BK32" s="119"/>
+      <c r="BK32" s="118"/>
       <c r="BL32" s="42"/>
-      <c r="BM32" s="119"/>
+      <c r="BM32" s="118"/>
       <c r="BN32" s="42"/>
-      <c r="BO32" s="119"/>
+      <c r="BO32" s="118"/>
       <c r="BP32" s="42"/>
-      <c r="BQ32" s="119"/>
+      <c r="BQ32" s="118"/>
       <c r="BR32" s="42"/>
-      <c r="BS32" s="119"/>
+      <c r="BS32" s="118"/>
       <c r="BT32" s="42"/>
-      <c r="BU32" s="119"/>
+      <c r="BU32" s="118"/>
       <c r="BV32" s="42"/>
       <c r="BW32" s="36"/>
     </row>
     <row r="33" spans="1:75" ht="17.25" customHeight="1">
       <c r="A33" s="36"/>
-      <c r="B33" s="131"/>
+      <c r="B33" s="129"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="131"/>
+      <c r="D33" s="129"/>
       <c r="E33" s="50"/>
-      <c r="F33" s="131"/>
+      <c r="F33" s="129"/>
       <c r="G33" s="50"/>
       <c r="H33" s="36"/>
-      <c r="I33" s="131"/>
+      <c r="I33" s="129"/>
       <c r="J33" s="50"/>
-      <c r="K33" s="131"/>
+      <c r="K33" s="129"/>
       <c r="L33" s="50"/>
-      <c r="M33" s="132" t="s">
+      <c r="M33" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N33" s="53"/>
-      <c r="O33" s="131"/>
+      <c r="O33" s="129"/>
       <c r="P33" s="50"/>
-      <c r="Q33" s="131"/>
+      <c r="Q33" s="129"/>
       <c r="R33" s="50"/>
-      <c r="S33" s="132" t="s">
+      <c r="S33" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T33" s="53"/>
-      <c r="U33" s="131"/>
+      <c r="U33" s="129"/>
       <c r="V33" s="50"/>
-      <c r="W33" s="131"/>
+      <c r="W33" s="129"/>
       <c r="X33" s="50"/>
-      <c r="Y33" s="131"/>
+      <c r="Y33" s="129"/>
       <c r="Z33" s="50"/>
-      <c r="AA33" s="131"/>
+      <c r="AA33" s="129"/>
       <c r="AB33" s="50"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="131"/>
+      <c r="AD33" s="129"/>
       <c r="AE33" s="50"/>
-      <c r="AF33" s="131"/>
+      <c r="AF33" s="129"/>
       <c r="AG33" s="50"/>
-      <c r="AH33" s="131"/>
+      <c r="AH33" s="129"/>
       <c r="AI33" s="50"/>
-      <c r="AJ33" s="131"/>
+      <c r="AJ33" s="129"/>
       <c r="AK33" s="50"/>
-      <c r="AL33" s="131"/>
+      <c r="AL33" s="129"/>
       <c r="AM33" s="50"/>
-      <c r="AN33" s="131"/>
+      <c r="AN33" s="129"/>
       <c r="AO33" s="50"/>
-      <c r="AP33" s="131"/>
+      <c r="AP33" s="129"/>
       <c r="AQ33" s="50"/>
-      <c r="AR33" s="131"/>
+      <c r="AR33" s="129"/>
       <c r="AS33" s="50"/>
-      <c r="AT33" s="131"/>
+      <c r="AT33" s="129"/>
       <c r="AU33" s="50"/>
-      <c r="AV33" s="131"/>
+      <c r="AV33" s="129"/>
       <c r="AW33" s="50"/>
-      <c r="AX33" s="131"/>
+      <c r="AX33" s="129"/>
       <c r="AY33" s="50"/>
-      <c r="AZ33" s="131"/>
+      <c r="AZ33" s="129"/>
       <c r="BA33" s="50"/>
       <c r="BB33" s="36"/>
       <c r="BC33" s="36"/>
-      <c r="BD33" s="131"/>
+      <c r="BD33" s="129"/>
       <c r="BE33" s="50"/>
-      <c r="BF33" s="131"/>
+      <c r="BF33" s="129"/>
       <c r="BG33" s="50"/>
-      <c r="BH33" s="131"/>
+      <c r="BH33" s="129"/>
       <c r="BI33" s="50"/>
-      <c r="BJ33" s="131"/>
+      <c r="BJ33" s="129"/>
       <c r="BK33" s="50"/>
-      <c r="BL33" s="131"/>
+      <c r="BL33" s="129"/>
       <c r="BM33" s="50"/>
-      <c r="BN33" s="131"/>
+      <c r="BN33" s="129"/>
       <c r="BO33" s="50"/>
-      <c r="BP33" s="131"/>
+      <c r="BP33" s="129"/>
       <c r="BQ33" s="50"/>
-      <c r="BR33" s="131"/>
+      <c r="BR33" s="129"/>
       <c r="BS33" s="50"/>
-      <c r="BT33" s="131"/>
+      <c r="BT33" s="129"/>
       <c r="BU33" s="50"/>
-      <c r="BV33" s="131"/>
+      <c r="BV33" s="129"/>
       <c r="BW33" s="50"/>
     </row>
     <row r="34" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A34" s="133"/>
+      <c r="A34" s="131"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="133"/>
+      <c r="C34" s="131"/>
       <c r="D34" s="42"/>
-      <c r="E34" s="133"/>
+      <c r="E34" s="131"/>
       <c r="F34" s="42"/>
-      <c r="G34" s="133"/>
+      <c r="G34" s="131"/>
       <c r="H34" s="42"/>
-      <c r="I34" s="133"/>
+      <c r="I34" s="131"/>
       <c r="J34" s="42"/>
-      <c r="K34" s="133"/>
+      <c r="K34" s="131"/>
       <c r="L34" s="42"/>
-      <c r="M34" s="133"/>
+      <c r="M34" s="131"/>
       <c r="N34" s="42"/>
-      <c r="O34" s="133"/>
+      <c r="O34" s="131"/>
       <c r="P34" s="42"/>
-      <c r="Q34" s="133"/>
+      <c r="Q34" s="131"/>
       <c r="R34" s="42"/>
-      <c r="S34" s="133"/>
+      <c r="S34" s="131"/>
       <c r="T34" s="42"/>
-      <c r="U34" s="133"/>
+      <c r="U34" s="131"/>
       <c r="V34" s="42"/>
-      <c r="W34" s="133"/>
+      <c r="W34" s="131"/>
       <c r="X34" s="42"/>
-      <c r="Y34" s="133"/>
+      <c r="Y34" s="131"/>
       <c r="Z34" s="42"/>
-      <c r="AA34" s="133"/>
+      <c r="AA34" s="131"/>
       <c r="AB34" s="42"/>
-      <c r="AC34" s="133"/>
+      <c r="AC34" s="131"/>
       <c r="AD34" s="42"/>
-      <c r="AE34" s="133"/>
+      <c r="AE34" s="131"/>
       <c r="AF34" s="42"/>
-      <c r="AG34" s="133"/>
+      <c r="AG34" s="131"/>
       <c r="AH34" s="42"/>
-      <c r="AI34" s="133"/>
+      <c r="AI34" s="131"/>
       <c r="AJ34" s="42"/>
-      <c r="AK34" s="133"/>
+      <c r="AK34" s="131"/>
       <c r="AL34" s="42"/>
-      <c r="AM34" s="133"/>
+      <c r="AM34" s="131"/>
       <c r="AN34" s="42"/>
-      <c r="AO34" s="133"/>
+      <c r="AO34" s="131"/>
       <c r="AP34" s="42"/>
-      <c r="AQ34" s="133"/>
+      <c r="AQ34" s="131"/>
       <c r="AR34" s="42"/>
-      <c r="AS34" s="133"/>
+      <c r="AS34" s="131"/>
       <c r="AT34" s="42"/>
-      <c r="AU34" s="133"/>
+      <c r="AU34" s="131"/>
       <c r="AV34" s="42"/>
-      <c r="AW34" s="133"/>
+      <c r="AW34" s="131"/>
       <c r="AX34" s="42"/>
-      <c r="AY34" s="133"/>
+      <c r="AY34" s="131"/>
       <c r="AZ34" s="42"/>
-      <c r="BA34" s="133"/>
+      <c r="BA34" s="131"/>
       <c r="BB34" s="42"/>
-      <c r="BC34" s="133"/>
+      <c r="BC34" s="131"/>
       <c r="BD34" s="42"/>
-      <c r="BE34" s="133"/>
+      <c r="BE34" s="131"/>
       <c r="BF34" s="42"/>
-      <c r="BG34" s="133"/>
+      <c r="BG34" s="131"/>
       <c r="BH34" s="42"/>
-      <c r="BI34" s="133"/>
+      <c r="BI34" s="131"/>
       <c r="BJ34" s="42"/>
-      <c r="BK34" s="133"/>
+      <c r="BK34" s="131"/>
       <c r="BL34" s="42"/>
-      <c r="BM34" s="133"/>
+      <c r="BM34" s="131"/>
       <c r="BN34" s="42"/>
-      <c r="BO34" s="133"/>
+      <c r="BO34" s="131"/>
       <c r="BP34" s="42"/>
-      <c r="BQ34" s="133"/>
+      <c r="BQ34" s="131"/>
       <c r="BR34" s="42"/>
-      <c r="BS34" s="133"/>
+      <c r="BS34" s="131"/>
       <c r="BT34" s="42"/>
-      <c r="BU34" s="133"/>
+      <c r="BU34" s="131"/>
       <c r="BV34" s="42"/>
       <c r="BW34" s="39"/>
     </row>
     <row r="35" spans="1:75" ht="17.25" customHeight="1">
       <c r="A35" s="36"/>
-      <c r="B35" s="134"/>
+      <c r="B35" s="132"/>
       <c r="C35" s="42"/>
-      <c r="D35" s="134"/>
+      <c r="D35" s="132"/>
       <c r="E35" s="42"/>
-      <c r="F35" s="134"/>
+      <c r="F35" s="132"/>
       <c r="G35" s="42"/>
       <c r="H35" s="36"/>
-      <c r="I35" s="131"/>
+      <c r="I35" s="129"/>
       <c r="J35" s="50"/>
-      <c r="K35" s="131"/>
+      <c r="K35" s="129"/>
       <c r="L35" s="50"/>
-      <c r="M35" s="132" t="s">
+      <c r="M35" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N35" s="53"/>
-      <c r="O35" s="131"/>
+      <c r="O35" s="129"/>
       <c r="P35" s="50"/>
-      <c r="Q35" s="131"/>
+      <c r="Q35" s="129"/>
       <c r="R35" s="50"/>
-      <c r="S35" s="132" t="s">
+      <c r="S35" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T35" s="53"/>
-      <c r="U35" s="131"/>
+      <c r="U35" s="129"/>
       <c r="V35" s="50"/>
-      <c r="W35" s="131"/>
+      <c r="W35" s="129"/>
       <c r="X35" s="50"/>
-      <c r="Y35" s="131"/>
+      <c r="Y35" s="129"/>
       <c r="Z35" s="50"/>
-      <c r="AA35" s="131"/>
+      <c r="AA35" s="129"/>
       <c r="AB35" s="50"/>
       <c r="AC35" s="36"/>
-      <c r="AD35" s="131"/>
+      <c r="AD35" s="129"/>
       <c r="AE35" s="50"/>
-      <c r="AF35" s="131"/>
+      <c r="AF35" s="129"/>
       <c r="AG35" s="50"/>
-      <c r="AH35" s="131"/>
+      <c r="AH35" s="129"/>
       <c r="AI35" s="50"/>
-      <c r="AJ35" s="131"/>
+      <c r="AJ35" s="129"/>
       <c r="AK35" s="50"/>
-      <c r="AL35" s="131"/>
+      <c r="AL35" s="129"/>
       <c r="AM35" s="50"/>
-      <c r="AN35" s="131"/>
+      <c r="AN35" s="129"/>
       <c r="AO35" s="50"/>
-      <c r="AP35" s="131"/>
+      <c r="AP35" s="129"/>
       <c r="AQ35" s="50"/>
-      <c r="AR35" s="131"/>
+      <c r="AR35" s="129"/>
       <c r="AS35" s="50"/>
-      <c r="AT35" s="131"/>
+      <c r="AT35" s="129"/>
       <c r="AU35" s="50"/>
-      <c r="AV35" s="131"/>
+      <c r="AV35" s="129"/>
       <c r="AW35" s="50"/>
-      <c r="AX35" s="131"/>
+      <c r="AX35" s="129"/>
       <c r="AY35" s="50"/>
-      <c r="AZ35" s="131"/>
+      <c r="AZ35" s="129"/>
       <c r="BA35" s="50"/>
       <c r="BB35" s="36"/>
       <c r="BC35" s="36"/>
-      <c r="BD35" s="131"/>
+      <c r="BD35" s="129"/>
       <c r="BE35" s="50"/>
-      <c r="BF35" s="131"/>
+      <c r="BF35" s="129"/>
       <c r="BG35" s="50"/>
-      <c r="BH35" s="131"/>
+      <c r="BH35" s="129"/>
       <c r="BI35" s="50"/>
-      <c r="BJ35" s="131"/>
+      <c r="BJ35" s="129"/>
       <c r="BK35" s="50"/>
-      <c r="BL35" s="131"/>
+      <c r="BL35" s="129"/>
       <c r="BM35" s="50"/>
-      <c r="BN35" s="131"/>
+      <c r="BN35" s="129"/>
       <c r="BO35" s="50"/>
-      <c r="BP35" s="131"/>
+      <c r="BP35" s="129"/>
       <c r="BQ35" s="50"/>
-      <c r="BR35" s="131"/>
+      <c r="BR35" s="129"/>
       <c r="BS35" s="50"/>
-      <c r="BT35" s="131"/>
+      <c r="BT35" s="129"/>
       <c r="BU35" s="50"/>
-      <c r="BV35" s="131"/>
+      <c r="BV35" s="129"/>
       <c r="BW35" s="50"/>
     </row>
     <row r="36" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A36" s="119"/>
+      <c r="A36" s="118"/>
       <c r="B36" s="42"/>
-      <c r="C36" s="119"/>
+      <c r="C36" s="118"/>
       <c r="D36" s="42"/>
-      <c r="E36" s="119"/>
+      <c r="E36" s="118"/>
       <c r="F36" s="42"/>
-      <c r="G36" s="119"/>
+      <c r="G36" s="118"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="119"/>
+      <c r="I36" s="118"/>
       <c r="J36" s="42"/>
-      <c r="K36" s="119"/>
+      <c r="K36" s="118"/>
       <c r="L36" s="42"/>
-      <c r="M36" s="119"/>
+      <c r="M36" s="118"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="119"/>
+      <c r="O36" s="118"/>
       <c r="P36" s="42"/>
-      <c r="Q36" s="119"/>
+      <c r="Q36" s="118"/>
       <c r="R36" s="42"/>
-      <c r="S36" s="119"/>
+      <c r="S36" s="118"/>
       <c r="T36" s="42"/>
-      <c r="U36" s="119"/>
+      <c r="U36" s="118"/>
       <c r="V36" s="42"/>
-      <c r="W36" s="119"/>
+      <c r="W36" s="118"/>
       <c r="X36" s="42"/>
-      <c r="Y36" s="119"/>
+      <c r="Y36" s="118"/>
       <c r="Z36" s="42"/>
-      <c r="AA36" s="119"/>
+      <c r="AA36" s="118"/>
       <c r="AB36" s="42"/>
-      <c r="AC36" s="119"/>
+      <c r="AC36" s="118"/>
       <c r="AD36" s="42"/>
-      <c r="AE36" s="119"/>
+      <c r="AE36" s="118"/>
       <c r="AF36" s="42"/>
-      <c r="AG36" s="119"/>
+      <c r="AG36" s="118"/>
       <c r="AH36" s="42"/>
-      <c r="AI36" s="119"/>
+      <c r="AI36" s="118"/>
       <c r="AJ36" s="42"/>
-      <c r="AK36" s="119"/>
+      <c r="AK36" s="118"/>
       <c r="AL36" s="42"/>
-      <c r="AM36" s="119"/>
+      <c r="AM36" s="118"/>
       <c r="AN36" s="42"/>
-      <c r="AO36" s="119"/>
+      <c r="AO36" s="118"/>
       <c r="AP36" s="42"/>
-      <c r="AQ36" s="119"/>
+      <c r="AQ36" s="118"/>
       <c r="AR36" s="42"/>
-      <c r="AS36" s="119"/>
+      <c r="AS36" s="118"/>
       <c r="AT36" s="42"/>
-      <c r="AU36" s="119"/>
+      <c r="AU36" s="118"/>
       <c r="AV36" s="42"/>
-      <c r="AW36" s="119"/>
+      <c r="AW36" s="118"/>
       <c r="AX36" s="42"/>
-      <c r="AY36" s="119"/>
+      <c r="AY36" s="118"/>
       <c r="AZ36" s="42"/>
-      <c r="BA36" s="119"/>
+      <c r="BA36" s="118"/>
       <c r="BB36" s="42"/>
-      <c r="BC36" s="119"/>
+      <c r="BC36" s="118"/>
       <c r="BD36" s="42"/>
-      <c r="BE36" s="119"/>
+      <c r="BE36" s="118"/>
       <c r="BF36" s="42"/>
-      <c r="BG36" s="119"/>
+      <c r="BG36" s="118"/>
       <c r="BH36" s="42"/>
-      <c r="BI36" s="119"/>
+      <c r="BI36" s="118"/>
       <c r="BJ36" s="42"/>
-      <c r="BK36" s="119"/>
+      <c r="BK36" s="118"/>
       <c r="BL36" s="42"/>
-      <c r="BM36" s="119"/>
+      <c r="BM36" s="118"/>
       <c r="BN36" s="42"/>
-      <c r="BO36" s="119"/>
+      <c r="BO36" s="118"/>
       <c r="BP36" s="42"/>
-      <c r="BQ36" s="119"/>
+      <c r="BQ36" s="118"/>
       <c r="BR36" s="42"/>
-      <c r="BS36" s="119"/>
+      <c r="BS36" s="118"/>
       <c r="BT36" s="42"/>
-      <c r="BU36" s="119"/>
+      <c r="BU36" s="118"/>
       <c r="BV36" s="42"/>
       <c r="BW36" s="36"/>
     </row>
     <row r="37" spans="1:75" ht="17.25" customHeight="1">
       <c r="A37" s="36"/>
-      <c r="B37" s="131"/>
+      <c r="B37" s="129"/>
       <c r="C37" s="50"/>
-      <c r="D37" s="131"/>
+      <c r="D37" s="129"/>
       <c r="E37" s="50"/>
-      <c r="F37" s="131"/>
+      <c r="F37" s="129"/>
       <c r="G37" s="50"/>
       <c r="H37" s="36"/>
-      <c r="I37" s="131"/>
+      <c r="I37" s="129"/>
       <c r="J37" s="50"/>
-      <c r="K37" s="131"/>
+      <c r="K37" s="129"/>
       <c r="L37" s="50"/>
-      <c r="M37" s="132" t="s">
+      <c r="M37" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N37" s="53"/>
-      <c r="O37" s="131"/>
+      <c r="O37" s="129"/>
       <c r="P37" s="50"/>
-      <c r="Q37" s="131"/>
+      <c r="Q37" s="129"/>
       <c r="R37" s="50"/>
-      <c r="S37" s="132" t="s">
+      <c r="S37" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T37" s="53"/>
-      <c r="U37" s="131"/>
+      <c r="U37" s="129"/>
       <c r="V37" s="50"/>
-      <c r="W37" s="131"/>
+      <c r="W37" s="129"/>
       <c r="X37" s="50"/>
-      <c r="Y37" s="131"/>
+      <c r="Y37" s="129"/>
       <c r="Z37" s="50"/>
-      <c r="AA37" s="131"/>
+      <c r="AA37" s="129"/>
       <c r="AB37" s="50"/>
       <c r="AC37" s="36"/>
-      <c r="AD37" s="131"/>
+      <c r="AD37" s="129"/>
       <c r="AE37" s="50"/>
-      <c r="AF37" s="131"/>
+      <c r="AF37" s="129"/>
       <c r="AG37" s="50"/>
-      <c r="AH37" s="131"/>
+      <c r="AH37" s="129"/>
       <c r="AI37" s="50"/>
-      <c r="AJ37" s="131"/>
+      <c r="AJ37" s="129"/>
       <c r="AK37" s="50"/>
-      <c r="AL37" s="131"/>
+      <c r="AL37" s="129"/>
       <c r="AM37" s="50"/>
-      <c r="AN37" s="131"/>
+      <c r="AN37" s="129"/>
       <c r="AO37" s="50"/>
-      <c r="AP37" s="131"/>
+      <c r="AP37" s="129"/>
       <c r="AQ37" s="50"/>
-      <c r="AR37" s="131"/>
+      <c r="AR37" s="129"/>
       <c r="AS37" s="50"/>
-      <c r="AT37" s="131"/>
+      <c r="AT37" s="129"/>
       <c r="AU37" s="50"/>
-      <c r="AV37" s="131"/>
+      <c r="AV37" s="129"/>
       <c r="AW37" s="50"/>
-      <c r="AX37" s="131"/>
+      <c r="AX37" s="129"/>
       <c r="AY37" s="50"/>
-      <c r="AZ37" s="131"/>
+      <c r="AZ37" s="129"/>
       <c r="BA37" s="50"/>
       <c r="BB37" s="36"/>
       <c r="BC37" s="36"/>
-      <c r="BD37" s="131"/>
+      <c r="BD37" s="129"/>
       <c r="BE37" s="50"/>
-      <c r="BF37" s="131"/>
+      <c r="BF37" s="129"/>
       <c r="BG37" s="50"/>
-      <c r="BH37" s="131"/>
+      <c r="BH37" s="129"/>
       <c r="BI37" s="50"/>
-      <c r="BJ37" s="131"/>
+      <c r="BJ37" s="129"/>
       <c r="BK37" s="50"/>
-      <c r="BL37" s="131"/>
+      <c r="BL37" s="129"/>
       <c r="BM37" s="50"/>
-      <c r="BN37" s="131"/>
+      <c r="BN37" s="129"/>
       <c r="BO37" s="50"/>
-      <c r="BP37" s="131"/>
+      <c r="BP37" s="129"/>
       <c r="BQ37" s="50"/>
-      <c r="BR37" s="131"/>
+      <c r="BR37" s="129"/>
       <c r="BS37" s="50"/>
-      <c r="BT37" s="131"/>
+      <c r="BT37" s="129"/>
       <c r="BU37" s="50"/>
-      <c r="BV37" s="131"/>
+      <c r="BV37" s="129"/>
       <c r="BW37" s="50"/>
     </row>
     <row r="38" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A38" s="133"/>
+      <c r="A38" s="131"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="133"/>
+      <c r="C38" s="131"/>
       <c r="D38" s="42"/>
-      <c r="E38" s="133"/>
+      <c r="E38" s="131"/>
       <c r="F38" s="42"/>
-      <c r="G38" s="133"/>
+      <c r="G38" s="131"/>
       <c r="H38" s="42"/>
-      <c r="I38" s="133"/>
+      <c r="I38" s="131"/>
       <c r="J38" s="42"/>
-      <c r="K38" s="133"/>
+      <c r="K38" s="131"/>
       <c r="L38" s="42"/>
-      <c r="M38" s="133"/>
+      <c r="M38" s="131"/>
       <c r="N38" s="42"/>
-      <c r="O38" s="133"/>
+      <c r="O38" s="131"/>
       <c r="P38" s="42"/>
-      <c r="Q38" s="133"/>
+      <c r="Q38" s="131"/>
       <c r="R38" s="42"/>
-      <c r="S38" s="133"/>
+      <c r="S38" s="131"/>
       <c r="T38" s="42"/>
-      <c r="U38" s="133"/>
+      <c r="U38" s="131"/>
       <c r="V38" s="42"/>
-      <c r="W38" s="133"/>
+      <c r="W38" s="131"/>
       <c r="X38" s="42"/>
-      <c r="Y38" s="133"/>
+      <c r="Y38" s="131"/>
       <c r="Z38" s="42"/>
-      <c r="AA38" s="133"/>
+      <c r="AA38" s="131"/>
       <c r="AB38" s="42"/>
-      <c r="AC38" s="133"/>
+      <c r="AC38" s="131"/>
       <c r="AD38" s="42"/>
-      <c r="AE38" s="133"/>
+      <c r="AE38" s="131"/>
       <c r="AF38" s="42"/>
-      <c r="AG38" s="133"/>
+      <c r="AG38" s="131"/>
       <c r="AH38" s="42"/>
-      <c r="AI38" s="133"/>
+      <c r="AI38" s="131"/>
       <c r="AJ38" s="42"/>
-      <c r="AK38" s="133"/>
+      <c r="AK38" s="131"/>
       <c r="AL38" s="42"/>
-      <c r="AM38" s="133"/>
+      <c r="AM38" s="131"/>
       <c r="AN38" s="42"/>
-      <c r="AO38" s="133"/>
+      <c r="AO38" s="131"/>
       <c r="AP38" s="42"/>
-      <c r="AQ38" s="133"/>
+      <c r="AQ38" s="131"/>
       <c r="AR38" s="42"/>
-      <c r="AS38" s="133"/>
+      <c r="AS38" s="131"/>
       <c r="AT38" s="42"/>
-      <c r="AU38" s="133"/>
+      <c r="AU38" s="131"/>
       <c r="AV38" s="42"/>
-      <c r="AW38" s="133"/>
+      <c r="AW38" s="131"/>
       <c r="AX38" s="42"/>
-      <c r="AY38" s="133"/>
+      <c r="AY38" s="131"/>
       <c r="AZ38" s="42"/>
-      <c r="BA38" s="133"/>
+      <c r="BA38" s="131"/>
       <c r="BB38" s="42"/>
-      <c r="BC38" s="133"/>
+      <c r="BC38" s="131"/>
       <c r="BD38" s="42"/>
-      <c r="BE38" s="133"/>
+      <c r="BE38" s="131"/>
       <c r="BF38" s="42"/>
-      <c r="BG38" s="133"/>
+      <c r="BG38" s="131"/>
       <c r="BH38" s="42"/>
-      <c r="BI38" s="133"/>
+      <c r="BI38" s="131"/>
       <c r="BJ38" s="42"/>
-      <c r="BK38" s="133"/>
+      <c r="BK38" s="131"/>
       <c r="BL38" s="42"/>
-      <c r="BM38" s="133"/>
+      <c r="BM38" s="131"/>
       <c r="BN38" s="42"/>
-      <c r="BO38" s="133"/>
+      <c r="BO38" s="131"/>
       <c r="BP38" s="42"/>
-      <c r="BQ38" s="133"/>
+      <c r="BQ38" s="131"/>
       <c r="BR38" s="42"/>
-      <c r="BS38" s="133"/>
+      <c r="BS38" s="131"/>
       <c r="BT38" s="42"/>
-      <c r="BU38" s="133"/>
+      <c r="BU38" s="131"/>
       <c r="BV38" s="42"/>
       <c r="BW38" s="39"/>
     </row>
     <row r="39" spans="1:75" ht="17.25" customHeight="1">
       <c r="A39" s="36"/>
-      <c r="B39" s="134"/>
+      <c r="B39" s="132"/>
       <c r="C39" s="42"/>
-      <c r="D39" s="134"/>
+      <c r="D39" s="132"/>
       <c r="E39" s="42"/>
-      <c r="F39" s="134"/>
+      <c r="F39" s="132"/>
       <c r="G39" s="42"/>
       <c r="H39" s="36"/>
-      <c r="I39" s="131"/>
+      <c r="I39" s="129"/>
       <c r="J39" s="50"/>
-      <c r="K39" s="131"/>
+      <c r="K39" s="129"/>
       <c r="L39" s="50"/>
-      <c r="M39" s="132" t="s">
+      <c r="M39" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N39" s="53"/>
-      <c r="O39" s="131"/>
+      <c r="O39" s="129"/>
       <c r="P39" s="50"/>
-      <c r="Q39" s="131"/>
+      <c r="Q39" s="129"/>
       <c r="R39" s="50"/>
-      <c r="S39" s="132" t="s">
+      <c r="S39" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T39" s="53"/>
-      <c r="U39" s="131"/>
+      <c r="U39" s="129"/>
       <c r="V39" s="50"/>
-      <c r="W39" s="131"/>
+      <c r="W39" s="129"/>
       <c r="X39" s="50"/>
-      <c r="Y39" s="131"/>
+      <c r="Y39" s="129"/>
       <c r="Z39" s="50"/>
-      <c r="AA39" s="131"/>
+      <c r="AA39" s="129"/>
       <c r="AB39" s="50"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="131"/>
+      <c r="AD39" s="129"/>
       <c r="AE39" s="50"/>
-      <c r="AF39" s="131"/>
+      <c r="AF39" s="129"/>
       <c r="AG39" s="50"/>
-      <c r="AH39" s="131"/>
+      <c r="AH39" s="129"/>
       <c r="AI39" s="50"/>
-      <c r="AJ39" s="131"/>
+      <c r="AJ39" s="129"/>
       <c r="AK39" s="50"/>
-      <c r="AL39" s="131"/>
+      <c r="AL39" s="129"/>
       <c r="AM39" s="50"/>
-      <c r="AN39" s="131"/>
+      <c r="AN39" s="129"/>
       <c r="AO39" s="50"/>
-      <c r="AP39" s="131"/>
+      <c r="AP39" s="129"/>
       <c r="AQ39" s="50"/>
-      <c r="AR39" s="131"/>
+      <c r="AR39" s="129"/>
       <c r="AS39" s="50"/>
-      <c r="AT39" s="131"/>
+      <c r="AT39" s="129"/>
       <c r="AU39" s="50"/>
-      <c r="AV39" s="131"/>
+      <c r="AV39" s="129"/>
       <c r="AW39" s="50"/>
-      <c r="AX39" s="131"/>
+      <c r="AX39" s="129"/>
       <c r="AY39" s="50"/>
-      <c r="AZ39" s="131"/>
+      <c r="AZ39" s="129"/>
       <c r="BA39" s="50"/>
       <c r="BB39" s="36"/>
       <c r="BC39" s="36"/>
-      <c r="BD39" s="131"/>
+      <c r="BD39" s="129"/>
       <c r="BE39" s="50"/>
-      <c r="BF39" s="131"/>
+      <c r="BF39" s="129"/>
       <c r="BG39" s="50"/>
-      <c r="BH39" s="131"/>
+      <c r="BH39" s="129"/>
       <c r="BI39" s="50"/>
-      <c r="BJ39" s="131"/>
+      <c r="BJ39" s="129"/>
       <c r="BK39" s="50"/>
-      <c r="BL39" s="131"/>
+      <c r="BL39" s="129"/>
       <c r="BM39" s="50"/>
-      <c r="BN39" s="131"/>
+      <c r="BN39" s="129"/>
       <c r="BO39" s="50"/>
-      <c r="BP39" s="131"/>
+      <c r="BP39" s="129"/>
       <c r="BQ39" s="50"/>
-      <c r="BR39" s="131"/>
+      <c r="BR39" s="129"/>
       <c r="BS39" s="50"/>
-      <c r="BT39" s="131"/>
+      <c r="BT39" s="129"/>
       <c r="BU39" s="50"/>
-      <c r="BV39" s="131"/>
+      <c r="BV39" s="129"/>
       <c r="BW39" s="50"/>
     </row>
     <row r="40" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A40" s="119"/>
+      <c r="A40" s="118"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="119"/>
+      <c r="C40" s="118"/>
       <c r="D40" s="42"/>
-      <c r="E40" s="119"/>
+      <c r="E40" s="118"/>
       <c r="F40" s="42"/>
-      <c r="G40" s="119"/>
+      <c r="G40" s="118"/>
       <c r="H40" s="42"/>
-      <c r="I40" s="119"/>
+      <c r="I40" s="118"/>
       <c r="J40" s="42"/>
-      <c r="K40" s="119"/>
+      <c r="K40" s="118"/>
       <c r="L40" s="42"/>
-      <c r="M40" s="119"/>
+      <c r="M40" s="118"/>
       <c r="N40" s="42"/>
-      <c r="O40" s="119"/>
+      <c r="O40" s="118"/>
       <c r="P40" s="42"/>
-      <c r="Q40" s="119"/>
+      <c r="Q40" s="118"/>
       <c r="R40" s="42"/>
-      <c r="S40" s="119"/>
+      <c r="S40" s="118"/>
       <c r="T40" s="42"/>
-      <c r="U40" s="119"/>
+      <c r="U40" s="118"/>
       <c r="V40" s="42"/>
-      <c r="W40" s="119"/>
+      <c r="W40" s="118"/>
       <c r="X40" s="42"/>
-      <c r="Y40" s="119"/>
+      <c r="Y40" s="118"/>
       <c r="Z40" s="42"/>
-      <c r="AA40" s="119"/>
+      <c r="AA40" s="118"/>
       <c r="AB40" s="42"/>
-      <c r="AC40" s="119"/>
+      <c r="AC40" s="118"/>
       <c r="AD40" s="42"/>
-      <c r="AE40" s="119"/>
+      <c r="AE40" s="118"/>
       <c r="AF40" s="42"/>
-      <c r="AG40" s="119"/>
+      <c r="AG40" s="118"/>
       <c r="AH40" s="42"/>
-      <c r="AI40" s="119"/>
+      <c r="AI40" s="118"/>
       <c r="AJ40" s="42"/>
-      <c r="AK40" s="119"/>
+      <c r="AK40" s="118"/>
       <c r="AL40" s="42"/>
-      <c r="AM40" s="119"/>
+      <c r="AM40" s="118"/>
       <c r="AN40" s="42"/>
-      <c r="AO40" s="119"/>
+      <c r="AO40" s="118"/>
       <c r="AP40" s="42"/>
-      <c r="AQ40" s="119"/>
+      <c r="AQ40" s="118"/>
       <c r="AR40" s="42"/>
-      <c r="AS40" s="119"/>
+      <c r="AS40" s="118"/>
       <c r="AT40" s="42"/>
-      <c r="AU40" s="119"/>
+      <c r="AU40" s="118"/>
       <c r="AV40" s="42"/>
-      <c r="AW40" s="119"/>
+      <c r="AW40" s="118"/>
       <c r="AX40" s="42"/>
-      <c r="AY40" s="119"/>
+      <c r="AY40" s="118"/>
       <c r="AZ40" s="42"/>
-      <c r="BA40" s="119"/>
+      <c r="BA40" s="118"/>
       <c r="BB40" s="42"/>
-      <c r="BC40" s="119"/>
+      <c r="BC40" s="118"/>
       <c r="BD40" s="42"/>
-      <c r="BE40" s="119"/>
+      <c r="BE40" s="118"/>
       <c r="BF40" s="42"/>
-      <c r="BG40" s="119"/>
+      <c r="BG40" s="118"/>
       <c r="BH40" s="42"/>
-      <c r="BI40" s="119"/>
+      <c r="BI40" s="118"/>
       <c r="BJ40" s="42"/>
-      <c r="BK40" s="119"/>
+      <c r="BK40" s="118"/>
       <c r="BL40" s="42"/>
-      <c r="BM40" s="119"/>
+      <c r="BM40" s="118"/>
       <c r="BN40" s="42"/>
-      <c r="BO40" s="119"/>
+      <c r="BO40" s="118"/>
       <c r="BP40" s="42"/>
-      <c r="BQ40" s="119"/>
+      <c r="BQ40" s="118"/>
       <c r="BR40" s="42"/>
-      <c r="BS40" s="119"/>
+      <c r="BS40" s="118"/>
       <c r="BT40" s="42"/>
-      <c r="BU40" s="119"/>
+      <c r="BU40" s="118"/>
       <c r="BV40" s="42"/>
       <c r="BW40" s="36"/>
     </row>
     <row r="41" spans="1:75" ht="17.25" customHeight="1">
       <c r="A41" s="36"/>
-      <c r="B41" s="131"/>
+      <c r="B41" s="129"/>
       <c r="C41" s="50"/>
-      <c r="D41" s="131"/>
+      <c r="D41" s="129"/>
       <c r="E41" s="50"/>
-      <c r="F41" s="131"/>
+      <c r="F41" s="129"/>
       <c r="G41" s="50"/>
       <c r="H41" s="36"/>
-      <c r="I41" s="131"/>
+      <c r="I41" s="129"/>
       <c r="J41" s="50"/>
-      <c r="K41" s="131"/>
+      <c r="K41" s="129"/>
       <c r="L41" s="50"/>
-      <c r="M41" s="132" t="s">
+      <c r="M41" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N41" s="53"/>
-      <c r="O41" s="131"/>
+      <c r="O41" s="129"/>
       <c r="P41" s="50"/>
-      <c r="Q41" s="131"/>
+      <c r="Q41" s="129"/>
       <c r="R41" s="50"/>
-      <c r="S41" s="132" t="s">
+      <c r="S41" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T41" s="53"/>
-      <c r="U41" s="131"/>
+      <c r="U41" s="129"/>
       <c r="V41" s="50"/>
-      <c r="W41" s="131"/>
+      <c r="W41" s="129"/>
       <c r="X41" s="50"/>
-      <c r="Y41" s="131"/>
+      <c r="Y41" s="129"/>
       <c r="Z41" s="50"/>
-      <c r="AA41" s="131"/>
+      <c r="AA41" s="129"/>
       <c r="AB41" s="50"/>
       <c r="AC41" s="36"/>
-      <c r="AD41" s="131"/>
+      <c r="AD41" s="129"/>
       <c r="AE41" s="50"/>
-      <c r="AF41" s="131"/>
+      <c r="AF41" s="129"/>
       <c r="AG41" s="50"/>
-      <c r="AH41" s="131"/>
+      <c r="AH41" s="129"/>
       <c r="AI41" s="50"/>
-      <c r="AJ41" s="131"/>
+      <c r="AJ41" s="129"/>
       <c r="AK41" s="50"/>
-      <c r="AL41" s="131"/>
+      <c r="AL41" s="129"/>
       <c r="AM41" s="50"/>
-      <c r="AN41" s="131"/>
+      <c r="AN41" s="129"/>
       <c r="AO41" s="50"/>
-      <c r="AP41" s="131"/>
+      <c r="AP41" s="129"/>
       <c r="AQ41" s="50"/>
-      <c r="AR41" s="131"/>
+      <c r="AR41" s="129"/>
       <c r="AS41" s="50"/>
-      <c r="AT41" s="131"/>
+      <c r="AT41" s="129"/>
       <c r="AU41" s="50"/>
-      <c r="AV41" s="131"/>
+      <c r="AV41" s="129"/>
       <c r="AW41" s="50"/>
-      <c r="AX41" s="131"/>
+      <c r="AX41" s="129"/>
       <c r="AY41" s="50"/>
-      <c r="AZ41" s="131"/>
+      <c r="AZ41" s="129"/>
       <c r="BA41" s="50"/>
       <c r="BB41" s="36"/>
       <c r="BC41" s="36"/>
-      <c r="BD41" s="131"/>
+      <c r="BD41" s="129"/>
       <c r="BE41" s="50"/>
-      <c r="BF41" s="131"/>
+      <c r="BF41" s="129"/>
       <c r="BG41" s="50"/>
-      <c r="BH41" s="131"/>
+      <c r="BH41" s="129"/>
       <c r="BI41" s="50"/>
-      <c r="BJ41" s="131"/>
+      <c r="BJ41" s="129"/>
       <c r="BK41" s="50"/>
-      <c r="BL41" s="131"/>
+      <c r="BL41" s="129"/>
       <c r="BM41" s="50"/>
-      <c r="BN41" s="131"/>
+      <c r="BN41" s="129"/>
       <c r="BO41" s="50"/>
-      <c r="BP41" s="131"/>
+      <c r="BP41" s="129"/>
       <c r="BQ41" s="50"/>
-      <c r="BR41" s="131"/>
+      <c r="BR41" s="129"/>
       <c r="BS41" s="50"/>
-      <c r="BT41" s="131"/>
+      <c r="BT41" s="129"/>
       <c r="BU41" s="50"/>
-      <c r="BV41" s="131"/>
+      <c r="BV41" s="129"/>
       <c r="BW41" s="50"/>
     </row>
     <row r="42" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A42" s="133"/>
+      <c r="A42" s="131"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="133"/>
+      <c r="C42" s="131"/>
       <c r="D42" s="42"/>
-      <c r="E42" s="133"/>
+      <c r="E42" s="131"/>
       <c r="F42" s="42"/>
-      <c r="G42" s="133"/>
+      <c r="G42" s="131"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="133"/>
+      <c r="I42" s="131"/>
       <c r="J42" s="42"/>
-      <c r="K42" s="133"/>
+      <c r="K42" s="131"/>
       <c r="L42" s="42"/>
-      <c r="M42" s="133"/>
+      <c r="M42" s="131"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="133"/>
+      <c r="O42" s="131"/>
       <c r="P42" s="42"/>
-      <c r="Q42" s="133"/>
+      <c r="Q42" s="131"/>
       <c r="R42" s="42"/>
-      <c r="S42" s="133"/>
+      <c r="S42" s="131"/>
       <c r="T42" s="42"/>
-      <c r="U42" s="133"/>
+      <c r="U42" s="131"/>
       <c r="V42" s="42"/>
-      <c r="W42" s="133"/>
+      <c r="W42" s="131"/>
       <c r="X42" s="42"/>
-      <c r="Y42" s="133"/>
+      <c r="Y42" s="131"/>
       <c r="Z42" s="42"/>
-      <c r="AA42" s="133"/>
+      <c r="AA42" s="131"/>
       <c r="AB42" s="42"/>
-      <c r="AC42" s="133"/>
+      <c r="AC42" s="131"/>
       <c r="AD42" s="42"/>
-      <c r="AE42" s="133"/>
+      <c r="AE42" s="131"/>
       <c r="AF42" s="42"/>
-      <c r="AG42" s="133"/>
+      <c r="AG42" s="131"/>
       <c r="AH42" s="42"/>
-      <c r="AI42" s="133"/>
+      <c r="AI42" s="131"/>
       <c r="AJ42" s="42"/>
-      <c r="AK42" s="133"/>
+      <c r="AK42" s="131"/>
       <c r="AL42" s="42"/>
-      <c r="AM42" s="133"/>
+      <c r="AM42" s="131"/>
       <c r="AN42" s="42"/>
-      <c r="AO42" s="133"/>
+      <c r="AO42" s="131"/>
       <c r="AP42" s="42"/>
-      <c r="AQ42" s="133"/>
+      <c r="AQ42" s="131"/>
       <c r="AR42" s="42"/>
-      <c r="AS42" s="133"/>
+      <c r="AS42" s="131"/>
       <c r="AT42" s="42"/>
-      <c r="AU42" s="133"/>
+      <c r="AU42" s="131"/>
       <c r="AV42" s="42"/>
-      <c r="AW42" s="133"/>
+      <c r="AW42" s="131"/>
       <c r="AX42" s="42"/>
-      <c r="AY42" s="133"/>
+      <c r="AY42" s="131"/>
       <c r="AZ42" s="42"/>
-      <c r="BA42" s="133"/>
+      <c r="BA42" s="131"/>
       <c r="BB42" s="42"/>
-      <c r="BC42" s="133"/>
+      <c r="BC42" s="131"/>
       <c r="BD42" s="42"/>
-      <c r="BE42" s="133"/>
+      <c r="BE42" s="131"/>
       <c r="BF42" s="42"/>
-      <c r="BG42" s="133"/>
+      <c r="BG42" s="131"/>
       <c r="BH42" s="42"/>
-      <c r="BI42" s="133"/>
+      <c r="BI42" s="131"/>
       <c r="BJ42" s="42"/>
-      <c r="BK42" s="133"/>
+      <c r="BK42" s="131"/>
       <c r="BL42" s="42"/>
-      <c r="BM42" s="133"/>
+      <c r="BM42" s="131"/>
       <c r="BN42" s="42"/>
-      <c r="BO42" s="133"/>
+      <c r="BO42" s="131"/>
       <c r="BP42" s="42"/>
-      <c r="BQ42" s="133"/>
+      <c r="BQ42" s="131"/>
       <c r="BR42" s="42"/>
-      <c r="BS42" s="133"/>
+      <c r="BS42" s="131"/>
       <c r="BT42" s="42"/>
-      <c r="BU42" s="133"/>
+      <c r="BU42" s="131"/>
       <c r="BV42" s="42"/>
       <c r="BW42" s="39"/>
     </row>
     <row r="43" spans="1:75" ht="17.25" customHeight="1">
       <c r="A43" s="36"/>
-      <c r="B43" s="134"/>
+      <c r="B43" s="132"/>
       <c r="C43" s="42"/>
-      <c r="D43" s="134"/>
+      <c r="D43" s="132"/>
       <c r="E43" s="42"/>
-      <c r="F43" s="134"/>
+      <c r="F43" s="132"/>
       <c r="G43" s="42"/>
       <c r="H43" s="36"/>
-      <c r="I43" s="131"/>
+      <c r="I43" s="129"/>
       <c r="J43" s="50"/>
-      <c r="K43" s="131"/>
+      <c r="K43" s="129"/>
       <c r="L43" s="50"/>
-      <c r="M43" s="132" t="s">
+      <c r="M43" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N43" s="53"/>
-      <c r="O43" s="131"/>
+      <c r="O43" s="129"/>
       <c r="P43" s="50"/>
-      <c r="Q43" s="131"/>
+      <c r="Q43" s="129"/>
       <c r="R43" s="50"/>
-      <c r="S43" s="132" t="s">
+      <c r="S43" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T43" s="53"/>
-      <c r="U43" s="131"/>
+      <c r="U43" s="129"/>
       <c r="V43" s="50"/>
-      <c r="W43" s="131"/>
+      <c r="W43" s="129"/>
       <c r="X43" s="50"/>
-      <c r="Y43" s="131"/>
+      <c r="Y43" s="129"/>
       <c r="Z43" s="50"/>
-      <c r="AA43" s="131"/>
+      <c r="AA43" s="129"/>
       <c r="AB43" s="50"/>
       <c r="AC43" s="36"/>
-      <c r="AD43" s="131"/>
+      <c r="AD43" s="129"/>
       <c r="AE43" s="50"/>
-      <c r="AF43" s="131"/>
+      <c r="AF43" s="129"/>
       <c r="AG43" s="50"/>
-      <c r="AH43" s="131"/>
+      <c r="AH43" s="129"/>
       <c r="AI43" s="50"/>
-      <c r="AJ43" s="131"/>
+      <c r="AJ43" s="129"/>
       <c r="AK43" s="50"/>
-      <c r="AL43" s="131"/>
+      <c r="AL43" s="129"/>
       <c r="AM43" s="50"/>
-      <c r="AN43" s="131"/>
+      <c r="AN43" s="129"/>
       <c r="AO43" s="50"/>
-      <c r="AP43" s="131"/>
+      <c r="AP43" s="129"/>
       <c r="AQ43" s="50"/>
-      <c r="AR43" s="131"/>
+      <c r="AR43" s="129"/>
       <c r="AS43" s="50"/>
-      <c r="AT43" s="131"/>
+      <c r="AT43" s="129"/>
       <c r="AU43" s="50"/>
-      <c r="AV43" s="131"/>
+      <c r="AV43" s="129"/>
       <c r="AW43" s="50"/>
-      <c r="AX43" s="131"/>
+      <c r="AX43" s="129"/>
       <c r="AY43" s="50"/>
-      <c r="AZ43" s="131"/>
+      <c r="AZ43" s="129"/>
       <c r="BA43" s="50"/>
       <c r="BB43" s="36"/>
       <c r="BC43" s="36"/>
-      <c r="BD43" s="131"/>
+      <c r="BD43" s="129"/>
       <c r="BE43" s="50"/>
-      <c r="BF43" s="131"/>
+      <c r="BF43" s="129"/>
       <c r="BG43" s="50"/>
-      <c r="BH43" s="131"/>
+      <c r="BH43" s="129"/>
       <c r="BI43" s="50"/>
-      <c r="BJ43" s="131"/>
+      <c r="BJ43" s="129"/>
       <c r="BK43" s="50"/>
-      <c r="BL43" s="131"/>
+      <c r="BL43" s="129"/>
       <c r="BM43" s="50"/>
-      <c r="BN43" s="131"/>
+      <c r="BN43" s="129"/>
       <c r="BO43" s="50"/>
-      <c r="BP43" s="131"/>
+      <c r="BP43" s="129"/>
       <c r="BQ43" s="50"/>
-      <c r="BR43" s="131"/>
+      <c r="BR43" s="129"/>
       <c r="BS43" s="50"/>
-      <c r="BT43" s="131"/>
+      <c r="BT43" s="129"/>
       <c r="BU43" s="50"/>
-      <c r="BV43" s="131"/>
+      <c r="BV43" s="129"/>
       <c r="BW43" s="50"/>
     </row>
     <row r="44" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A44" s="119"/>
+      <c r="A44" s="118"/>
       <c r="B44" s="42"/>
-      <c r="C44" s="119"/>
+      <c r="C44" s="118"/>
       <c r="D44" s="42"/>
-      <c r="E44" s="119"/>
+      <c r="E44" s="118"/>
       <c r="F44" s="42"/>
-      <c r="G44" s="119"/>
+      <c r="G44" s="118"/>
       <c r="H44" s="42"/>
-      <c r="I44" s="119"/>
+      <c r="I44" s="118"/>
       <c r="J44" s="42"/>
-      <c r="K44" s="119"/>
+      <c r="K44" s="118"/>
       <c r="L44" s="42"/>
-      <c r="M44" s="119"/>
+      <c r="M44" s="118"/>
       <c r="N44" s="42"/>
-      <c r="O44" s="119"/>
+      <c r="O44" s="118"/>
       <c r="P44" s="42"/>
-      <c r="Q44" s="119"/>
+      <c r="Q44" s="118"/>
       <c r="R44" s="42"/>
-      <c r="S44" s="119"/>
+      <c r="S44" s="118"/>
       <c r="T44" s="42"/>
-      <c r="U44" s="119"/>
+      <c r="U44" s="118"/>
       <c r="V44" s="42"/>
-      <c r="W44" s="119"/>
+      <c r="W44" s="118"/>
       <c r="X44" s="42"/>
-      <c r="Y44" s="119"/>
+      <c r="Y44" s="118"/>
       <c r="Z44" s="42"/>
-      <c r="AA44" s="119"/>
+      <c r="AA44" s="118"/>
       <c r="AB44" s="42"/>
-      <c r="AC44" s="119"/>
+      <c r="AC44" s="118"/>
       <c r="AD44" s="42"/>
-      <c r="AE44" s="119"/>
+      <c r="AE44" s="118"/>
       <c r="AF44" s="42"/>
-      <c r="AG44" s="119"/>
+      <c r="AG44" s="118"/>
       <c r="AH44" s="42"/>
-      <c r="AI44" s="119"/>
+      <c r="AI44" s="118"/>
       <c r="AJ44" s="42"/>
-      <c r="AK44" s="119"/>
+      <c r="AK44" s="118"/>
       <c r="AL44" s="42"/>
-      <c r="AM44" s="119"/>
+      <c r="AM44" s="118"/>
       <c r="AN44" s="42"/>
-      <c r="AO44" s="119"/>
+      <c r="AO44" s="118"/>
       <c r="AP44" s="42"/>
-      <c r="AQ44" s="119"/>
+      <c r="AQ44" s="118"/>
       <c r="AR44" s="42"/>
-      <c r="AS44" s="119"/>
+      <c r="AS44" s="118"/>
       <c r="AT44" s="42"/>
-      <c r="AU44" s="119"/>
+      <c r="AU44" s="118"/>
       <c r="AV44" s="42"/>
-      <c r="AW44" s="119"/>
+      <c r="AW44" s="118"/>
       <c r="AX44" s="42"/>
-      <c r="AY44" s="119"/>
+      <c r="AY44" s="118"/>
       <c r="AZ44" s="42"/>
-      <c r="BA44" s="119"/>
+      <c r="BA44" s="118"/>
       <c r="BB44" s="42"/>
-      <c r="BC44" s="119"/>
+      <c r="BC44" s="118"/>
       <c r="BD44" s="42"/>
-      <c r="BE44" s="119"/>
+      <c r="BE44" s="118"/>
       <c r="BF44" s="42"/>
-      <c r="BG44" s="119"/>
+      <c r="BG44" s="118"/>
       <c r="BH44" s="42"/>
-      <c r="BI44" s="119"/>
+      <c r="BI44" s="118"/>
       <c r="BJ44" s="42"/>
-      <c r="BK44" s="119"/>
+      <c r="BK44" s="118"/>
       <c r="BL44" s="42"/>
-      <c r="BM44" s="119"/>
+      <c r="BM44" s="118"/>
       <c r="BN44" s="42"/>
-      <c r="BO44" s="119"/>
+      <c r="BO44" s="118"/>
       <c r="BP44" s="42"/>
-      <c r="BQ44" s="119"/>
+      <c r="BQ44" s="118"/>
       <c r="BR44" s="42"/>
-      <c r="BS44" s="119"/>
+      <c r="BS44" s="118"/>
       <c r="BT44" s="42"/>
-      <c r="BU44" s="119"/>
+      <c r="BU44" s="118"/>
       <c r="BV44" s="42"/>
       <c r="BW44" s="36"/>
     </row>
     <row r="45" spans="1:75" ht="17.25" customHeight="1">
       <c r="A45" s="36"/>
-      <c r="B45" s="131"/>
+      <c r="B45" s="129"/>
       <c r="C45" s="50"/>
-      <c r="D45" s="131"/>
+      <c r="D45" s="129"/>
       <c r="E45" s="50"/>
-      <c r="F45" s="131"/>
+      <c r="F45" s="129"/>
       <c r="G45" s="50"/>
       <c r="H45" s="36"/>
-      <c r="I45" s="131"/>
+      <c r="I45" s="129"/>
       <c r="J45" s="50"/>
-      <c r="K45" s="131"/>
+      <c r="K45" s="129"/>
       <c r="L45" s="50"/>
-      <c r="M45" s="132" t="s">
+      <c r="M45" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N45" s="53"/>
-      <c r="O45" s="131"/>
+      <c r="O45" s="129"/>
       <c r="P45" s="50"/>
-      <c r="Q45" s="131"/>
+      <c r="Q45" s="129"/>
       <c r="R45" s="50"/>
-      <c r="S45" s="132" t="s">
+      <c r="S45" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T45" s="53"/>
-      <c r="U45" s="131"/>
+      <c r="U45" s="129"/>
       <c r="V45" s="50"/>
-      <c r="W45" s="131"/>
+      <c r="W45" s="129"/>
       <c r="X45" s="50"/>
-      <c r="Y45" s="131"/>
+      <c r="Y45" s="129"/>
       <c r="Z45" s="50"/>
-      <c r="AA45" s="131"/>
+      <c r="AA45" s="129"/>
       <c r="AB45" s="50"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="131"/>
+      <c r="AD45" s="129"/>
       <c r="AE45" s="50"/>
-      <c r="AF45" s="131"/>
+      <c r="AF45" s="129"/>
       <c r="AG45" s="50"/>
-      <c r="AH45" s="131"/>
+      <c r="AH45" s="129"/>
       <c r="AI45" s="50"/>
-      <c r="AJ45" s="131"/>
+      <c r="AJ45" s="129"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="131"/>
+      <c r="AL45" s="129"/>
       <c r="AM45" s="50"/>
-      <c r="AN45" s="131"/>
+      <c r="AN45" s="129"/>
       <c r="AO45" s="50"/>
-      <c r="AP45" s="131"/>
+      <c r="AP45" s="129"/>
       <c r="AQ45" s="50"/>
-      <c r="AR45" s="131"/>
+      <c r="AR45" s="129"/>
       <c r="AS45" s="50"/>
-      <c r="AT45" s="131"/>
+      <c r="AT45" s="129"/>
       <c r="AU45" s="50"/>
-      <c r="AV45" s="131"/>
+      <c r="AV45" s="129"/>
       <c r="AW45" s="50"/>
-      <c r="AX45" s="131"/>
+      <c r="AX45" s="129"/>
       <c r="AY45" s="50"/>
-      <c r="AZ45" s="131"/>
+      <c r="AZ45" s="129"/>
       <c r="BA45" s="50"/>
       <c r="BB45" s="36"/>
       <c r="BC45" s="36"/>
-      <c r="BD45" s="131"/>
+      <c r="BD45" s="129"/>
       <c r="BE45" s="50"/>
-      <c r="BF45" s="131"/>
+      <c r="BF45" s="129"/>
       <c r="BG45" s="50"/>
-      <c r="BH45" s="131"/>
+      <c r="BH45" s="129"/>
       <c r="BI45" s="50"/>
-      <c r="BJ45" s="131"/>
+      <c r="BJ45" s="129"/>
       <c r="BK45" s="50"/>
-      <c r="BL45" s="131"/>
+      <c r="BL45" s="129"/>
       <c r="BM45" s="50"/>
-      <c r="BN45" s="131"/>
+      <c r="BN45" s="129"/>
       <c r="BO45" s="50"/>
-      <c r="BP45" s="131"/>
+      <c r="BP45" s="129"/>
       <c r="BQ45" s="50"/>
-      <c r="BR45" s="131"/>
+      <c r="BR45" s="129"/>
       <c r="BS45" s="50"/>
-      <c r="BT45" s="131"/>
+      <c r="BT45" s="129"/>
       <c r="BU45" s="50"/>
-      <c r="BV45" s="131"/>
+      <c r="BV45" s="129"/>
       <c r="BW45" s="50"/>
     </row>
     <row r="46" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A46" s="133"/>
+      <c r="A46" s="131"/>
       <c r="B46" s="42"/>
-      <c r="C46" s="133"/>
+      <c r="C46" s="131"/>
       <c r="D46" s="42"/>
-      <c r="E46" s="133"/>
+      <c r="E46" s="131"/>
       <c r="F46" s="42"/>
-      <c r="G46" s="133"/>
+      <c r="G46" s="131"/>
       <c r="H46" s="42"/>
-      <c r="I46" s="133"/>
+      <c r="I46" s="131"/>
       <c r="J46" s="42"/>
-      <c r="K46" s="133"/>
+      <c r="K46" s="131"/>
       <c r="L46" s="42"/>
-      <c r="M46" s="133"/>
+      <c r="M46" s="131"/>
       <c r="N46" s="42"/>
-      <c r="O46" s="133"/>
+      <c r="O46" s="131"/>
       <c r="P46" s="42"/>
-      <c r="Q46" s="133"/>
+      <c r="Q46" s="131"/>
       <c r="R46" s="42"/>
-      <c r="S46" s="133"/>
+      <c r="S46" s="131"/>
       <c r="T46" s="42"/>
-      <c r="U46" s="133"/>
+      <c r="U46" s="131"/>
       <c r="V46" s="42"/>
-      <c r="W46" s="133"/>
+      <c r="W46" s="131"/>
       <c r="X46" s="42"/>
-      <c r="Y46" s="133"/>
+      <c r="Y46" s="131"/>
       <c r="Z46" s="42"/>
-      <c r="AA46" s="133"/>
+      <c r="AA46" s="131"/>
       <c r="AB46" s="42"/>
-      <c r="AC46" s="133"/>
+      <c r="AC46" s="131"/>
       <c r="AD46" s="42"/>
-      <c r="AE46" s="133"/>
+      <c r="AE46" s="131"/>
       <c r="AF46" s="42"/>
-      <c r="AG46" s="133"/>
+      <c r="AG46" s="131"/>
       <c r="AH46" s="42"/>
-      <c r="AI46" s="133"/>
+      <c r="AI46" s="131"/>
       <c r="AJ46" s="42"/>
-      <c r="AK46" s="133"/>
+      <c r="AK46" s="131"/>
       <c r="AL46" s="42"/>
-      <c r="AM46" s="133"/>
+      <c r="AM46" s="131"/>
       <c r="AN46" s="42"/>
-      <c r="AO46" s="133"/>
+      <c r="AO46" s="131"/>
       <c r="AP46" s="42"/>
-      <c r="AQ46" s="133"/>
+      <c r="AQ46" s="131"/>
       <c r="AR46" s="42"/>
-      <c r="AS46" s="133"/>
+      <c r="AS46" s="131"/>
       <c r="AT46" s="42"/>
-      <c r="AU46" s="133"/>
+      <c r="AU46" s="131"/>
       <c r="AV46" s="42"/>
-      <c r="AW46" s="133"/>
+      <c r="AW46" s="131"/>
       <c r="AX46" s="42"/>
-      <c r="AY46" s="133"/>
+      <c r="AY46" s="131"/>
       <c r="AZ46" s="42"/>
-      <c r="BA46" s="133"/>
+      <c r="BA46" s="131"/>
       <c r="BB46" s="42"/>
-      <c r="BC46" s="133"/>
+      <c r="BC46" s="131"/>
       <c r="BD46" s="42"/>
-      <c r="BE46" s="133"/>
+      <c r="BE46" s="131"/>
       <c r="BF46" s="42"/>
-      <c r="BG46" s="133"/>
+      <c r="BG46" s="131"/>
       <c r="BH46" s="42"/>
-      <c r="BI46" s="133"/>
+      <c r="BI46" s="131"/>
       <c r="BJ46" s="42"/>
-      <c r="BK46" s="133"/>
+      <c r="BK46" s="131"/>
       <c r="BL46" s="42"/>
-      <c r="BM46" s="133"/>
+      <c r="BM46" s="131"/>
       <c r="BN46" s="42"/>
-      <c r="BO46" s="133"/>
+      <c r="BO46" s="131"/>
       <c r="BP46" s="42"/>
-      <c r="BQ46" s="133"/>
+      <c r="BQ46" s="131"/>
       <c r="BR46" s="42"/>
-      <c r="BS46" s="133"/>
+      <c r="BS46" s="131"/>
       <c r="BT46" s="42"/>
-      <c r="BU46" s="133"/>
+      <c r="BU46" s="131"/>
       <c r="BV46" s="42"/>
       <c r="BW46" s="39"/>
     </row>
     <row r="47" spans="1:75" ht="17.25" customHeight="1">
       <c r="A47" s="36"/>
-      <c r="B47" s="134"/>
+      <c r="B47" s="132"/>
       <c r="C47" s="42"/>
-      <c r="D47" s="134"/>
+      <c r="D47" s="132"/>
       <c r="E47" s="42"/>
-      <c r="F47" s="134"/>
+      <c r="F47" s="132"/>
       <c r="G47" s="42"/>
       <c r="H47" s="36"/>
-      <c r="I47" s="131"/>
+      <c r="I47" s="129"/>
       <c r="J47" s="50"/>
-      <c r="K47" s="131"/>
+      <c r="K47" s="129"/>
       <c r="L47" s="50"/>
-      <c r="M47" s="132" t="s">
+      <c r="M47" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N47" s="53"/>
-      <c r="O47" s="131"/>
+      <c r="O47" s="129"/>
       <c r="P47" s="50"/>
-      <c r="Q47" s="131"/>
+      <c r="Q47" s="129"/>
       <c r="R47" s="50"/>
-      <c r="S47" s="132" t="s">
+      <c r="S47" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T47" s="53"/>
-      <c r="U47" s="131"/>
+      <c r="U47" s="129"/>
       <c r="V47" s="50"/>
-      <c r="W47" s="131"/>
+      <c r="W47" s="129"/>
       <c r="X47" s="50"/>
-      <c r="Y47" s="131"/>
+      <c r="Y47" s="129"/>
       <c r="Z47" s="50"/>
-      <c r="AA47" s="131"/>
+      <c r="AA47" s="129"/>
       <c r="AB47" s="50"/>
       <c r="AC47" s="36"/>
-      <c r="AD47" s="131"/>
+      <c r="AD47" s="129"/>
       <c r="AE47" s="50"/>
-      <c r="AF47" s="131"/>
+      <c r="AF47" s="129"/>
       <c r="AG47" s="50"/>
-      <c r="AH47" s="131"/>
+      <c r="AH47" s="129"/>
       <c r="AI47" s="50"/>
-      <c r="AJ47" s="131"/>
+      <c r="AJ47" s="129"/>
       <c r="AK47" s="50"/>
-      <c r="AL47" s="131"/>
+      <c r="AL47" s="129"/>
       <c r="AM47" s="50"/>
-      <c r="AN47" s="131"/>
+      <c r="AN47" s="129"/>
       <c r="AO47" s="50"/>
-      <c r="AP47" s="131"/>
+      <c r="AP47" s="129"/>
       <c r="AQ47" s="50"/>
-      <c r="AR47" s="131"/>
+      <c r="AR47" s="129"/>
       <c r="AS47" s="50"/>
-      <c r="AT47" s="131"/>
+      <c r="AT47" s="129"/>
       <c r="AU47" s="50"/>
-      <c r="AV47" s="131"/>
+      <c r="AV47" s="129"/>
       <c r="AW47" s="50"/>
-      <c r="AX47" s="131"/>
+      <c r="AX47" s="129"/>
       <c r="AY47" s="50"/>
-      <c r="AZ47" s="131"/>
+      <c r="AZ47" s="129"/>
       <c r="BA47" s="50"/>
       <c r="BB47" s="36"/>
       <c r="BC47" s="36"/>
-      <c r="BD47" s="131"/>
+      <c r="BD47" s="129"/>
       <c r="BE47" s="50"/>
-      <c r="BF47" s="131"/>
+      <c r="BF47" s="129"/>
       <c r="BG47" s="50"/>
-      <c r="BH47" s="131"/>
+      <c r="BH47" s="129"/>
       <c r="BI47" s="50"/>
-      <c r="BJ47" s="131"/>
+      <c r="BJ47" s="129"/>
       <c r="BK47" s="50"/>
-      <c r="BL47" s="131"/>
+      <c r="BL47" s="129"/>
       <c r="BM47" s="50"/>
-      <c r="BN47" s="131"/>
+      <c r="BN47" s="129"/>
       <c r="BO47" s="50"/>
-      <c r="BP47" s="131"/>
+      <c r="BP47" s="129"/>
       <c r="BQ47" s="50"/>
-      <c r="BR47" s="131"/>
+      <c r="BR47" s="129"/>
       <c r="BS47" s="50"/>
-      <c r="BT47" s="131"/>
+      <c r="BT47" s="129"/>
       <c r="BU47" s="50"/>
-      <c r="BV47" s="131"/>
+      <c r="BV47" s="129"/>
       <c r="BW47" s="50"/>
     </row>
     <row r="48" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A48" s="119"/>
+      <c r="A48" s="118"/>
       <c r="B48" s="42"/>
-      <c r="C48" s="119"/>
+      <c r="C48" s="118"/>
       <c r="D48" s="42"/>
-      <c r="E48" s="119"/>
+      <c r="E48" s="118"/>
       <c r="F48" s="42"/>
-      <c r="G48" s="119"/>
+      <c r="G48" s="118"/>
       <c r="H48" s="42"/>
-      <c r="I48" s="119"/>
+      <c r="I48" s="118"/>
       <c r="J48" s="42"/>
-      <c r="K48" s="119"/>
+      <c r="K48" s="118"/>
       <c r="L48" s="42"/>
-      <c r="M48" s="119"/>
+      <c r="M48" s="118"/>
       <c r="N48" s="42"/>
-      <c r="O48" s="119"/>
+      <c r="O48" s="118"/>
       <c r="P48" s="42"/>
-      <c r="Q48" s="119"/>
+      <c r="Q48" s="118"/>
       <c r="R48" s="42"/>
-      <c r="S48" s="119"/>
+      <c r="S48" s="118"/>
       <c r="T48" s="42"/>
-      <c r="U48" s="119"/>
+      <c r="U48" s="118"/>
       <c r="V48" s="42"/>
-      <c r="W48" s="119"/>
+      <c r="W48" s="118"/>
       <c r="X48" s="42"/>
-      <c r="Y48" s="119"/>
+      <c r="Y48" s="118"/>
       <c r="Z48" s="42"/>
-      <c r="AA48" s="119"/>
+      <c r="AA48" s="118"/>
       <c r="AB48" s="42"/>
-      <c r="AC48" s="119"/>
+      <c r="AC48" s="118"/>
       <c r="AD48" s="42"/>
-      <c r="AE48" s="119"/>
+      <c r="AE48" s="118"/>
       <c r="AF48" s="42"/>
-      <c r="AG48" s="119"/>
+      <c r="AG48" s="118"/>
       <c r="AH48" s="42"/>
-      <c r="AI48" s="119"/>
+      <c r="AI48" s="118"/>
       <c r="AJ48" s="42"/>
-      <c r="AK48" s="119"/>
+      <c r="AK48" s="118"/>
       <c r="AL48" s="42"/>
-      <c r="AM48" s="119"/>
+      <c r="AM48" s="118"/>
       <c r="AN48" s="42"/>
-      <c r="AO48" s="119"/>
+      <c r="AO48" s="118"/>
       <c r="AP48" s="42"/>
-      <c r="AQ48" s="119"/>
+      <c r="AQ48" s="118"/>
       <c r="AR48" s="42"/>
-      <c r="AS48" s="119"/>
+      <c r="AS48" s="118"/>
       <c r="AT48" s="42"/>
-      <c r="AU48" s="119"/>
+      <c r="AU48" s="118"/>
       <c r="AV48" s="42"/>
-      <c r="AW48" s="119"/>
+      <c r="AW48" s="118"/>
       <c r="AX48" s="42"/>
-      <c r="AY48" s="119"/>
+      <c r="AY48" s="118"/>
       <c r="AZ48" s="42"/>
-      <c r="BA48" s="119"/>
+      <c r="BA48" s="118"/>
       <c r="BB48" s="42"/>
-      <c r="BC48" s="119"/>
+      <c r="BC48" s="118"/>
       <c r="BD48" s="42"/>
-      <c r="BE48" s="119"/>
+      <c r="BE48" s="118"/>
       <c r="BF48" s="42"/>
-      <c r="BG48" s="119"/>
+      <c r="BG48" s="118"/>
       <c r="BH48" s="42"/>
-      <c r="BI48" s="119"/>
+      <c r="BI48" s="118"/>
       <c r="BJ48" s="42"/>
-      <c r="BK48" s="119"/>
+      <c r="BK48" s="118"/>
       <c r="BL48" s="42"/>
-      <c r="BM48" s="119"/>
+      <c r="BM48" s="118"/>
       <c r="BN48" s="42"/>
-      <c r="BO48" s="119"/>
+      <c r="BO48" s="118"/>
       <c r="BP48" s="42"/>
-      <c r="BQ48" s="119"/>
+      <c r="BQ48" s="118"/>
       <c r="BR48" s="42"/>
-      <c r="BS48" s="119"/>
+      <c r="BS48" s="118"/>
       <c r="BT48" s="42"/>
-      <c r="BU48" s="119"/>
+      <c r="BU48" s="118"/>
       <c r="BV48" s="42"/>
       <c r="BW48" s="36"/>
     </row>
     <row r="49" spans="1:75" ht="17.25" customHeight="1">
       <c r="A49" s="36"/>
-      <c r="B49" s="131"/>
+      <c r="B49" s="129"/>
       <c r="C49" s="50"/>
-      <c r="D49" s="131"/>
+      <c r="D49" s="129"/>
       <c r="E49" s="50"/>
-      <c r="F49" s="131"/>
+      <c r="F49" s="129"/>
       <c r="G49" s="50"/>
       <c r="H49" s="36"/>
-      <c r="I49" s="131"/>
+      <c r="I49" s="129"/>
       <c r="J49" s="50"/>
-      <c r="K49" s="131"/>
+      <c r="K49" s="129"/>
       <c r="L49" s="50"/>
-      <c r="M49" s="132" t="s">
+      <c r="M49" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N49" s="53"/>
-      <c r="O49" s="131"/>
+      <c r="O49" s="129"/>
       <c r="P49" s="50"/>
-      <c r="Q49" s="131"/>
+      <c r="Q49" s="129"/>
       <c r="R49" s="50"/>
-      <c r="S49" s="132" t="s">
+      <c r="S49" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T49" s="53"/>
-      <c r="U49" s="131"/>
+      <c r="U49" s="129"/>
       <c r="V49" s="50"/>
-      <c r="W49" s="131"/>
+      <c r="W49" s="129"/>
       <c r="X49" s="50"/>
-      <c r="Y49" s="131"/>
+      <c r="Y49" s="129"/>
       <c r="Z49" s="50"/>
-      <c r="AA49" s="131"/>
+      <c r="AA49" s="129"/>
       <c r="AB49" s="50"/>
       <c r="AC49" s="36"/>
-      <c r="AD49" s="131"/>
+      <c r="AD49" s="129"/>
       <c r="AE49" s="50"/>
-      <c r="AF49" s="131"/>
+      <c r="AF49" s="129"/>
       <c r="AG49" s="50"/>
-      <c r="AH49" s="131"/>
+      <c r="AH49" s="129"/>
       <c r="AI49" s="50"/>
-      <c r="AJ49" s="131"/>
+      <c r="AJ49" s="129"/>
       <c r="AK49" s="50"/>
-      <c r="AL49" s="131"/>
+      <c r="AL49" s="129"/>
       <c r="AM49" s="50"/>
-      <c r="AN49" s="131"/>
+      <c r="AN49" s="129"/>
       <c r="AO49" s="50"/>
-      <c r="AP49" s="131"/>
+      <c r="AP49" s="129"/>
       <c r="AQ49" s="50"/>
-      <c r="AR49" s="131"/>
+      <c r="AR49" s="129"/>
       <c r="AS49" s="50"/>
-      <c r="AT49" s="131"/>
+      <c r="AT49" s="129"/>
       <c r="AU49" s="50"/>
-      <c r="AV49" s="131"/>
+      <c r="AV49" s="129"/>
       <c r="AW49" s="50"/>
-      <c r="AX49" s="131"/>
+      <c r="AX49" s="129"/>
       <c r="AY49" s="50"/>
-      <c r="AZ49" s="131"/>
+      <c r="AZ49" s="129"/>
       <c r="BA49" s="50"/>
       <c r="BB49" s="36"/>
       <c r="BC49" s="36"/>
-      <c r="BD49" s="131"/>
+      <c r="BD49" s="129"/>
       <c r="BE49" s="50"/>
-      <c r="BF49" s="131"/>
+      <c r="BF49" s="129"/>
       <c r="BG49" s="50"/>
-      <c r="BH49" s="131"/>
+      <c r="BH49" s="129"/>
       <c r="BI49" s="50"/>
-      <c r="BJ49" s="131"/>
+      <c r="BJ49" s="129"/>
       <c r="BK49" s="50"/>
-      <c r="BL49" s="131"/>
+      <c r="BL49" s="129"/>
       <c r="BM49" s="50"/>
-      <c r="BN49" s="131"/>
+      <c r="BN49" s="129"/>
       <c r="BO49" s="50"/>
-      <c r="BP49" s="131"/>
+      <c r="BP49" s="129"/>
       <c r="BQ49" s="50"/>
-      <c r="BR49" s="131"/>
+      <c r="BR49" s="129"/>
       <c r="BS49" s="50"/>
-      <c r="BT49" s="131"/>
+      <c r="BT49" s="129"/>
       <c r="BU49" s="50"/>
-      <c r="BV49" s="131"/>
+      <c r="BV49" s="129"/>
       <c r="BW49" s="50"/>
     </row>
     <row r="50" spans="1:75" ht="7.5" customHeight="1">
-      <c r="A50" s="133"/>
+      <c r="A50" s="131"/>
       <c r="B50" s="42"/>
-      <c r="C50" s="133"/>
+      <c r="C50" s="131"/>
       <c r="D50" s="42"/>
-      <c r="E50" s="133"/>
+      <c r="E50" s="131"/>
       <c r="F50" s="42"/>
-      <c r="G50" s="133"/>
+      <c r="G50" s="131"/>
       <c r="H50" s="42"/>
-      <c r="I50" s="133"/>
+      <c r="I50" s="131"/>
       <c r="J50" s="42"/>
-      <c r="K50" s="133"/>
+      <c r="K50" s="131"/>
       <c r="L50" s="42"/>
-      <c r="M50" s="133"/>
+      <c r="M50" s="131"/>
       <c r="N50" s="42"/>
-      <c r="O50" s="133"/>
+      <c r="O50" s="131"/>
       <c r="P50" s="42"/>
-      <c r="Q50" s="133"/>
+      <c r="Q50" s="131"/>
       <c r="R50" s="42"/>
-      <c r="S50" s="133"/>
+      <c r="S50" s="131"/>
       <c r="T50" s="42"/>
-      <c r="U50" s="133"/>
+      <c r="U50" s="131"/>
       <c r="V50" s="42"/>
-      <c r="W50" s="133"/>
+      <c r="W50" s="131"/>
       <c r="X50" s="42"/>
-      <c r="Y50" s="133"/>
+      <c r="Y50" s="131"/>
       <c r="Z50" s="42"/>
-      <c r="AA50" s="133"/>
+      <c r="AA50" s="131"/>
       <c r="AB50" s="42"/>
-      <c r="AC50" s="133"/>
+      <c r="AC50" s="131"/>
       <c r="AD50" s="42"/>
-      <c r="AE50" s="133"/>
+      <c r="AE50" s="131"/>
       <c r="AF50" s="42"/>
-      <c r="AG50" s="133"/>
+      <c r="AG50" s="131"/>
       <c r="AH50" s="42"/>
-      <c r="AI50" s="133"/>
+      <c r="AI50" s="131"/>
       <c r="AJ50" s="42"/>
-      <c r="AK50" s="133"/>
+      <c r="AK50" s="131"/>
       <c r="AL50" s="42"/>
-      <c r="AM50" s="133"/>
+      <c r="AM50" s="131"/>
       <c r="AN50" s="42"/>
-      <c r="AO50" s="133"/>
+      <c r="AO50" s="131"/>
       <c r="AP50" s="42"/>
-      <c r="AQ50" s="133"/>
+      <c r="AQ50" s="131"/>
       <c r="AR50" s="42"/>
-      <c r="AS50" s="133"/>
+      <c r="AS50" s="131"/>
       <c r="AT50" s="42"/>
-      <c r="AU50" s="133"/>
+      <c r="AU50" s="131"/>
       <c r="AV50" s="42"/>
-      <c r="AW50" s="133"/>
+      <c r="AW50" s="131"/>
       <c r="AX50" s="42"/>
-      <c r="AY50" s="133"/>
+      <c r="AY50" s="131"/>
       <c r="AZ50" s="42"/>
-      <c r="BA50" s="133"/>
+      <c r="BA50" s="131"/>
       <c r="BB50" s="42"/>
-      <c r="BC50" s="133"/>
+      <c r="BC50" s="131"/>
       <c r="BD50" s="42"/>
-      <c r="BE50" s="133"/>
+      <c r="BE50" s="131"/>
       <c r="BF50" s="42"/>
-      <c r="BG50" s="133"/>
+      <c r="BG50" s="131"/>
       <c r="BH50" s="42"/>
-      <c r="BI50" s="133"/>
+      <c r="BI50" s="131"/>
       <c r="BJ50" s="42"/>
-      <c r="BK50" s="133"/>
+      <c r="BK50" s="131"/>
       <c r="BL50" s="42"/>
-      <c r="BM50" s="133"/>
+      <c r="BM50" s="131"/>
       <c r="BN50" s="42"/>
-      <c r="BO50" s="133"/>
+      <c r="BO50" s="131"/>
       <c r="BP50" s="42"/>
-      <c r="BQ50" s="133"/>
+      <c r="BQ50" s="131"/>
       <c r="BR50" s="42"/>
-      <c r="BS50" s="133"/>
+      <c r="BS50" s="131"/>
       <c r="BT50" s="42"/>
-      <c r="BU50" s="133"/>
+      <c r="BU50" s="131"/>
       <c r="BV50" s="42"/>
       <c r="BW50" s="39"/>
     </row>
     <row r="51" spans="1:75" ht="17.25" customHeight="1">
       <c r="A51" s="36"/>
-      <c r="B51" s="134"/>
+      <c r="B51" s="132"/>
       <c r="C51" s="42"/>
-      <c r="D51" s="134"/>
+      <c r="D51" s="132"/>
       <c r="E51" s="42"/>
-      <c r="F51" s="134"/>
+      <c r="F51" s="132"/>
       <c r="G51" s="42"/>
       <c r="H51" s="36"/>
-      <c r="I51" s="131"/>
+      <c r="I51" s="129"/>
       <c r="J51" s="50"/>
-      <c r="K51" s="131"/>
+      <c r="K51" s="129"/>
       <c r="L51" s="50"/>
-      <c r="M51" s="132" t="s">
+      <c r="M51" s="130" t="s">
         <v>44</v>
       </c>
       <c r="N51" s="53"/>
-      <c r="O51" s="131"/>
+      <c r="O51" s="129"/>
       <c r="P51" s="50"/>
-      <c r="Q51" s="131"/>
+      <c r="Q51" s="129"/>
       <c r="R51" s="50"/>
-      <c r="S51" s="132" t="s">
+      <c r="S51" s="130" t="s">
         <v>44</v>
       </c>
       <c r="T51" s="53"/>
-      <c r="U51" s="131"/>
+      <c r="U51" s="129"/>
       <c r="V51" s="50"/>
-      <c r="W51" s="131"/>
+      <c r="W51" s="129"/>
       <c r="X51" s="50"/>
-      <c r="Y51" s="131"/>
+      <c r="Y51" s="129"/>
       <c r="Z51" s="50"/>
-      <c r="AA51" s="131"/>
+      <c r="AA51" s="129"/>
       <c r="AB51" s="50"/>
       <c r="AC51" s="36"/>
-      <c r="AD51" s="131"/>
+      <c r="AD51" s="129"/>
       <c r="AE51" s="50"/>
-      <c r="AF51" s="131"/>
+      <c r="AF51" s="129"/>
       <c r="AG51" s="50"/>
-      <c r="AH51" s="131"/>
+      <c r="AH51" s="129"/>
       <c r="AI51" s="50"/>
-      <c r="AJ51" s="131"/>
+      <c r="AJ51" s="129"/>
       <c r="AK51" s="50"/>
-      <c r="AL51" s="131"/>
+      <c r="AL51" s="129"/>
       <c r="AM51" s="50"/>
-      <c r="AN51" s="131"/>
+      <c r="AN51" s="129"/>
       <c r="AO51" s="50"/>
-      <c r="AP51" s="131"/>
+      <c r="AP51" s="129"/>
       <c r="AQ51" s="50"/>
-      <c r="AR51" s="131"/>
+      <c r="AR51" s="129"/>
       <c r="AS51" s="50"/>
-      <c r="AT51" s="131"/>
+      <c r="AT51" s="129"/>
       <c r="AU51" s="50"/>
-      <c r="AV51" s="131"/>
+      <c r="AV51" s="129"/>
       <c r="AW51" s="50"/>
-      <c r="AX51" s="131"/>
+      <c r="AX51" s="129"/>
       <c r="AY51" s="50"/>
-      <c r="AZ51" s="131"/>
+      <c r="AZ51" s="129"/>
       <c r="BA51" s="50"/>
       <c r="BB51" s="36"/>
       <c r="BC51" s="36"/>
-      <c r="BD51" s="131"/>
+      <c r="BD51" s="129"/>
       <c r="BE51" s="50"/>
-      <c r="BF51" s="131"/>
+      <c r="BF51" s="129"/>
       <c r="BG51" s="50"/>
-      <c r="BH51" s="131"/>
+      <c r="BH51" s="129"/>
       <c r="BI51" s="50"/>
-      <c r="BJ51" s="131"/>
+      <c r="BJ51" s="129"/>
       <c r="BK51" s="50"/>
-      <c r="BL51" s="131"/>
+      <c r="BL51" s="129"/>
       <c r="BM51" s="50"/>
-      <c r="BN51" s="131"/>
+      <c r="BN51" s="129"/>
       <c r="BO51" s="50"/>
-      <c r="BP51" s="131"/>
+      <c r="BP51" s="129"/>
       <c r="BQ51" s="50"/>
-      <c r="BR51" s="131"/>
+      <c r="BR51" s="129"/>
       <c r="BS51" s="50"/>
-      <c r="BT51" s="131"/>
+      <c r="BT51" s="129"/>
       <c r="BU51" s="50"/>
-      <c r="BV51" s="131"/>
+      <c r="BV51" s="129"/>
       <c r="BW51" s="50"/>
     </row>
     <row r="52" spans="1:75" ht="9.75" customHeight="1">
-      <c r="A52" s="119"/>
+      <c r="A52" s="118"/>
       <c r="B52" s="42"/>
-      <c r="C52" s="119"/>
+      <c r="C52" s="118"/>
       <c r="D52" s="42"/>
-      <c r="E52" s="119"/>
+      <c r="E52" s="118"/>
       <c r="F52" s="42"/>
-      <c r="G52" s="119"/>
+      <c r="G52" s="118"/>
       <c r="H52" s="42"/>
-      <c r="I52" s="119"/>
+      <c r="I52" s="118"/>
       <c r="J52" s="42"/>
-      <c r="K52" s="119"/>
+      <c r="K52" s="118"/>
       <c r="L52" s="42"/>
-      <c r="M52" s="119"/>
+      <c r="M52" s="118"/>
       <c r="N52" s="42"/>
-      <c r="O52" s="119"/>
+      <c r="O52" s="118"/>
       <c r="P52" s="42"/>
-      <c r="Q52" s="119"/>
+      <c r="Q52" s="118"/>
       <c r="R52" s="42"/>
-      <c r="S52" s="119"/>
+      <c r="S52" s="118"/>
       <c r="T52" s="42"/>
-      <c r="U52" s="119"/>
+      <c r="U52" s="118"/>
       <c r="V52" s="42"/>
-      <c r="W52" s="119"/>
+      <c r="W52" s="118"/>
       <c r="X52" s="42"/>
-      <c r="Y52" s="119"/>
+      <c r="Y52" s="118"/>
       <c r="Z52" s="42"/>
-      <c r="AA52" s="119"/>
+      <c r="AA52" s="118"/>
       <c r="AB52" s="42"/>
-      <c r="AC52" s="119"/>
+      <c r="AC52" s="118"/>
       <c r="AD52" s="42"/>
-      <c r="AE52" s="119"/>
+      <c r="AE52" s="118"/>
       <c r="AF52" s="42"/>
-      <c r="AG52" s="119"/>
+      <c r="AG52" s="118"/>
       <c r="AH52" s="42"/>
-      <c r="AI52" s="119"/>
+      <c r="AI52" s="118"/>
       <c r="AJ52" s="42"/>
-      <c r="AK52" s="119"/>
+      <c r="AK52" s="118"/>
       <c r="AL52" s="42"/>
-      <c r="AM52" s="119"/>
+      <c r="AM52" s="118"/>
       <c r="AN52" s="42"/>
-      <c r="AO52" s="119"/>
+      <c r="AO52" s="118"/>
       <c r="AP52" s="42"/>
-      <c r="AQ52" s="119"/>
+      <c r="AQ52" s="118"/>
       <c r="AR52" s="42"/>
-      <c r="AS52" s="119"/>
+      <c r="AS52" s="118"/>
       <c r="AT52" s="42"/>
-      <c r="AU52" s="119"/>
+      <c r="AU52" s="118"/>
       <c r="AV52" s="42"/>
-      <c r="AW52" s="119"/>
+      <c r="AW52" s="118"/>
       <c r="AX52" s="42"/>
-      <c r="AY52" s="119"/>
+      <c r="AY52" s="118"/>
       <c r="AZ52" s="42"/>
-      <c r="BA52" s="119"/>
+      <c r="BA52" s="118"/>
       <c r="BB52" s="42"/>
-      <c r="BC52" s="119"/>
+      <c r="BC52" s="118"/>
       <c r="BD52" s="42"/>
-      <c r="BE52" s="119"/>
+      <c r="BE52" s="118"/>
       <c r="BF52" s="42"/>
-      <c r="BG52" s="119"/>
+      <c r="BG52" s="118"/>
       <c r="BH52" s="42"/>
-      <c r="BI52" s="119"/>
+      <c r="BI52" s="118"/>
       <c r="BJ52" s="42"/>
-      <c r="BK52" s="119"/>
+      <c r="BK52" s="118"/>
       <c r="BL52" s="42"/>
-      <c r="BM52" s="119"/>
+      <c r="BM52" s="118"/>
       <c r="BN52" s="42"/>
-      <c r="BO52" s="119"/>
+      <c r="BO52" s="118"/>
       <c r="BP52" s="42"/>
-      <c r="BQ52" s="119"/>
+      <c r="BQ52" s="118"/>
       <c r="BR52" s="42"/>
-      <c r="BS52" s="119"/>
+      <c r="BS52" s="118"/>
       <c r="BT52" s="42"/>
-      <c r="BU52" s="119"/>
+      <c r="BU52" s="118"/>
       <c r="BV52" s="42"/>
       <c r="BW52" s="36"/>
     </row>
     <row r="53" spans="1:75" ht="17.25" customHeight="1">
-      <c r="A53" s="149" t="s">
+      <c r="A53" s="146" t="s">
         <v>220</v>
       </c>
       <c r="B53" s="42"/>
@@ -13041,51 +13049,51 @@
       <c r="AA53" s="42"/>
       <c r="AB53" s="42"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="131"/>
+      <c r="AD53" s="129"/>
       <c r="AE53" s="50"/>
-      <c r="AF53" s="131"/>
+      <c r="AF53" s="129"/>
       <c r="AG53" s="50"/>
-      <c r="AH53" s="131"/>
+      <c r="AH53" s="129"/>
       <c r="AI53" s="50"/>
-      <c r="AJ53" s="131"/>
+      <c r="AJ53" s="129"/>
       <c r="AK53" s="50"/>
-      <c r="AL53" s="131"/>
+      <c r="AL53" s="129"/>
       <c r="AM53" s="50"/>
-      <c r="AN53" s="131"/>
+      <c r="AN53" s="129"/>
       <c r="AO53" s="50"/>
-      <c r="AP53" s="131"/>
+      <c r="AP53" s="129"/>
       <c r="AQ53" s="50"/>
-      <c r="AR53" s="131"/>
+      <c r="AR53" s="129"/>
       <c r="AS53" s="50"/>
-      <c r="AT53" s="131"/>
+      <c r="AT53" s="129"/>
       <c r="AU53" s="50"/>
-      <c r="AV53" s="131"/>
+      <c r="AV53" s="129"/>
       <c r="AW53" s="50"/>
-      <c r="AX53" s="131"/>
+      <c r="AX53" s="129"/>
       <c r="AY53" s="50"/>
-      <c r="AZ53" s="131"/>
+      <c r="AZ53" s="129"/>
       <c r="BA53" s="50"/>
       <c r="BB53" s="36"/>
       <c r="BC53" s="36"/>
-      <c r="BD53" s="131"/>
+      <c r="BD53" s="129"/>
       <c r="BE53" s="50"/>
-      <c r="BF53" s="131"/>
+      <c r="BF53" s="129"/>
       <c r="BG53" s="50"/>
-      <c r="BH53" s="131"/>
+      <c r="BH53" s="129"/>
       <c r="BI53" s="50"/>
-      <c r="BJ53" s="131"/>
+      <c r="BJ53" s="129"/>
       <c r="BK53" s="50"/>
-      <c r="BL53" s="131"/>
+      <c r="BL53" s="129"/>
       <c r="BM53" s="50"/>
-      <c r="BN53" s="131"/>
+      <c r="BN53" s="129"/>
       <c r="BO53" s="50"/>
-      <c r="BP53" s="131"/>
+      <c r="BP53" s="129"/>
       <c r="BQ53" s="50"/>
-      <c r="BR53" s="131"/>
+      <c r="BR53" s="129"/>
       <c r="BS53" s="50"/>
-      <c r="BT53" s="131"/>
+      <c r="BT53" s="129"/>
       <c r="BU53" s="50"/>
-      <c r="BV53" s="131"/>
+      <c r="BV53" s="129"/>
       <c r="BW53" s="50"/>
     </row>
     <row r="54" spans="1:75" ht="7.5" customHeight="1">
@@ -13117,51 +13125,51 @@
       <c r="Z54" s="39"/>
       <c r="AA54" s="39"/>
       <c r="AB54" s="39"/>
-      <c r="AC54" s="133"/>
+      <c r="AC54" s="131"/>
       <c r="AD54" s="42"/>
-      <c r="AE54" s="133"/>
+      <c r="AE54" s="131"/>
       <c r="AF54" s="42"/>
-      <c r="AG54" s="133"/>
+      <c r="AG54" s="131"/>
       <c r="AH54" s="42"/>
-      <c r="AI54" s="133"/>
+      <c r="AI54" s="131"/>
       <c r="AJ54" s="42"/>
-      <c r="AK54" s="133"/>
+      <c r="AK54" s="131"/>
       <c r="AL54" s="42"/>
-      <c r="AM54" s="133"/>
+      <c r="AM54" s="131"/>
       <c r="AN54" s="42"/>
-      <c r="AO54" s="133"/>
+      <c r="AO54" s="131"/>
       <c r="AP54" s="42"/>
-      <c r="AQ54" s="133"/>
+      <c r="AQ54" s="131"/>
       <c r="AR54" s="42"/>
-      <c r="AS54" s="133"/>
+      <c r="AS54" s="131"/>
       <c r="AT54" s="42"/>
-      <c r="AU54" s="133"/>
+      <c r="AU54" s="131"/>
       <c r="AV54" s="42"/>
-      <c r="AW54" s="133"/>
+      <c r="AW54" s="131"/>
       <c r="AX54" s="42"/>
-      <c r="AY54" s="133"/>
+      <c r="AY54" s="131"/>
       <c r="AZ54" s="42"/>
-      <c r="BA54" s="133"/>
+      <c r="BA54" s="131"/>
       <c r="BB54" s="42"/>
-      <c r="BC54" s="133"/>
+      <c r="BC54" s="131"/>
       <c r="BD54" s="42"/>
-      <c r="BE54" s="133"/>
+      <c r="BE54" s="131"/>
       <c r="BF54" s="42"/>
-      <c r="BG54" s="133"/>
+      <c r="BG54" s="131"/>
       <c r="BH54" s="42"/>
-      <c r="BI54" s="133"/>
+      <c r="BI54" s="131"/>
       <c r="BJ54" s="42"/>
-      <c r="BK54" s="133"/>
+      <c r="BK54" s="131"/>
       <c r="BL54" s="42"/>
-      <c r="BM54" s="133"/>
+      <c r="BM54" s="131"/>
       <c r="BN54" s="42"/>
-      <c r="BO54" s="133"/>
+      <c r="BO54" s="131"/>
       <c r="BP54" s="42"/>
-      <c r="BQ54" s="133"/>
+      <c r="BQ54" s="131"/>
       <c r="BR54" s="42"/>
-      <c r="BS54" s="133"/>
+      <c r="BS54" s="131"/>
       <c r="BT54" s="42"/>
-      <c r="BU54" s="133"/>
+      <c r="BU54" s="131"/>
       <c r="BV54" s="42"/>
       <c r="BW54" s="39"/>
     </row>
@@ -13195,55 +13203,55 @@
       <c r="AA55" s="40"/>
       <c r="AB55" s="40"/>
       <c r="AC55" s="36"/>
-      <c r="AD55" s="131"/>
+      <c r="AD55" s="129"/>
       <c r="AE55" s="50"/>
-      <c r="AF55" s="131"/>
+      <c r="AF55" s="129"/>
       <c r="AG55" s="50"/>
-      <c r="AH55" s="131"/>
+      <c r="AH55" s="129"/>
       <c r="AI55" s="50"/>
-      <c r="AJ55" s="131"/>
+      <c r="AJ55" s="129"/>
       <c r="AK55" s="50"/>
-      <c r="AL55" s="131"/>
+      <c r="AL55" s="129"/>
       <c r="AM55" s="50"/>
-      <c r="AN55" s="131"/>
+      <c r="AN55" s="129"/>
       <c r="AO55" s="50"/>
-      <c r="AP55" s="131"/>
+      <c r="AP55" s="129"/>
       <c r="AQ55" s="50"/>
-      <c r="AR55" s="131"/>
+      <c r="AR55" s="129"/>
       <c r="AS55" s="50"/>
-      <c r="AT55" s="131"/>
+      <c r="AT55" s="129"/>
       <c r="AU55" s="50"/>
-      <c r="AV55" s="131"/>
+      <c r="AV55" s="129"/>
       <c r="AW55" s="50"/>
-      <c r="AX55" s="131"/>
+      <c r="AX55" s="129"/>
       <c r="AY55" s="50"/>
-      <c r="AZ55" s="131"/>
+      <c r="AZ55" s="129"/>
       <c r="BA55" s="50"/>
       <c r="BB55" s="36"/>
       <c r="BC55" s="36"/>
-      <c r="BD55" s="131"/>
+      <c r="BD55" s="129"/>
       <c r="BE55" s="50"/>
-      <c r="BF55" s="131"/>
+      <c r="BF55" s="129"/>
       <c r="BG55" s="50"/>
-      <c r="BH55" s="131"/>
+      <c r="BH55" s="129"/>
       <c r="BI55" s="50"/>
-      <c r="BJ55" s="131"/>
+      <c r="BJ55" s="129"/>
       <c r="BK55" s="50"/>
-      <c r="BL55" s="131"/>
+      <c r="BL55" s="129"/>
       <c r="BM55" s="50"/>
-      <c r="BN55" s="131"/>
+      <c r="BN55" s="129"/>
       <c r="BO55" s="50"/>
-      <c r="BP55" s="131"/>
+      <c r="BP55" s="129"/>
       <c r="BQ55" s="50"/>
-      <c r="BR55" s="131"/>
+      <c r="BR55" s="129"/>
       <c r="BS55" s="50"/>
-      <c r="BT55" s="131"/>
+      <c r="BT55" s="129"/>
       <c r="BU55" s="50"/>
-      <c r="BV55" s="131"/>
+      <c r="BV55" s="129"/>
       <c r="BW55" s="50"/>
     </row>
     <row r="56" spans="1:75" ht="45" customHeight="1">
-      <c r="A56" s="150" t="s">
+      <c r="A56" s="147" t="s">
         <v>221</v>
       </c>
       <c r="B56" s="42"/>
@@ -13938,7 +13946,7 @@
       <c r="BW64" s="33"/>
     </row>
     <row r="65" spans="1:75" ht="14.25" customHeight="1">
-      <c r="A65" s="141"/>
+      <c r="A65" s="138"/>
       <c r="B65" s="75"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
@@ -14092,7 +14100,7 @@
       <c r="BW66" s="21"/>
     </row>
     <row r="67" spans="1:75" ht="16.5" customHeight="1">
-      <c r="A67" s="130"/>
+      <c r="A67" s="128"/>
       <c r="B67" s="42"/>
       <c r="C67" s="42"/>
       <c r="D67" s="42"/>
@@ -15854,15 +15862,15 @@
       </c>
       <c r="W1" s="99" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="X1" s="115" t="str">
+        <v>0</v>
+      </c>
+      <c r="X1" s="151" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
-      </c>
-      <c r="Y1" s="115" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y1" s="151" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Z1" s="98"/>
       <c r="AA1" s="42"/>
@@ -15904,9 +15912,9 @@
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
       <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="100"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="152"/>
       <c r="Z2" s="98"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -16128,7 +16136,7 @@
       <c r="AO6" s="42"/>
     </row>
     <row r="7" spans="1:41" ht="31.5" customHeight="1">
-      <c r="A7" s="151" t="s">
+      <c r="A7" s="148" t="s">
         <v>222</v>
       </c>
       <c r="B7" s="42"/>
@@ -18555,7 +18563,7 @@
       <c r="AO61" s="3"/>
     </row>
     <row r="62" spans="1:41" ht="16.5" customHeight="1">
-      <c r="A62" s="130"/>
+      <c r="A62" s="128"/>
       <c r="B62" s="42"/>
       <c r="C62" s="42"/>
       <c r="D62" s="42"/>
@@ -18737,15 +18745,15 @@
       </c>
       <c r="V1" s="99" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="W1" s="99" t="str">
-        <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="X1" s="99" t="str">
-        <f>IF(Титул!AR1="","",Титул!AR1)</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="W1" s="153" t="str">
+        <f>IF(Титул!AS1="","",Титул!AS1)</f>
+        <v>1</v>
+      </c>
+      <c r="X1" s="153" t="str">
+        <f>IF(Титул!AU1="","",Титул!AU1)</f>
+        <v>2</v>
       </c>
       <c r="Y1" s="98"/>
       <c r="Z1" s="42"/>
@@ -18786,9 +18794,9 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
       <c r="Y2" s="98"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
@@ -19395,18 +19403,18 @@
         <v>56</v>
       </c>
       <c r="Y15" s="53"/>
-      <c r="Z15" s="152"/>
-      <c r="AA15" s="152"/>
-      <c r="AB15" s="152"/>
-      <c r="AC15" s="152"/>
-      <c r="AD15" s="152"/>
-      <c r="AE15" s="152"/>
-      <c r="AF15" s="152"/>
-      <c r="AG15" s="152"/>
-      <c r="AH15" s="152"/>
-      <c r="AI15" s="152"/>
-      <c r="AJ15" s="152"/>
-      <c r="AK15" s="152"/>
+      <c r="Z15" s="149"/>
+      <c r="AA15" s="149"/>
+      <c r="AB15" s="149"/>
+      <c r="AC15" s="149"/>
+      <c r="AD15" s="149"/>
+      <c r="AE15" s="149"/>
+      <c r="AF15" s="149"/>
+      <c r="AG15" s="149"/>
+      <c r="AH15" s="149"/>
+      <c r="AI15" s="149"/>
+      <c r="AJ15" s="149"/>
+      <c r="AK15" s="149"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
@@ -19525,17 +19533,17 @@
         <v>57</v>
       </c>
       <c r="Y18" s="53"/>
-      <c r="Z18" s="152"/>
-      <c r="AA18" s="152"/>
-      <c r="AB18" s="152"/>
-      <c r="AC18" s="152"/>
-      <c r="AD18" s="152"/>
-      <c r="AE18" s="152"/>
-      <c r="AF18" s="152"/>
-      <c r="AG18" s="152"/>
-      <c r="AH18" s="152"/>
-      <c r="AI18" s="152"/>
-      <c r="AJ18" s="152"/>
+      <c r="Z18" s="149"/>
+      <c r="AA18" s="149"/>
+      <c r="AB18" s="149"/>
+      <c r="AC18" s="149"/>
+      <c r="AD18" s="149"/>
+      <c r="AE18" s="149"/>
+      <c r="AF18" s="149"/>
+      <c r="AG18" s="149"/>
+      <c r="AH18" s="149"/>
+      <c r="AI18" s="149"/>
+      <c r="AJ18" s="149"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
@@ -19613,18 +19621,18 @@
         <v>59</v>
       </c>
       <c r="Y20" s="53"/>
-      <c r="Z20" s="152"/>
-      <c r="AA20" s="152"/>
-      <c r="AB20" s="152"/>
-      <c r="AC20" s="152"/>
-      <c r="AD20" s="152"/>
-      <c r="AE20" s="152"/>
-      <c r="AF20" s="152"/>
-      <c r="AG20" s="152"/>
-      <c r="AH20" s="152"/>
-      <c r="AI20" s="152"/>
-      <c r="AJ20" s="152"/>
-      <c r="AK20" s="152"/>
+      <c r="Z20" s="149"/>
+      <c r="AA20" s="149"/>
+      <c r="AB20" s="149"/>
+      <c r="AC20" s="149"/>
+      <c r="AD20" s="149"/>
+      <c r="AE20" s="149"/>
+      <c r="AF20" s="149"/>
+      <c r="AG20" s="149"/>
+      <c r="AH20" s="149"/>
+      <c r="AI20" s="149"/>
+      <c r="AJ20" s="149"/>
+      <c r="AK20" s="149"/>
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
@@ -19743,18 +19751,18 @@
         <v>61</v>
       </c>
       <c r="Y23" s="53"/>
-      <c r="Z23" s="152"/>
-      <c r="AA23" s="152"/>
-      <c r="AB23" s="152"/>
-      <c r="AC23" s="152"/>
-      <c r="AD23" s="152"/>
-      <c r="AE23" s="152"/>
-      <c r="AF23" s="152"/>
-      <c r="AG23" s="152"/>
-      <c r="AH23" s="152"/>
-      <c r="AI23" s="152"/>
-      <c r="AJ23" s="152"/>
-      <c r="AK23" s="152"/>
+      <c r="Z23" s="149"/>
+      <c r="AA23" s="149"/>
+      <c r="AB23" s="149"/>
+      <c r="AC23" s="149"/>
+      <c r="AD23" s="149"/>
+      <c r="AE23" s="149"/>
+      <c r="AF23" s="149"/>
+      <c r="AG23" s="149"/>
+      <c r="AH23" s="149"/>
+      <c r="AI23" s="149"/>
+      <c r="AJ23" s="149"/>
+      <c r="AK23" s="149"/>
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
@@ -19873,17 +19881,17 @@
         <v>62</v>
       </c>
       <c r="Y26" s="53"/>
-      <c r="Z26" s="152"/>
-      <c r="AA26" s="152"/>
-      <c r="AB26" s="152"/>
-      <c r="AC26" s="152"/>
-      <c r="AD26" s="152"/>
-      <c r="AE26" s="152"/>
-      <c r="AF26" s="152"/>
-      <c r="AG26" s="152"/>
-      <c r="AH26" s="152"/>
-      <c r="AI26" s="152"/>
-      <c r="AJ26" s="152"/>
+      <c r="Z26" s="149"/>
+      <c r="AA26" s="149"/>
+      <c r="AB26" s="149"/>
+      <c r="AC26" s="149"/>
+      <c r="AD26" s="149"/>
+      <c r="AE26" s="149"/>
+      <c r="AF26" s="149"/>
+      <c r="AG26" s="149"/>
+      <c r="AH26" s="149"/>
+      <c r="AI26" s="149"/>
+      <c r="AJ26" s="149"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
@@ -19961,18 +19969,18 @@
         <v>64</v>
       </c>
       <c r="Y28" s="53"/>
-      <c r="Z28" s="152"/>
-      <c r="AA28" s="152"/>
-      <c r="AB28" s="152"/>
-      <c r="AC28" s="152"/>
-      <c r="AD28" s="152"/>
-      <c r="AE28" s="152"/>
-      <c r="AF28" s="152"/>
-      <c r="AG28" s="152"/>
-      <c r="AH28" s="152"/>
-      <c r="AI28" s="152"/>
-      <c r="AJ28" s="152"/>
-      <c r="AK28" s="152"/>
+      <c r="Z28" s="149"/>
+      <c r="AA28" s="149"/>
+      <c r="AB28" s="149"/>
+      <c r="AC28" s="149"/>
+      <c r="AD28" s="149"/>
+      <c r="AE28" s="149"/>
+      <c r="AF28" s="149"/>
+      <c r="AG28" s="149"/>
+      <c r="AH28" s="149"/>
+      <c r="AI28" s="149"/>
+      <c r="AJ28" s="149"/>
+      <c r="AK28" s="149"/>
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
       <c r="AN28" s="3"/>
@@ -20091,18 +20099,18 @@
         <v>66</v>
       </c>
       <c r="Y31" s="53"/>
-      <c r="Z31" s="152"/>
-      <c r="AA31" s="152"/>
-      <c r="AB31" s="152"/>
-      <c r="AC31" s="152"/>
-      <c r="AD31" s="152"/>
-      <c r="AE31" s="152"/>
-      <c r="AF31" s="152"/>
-      <c r="AG31" s="152"/>
-      <c r="AH31" s="152"/>
-      <c r="AI31" s="152"/>
-      <c r="AJ31" s="152"/>
-      <c r="AK31" s="152"/>
+      <c r="Z31" s="149"/>
+      <c r="AA31" s="149"/>
+      <c r="AB31" s="149"/>
+      <c r="AC31" s="149"/>
+      <c r="AD31" s="149"/>
+      <c r="AE31" s="149"/>
+      <c r="AF31" s="149"/>
+      <c r="AG31" s="149"/>
+      <c r="AH31" s="149"/>
+      <c r="AI31" s="149"/>
+      <c r="AJ31" s="149"/>
+      <c r="AK31" s="149"/>
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
@@ -20221,17 +20229,17 @@
         <v>67</v>
       </c>
       <c r="Y34" s="53"/>
-      <c r="Z34" s="152"/>
-      <c r="AA34" s="152"/>
-      <c r="AB34" s="152"/>
-      <c r="AC34" s="152"/>
-      <c r="AD34" s="152"/>
-      <c r="AE34" s="152"/>
-      <c r="AF34" s="152"/>
-      <c r="AG34" s="152"/>
-      <c r="AH34" s="152"/>
-      <c r="AI34" s="152"/>
-      <c r="AJ34" s="152"/>
+      <c r="Z34" s="149"/>
+      <c r="AA34" s="149"/>
+      <c r="AB34" s="149"/>
+      <c r="AC34" s="149"/>
+      <c r="AD34" s="149"/>
+      <c r="AE34" s="149"/>
+      <c r="AF34" s="149"/>
+      <c r="AG34" s="149"/>
+      <c r="AH34" s="149"/>
+      <c r="AI34" s="149"/>
+      <c r="AJ34" s="149"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
@@ -20309,18 +20317,18 @@
         <v>69</v>
       </c>
       <c r="Y36" s="53"/>
-      <c r="Z36" s="152"/>
-      <c r="AA36" s="152"/>
-      <c r="AB36" s="152"/>
-      <c r="AC36" s="152"/>
-      <c r="AD36" s="152"/>
-      <c r="AE36" s="152"/>
-      <c r="AF36" s="152"/>
-      <c r="AG36" s="152"/>
-      <c r="AH36" s="152"/>
-      <c r="AI36" s="152"/>
-      <c r="AJ36" s="152"/>
-      <c r="AK36" s="152"/>
+      <c r="Z36" s="149"/>
+      <c r="AA36" s="149"/>
+      <c r="AB36" s="149"/>
+      <c r="AC36" s="149"/>
+      <c r="AD36" s="149"/>
+      <c r="AE36" s="149"/>
+      <c r="AF36" s="149"/>
+      <c r="AG36" s="149"/>
+      <c r="AH36" s="149"/>
+      <c r="AI36" s="149"/>
+      <c r="AJ36" s="149"/>
+      <c r="AK36" s="149"/>
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
@@ -20439,18 +20447,18 @@
         <v>71</v>
       </c>
       <c r="Y39" s="53"/>
-      <c r="Z39" s="152"/>
-      <c r="AA39" s="152"/>
-      <c r="AB39" s="152"/>
-      <c r="AC39" s="152"/>
-      <c r="AD39" s="152"/>
-      <c r="AE39" s="152"/>
-      <c r="AF39" s="152"/>
-      <c r="AG39" s="152"/>
-      <c r="AH39" s="152"/>
-      <c r="AI39" s="152"/>
-      <c r="AJ39" s="152"/>
-      <c r="AK39" s="152"/>
+      <c r="Z39" s="149"/>
+      <c r="AA39" s="149"/>
+      <c r="AB39" s="149"/>
+      <c r="AC39" s="149"/>
+      <c r="AD39" s="149"/>
+      <c r="AE39" s="149"/>
+      <c r="AF39" s="149"/>
+      <c r="AG39" s="149"/>
+      <c r="AH39" s="149"/>
+      <c r="AI39" s="149"/>
+      <c r="AJ39" s="149"/>
+      <c r="AK39" s="149"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
@@ -20527,18 +20535,18 @@
         <v>73</v>
       </c>
       <c r="Y41" s="53"/>
-      <c r="Z41" s="152"/>
-      <c r="AA41" s="152"/>
-      <c r="AB41" s="152"/>
-      <c r="AC41" s="152"/>
-      <c r="AD41" s="152"/>
-      <c r="AE41" s="152"/>
-      <c r="AF41" s="152"/>
-      <c r="AG41" s="152"/>
-      <c r="AH41" s="152"/>
-      <c r="AI41" s="152"/>
-      <c r="AJ41" s="152"/>
-      <c r="AK41" s="152"/>
+      <c r="Z41" s="149"/>
+      <c r="AA41" s="149"/>
+      <c r="AB41" s="149"/>
+      <c r="AC41" s="149"/>
+      <c r="AD41" s="149"/>
+      <c r="AE41" s="149"/>
+      <c r="AF41" s="149"/>
+      <c r="AG41" s="149"/>
+      <c r="AH41" s="149"/>
+      <c r="AI41" s="149"/>
+      <c r="AJ41" s="149"/>
+      <c r="AK41" s="149"/>
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
@@ -21125,15 +21133,15 @@
       </c>
       <c r="V1" s="99" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W1" s="153" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X1" s="153" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y1" s="106"/>
       <c r="Z1" s="42"/>
@@ -21174,9 +21182,9 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="154"/>
-      <c r="W2" s="154"/>
-      <c r="X2" s="154"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
       <c r="Y2" s="106"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
@@ -23567,15 +23575,15 @@
       </c>
       <c r="W1" s="99" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="X1" s="155" t="str">
+        <v>0</v>
+      </c>
+      <c r="X1" s="151" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
-      </c>
-      <c r="Y1" s="155" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y1" s="151" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Z1" s="98"/>
       <c r="AA1" s="42"/>
@@ -23617,9 +23625,9 @@
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
       <c r="V2" s="100"/>
-      <c r="W2" s="156"/>
-      <c r="X2" s="156"/>
-      <c r="Y2" s="156"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="152"/>
       <c r="Z2" s="98"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -26052,15 +26060,15 @@
       </c>
       <c r="V1" s="99" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="W1" s="155" t="str">
+        <v>0</v>
+      </c>
+      <c r="W1" s="151" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
-      </c>
-      <c r="X1" s="155" t="str">
+        <v>1</v>
+      </c>
+      <c r="X1" s="151" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y1" s="98"/>
       <c r="Z1" s="42"/>
@@ -26101,9 +26109,9 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="156"/>
-      <c r="W2" s="156"/>
-      <c r="X2" s="156"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
       <c r="Y2" s="98"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
@@ -26411,7 +26419,7 @@
       <c r="AN8" s="3"/>
     </row>
     <row r="9" spans="1:40" ht="12.75">
-      <c r="A9" s="116" t="s">
+      <c r="A9" s="115" t="s">
         <v>118</v>
       </c>
       <c r="B9" s="42"/>
@@ -30263,7 +30271,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="14.25" customHeight="1">
       <c r="A1" s="26"/>
-      <c r="B1" s="125"/>
+      <c r="B1" s="123"/>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
@@ -30271,60 +30279,60 @@
       <c r="G1" s="42"/>
       <c r="H1" s="42"/>
       <c r="I1" s="23"/>
-      <c r="J1" s="124" t="s">
+      <c r="J1" s="122" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="42"/>
       <c r="L1" s="53"/>
-      <c r="M1" s="126" t="str">
+      <c r="M1" s="124" t="str">
         <f>IF(Титул!Y1="","",Титул!Y1)</f>
         <v>1</v>
       </c>
-      <c r="N1" s="126" t="str">
+      <c r="N1" s="124" t="str">
         <f>IF(Титул!AA1="","",Титул!AA1)</f>
         <v>2</v>
       </c>
-      <c r="O1" s="126" t="str">
+      <c r="O1" s="124" t="str">
         <f>IF(Титул!AC1="","",Титул!AC1)</f>
         <v>3</v>
       </c>
-      <c r="P1" s="126" t="str">
+      <c r="P1" s="124" t="str">
         <f>IF(Титул!AE1="","",Титул!AE1)</f>
         <v>4</v>
       </c>
-      <c r="Q1" s="126" t="str">
+      <c r="Q1" s="124" t="str">
         <f>IF(Титул!AG1="","",Титул!AG1)</f>
         <v>5</v>
       </c>
-      <c r="R1" s="126" t="str">
+      <c r="R1" s="124" t="str">
         <f>IF(Титул!AI1="","",Титул!AI1)</f>
         <v>6</v>
       </c>
-      <c r="S1" s="126" t="str">
+      <c r="S1" s="124" t="str">
         <f>IF(Титул!AK1="","",Титул!AK1)</f>
         <v>7</v>
       </c>
-      <c r="T1" s="126" t="str">
+      <c r="T1" s="124" t="str">
         <f>IF(Титул!AM1="","",Титул!AM1)</f>
         <v>8</v>
       </c>
-      <c r="U1" s="126" t="str">
+      <c r="U1" s="124" t="str">
         <f>IF(Титул!AO1="","",Титул!AO1)</f>
         <v>9</v>
       </c>
-      <c r="V1" s="126" t="str">
+      <c r="V1" s="124" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="W1" s="123" t="str">
+        <v>0</v>
+      </c>
+      <c r="W1" s="154" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
-      </c>
-      <c r="X1" s="123" t="str">
+        <v>1</v>
+      </c>
+      <c r="X1" s="154" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
-      </c>
-      <c r="Y1" s="121"/>
+        <v>2</v>
+      </c>
+      <c r="Y1" s="120"/>
       <c r="Z1" s="42"/>
       <c r="AA1" s="42"/>
       <c r="AB1" s="42"/>
@@ -30363,10 +30371,10 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="121"/>
+      <c r="V2" s="150"/>
+      <c r="W2" s="150"/>
+      <c r="X2" s="150"/>
+      <c r="Y2" s="120"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -30435,7 +30443,7 @@
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="21"/>
-      <c r="J4" s="124" t="s">
+      <c r="J4" s="122" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="42"/>
@@ -30476,14 +30484,14 @@
         <f>IF(Титул!AO4="","",Титул!AO4)</f>
         <v/>
       </c>
-      <c r="V4" s="124" t="s">
+      <c r="V4" s="122" t="s">
         <v>12</v>
       </c>
       <c r="W4" s="53"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="29"/>
       <c r="Z4" s="29"/>
-      <c r="AA4" s="122"/>
+      <c r="AA4" s="121"/>
       <c r="AB4" s="42"/>
       <c r="AC4" s="42"/>
       <c r="AD4" s="42"/>
@@ -30583,7 +30591,7 @@
       <c r="AN6" s="42"/>
     </row>
     <row r="7" spans="1:40" ht="6" customHeight="1">
-      <c r="A7" s="125"/>
+      <c r="A7" s="123"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -30625,7 +30633,7 @@
       <c r="AN7" s="42"/>
     </row>
     <row r="8" spans="1:40" ht="42" customHeight="1">
-      <c r="A8" s="127" t="s">
+      <c r="A8" s="125" t="s">
         <v>137</v>
       </c>
       <c r="B8" s="42"/>
@@ -30670,7 +30678,7 @@
     </row>
     <row r="9" spans="1:40" ht="15" customHeight="1">
       <c r="A9" s="32"/>
-      <c r="B9" s="128" t="s">
+      <c r="B9" s="126" t="s">
         <v>50</v>
       </c>
       <c r="C9" s="42"/>
@@ -30695,13 +30703,13 @@
       <c r="V9" s="33"/>
       <c r="W9" s="33"/>
       <c r="X9" s="32"/>
-      <c r="Y9" s="128" t="s">
+      <c r="Y9" s="126" t="s">
         <v>51</v>
       </c>
       <c r="Z9" s="42"/>
       <c r="AA9" s="42"/>
       <c r="AB9" s="42"/>
-      <c r="AC9" s="128" t="s">
+      <c r="AC9" s="126" t="s">
         <v>52</v>
       </c>
       <c r="AD9" s="42"/>
@@ -30765,7 +30773,7 @@
       <c r="AN10" s="42"/>
     </row>
     <row r="11" spans="1:40" ht="27" customHeight="1">
-      <c r="A11" s="117" t="s">
+      <c r="A11" s="116" t="s">
         <v>95</v>
       </c>
       <c r="B11" s="42"/>
@@ -30851,7 +30859,7 @@
       <c r="AN12" s="21"/>
     </row>
     <row r="13" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="117" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="42"/>
@@ -30878,7 +30886,7 @@
       <c r="W13" s="21"/>
       <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
-      <c r="Z13" s="119" t="s">
+      <c r="Z13" s="118" t="s">
         <v>73</v>
       </c>
       <c r="AA13" s="53"/>
@@ -30927,7 +30935,7 @@
       <c r="AB14" s="35"/>
       <c r="AC14" s="35"/>
       <c r="AD14" s="35"/>
-      <c r="AE14" s="119"/>
+      <c r="AE14" s="118"/>
       <c r="AF14" s="42"/>
       <c r="AG14" s="34"/>
       <c r="AH14" s="34"/>
@@ -30939,7 +30947,7 @@
       <c r="AN14" s="34"/>
     </row>
     <row r="15" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="117" t="s">
         <v>97</v>
       </c>
       <c r="B15" s="42"/>
@@ -30966,7 +30974,7 @@
       <c r="W15" s="21"/>
       <c r="X15" s="21"/>
       <c r="Y15" s="21"/>
-      <c r="Z15" s="119" t="s">
+      <c r="Z15" s="118" t="s">
         <v>98</v>
       </c>
       <c r="AA15" s="53"/>
@@ -31015,7 +31023,7 @@
       <c r="AB16" s="35"/>
       <c r="AC16" s="35"/>
       <c r="AD16" s="35"/>
-      <c r="AE16" s="119"/>
+      <c r="AE16" s="118"/>
       <c r="AF16" s="42"/>
       <c r="AG16" s="34"/>
       <c r="AH16" s="34"/>
@@ -31027,7 +31035,7 @@
       <c r="AN16" s="34"/>
     </row>
     <row r="17" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="117" t="s">
         <v>99</v>
       </c>
       <c r="B17" s="42"/>
@@ -31054,7 +31062,7 @@
       <c r="W17" s="21"/>
       <c r="X17" s="21"/>
       <c r="Y17" s="21"/>
-      <c r="Z17" s="119" t="s">
+      <c r="Z17" s="118" t="s">
         <v>100</v>
       </c>
       <c r="AA17" s="53"/>
@@ -31103,7 +31111,7 @@
       <c r="AB18" s="35"/>
       <c r="AC18" s="35"/>
       <c r="AD18" s="35"/>
-      <c r="AE18" s="119"/>
+      <c r="AE18" s="118"/>
       <c r="AF18" s="42"/>
       <c r="AG18" s="34"/>
       <c r="AH18" s="34"/>
@@ -31115,7 +31123,7 @@
       <c r="AN18" s="34"/>
     </row>
     <row r="19" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A19" s="118" t="s">
+      <c r="A19" s="117" t="s">
         <v>101</v>
       </c>
       <c r="B19" s="42"/>
@@ -31142,7 +31150,7 @@
       <c r="W19" s="21"/>
       <c r="X19" s="21"/>
       <c r="Y19" s="21"/>
-      <c r="Z19" s="119" t="s">
+      <c r="Z19" s="118" t="s">
         <v>102</v>
       </c>
       <c r="AA19" s="53"/>
@@ -31191,7 +31199,7 @@
       <c r="AB20" s="35"/>
       <c r="AC20" s="35"/>
       <c r="AD20" s="35"/>
-      <c r="AE20" s="119"/>
+      <c r="AE20" s="118"/>
       <c r="AF20" s="42"/>
       <c r="AG20" s="34"/>
       <c r="AH20" s="34"/>
@@ -31203,7 +31211,7 @@
       <c r="AN20" s="34"/>
     </row>
     <row r="21" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A21" s="117" t="s">
+      <c r="A21" s="116" t="s">
         <v>109</v>
       </c>
       <c r="B21" s="42"/>
@@ -31247,7 +31255,7 @@
       <c r="AN21" s="21"/>
     </row>
     <row r="22" spans="1:40" ht="7.5" customHeight="1">
-      <c r="A22" s="120"/>
+      <c r="A22" s="119"/>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -31767,7 +31775,7 @@
       <c r="AN33" s="34"/>
     </row>
     <row r="34" spans="1:40" ht="7.5" customHeight="1">
-      <c r="A34" s="118"/>
+      <c r="A34" s="117"/>
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
       <c r="D34" s="42"/>
@@ -31809,7 +31817,7 @@
       <c r="AN34" s="34"/>
     </row>
     <row r="35" spans="1:40" ht="20.25">
-      <c r="A35" s="116" t="s">
+      <c r="A35" s="115" t="s">
         <v>142</v>
       </c>
       <c r="B35" s="42"/>
@@ -31922,7 +31930,7 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
-      <c r="Z37" s="119" t="s">
+      <c r="Z37" s="118" t="s">
         <v>120</v>
       </c>
       <c r="AA37" s="53"/>
@@ -32052,7 +32060,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-      <c r="Z40" s="119" t="s">
+      <c r="Z40" s="118" t="s">
         <v>122</v>
       </c>
       <c r="AA40" s="53"/>
@@ -32182,7 +32190,7 @@
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
-      <c r="Z43" s="119" t="s">
+      <c r="Z43" s="118" t="s">
         <v>124</v>
       </c>
       <c r="AA43" s="53"/>
@@ -32312,7 +32320,7 @@
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
-      <c r="Z46" s="119" t="s">
+      <c r="Z46" s="118" t="s">
         <v>126</v>
       </c>
       <c r="AA46" s="53"/>
@@ -32935,7 +32943,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="14.25" customHeight="1">
       <c r="A1" s="26"/>
-      <c r="B1" s="125"/>
+      <c r="B1" s="123"/>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
@@ -32943,60 +32951,60 @@
       <c r="G1" s="42"/>
       <c r="H1" s="42"/>
       <c r="I1" s="23"/>
-      <c r="J1" s="124" t="s">
+      <c r="J1" s="122" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="42"/>
       <c r="L1" s="53"/>
-      <c r="M1" s="126" t="str">
+      <c r="M1" s="124" t="str">
         <f>IF(Титул!Y1="","",Титул!Y1)</f>
         <v>1</v>
       </c>
-      <c r="N1" s="126" t="str">
+      <c r="N1" s="124" t="str">
         <f>IF(Титул!AA1="","",Титул!AA1)</f>
         <v>2</v>
       </c>
-      <c r="O1" s="126" t="str">
+      <c r="O1" s="124" t="str">
         <f>IF(Титул!AC1="","",Титул!AC1)</f>
         <v>3</v>
       </c>
-      <c r="P1" s="126" t="str">
+      <c r="P1" s="124" t="str">
         <f>IF(Титул!AE1="","",Титул!AE1)</f>
         <v>4</v>
       </c>
-      <c r="Q1" s="126" t="str">
+      <c r="Q1" s="124" t="str">
         <f>IF(Титул!AG1="","",Титул!AG1)</f>
         <v>5</v>
       </c>
-      <c r="R1" s="126" t="str">
+      <c r="R1" s="124" t="str">
         <f>IF(Титул!AI1="","",Титул!AI1)</f>
         <v>6</v>
       </c>
-      <c r="S1" s="126" t="str">
+      <c r="S1" s="124" t="str">
         <f>IF(Титул!AK1="","",Титул!AK1)</f>
         <v>7</v>
       </c>
-      <c r="T1" s="126" t="str">
+      <c r="T1" s="124" t="str">
         <f>IF(Титул!AM1="","",Титул!AM1)</f>
         <v>8</v>
       </c>
-      <c r="U1" s="126" t="str">
+      <c r="U1" s="124" t="str">
         <f>IF(Титул!AO1="","",Титул!AO1)</f>
         <v>9</v>
       </c>
-      <c r="V1" s="126" t="str">
+      <c r="V1" s="124" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="W1" s="123" t="str">
+        <v>0</v>
+      </c>
+      <c r="W1" s="154" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
-      </c>
-      <c r="X1" s="123" t="str">
+        <v>1</v>
+      </c>
+      <c r="X1" s="154" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
-      </c>
-      <c r="Y1" s="121"/>
+        <v>2</v>
+      </c>
+      <c r="Y1" s="120"/>
       <c r="Z1" s="42"/>
       <c r="AA1" s="42"/>
       <c r="AB1" s="42"/>
@@ -33035,10 +33043,10 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="121"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="120"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -33107,7 +33115,7 @@
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="21"/>
-      <c r="J4" s="124" t="s">
+      <c r="J4" s="122" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="42"/>
@@ -33148,14 +33156,14 @@
         <f>IF(Титул!AO4="","",Титул!AO4)</f>
         <v/>
       </c>
-      <c r="V4" s="124" t="s">
+      <c r="V4" s="122" t="s">
         <v>12</v>
       </c>
       <c r="W4" s="53"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="29"/>
       <c r="Z4" s="29"/>
-      <c r="AA4" s="122"/>
+      <c r="AA4" s="121"/>
       <c r="AB4" s="42"/>
       <c r="AC4" s="42"/>
       <c r="AD4" s="42"/>
@@ -33255,7 +33263,7 @@
       <c r="AN6" s="42"/>
     </row>
     <row r="7" spans="1:40" ht="6" customHeight="1">
-      <c r="A7" s="125"/>
+      <c r="A7" s="123"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -33339,7 +33347,7 @@
       <c r="AN8" s="21"/>
     </row>
     <row r="9" spans="1:40" ht="27" customHeight="1">
-      <c r="A9" s="117" t="s">
+      <c r="A9" s="116" t="s">
         <v>147</v>
       </c>
       <c r="B9" s="42"/>
@@ -33425,7 +33433,7 @@
       <c r="AN10" s="21"/>
     </row>
     <row r="11" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="117" t="s">
         <v>148</v>
       </c>
       <c r="B11" s="42"/>
@@ -33452,7 +33460,7 @@
       <c r="W11" s="21"/>
       <c r="X11" s="21"/>
       <c r="Y11" s="21"/>
-      <c r="Z11" s="119" t="s">
+      <c r="Z11" s="118" t="s">
         <v>129</v>
       </c>
       <c r="AA11" s="53"/>
@@ -33501,7 +33509,7 @@
       <c r="AB12" s="35"/>
       <c r="AC12" s="35"/>
       <c r="AD12" s="35"/>
-      <c r="AE12" s="119"/>
+      <c r="AE12" s="118"/>
       <c r="AF12" s="42"/>
       <c r="AG12" s="34"/>
       <c r="AH12" s="34"/>
@@ -33513,7 +33521,7 @@
       <c r="AN12" s="34"/>
     </row>
     <row r="13" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="117" t="s">
         <v>149</v>
       </c>
       <c r="B13" s="42"/>
@@ -33540,7 +33548,7 @@
       <c r="W13" s="21"/>
       <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
-      <c r="Z13" s="119" t="s">
+      <c r="Z13" s="118" t="s">
         <v>131</v>
       </c>
       <c r="AA13" s="53"/>
@@ -33589,7 +33597,7 @@
       <c r="AB14" s="35"/>
       <c r="AC14" s="35"/>
       <c r="AD14" s="35"/>
-      <c r="AE14" s="119"/>
+      <c r="AE14" s="118"/>
       <c r="AF14" s="42"/>
       <c r="AG14" s="34"/>
       <c r="AH14" s="34"/>
@@ -33601,7 +33609,7 @@
       <c r="AN14" s="34"/>
     </row>
     <row r="15" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="117" t="s">
         <v>150</v>
       </c>
       <c r="B15" s="42"/>
@@ -33628,7 +33636,7 @@
       <c r="W15" s="21"/>
       <c r="X15" s="21"/>
       <c r="Y15" s="21"/>
-      <c r="Z15" s="119" t="s">
+      <c r="Z15" s="118" t="s">
         <v>133</v>
       </c>
       <c r="AA15" s="53"/>
@@ -33677,7 +33685,7 @@
       <c r="AB16" s="35"/>
       <c r="AC16" s="35"/>
       <c r="AD16" s="35"/>
-      <c r="AE16" s="119"/>
+      <c r="AE16" s="118"/>
       <c r="AF16" s="42"/>
       <c r="AG16" s="34"/>
       <c r="AH16" s="34"/>
@@ -33689,7 +33697,7 @@
       <c r="AN16" s="34"/>
     </row>
     <row r="17" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="117" t="s">
         <v>151</v>
       </c>
       <c r="B17" s="42"/>
@@ -33716,7 +33724,7 @@
       <c r="W17" s="21"/>
       <c r="X17" s="21"/>
       <c r="Y17" s="21"/>
-      <c r="Z17" s="119" t="s">
+      <c r="Z17" s="118" t="s">
         <v>135</v>
       </c>
       <c r="AA17" s="53"/>
@@ -33765,7 +33773,7 @@
       <c r="AB18" s="35"/>
       <c r="AC18" s="35"/>
       <c r="AD18" s="35"/>
-      <c r="AE18" s="119"/>
+      <c r="AE18" s="118"/>
       <c r="AF18" s="42"/>
       <c r="AG18" s="34"/>
       <c r="AH18" s="34"/>
@@ -33890,7 +33898,7 @@
       <c r="W21" s="42"/>
       <c r="X21" s="42"/>
       <c r="Y21" s="42"/>
-      <c r="Z21" s="119" t="s">
+      <c r="Z21" s="118" t="s">
         <v>154</v>
       </c>
       <c r="AA21" s="53"/>
@@ -34020,7 +34028,7 @@
       <c r="W24" s="42"/>
       <c r="X24" s="42"/>
       <c r="Y24" s="42"/>
-      <c r="Z24" s="119" t="s">
+      <c r="Z24" s="118" t="s">
         <v>156</v>
       </c>
       <c r="AA24" s="53"/>
@@ -34150,7 +34158,7 @@
       <c r="W27" s="42"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="42"/>
-      <c r="Z27" s="119" t="s">
+      <c r="Z27" s="118" t="s">
         <v>158</v>
       </c>
       <c r="AA27" s="53"/>
@@ -34280,7 +34288,7 @@
       <c r="W30" s="42"/>
       <c r="X30" s="42"/>
       <c r="Y30" s="42"/>
-      <c r="Z30" s="119" t="s">
+      <c r="Z30" s="118" t="s">
         <v>160</v>
       </c>
       <c r="AA30" s="53"/>
@@ -34341,7 +34349,7 @@
       <c r="AN31" s="34"/>
     </row>
     <row r="32" spans="1:40" ht="13.5" customHeight="1">
-      <c r="A32" s="118"/>
+      <c r="A32" s="117"/>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
       <c r="D32" s="42"/>
@@ -35863,15 +35871,15 @@
       </c>
       <c r="W1" s="99" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="X1" s="115" t="str">
+        <v>0</v>
+      </c>
+      <c r="X1" s="151" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
-      </c>
-      <c r="Y1" s="115" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y1" s="151" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Z1" s="98"/>
       <c r="AA1" s="42"/>
@@ -35913,9 +35921,9 @@
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
       <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="100"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="152"/>
       <c r="Z2" s="98"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -36685,7 +36693,7 @@
       <c r="AO18" s="11"/>
     </row>
     <row r="19" spans="1:41" ht="12.75">
-      <c r="A19" s="129" t="s">
+      <c r="A19" s="127" t="s">
         <v>167</v>
       </c>
       <c r="B19" s="42"/>
@@ -37180,7 +37188,7 @@
       <c r="AO29" s="3"/>
     </row>
     <row r="30" spans="1:41" ht="19.5" customHeight="1">
-      <c r="A30" s="129" t="s">
+      <c r="A30" s="127" t="s">
         <v>174</v>
       </c>
       <c r="B30" s="42"/>
@@ -37585,7 +37593,7 @@
       <c r="AO38" s="3"/>
     </row>
     <row r="39" spans="1:41" ht="17.25" customHeight="1">
-      <c r="A39" s="129" t="s">
+      <c r="A39" s="127" t="s">
         <v>183</v>
       </c>
       <c r="B39" s="42"/>
@@ -38753,7 +38761,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="12.75">
       <c r="A1" s="26"/>
-      <c r="B1" s="125"/>
+      <c r="B1" s="123"/>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
@@ -38761,60 +38769,60 @@
       <c r="G1" s="42"/>
       <c r="H1" s="42"/>
       <c r="I1" s="23"/>
-      <c r="J1" s="124" t="s">
+      <c r="J1" s="122" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="42"/>
       <c r="L1" s="53"/>
-      <c r="M1" s="126" t="str">
+      <c r="M1" s="124" t="str">
         <f>IF(Титул!Y1="","",Титул!Y1)</f>
         <v>1</v>
       </c>
-      <c r="N1" s="126" t="str">
+      <c r="N1" s="124" t="str">
         <f>IF(Титул!AA1="","",Титул!AA1)</f>
         <v>2</v>
       </c>
-      <c r="O1" s="126" t="str">
+      <c r="O1" s="124" t="str">
         <f>IF(Титул!AC1="","",Титул!AC1)</f>
         <v>3</v>
       </c>
-      <c r="P1" s="126" t="str">
+      <c r="P1" s="124" t="str">
         <f>IF(Титул!AE1="","",Титул!AE1)</f>
         <v>4</v>
       </c>
-      <c r="Q1" s="126" t="str">
+      <c r="Q1" s="124" t="str">
         <f>IF(Титул!AG1="","",Титул!AG1)</f>
         <v>5</v>
       </c>
-      <c r="R1" s="126" t="str">
+      <c r="R1" s="124" t="str">
         <f>IF(Титул!AI1="","",Титул!AI1)</f>
         <v>6</v>
       </c>
-      <c r="S1" s="126" t="str">
+      <c r="S1" s="124" t="str">
         <f>IF(Титул!AK1="","",Титул!AK1)</f>
         <v>7</v>
       </c>
-      <c r="T1" s="126" t="str">
+      <c r="T1" s="124" t="str">
         <f>IF(Титул!AM1="","",Титул!AM1)</f>
         <v>8</v>
       </c>
-      <c r="U1" s="126" t="str">
+      <c r="U1" s="124" t="str">
         <f>IF(Титул!AO1="","",Титул!AO1)</f>
         <v>9</v>
       </c>
-      <c r="V1" s="126" t="str">
+      <c r="V1" s="124" t="str">
         <f>IF(Титул!AQ1="","",Титул!AQ1)</f>
-        <v/>
-      </c>
-      <c r="W1" s="123" t="str">
+        <v>0</v>
+      </c>
+      <c r="W1" s="154" t="str">
         <f>IF(Титул!AS1="","",Титул!AS1)</f>
-        <v/>
-      </c>
-      <c r="X1" s="123" t="str">
+        <v>1</v>
+      </c>
+      <c r="X1" s="154" t="str">
         <f>IF(Титул!AU1="","",Титул!AU1)</f>
-        <v/>
-      </c>
-      <c r="Y1" s="121"/>
+        <v>2</v>
+      </c>
+      <c r="Y1" s="120"/>
       <c r="Z1" s="42"/>
       <c r="AA1" s="42"/>
       <c r="AB1" s="42"/>
@@ -38853,10 +38861,10 @@
       <c r="S2" s="100"/>
       <c r="T2" s="100"/>
       <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="121"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="120"/>
       <c r="Z2" s="42"/>
       <c r="AA2" s="42"/>
       <c r="AB2" s="42"/>
@@ -38925,7 +38933,7 @@
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="21"/>
-      <c r="J4" s="124" t="s">
+      <c r="J4" s="122" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="42"/>
@@ -38966,14 +38974,14 @@
         <f>IF(Титул!AO4="","",Титул!AO4)</f>
         <v/>
       </c>
-      <c r="V4" s="124" t="s">
+      <c r="V4" s="122" t="s">
         <v>12</v>
       </c>
       <c r="W4" s="53"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="29"/>
       <c r="Z4" s="29"/>
-      <c r="AA4" s="122"/>
+      <c r="AA4" s="121"/>
       <c r="AB4" s="42"/>
       <c r="AC4" s="42"/>
       <c r="AD4" s="42"/>
@@ -39073,7 +39081,7 @@
       <c r="AN6" s="42"/>
     </row>
     <row r="7" spans="1:40" ht="6" customHeight="1">
-      <c r="A7" s="125"/>
+      <c r="A7" s="123"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -39116,7 +39124,7 @@
     </row>
     <row r="8" spans="1:40" ht="16.5" customHeight="1">
       <c r="A8" s="32"/>
-      <c r="B8" s="128" t="s">
+      <c r="B8" s="126" t="s">
         <v>50</v>
       </c>
       <c r="C8" s="42"/>
@@ -39142,13 +39150,13 @@
       <c r="W8" s="42"/>
       <c r="X8" s="42"/>
       <c r="Y8" s="21"/>
-      <c r="Z8" s="128" t="s">
+      <c r="Z8" s="126" t="s">
         <v>51</v>
       </c>
       <c r="AA8" s="42"/>
       <c r="AB8" s="42"/>
       <c r="AC8" s="42"/>
-      <c r="AD8" s="128" t="s">
+      <c r="AD8" s="126" t="s">
         <v>52</v>
       </c>
       <c r="AE8" s="42"/>
@@ -39211,7 +39219,7 @@
       <c r="AN9" s="42"/>
     </row>
     <row r="10" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A10" s="129" t="s">
+      <c r="A10" s="127" t="s">
         <v>109</v>
       </c>
       <c r="B10" s="42"/>
@@ -39283,7 +39291,7 @@
       <c r="X11" s="42"/>
       <c r="Y11" s="42"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="119" t="s">
+      <c r="AA11" s="118" t="s">
         <v>199</v>
       </c>
       <c r="AB11" s="42"/>
@@ -39371,7 +39379,7 @@
       <c r="X13" s="42"/>
       <c r="Y13" s="42"/>
       <c r="Z13" s="3"/>
-      <c r="AA13" s="119" t="s">
+      <c r="AA13" s="118" t="s">
         <v>201</v>
       </c>
       <c r="AB13" s="42"/>
@@ -39459,7 +39467,7 @@
       <c r="X15" s="42"/>
       <c r="Y15" s="42"/>
       <c r="Z15" s="3"/>
-      <c r="AA15" s="119" t="s">
+      <c r="AA15" s="118" t="s">
         <v>203</v>
       </c>
       <c r="AB15" s="42"/>
@@ -39547,7 +39555,7 @@
       <c r="X17" s="42"/>
       <c r="Y17" s="42"/>
       <c r="Z17" s="3"/>
-      <c r="AA17" s="119" t="s">
+      <c r="AA17" s="118" t="s">
         <v>205</v>
       </c>
       <c r="AB17" s="42"/>
@@ -39635,7 +39643,7 @@
       <c r="X19" s="42"/>
       <c r="Y19" s="42"/>
       <c r="Z19" s="42"/>
-      <c r="AA19" s="119" t="s">
+      <c r="AA19" s="118" t="s">
         <v>207</v>
       </c>
       <c r="AB19" s="42"/>
@@ -40721,7 +40729,7 @@
       <c r="AN44" s="21"/>
     </row>
     <row r="45" spans="1:40" ht="16.5" customHeight="1">
-      <c r="A45" s="130"/>
+      <c r="A45" s="128"/>
       <c r="B45" s="42"/>
       <c r="C45" s="42"/>
       <c r="D45" s="42"/>
